--- a/backtest/controle-alleen-etf/backtest.xlsx
+++ b/backtest/controle-alleen-etf/backtest.xlsx
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.025521151976418</v>
+        <v>1.029060749914138</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.1516373731015053</v>
+        <v>0.15203964435873</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>-0.1944108750310027</v>
@@ -490,7 +490,7 @@
         <v>1.1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>20228.9</v>
+        <v>20264.25</v>
       </c>
     </row>
     <row r="3">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9099501640159735</v>
+        <v>0.9161629251587753</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1381830195046247</v>
+        <v>0.1389226245278337</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.2303250572697891</v>
+        <v>-0.2303251037363384</v>
       </c>
       <c r="E4" t="n">
         <v>0.77</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19099.50164015973</v>
+        <v>19161.62925158775</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
         <v>0.06830789978238738</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.09413977559118658</v>
+        <v>0.09413970068966004</v>
       </c>
     </row>
     <row r="3">
@@ -604,7 +604,7 @@
         <v>-0.1354140192485231</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.1307684331744614</v>
+        <v>-0.1307684463920527</v>
       </c>
     </row>
     <row r="4">
@@ -618,7 +618,7 @@
         <v>0.1989455715883754</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.2153105049708681</v>
+        <v>0.2153106066474764</v>
       </c>
     </row>
     <row r="5">
@@ -632,7 +632,7 @@
         <v>0.2722609034779582</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3283173244071134</v>
+        <v>0.3283174654574843</v>
       </c>
     </row>
     <row r="6">
@@ -646,7 +646,7 @@
         <v>0.0707564790521269</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.04279560166903007</v>
+        <v>0.04279549093743906</v>
       </c>
     </row>
     <row r="7">
@@ -654,13 +654,13 @@
         <v>2026</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.1886103431762829</v>
+        <v>0.1906874395893989</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0.1719717398412692</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.192958840418747</v>
+        <v>0.1968393439357246</v>
       </c>
     </row>
   </sheetData>
@@ -782,16 +782,16 @@
         <v>0.6482490272373541</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.01338489020598255</v>
+        <v>0.01338498379397302</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.06632519155352312</v>
+        <v>-0.06632535208484813</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.1489282522307223</v>
+        <v>-0.1489283036113312</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1792148175161967</v>
+        <v>0.1792148887073499</v>
       </c>
     </row>
   </sheetData>
@@ -865,7 +865,7 @@
         <v>10002.02886373414</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>10024.8385986201</v>
+        <v>10024.84006151556</v>
       </c>
     </row>
     <row r="4">
@@ -881,7 +881,7 @@
         <v>10052.07657711906</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>10087.53442603558</v>
+        <v>10087.5322348734</v>
       </c>
     </row>
     <row r="5">
@@ -897,7 +897,7 @@
         <v>10086.56829257495</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10111.39490909282</v>
+        <v>10111.39636759432</v>
       </c>
     </row>
     <row r="6">
@@ -913,7 +913,7 @@
         <v>10068.30748699221</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10117.72143428081</v>
+        <v>10117.72070647216</v>
       </c>
     </row>
     <row r="7">
@@ -929,7 +929,7 @@
         <v>10093.33185967239</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10133.03452698213</v>
+        <v>10133.0352566485</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
         <v>10147.43626855015</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10174.46820100712</v>
+        <v>10174.46674352357</v>
       </c>
     </row>
     <row r="9">
@@ -961,7 +961,7 @@
         <v>10224.53618637394</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10208.51849514344</v>
+        <v>10208.51776462032</v>
       </c>
     </row>
     <row r="10">
@@ -977,7 +977,7 @@
         <v>10178.54723243276</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10175.09449945151</v>
+        <v>10175.09376808008</v>
       </c>
     </row>
     <row r="11">
@@ -993,7 +993,7 @@
         <v>10146.08438071102</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10271.60426961897</v>
+        <v>10271.60573212431</v>
       </c>
     </row>
     <row r="12">
@@ -1009,7 +1009,7 @@
         <v>10245.50283158584</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10218.89838592225</v>
+        <v>10218.89911194957</v>
       </c>
     </row>
     <row r="13">
@@ -1025,7 +1025,7 @@
         <v>10263.08666127356</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>10348.90380163111</v>
+        <v>10348.90233362903</v>
       </c>
     </row>
     <row r="14">
@@ -1121,7 +1121,7 @@
         <v>10398.34974741885</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>10482.42885850149</v>
+        <v>10482.42666311502</v>
       </c>
     </row>
     <row r="20">
@@ -1153,7 +1153,7 @@
         <v>10447.04454098919</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>10497.07301965032</v>
+        <v>10497.07228112808</v>
       </c>
     </row>
     <row r="22">
@@ -1169,7 +1169,7 @@
         <v>10510.61835659354</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>10608.72681229065</v>
+        <v>10608.72533071646</v>
       </c>
     </row>
     <row r="23">
@@ -1185,7 +1185,7 @@
         <v>10559.31315016388</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>10620.86793136321</v>
+        <v>10620.86496583979</v>
       </c>
     </row>
     <row r="24">
@@ -1217,7 +1217,7 @@
         <v>10643.85257900469</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>10750.18518364354</v>
+        <v>10750.18668218294</v>
       </c>
     </row>
     <row r="26">
@@ -1233,7 +1233,7 @@
         <v>10604.6261601855</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>10786.6955974158</v>
+        <v>10786.69784522489</v>
       </c>
     </row>
     <row r="27">
@@ -1249,7 +1249,7 @@
         <v>10643.17560310967</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>10722.671091334</v>
+        <v>10722.67332980397</v>
       </c>
     </row>
     <row r="28">
@@ -1281,7 +1281,7 @@
         <v>10559.98909408345</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>10826.92015654156</v>
+        <v>10826.91864746681</v>
       </c>
     </row>
     <row r="30">
@@ -1329,7 +1329,7 @@
         <v>10312.45739876347</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>10644.49257124233</v>
+        <v>10644.49181451637</v>
       </c>
     </row>
     <row r="33">
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>10625.91</v>
+        <v>10625.92</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>10440.95794978676</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>10695.34670968577</v>
+        <v>10695.34520743096</v>
       </c>
     </row>
     <row r="34">
@@ -1361,7 +1361,7 @@
         <v>10323.95463724876</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>10487.00395596056</v>
+        <v>10487.00320485012</v>
       </c>
     </row>
     <row r="35">
@@ -1377,7 +1377,7 @@
         <v>10412.5528255333</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>10336.79258244071</v>
+        <v>10336.79033643847</v>
       </c>
     </row>
     <row r="36">
@@ -1393,7 +1393,7 @@
         <v>10230.62380955182</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>10505.10273367788</v>
+        <v>10505.09973615784</v>
       </c>
     </row>
     <row r="37">
@@ -1409,7 +1409,7 @@
         <v>10200.18982156422</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>10425.95390786089</v>
+        <v>10425.9531575987</v>
       </c>
     </row>
     <row r="38">
@@ -1425,7 +1425,7 @@
         <v>10318.54502194135</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>10550.74323565008</v>
+        <v>10550.741734939</v>
       </c>
     </row>
     <row r="39">
@@ -1441,7 +1441,7 @@
         <v>10594.48080953933</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>10786.27131311493</v>
+        <v>10786.27206467495</v>
       </c>
     </row>
     <row r="40">
@@ -1457,7 +1457,7 @@
         <v>10509.94138069853</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>10824.59541288174</v>
+        <v>10824.59616512034</v>
       </c>
     </row>
     <row r="41">
@@ -1473,7 +1473,7 @@
         <v>10549.16779951772</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>10686.0433620212</v>
+        <v>10686.04485733721</v>
       </c>
     </row>
     <row r="42">
@@ -1489,7 +1489,7 @@
         <v>10485.59398391336</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>10836.56921510275</v>
+        <v>10836.56846398383</v>
       </c>
     </row>
     <row r="43">
@@ -1505,7 +1505,7 @@
         <v>10470.71599385479</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>10722.98551054186</v>
+        <v>10722.98701031969</v>
       </c>
     </row>
     <row r="44">
@@ -1521,7 +1521,7 @@
         <v>10367.91575943125</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>10674.14876666338</v>
+        <v>10674.1480150185</v>
       </c>
     </row>
     <row r="45">
@@ -1537,7 +1537,7 @@
         <v>10384.1466693044</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10864.17659195019</v>
+        <v>10864.17734520671</v>
       </c>
     </row>
     <row r="46">
@@ -1553,7 +1553,7 @@
         <v>10530.23105001541</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>10740.23749163448</v>
+        <v>10740.23974550038</v>
       </c>
     </row>
     <row r="47">
@@ -1569,7 +1569,7 @@
         <v>10440.95794978676</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>10585.260783127</v>
+        <v>10585.26003471401</v>
       </c>
     </row>
     <row r="48">
@@ -1585,7 +1585,7 @@
         <v>10211.0100841545</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>10557.096905978</v>
+        <v>10557.09615153391</v>
       </c>
     </row>
     <row r="49">
@@ -1665,7 +1665,7 @@
         <v>10670.90478344356</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>10995.12884843512</v>
+        <v>10995.128099369</v>
       </c>
     </row>
     <row r="54">
@@ -1681,7 +1681,7 @@
         <v>10733.12567923334</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>10980.54497681952</v>
+        <v>10980.54273076623</v>
       </c>
     </row>
     <row r="55">
@@ -1697,7 +1697,7 @@
         <v>10674.96251091185</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>11009.41456543725</v>
+        <v>11009.41531513109</v>
       </c>
     </row>
     <row r="56">
@@ -1729,7 +1729,7 @@
         <v>10683.07899782387</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>10941.39775591186</v>
+        <v>10941.3970068966</v>
       </c>
     </row>
     <row r="58">
@@ -1745,7 +1745,7 @@
         <v>10704.72055497989</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>10957.88762489175</v>
+        <v>10957.88613324023</v>
       </c>
     </row>
     <row r="59">
@@ -1761,7 +1761,7 @@
         <v>10752.73940463066</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>11023.23896510535</v>
+        <v>11023.23971563049</v>
       </c>
     </row>
     <row r="60">
@@ -1777,7 +1777,7 @@
         <v>10720.95249682848</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>10829.4072053383</v>
+        <v>10829.40946062909</v>
       </c>
     </row>
     <row r="61">
@@ -1793,7 +1793,7 @@
         <v>10561.34201389803</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>10790.67089607073</v>
+        <v>10790.67014629204</v>
       </c>
     </row>
     <row r="62">
@@ -1809,7 +1809,7 @@
         <v>10479.50739271093</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>10763.8181020605</v>
+        <v>10763.81584941613</v>
       </c>
     </row>
     <row r="63">
@@ -1825,7 +1825,7 @@
         <v>10345.59722638022</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>10696.37787998306</v>
+        <v>10696.37862708968</v>
       </c>
     </row>
     <row r="64">
@@ -1841,7 +1841,7 @@
         <v>10469.36307404021</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>10816.23047606843</v>
+        <v>10816.22972740944</v>
       </c>
     </row>
     <row r="65">
@@ -1873,7 +1873,7 @@
         <v>10488.97576746208</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>10592.05564716862</v>
+        <v>10592.05490578776</v>
       </c>
     </row>
     <row r="67">
@@ -1889,7 +1889,7 @@
         <v>10346.9501461948</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>10582.08139494341</v>
+        <v>10582.08213532338</v>
       </c>
     </row>
     <row r="68">
@@ -1899,13 +1899,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>10421.67</v>
+        <v>10421.66</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>10432.16551895517</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>10625.12170983582</v>
+        <v>10625.12245322712</v>
       </c>
     </row>
     <row r="69">
@@ -1921,7 +1921,7 @@
         <v>10316.51512623175</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>10437.07409669334</v>
+        <v>10437.07558349289</v>
       </c>
     </row>
     <row r="70">
@@ -1937,7 +1937,7 @@
         <v>10273.90795583929</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>10402.47838748053</v>
+        <v>10402.4791361904</v>
       </c>
     </row>
     <row r="71">
@@ -1953,7 +1953,7 @@
         <v>10357.77040878508</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>10274.87084137149</v>
+        <v>10274.87308477805</v>
       </c>
     </row>
     <row r="72">
@@ -1969,7 +1969,7 @@
         <v>10118.35520037713</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>10099.56452466746</v>
+        <v>10099.56527442916</v>
       </c>
     </row>
     <row r="73">
@@ -1985,7 +1985,7 @@
         <v>9705.12643092426</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>10117.66936988425</v>
+        <v>10117.67011781369</v>
       </c>
     </row>
     <row r="74">
@@ -2001,7 +2001,7 @@
         <v>9812.660336735653</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>10009.44316707987</v>
+        <v>10009.44391615451</v>
       </c>
     </row>
     <row r="75">
@@ -2049,7 +2049,7 @@
         <v>9934.397320661501</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>10343.53744245606</v>
+        <v>10343.53668148033</v>
       </c>
     </row>
     <row r="78">
@@ -2065,7 +2065,7 @@
         <v>10144.05551697687</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>10524.78875384454</v>
+        <v>10524.79027506652</v>
       </c>
     </row>
     <row r="79">
@@ -2081,7 +2081,7 @@
         <v>10229.94683365681</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>10522.99218054762</v>
+        <v>10522.99142517042</v>
       </c>
     </row>
     <row r="80">
@@ -2129,7 +2129,7 @@
         <v>9966.184228463679</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>10236.37555708815</v>
+        <v>10236.37481532551</v>
       </c>
     </row>
     <row r="83">
@@ -2145,7 +2145,7 @@
         <v>10025.70031659975</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>10186.25384542037</v>
+        <v>10186.25236440601</v>
       </c>
     </row>
     <row r="84">
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>10220</v>
+        <v>10220.01</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>10215.06781162279</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>10451.29279709276</v>
+        <v>10451.29353979692</v>
       </c>
     </row>
     <row r="86">
@@ -2209,7 +2209,7 @@
         <v>10089.27310022865</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>10066.2008731946</v>
+        <v>10066.20310242671</v>
       </c>
     </row>
     <row r="88">
@@ -2241,7 +2241,7 @@
         <v>10068.98446288722</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>10293.55571675323</v>
+        <v>10293.55496649959</v>
       </c>
     </row>
     <row r="90">
@@ -2273,7 +2273,7 @@
         <v>9985.120977965982</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>10023.84542725952</v>
+        <v>10023.8491557947</v>
       </c>
     </row>
     <row r="92">
@@ -2289,7 +2289,7 @@
         <v>9866.089833669294</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>9966.643568428884</v>
+        <v>9966.644314712707</v>
       </c>
     </row>
     <row r="93">
@@ -2305,7 +2305,7 @@
         <v>9753.821224494597</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>10010.03205899361</v>
+        <v>10010.03280852628</v>
       </c>
     </row>
     <row r="94">
@@ -2321,7 +2321,7 @@
         <v>9778.168621279767</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>9909.220652293543</v>
+        <v>9909.222152359871</v>
       </c>
     </row>
     <row r="95">
@@ -2337,7 +2337,7 @@
         <v>9722.710260611984</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>9716.712210173797</v>
+        <v>9716.713707661451</v>
       </c>
     </row>
     <row r="96">
@@ -2353,7 +2353,7 @@
         <v>9591.505933910435</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>9883.386698685728</v>
+        <v>9883.38819927797</v>
       </c>
     </row>
     <row r="97">
@@ -2369,7 +2369,7 @@
         <v>9897.199765576457</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>10205.26667314618</v>
+        <v>10205.26743115296</v>
       </c>
     </row>
     <row r="98">
@@ -2385,7 +2385,7 @@
         <v>9947.923422880938</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>10187.92787724103</v>
+        <v>10187.92863590105</v>
       </c>
     </row>
     <row r="99">
@@ -2401,7 +2401,7 @@
         <v>9887.055446905741</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>10001.5790162534</v>
+        <v>10001.57750364985</v>
       </c>
     </row>
     <row r="100">
@@ -2417,7 +2417,7 @@
         <v>9995.942272531713</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>10261.65376335495</v>
+        <v>10261.65223945258</v>
       </c>
     </row>
     <row r="101">
@@ -2433,7 +2433,7 @@
         <v>9968.889036117387</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>10229.32328947301</v>
+        <v>10229.32176277123</v>
       </c>
     </row>
     <row r="102">
@@ -2465,7 +2465,7 @@
         <v>9835.654813706244</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>10062.45715922992</v>
+        <v>10062.45793927455</v>
       </c>
     </row>
     <row r="104">
@@ -2497,7 +2497,7 @@
         <v>9762.613655326186</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>10231.60480497868</v>
+        <v>10231.60169158619</v>
       </c>
     </row>
     <row r="106">
@@ -2513,7 +2513,7 @@
         <v>9698.362863826815</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>10023.89097301767</v>
+        <v>10023.89250502956</v>
       </c>
     </row>
     <row r="107">
@@ -2529,7 +2529,7 @@
         <v>9799.810178435779</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>9950.247015226105</v>
+        <v>9950.247785396959</v>
       </c>
     </row>
     <row r="108">
@@ -2545,7 +2545,7 @@
         <v>9692.276272624385</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>9951.505944159717</v>
+        <v>9951.505168220612</v>
       </c>
     </row>
     <row r="109">
@@ -2609,7 +2609,7 @@
         <v>10167.04999394746</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>10480.6758555186</v>
+        <v>10480.67661975164</v>
       </c>
     </row>
     <row r="113">
@@ -2625,7 +2625,7 @@
         <v>10240.76812822254</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>10531.10746211214</v>
+        <v>10531.10899838221</v>
       </c>
     </row>
     <row r="114">
@@ -2641,7 +2641,7 @@
         <v>10348.97900992895</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>10679.39915815116</v>
+        <v>10679.39607838375</v>
       </c>
     </row>
     <row r="115">
@@ -2657,7 +2657,7 @@
         <v>10326.66047687792</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>10529.90072639278</v>
+        <v>10529.90303359731</v>
       </c>
     </row>
     <row r="116">
@@ -2673,7 +2673,7 @@
         <v>10320.57388567549</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>10711.38647681224</v>
+        <v>10711.38801822286</v>
       </c>
     </row>
     <row r="117">
@@ -2689,7 +2689,7 @@
         <v>10376.70715828739</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>10760.49734501197</v>
+        <v>10760.49888596444</v>
       </c>
     </row>
     <row r="118">
@@ -2705,7 +2705,7 @@
         <v>10409.17104198458</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>10864.3603412415</v>
+        <v>10864.35879640397</v>
       </c>
     </row>
     <row r="119">
@@ -2721,7 +2721,7 @@
         <v>10484.9180399938</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>10986.80239287365</v>
+        <v>10986.80316445268</v>
       </c>
     </row>
     <row r="120">
@@ -2737,7 +2737,7 @@
         <v>10438.2521101576</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>10822.80942995345</v>
+        <v>10822.80866516901</v>
       </c>
     </row>
     <row r="121">
@@ -2753,7 +2753,7 @@
         <v>10428.78373540645</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>10589.09632125644</v>
+        <v>10589.09784118908</v>
       </c>
     </row>
     <row r="122">
@@ -2785,7 +2785,7 @@
         <v>10506.56062912526</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>10821.13556225585</v>
+        <v>10821.13402656253</v>
       </c>
     </row>
     <row r="124">
@@ -2801,7 +2801,7 @@
         <v>10544.43412812987</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>10753.97096588107</v>
+        <v>10753.97173872399</v>
       </c>
     </row>
     <row r="125">
@@ -2817,7 +2817,7 @@
         <v>10340.86252301692</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>10714.21507639767</v>
+        <v>10714.21352087188</v>
       </c>
     </row>
     <row r="126">
@@ -2833,7 +2833,7 @@
         <v>10313.81031857805</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>10776.30683237624</v>
+        <v>10776.30527567999</v>
       </c>
     </row>
     <row r="127">
@@ -2849,7 +2849,7 @@
         <v>10456.51291574034</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>10780.51953987446</v>
+        <v>10780.52032061474</v>
       </c>
     </row>
     <row r="128">
@@ -2865,7 +2865,7 @@
         <v>10300.96016027817</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>10576.68521249305</v>
+        <v>10576.6859917912</v>
       </c>
     </row>
     <row r="129">
@@ -2881,7 +2881,7 @@
         <v>10355.74154505094</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>10544.26404518886</v>
+        <v>10544.26560478625</v>
       </c>
     </row>
     <row r="130">
@@ -2907,13 +2907,13 @@
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>10478.81</v>
+        <v>10478.82</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>10371.97348689954</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>10514.24811756289</v>
+        <v>10514.24656062907</v>
       </c>
     </row>
     <row r="132">
@@ -2929,7 +2929,7 @@
         <v>10371.97348689954</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>10587.68671040812</v>
+        <v>10587.68514259962</v>
       </c>
     </row>
     <row r="133">
@@ -2945,7 +2945,7 @@
         <v>10371.97348689954</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>10597.65535488286</v>
+        <v>10597.65613920271</v>
       </c>
     </row>
     <row r="134">
@@ -2977,7 +2977,7 @@
         <v>10399.02569133841</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>10781.4605076387</v>
+        <v>10781.45893597901</v>
       </c>
     </row>
     <row r="136">
@@ -3009,7 +3009,7 @@
         <v>10153.52389172803</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>10290.02809851049</v>
+        <v>10290.02888138833</v>
       </c>
     </row>
     <row r="138">
@@ -3025,7 +3025,7 @@
         <v>9969.566012012401</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>10372.78710931732</v>
+        <v>10372.7863246921</v>
       </c>
     </row>
     <row r="139">
@@ -3041,7 +3041,7 @@
         <v>9983.768058151403</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>10163.41517673698</v>
+        <v>10163.41676017048</v>
       </c>
     </row>
     <row r="140">
@@ -3057,7 +3057,7 @@
         <v>10073.71813427507</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>10259.59071243887</v>
+        <v>10259.58752456882</v>
       </c>
     </row>
     <row r="141">
@@ -3073,7 +3073,7 @@
         <v>10128.49951904784</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>10606.96215186875</v>
+        <v>10606.96375917235</v>
       </c>
     </row>
     <row r="142">
@@ -3089,7 +3089,7 @@
         <v>10152.84691583301</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>10264.46457032585</v>
+        <v>10264.46618541647</v>
       </c>
     </row>
     <row r="143">
@@ -3105,7 +3105,7 @@
         <v>9934.397320661501</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>10295.12039600053</v>
+        <v>10295.11959088977</v>
       </c>
     </row>
     <row r="144">
@@ -3121,7 +3121,7 @@
         <v>10077.09991782379</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>10368.79418699334</v>
+        <v>10368.79337982123</v>
       </c>
     </row>
     <row r="145">
@@ -3137,7 +3137,7 @@
         <v>9945.894559146796</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>10664.79165453175</v>
+        <v>10664.79246021089</v>
       </c>
     </row>
     <row r="146">
@@ -3153,7 +3153,7 @@
         <v>9969.566012012401</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>10194.76701906057</v>
+        <v>10194.76861616798</v>
       </c>
     </row>
     <row r="147">
@@ -3185,7 +3185,7 @@
         <v>9575.949935981404</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>9893.542851670618</v>
+        <v>9893.545267868156</v>
       </c>
     </row>
     <row r="149">
@@ -3201,7 +3201,7 @@
         <v>9513.05309627206</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>9884.862520652354</v>
+        <v>9884.863323489826</v>
       </c>
     </row>
     <row r="150">
@@ -3233,7 +3233,7 @@
         <v>9549.57367546209</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>9766.959844136638</v>
+        <v>9766.960651045785</v>
       </c>
     </row>
     <row r="152">
@@ -3265,7 +3265,7 @@
         <v>9749.086521131298</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>10067.00169034896</v>
+        <v>10067.00087476215</v>
       </c>
     </row>
     <row r="154">
@@ -3297,7 +3297,7 @@
         <v>9651.697965966068</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>9722.29943457934</v>
+        <v>9722.296217766856</v>
       </c>
     </row>
     <row r="156">
@@ -3313,7 +3313,7 @@
         <v>9472.473757638296</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>9732.057891835704</v>
+        <v>9732.059511778307</v>
       </c>
     </row>
     <row r="157">
@@ -3329,7 +3329,7 @@
         <v>9442.039769650695</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>9638.522609309022</v>
+        <v>9638.521807472483</v>
       </c>
     </row>
     <row r="158">
@@ -3345,7 +3345,7 @@
         <v>9553.631402930378</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>9827.376651085922</v>
+        <v>9827.3750460218</v>
       </c>
     </row>
     <row r="159">
@@ -3393,7 +3393,7 @@
         <v>9646.287318683204</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>9925.429184734994</v>
+        <v>9925.431566018266</v>
       </c>
     </row>
     <row r="162">
@@ -3409,7 +3409,7 @@
         <v>9833.6259499721</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>10125.18465621785</v>
+        <v>10125.18702722004</v>
       </c>
     </row>
     <row r="163">
@@ -3425,7 +3425,7 @@
         <v>9893.817982027735</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>10126.59733697961</v>
+        <v>10126.59970831261</v>
       </c>
     </row>
     <row r="164">
@@ -3441,7 +3441,7 @@
         <v>9805.220825718645</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>10030.44436304504</v>
+        <v>10030.44515040176</v>
       </c>
     </row>
     <row r="165">
@@ -3457,7 +3457,7 @@
         <v>9795.076507047928</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>9985.863275045183</v>
+        <v>9985.864855543734</v>
       </c>
     </row>
     <row r="166">
@@ -3473,7 +3473,7 @@
         <v>9816.042120284375</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>10252.38071306626</v>
+        <v>10252.38230542347</v>
       </c>
     </row>
     <row r="167">
@@ -3489,7 +3489,7 @@
         <v>9778.168621279767</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>9993.232506749544</v>
+        <v>9993.231717747245</v>
       </c>
     </row>
     <row r="168">
@@ -3505,7 +3505,7 @@
         <v>9872.852368791288</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>10047.04418683702</v>
+        <v>10047.04260515103</v>
       </c>
     </row>
     <row r="169">
@@ -3521,7 +3521,7 @@
         <v>9834.978869786679</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>10176.27386924165</v>
+        <v>10176.27545605119</v>
       </c>
     </row>
     <row r="170">
@@ -3537,7 +3537,7 @@
         <v>9853.239675369419</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>10058.85452182725</v>
+        <v>10058.85610756798</v>
       </c>
     </row>
     <row r="171">
@@ -3553,7 +3553,7 @@
         <v>9760.584791592042</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>9802.187220258511</v>
+        <v>9802.18880318302</v>
       </c>
     </row>
     <row r="172">
@@ -3617,7 +3617,7 @@
         <v>9235.08741296448</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>9504.849755202675</v>
+        <v>9504.850567667921</v>
       </c>
     </row>
     <row r="176">
@@ -3633,7 +3633,7 @@
         <v>8953.064002188614</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>9176.556280237177</v>
+        <v>9176.557091489374</v>
       </c>
     </row>
     <row r="177">
@@ -3649,7 +3649,7 @@
         <v>8967.266048327616</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>9117.296848138571</v>
+        <v>9117.296043859096</v>
       </c>
     </row>
     <row r="178">
@@ -3665,7 +3665,7 @@
         <v>9011.90311442967</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>9165.473024594683</v>
+        <v>9165.472216065362</v>
       </c>
     </row>
     <row r="179">
@@ -3681,7 +3681,7 @@
         <v>9112.674485119069</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>9369.977821342998</v>
+        <v>9369.97701507011</v>
       </c>
     </row>
     <row r="180">
@@ -3697,7 +3697,7 @@
         <v>9097.795463085051</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>9342.461824722313</v>
+        <v>9342.461019357044</v>
       </c>
     </row>
     <row r="181">
@@ -3713,7 +3713,7 @@
         <v>9118.761076321498</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>9405.92089430275</v>
+        <v>9405.922500232085</v>
       </c>
     </row>
     <row r="182">
@@ -3729,7 +3729,7 @@
         <v>9332.477000105158</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>9745.571867814737</v>
+        <v>9745.57106149096</v>
       </c>
     </row>
     <row r="183">
@@ -3745,7 +3745,7 @@
         <v>9363.586932012322</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>9666.063849557158</v>
+        <v>9666.064652369179</v>
       </c>
     </row>
     <row r="184">
@@ -3761,7 +3761,7 @@
         <v>9358.853260624472</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>9455.353407744846</v>
+        <v>9455.35260605258</v>
       </c>
     </row>
     <row r="185">
@@ -3777,7 +3777,7 @@
         <v>9276.342695517811</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>9499.135148359012</v>
+        <v>9499.133536237205</v>
       </c>
     </row>
     <row r="186">
@@ -3793,7 +3793,7 @@
         <v>9185.039699579564</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>9491.366112586395</v>
+        <v>9491.367736583827</v>
       </c>
     </row>
     <row r="187">
@@ -3841,7 +3841,7 @@
         <v>9253.34821854722</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>9622.21563746117</v>
+        <v>9622.214011377144</v>
       </c>
     </row>
     <row r="190">
@@ -3857,7 +3857,7 @@
         <v>9454.889927950569</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>9819.909055264969</v>
+        <v>9819.908228311471</v>
       </c>
     </row>
     <row r="191">
@@ -3873,7 +3873,7 @@
         <v>9644.934398868625</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>10036.71061105758</v>
+        <v>10036.70977831888</v>
       </c>
     </row>
     <row r="192">
@@ -3889,7 +3889,7 @@
         <v>9711.889998021703</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>10044.80010896776</v>
+        <v>10044.79927487185</v>
       </c>
     </row>
     <row r="193">
@@ -3905,7 +3905,7 @@
         <v>9647.639206522332</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>9933.685492235938</v>
+        <v>9933.684657834679</v>
       </c>
     </row>
     <row r="194">
@@ -3937,7 +3937,7 @@
         <v>9522.521471023212</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>9923.912578754715</v>
+        <v>9923.914269679955</v>
       </c>
     </row>
     <row r="196">
@@ -3969,7 +3969,7 @@
         <v>9613.147491066447</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>10096.44152310148</v>
+        <v>10096.43898483051</v>
       </c>
     </row>
     <row r="198">
@@ -3985,7 +3985,7 @@
         <v>9653.049853805198</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>9943.00412341083</v>
+        <v>9943.003283241356</v>
       </c>
     </row>
     <row r="199">
@@ -4001,7 +4001,7 @@
         <v>9666.575956024637</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>10162.47576086585</v>
+        <v>10162.47659698907</v>
       </c>
     </row>
     <row r="200">
@@ -4017,7 +4017,7 @@
         <v>9796.429426862507</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>10141.12373943649</v>
+        <v>10141.12539760184</v>
       </c>
     </row>
     <row r="201">
@@ -4033,7 +4033,7 @@
         <v>9819.423903833098</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>10293.23720989381</v>
+        <v>10293.23970900047</v>
       </c>
     </row>
     <row r="202">
@@ -4049,7 +4049,7 @@
         <v>9817.395040098954</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>10159.52390668263</v>
+        <v>10159.52224685468</v>
       </c>
     </row>
     <row r="203">
@@ -4065,7 +4065,7 @@
         <v>9817.395040098954</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>10192.65763902453</v>
+        <v>10192.65930224543</v>
       </c>
     </row>
     <row r="204">
@@ -4081,7 +4081,7 @@
         <v>9801.839042169922</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>10047.72315211119</v>
+        <v>10047.72149291099</v>
       </c>
     </row>
     <row r="205">
@@ -4097,7 +4097,7 @@
         <v>9900.58154912518</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>10405.70248619344</v>
+        <v>10405.69997395581</v>
       </c>
     </row>
     <row r="206">
@@ -4113,7 +4113,7 @@
         <v>10031.11096388261</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>10453.92521884235</v>
+        <v>10453.92937320469</v>
       </c>
     </row>
     <row r="207">
@@ -4129,7 +4129,7 @@
         <v>10123.76584765999</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>10623.98260647369</v>
+        <v>10623.98427098413</v>
       </c>
     </row>
     <row r="208">
@@ -4145,7 +4145,7 @@
         <v>10142.02665324273</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>10576.00323187646</v>
+        <v>10576.00489379119</v>
       </c>
     </row>
     <row r="209">
@@ -4161,7 +4161,7 @@
         <v>10144.05551697687</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>10451.85723793137</v>
+        <v>10451.85558461808</v>
       </c>
     </row>
     <row r="210">
@@ -4193,7 +4193,7 @@
         <v>10208.30527650079</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>10716.66676574473</v>
+        <v>10716.66593064782</v>
       </c>
     </row>
     <row r="212">
@@ -4209,7 +4209,7 @@
         <v>10189.36852699849</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>10604.44392086822</v>
+        <v>10604.44226536647</v>
       </c>
     </row>
     <row r="213">
@@ -4241,7 +4241,7 @@
         <v>10151.49502799388</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>10601.96468829287</v>
+        <v>10601.96552011544</v>
       </c>
     </row>
     <row r="215">
@@ -4257,7 +4257,7 @@
         <v>10239.41520840796</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>10813.50016254714</v>
+        <v>10813.49850061552</v>
       </c>
     </row>
     <row r="216">
@@ -4273,7 +4273,7 @@
         <v>10300.96016027817</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>10716.25037671619</v>
+        <v>10716.24872973093</v>
       </c>
     </row>
     <row r="217">
@@ -4289,7 +4289,7 @@
         <v>10400.37861115299</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>10880.82832801788</v>
+        <v>10880.82750579766</v>
       </c>
     </row>
     <row r="218">
@@ -4305,7 +4305,7 @@
         <v>10515.35202798139</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>10989.91521455972</v>
+        <v>10989.9160416151</v>
       </c>
     </row>
     <row r="219">
@@ -4353,7 +4353,7 @@
         <v>10559.31315016388</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>11047.15281796122</v>
+        <v>11047.15365120884</v>
       </c>
     </row>
     <row r="222">
@@ -4385,7 +4385,7 @@
         <v>10434.19438268931</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>10825.92483407554</v>
+        <v>10825.92398879109</v>
       </c>
     </row>
     <row r="224">
@@ -4417,7 +4417,7 @@
         <v>10396.32088368471</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>10908.56596392762</v>
+        <v>10908.56681500572</v>
       </c>
     </row>
     <row r="226">
@@ -4433,7 +4433,7 @@
         <v>10448.39746080377</v>
       </c>
       <c r="D226" s="3" t="n">
-        <v>11060.14225247494</v>
+        <v>11060.14310336645</v>
       </c>
     </row>
     <row r="227">
@@ -4449,7 +4449,7 @@
         <v>10299.60724046359</v>
       </c>
       <c r="D227" s="3" t="n">
-        <v>10683.42107161185</v>
+        <v>10683.42277302153</v>
       </c>
     </row>
     <row r="228">
@@ -4481,7 +4481,7 @@
         <v>10014.87902203402</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>10451.48134765536</v>
+        <v>10451.48219472972</v>
       </c>
     </row>
     <row r="230">
@@ -4497,7 +4497,7 @@
         <v>9916.136515078761</v>
       </c>
       <c r="D230" s="3" t="n">
-        <v>10360.53147367079</v>
+        <v>10360.53062752955</v>
       </c>
     </row>
     <row r="231">
@@ -4513,7 +4513,7 @@
         <v>9860.679186386427</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>10378.55688917488</v>
+        <v>10378.55773413704</v>
       </c>
     </row>
     <row r="232">
@@ -4529,7 +4529,7 @@
         <v>9995.265296636699</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>10358.606771628</v>
+        <v>10358.60591930299</v>
       </c>
     </row>
     <row r="233">
@@ -4545,7 +4545,7 @@
         <v>9933.721376741936</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>10403.45244839631</v>
+        <v>10403.45159238131</v>
       </c>
     </row>
     <row r="234">
@@ -4577,7 +4577,7 @@
         <v>9880.96885570331</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>10562.62274553243</v>
+        <v>10562.62360253994</v>
       </c>
     </row>
     <row r="236">
@@ -4609,7 +4609,7 @@
         <v>10100.7713706894</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>10673.82189383287</v>
+        <v>10673.82443556459</v>
       </c>
     </row>
     <row r="238">
@@ -4641,7 +4641,7 @@
         <v>9992.560488982992</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>10199.68308995804</v>
+        <v>10199.68392737058</v>
       </c>
     </row>
     <row r="240">
@@ -4657,7 +4657,7 @@
         <v>9916.136515078761</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>10389.92130916197</v>
+        <v>10389.92215895068</v>
       </c>
     </row>
     <row r="241">
@@ -4673,7 +4673,7 @@
         <v>9860.679186386427</v>
       </c>
       <c r="D241" s="3" t="n">
-        <v>10269.91038974501</v>
+        <v>10269.91123936412</v>
       </c>
     </row>
     <row r="242">
@@ -4689,7 +4689,7 @@
         <v>9675.368386856224</v>
       </c>
       <c r="D242" s="3" t="n">
-        <v>10187.18755042963</v>
+        <v>10187.18839968401</v>
       </c>
     </row>
     <row r="243">
@@ -4705,7 +4705,7 @@
         <v>9703.097567190116</v>
       </c>
       <c r="D243" s="3" t="n">
-        <v>10231.32446767507</v>
+        <v>10231.32362130477</v>
       </c>
     </row>
     <row r="244">
@@ -4721,7 +4721,7 @@
         <v>9690.923352809807</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>10106.58543911487</v>
+        <v>10106.58374759593</v>
       </c>
     </row>
     <row r="245">
@@ -4753,7 +4753,7 @@
         <v>9596.239605298286</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>10046.07514977463</v>
+        <v>10046.07428690568</v>
       </c>
     </row>
     <row r="247">
@@ -4769,7 +4769,7 @@
         <v>9481.942132389448</v>
       </c>
       <c r="D247" s="3" t="n">
-        <v>9866.880775768317</v>
+        <v>9866.879913849383</v>
       </c>
     </row>
     <row r="248">
@@ -4801,7 +4801,7 @@
         <v>9502.23180170633</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>9964.900870101683</v>
+        <v>9964.898225814783</v>
       </c>
     </row>
     <row r="250">
@@ -4817,7 +4817,7 @@
         <v>9537.40049305723</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>10190.11335847897</v>
+        <v>10190.11159056539</v>
       </c>
     </row>
     <row r="251">
@@ -4833,7 +4833,7 @@
         <v>9308.129603319989</v>
       </c>
       <c r="D251" s="3" t="n">
-        <v>9862.167958465783</v>
+        <v>9862.166210944475</v>
       </c>
     </row>
     <row r="252">
@@ -4849,7 +4849,7 @@
         <v>9373.732282658488</v>
       </c>
       <c r="D252" s="3" t="n">
-        <v>9589.761248021941</v>
+        <v>9589.762110992659</v>
       </c>
     </row>
     <row r="253">
@@ -4865,7 +4865,7 @@
         <v>9356.824396890328</v>
       </c>
       <c r="D253" s="3" t="n">
-        <v>9879.997774908072</v>
+        <v>9879.996908688463</v>
       </c>
     </row>
     <row r="254">
@@ -4897,7 +4897,7 @@
         <v>9531.31286987935</v>
       </c>
       <c r="D255" s="3" t="n">
-        <v>9967.374116830159</v>
+        <v>9967.375816017466</v>
       </c>
     </row>
     <row r="256">
@@ -4913,7 +4913,7 @@
         <v>9606.383923969002</v>
       </c>
       <c r="D256" s="3" t="n">
-        <v>9937.536613420109</v>
+        <v>9937.534901661518</v>
       </c>
     </row>
     <row r="257">
@@ -4929,7 +4929,7 @@
         <v>9418.36831678509</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>9780.69047796851</v>
+        <v>9780.688744884557</v>
       </c>
     </row>
     <row r="258">
@@ -4945,7 +4945,7 @@
         <v>9378.46595404634</v>
       </c>
       <c r="D258" s="3" t="n">
-        <v>9759.882857119936</v>
+        <v>9759.881985768343</v>
       </c>
     </row>
     <row r="259">
@@ -4977,7 +4977,7 @@
         <v>9283.105230639805</v>
       </c>
       <c r="D260" s="3" t="n">
-        <v>9700.807788105771</v>
+        <v>9700.806913624114</v>
       </c>
     </row>
     <row r="261">
@@ -4993,7 +4993,7 @@
         <v>9292.573605390957</v>
       </c>
       <c r="D261" s="3" t="n">
-        <v>9948.80587723491</v>
+        <v>9948.80325590225</v>
       </c>
     </row>
     <row r="262">
@@ -5009,7 +5009,7 @@
         <v>9324.360513193134</v>
       </c>
       <c r="D262" s="3" t="n">
-        <v>9678.857577883638</v>
+        <v>9678.858447776254</v>
       </c>
     </row>
     <row r="263">
@@ -5025,7 +5025,7 @@
         <v>9412.281725582661</v>
       </c>
       <c r="D263" s="3" t="n">
-        <v>9939.774129731488</v>
+        <v>9939.771516847433</v>
       </c>
     </row>
     <row r="264">
@@ -5041,7 +5041,7 @@
         <v>9431.218475084965</v>
       </c>
       <c r="D264" s="3" t="n">
-        <v>9947.255096427385</v>
+        <v>9947.254234932641</v>
       </c>
     </row>
     <row r="265">
@@ -5073,7 +5073,7 @@
         <v>9484.647972018605</v>
       </c>
       <c r="D266" s="3" t="n">
-        <v>9874.081923514801</v>
+        <v>9874.08018642704</v>
       </c>
     </row>
     <row r="267">
@@ -5089,7 +5089,7 @@
         <v>9444.068633384839</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>10101.19649843948</v>
+        <v>10101.19563099844</v>
       </c>
     </row>
     <row r="268">
@@ -5105,7 +5105,7 @@
         <v>9542.134164445082</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>10140.60803709318</v>
+        <v>10140.61061798921</v>
       </c>
     </row>
     <row r="269">
@@ -5121,7 +5121,7 @@
         <v>9645.61034278819</v>
       </c>
       <c r="D269" s="3" t="n">
-        <v>10275.00870948854</v>
+        <v>10275.01214148815</v>
       </c>
     </row>
     <row r="270">
@@ -5137,7 +5137,7 @@
         <v>9664.547092290493</v>
       </c>
       <c r="D270" s="3" t="n">
-        <v>10118.55846177404</v>
+        <v>10118.55675907479</v>
       </c>
     </row>
     <row r="271">
@@ -5153,7 +5153,7 @@
         <v>9636.818943932052</v>
       </c>
       <c r="D271" s="3" t="n">
-        <v>9936.667481864419</v>
+        <v>9936.666641330225</v>
       </c>
     </row>
     <row r="272">
@@ -5185,7 +5185,7 @@
         <v>9784.931156401763</v>
       </c>
       <c r="D273" s="3" t="n">
-        <v>10238.5053560404</v>
+        <v>10238.50620813649</v>
       </c>
     </row>
     <row r="274">
@@ -5201,7 +5201,7 @@
         <v>9801.839042169922</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>10264.53559544767</v>
+        <v>10264.53645346454</v>
       </c>
     </row>
     <row r="275">
@@ -5217,7 +5217,7 @@
         <v>9737.589282646002</v>
       </c>
       <c r="D275" s="3" t="n">
-        <v>10015.44118267677</v>
+        <v>10015.44290016949</v>
       </c>
     </row>
     <row r="276">
@@ -5249,7 +5249,7 @@
         <v>9550.926595276669</v>
       </c>
       <c r="D277" s="3" t="n">
-        <v>10187.28172246584</v>
+        <v>10187.27998237546</v>
       </c>
     </row>
     <row r="278">
@@ -5281,7 +5281,7 @@
         <v>9680.103090219525</v>
       </c>
       <c r="D279" s="3" t="n">
-        <v>10062.57890772773</v>
+        <v>10062.58060109593</v>
       </c>
     </row>
     <row r="280">
@@ -5297,7 +5297,7 @@
         <v>9574.598048142274</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>9794.44918556268</v>
+        <v>9794.447502644931</v>
       </c>
     </row>
     <row r="281">
@@ -5329,7 +5329,7 @@
         <v>9767.347326714036</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>10318.69487928331</v>
+        <v>10318.69404701962</v>
       </c>
     </row>
     <row r="283">
@@ -5345,7 +5345,7 @@
         <v>9802.516018064936</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>10095.87652471335</v>
+        <v>10095.87816727064</v>
       </c>
     </row>
     <row r="284">
@@ -5361,7 +5361,7 @@
         <v>9855.944483023126</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>10191.13750657819</v>
+        <v>10191.13504052817</v>
       </c>
     </row>
     <row r="285">
@@ -5377,7 +5377,7 @@
         <v>9722.710260611984</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>10075.71459145384</v>
+        <v>10075.71377249938</v>
       </c>
     </row>
     <row r="286">
@@ -5393,7 +5393,7 @@
         <v>9680.103090219525</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>10008.99105831645</v>
+        <v>10008.98942626064</v>
       </c>
     </row>
     <row r="287">
@@ -5409,7 +5409,7 @@
         <v>9750.439440945876</v>
       </c>
       <c r="D287" s="3" t="n">
-        <v>10086.72820764701</v>
+        <v>10086.72738899802</v>
       </c>
     </row>
     <row r="288">
@@ -5425,7 +5425,7 @@
         <v>9782.902292667619</v>
       </c>
       <c r="D288" s="3" t="n">
-        <v>10080.04452637244</v>
+        <v>10080.04370528039</v>
       </c>
     </row>
     <row r="289">
@@ -5441,7 +5441,7 @@
         <v>9851.210811635276</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>10300.65161006095</v>
+        <v>10300.64912629923</v>
       </c>
     </row>
     <row r="290">
@@ -5457,7 +5457,7 @@
         <v>9888.408366720319</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>10299.82127971338</v>
+        <v>10299.82045704362</v>
       </c>
     </row>
     <row r="291">
@@ -5473,7 +5473,7 @@
         <v>9904.639276593465</v>
       </c>
       <c r="D291" s="3" t="n">
-        <v>10195.84904925231</v>
+        <v>10195.84823488704</v>
       </c>
     </row>
     <row r="292">
@@ -5505,7 +5505,7 @@
         <v>9816.042120284375</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>10078.030628128</v>
+        <v>10078.0322645101</v>
       </c>
     </row>
     <row r="294">
@@ -5521,7 +5521,7 @@
         <v>9757.878951962884</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>10082.10344255009</v>
+        <v>10082.10508240993</v>
       </c>
     </row>
     <row r="295">
@@ -5585,7 +5585,7 @@
         <v>9788.989915845497</v>
       </c>
       <c r="D298" s="3" t="n">
-        <v>10001.29244624293</v>
+        <v>10001.29003279373</v>
       </c>
     </row>
     <row r="299">
@@ -5601,7 +5601,7 @@
         <v>9652.373909885633</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>9901.504504512202</v>
+        <v>9901.505312617403</v>
       </c>
     </row>
     <row r="300">
@@ -5633,7 +5633,7 @@
         <v>9623.968785632178</v>
       </c>
       <c r="D301" s="3" t="n">
-        <v>9946.618494885441</v>
+        <v>9946.619301735116</v>
       </c>
     </row>
     <row r="302">
@@ -5649,7 +5649,7 @@
         <v>9668.60585173423</v>
       </c>
       <c r="D302" s="3" t="n">
-        <v>9828.93357746829</v>
+        <v>9828.931970860183</v>
       </c>
     </row>
     <row r="303">
@@ -5665,7 +5665,7 @@
         <v>9627.350569180899</v>
       </c>
       <c r="D303" s="3" t="n">
-        <v>10006.12206792577</v>
+        <v>10006.11884327522</v>
       </c>
     </row>
     <row r="304">
@@ -5681,7 +5681,7 @@
         <v>9765.994406899457</v>
       </c>
       <c r="D304" s="3" t="n">
-        <v>10063.19578780171</v>
+        <v>10063.19337379248</v>
       </c>
     </row>
     <row r="305">
@@ -5697,7 +5697,7 @@
         <v>9745.705769558024</v>
       </c>
       <c r="D305" s="3" t="n">
-        <v>9918.95775265329</v>
+        <v>9918.956156173486</v>
       </c>
     </row>
     <row r="306">
@@ -5713,7 +5713,7 @@
         <v>9409.576917928953</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>9631.285026246165</v>
+        <v>9631.283437197257</v>
       </c>
     </row>
     <row r="307">
@@ -5729,7 +5729,7 @@
         <v>9333.828887944288</v>
       </c>
       <c r="D307" s="3" t="n">
-        <v>9549.586164877344</v>
+        <v>9549.583773287748</v>
       </c>
     </row>
     <row r="308">
@@ -5761,7 +5761,7 @@
         <v>9262.139617403358</v>
       </c>
       <c r="D309" s="3" t="n">
-        <v>9504.76705034423</v>
+        <v>9504.767849491727</v>
       </c>
     </row>
     <row r="310">
@@ -5777,7 +5777,7 @@
         <v>9433.247338819108</v>
       </c>
       <c r="D310" s="3" t="n">
-        <v>9635.623356367849</v>
+        <v>9635.622558153467</v>
       </c>
     </row>
     <row r="311">
@@ -5809,7 +5809,7 @@
         <v>9308.805547239554</v>
       </c>
       <c r="D312" s="3" t="n">
-        <v>9574.116849835182</v>
+        <v>9574.115249843728</v>
       </c>
     </row>
     <row r="313">
@@ -5825,7 +5825,7 @@
         <v>9308.805547239554</v>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9516.252562307191</v>
+        <v>9516.250971985806</v>
       </c>
     </row>
     <row r="314">
@@ -5841,7 +5841,7 @@
         <v>9310.158467054132</v>
       </c>
       <c r="D314" s="3" t="n">
-        <v>9503.295853469765</v>
+        <v>9503.295056247778</v>
       </c>
     </row>
     <row r="315">
@@ -5857,7 +5857,7 @@
         <v>9259.43480974965</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>9387.883939288113</v>
+        <v>9387.885534190062</v>
       </c>
     </row>
     <row r="316">
@@ -5873,7 +5873,7 @@
         <v>9327.742296741857</v>
       </c>
       <c r="D316" s="3" t="n">
-        <v>9563.985489826029</v>
+        <v>9563.987085915685</v>
       </c>
     </row>
     <row r="317">
@@ -5889,7 +5889,7 @@
         <v>9236.440332779059</v>
       </c>
       <c r="D317" s="3" t="n">
-        <v>9510.608314632702</v>
+        <v>9510.607518946077</v>
       </c>
     </row>
     <row r="318">
@@ -5905,7 +5905,7 @@
         <v>9449.479280667705</v>
       </c>
       <c r="D318" s="3" t="n">
-        <v>9467.111774300045</v>
+        <v>9467.110982252472</v>
       </c>
     </row>
     <row r="319">
@@ -5921,7 +5921,7 @@
         <v>9355.471477075749</v>
       </c>
       <c r="D319" s="3" t="n">
-        <v>9455.5265590543</v>
+        <v>9455.524970208877</v>
       </c>
     </row>
     <row r="320">
@@ -6001,7 +6001,7 @@
         <v>9431.218475084965</v>
       </c>
       <c r="D324" s="3" t="n">
-        <v>9647.741733988962</v>
+        <v>9647.740943671839</v>
       </c>
     </row>
     <row r="325">
@@ -6017,7 +6017,7 @@
         <v>9515.081960006204</v>
       </c>
       <c r="D325" s="3" t="n">
-        <v>9764.521027987403</v>
+        <v>9764.521817880437</v>
       </c>
     </row>
     <row r="326">
@@ -6033,7 +6033,7 @@
         <v>9542.134164445082</v>
       </c>
       <c r="D326" s="3" t="n">
-        <v>9775.443750228809</v>
+        <v>9775.44690186106</v>
       </c>
     </row>
     <row r="327">
@@ -6049,7 +6049,7 @@
         <v>9573.245128327695</v>
       </c>
       <c r="D327" s="3" t="n">
-        <v>9728.214498396968</v>
+        <v>9728.213717325891</v>
       </c>
     </row>
     <row r="328">
@@ -6065,7 +6065,7 @@
         <v>9621.939921898034</v>
       </c>
       <c r="D328" s="3" t="n">
-        <v>9760.22637913108</v>
+        <v>9760.225595489792</v>
       </c>
     </row>
     <row r="329">
@@ -6081,7 +6081,7 @@
         <v>9648.992126336911</v>
       </c>
       <c r="D329" s="3" t="n">
-        <v>9737.390378041126</v>
+        <v>9737.391944526342</v>
       </c>
     </row>
     <row r="330">
@@ -6097,7 +6097,7 @@
         <v>9594.210741564142</v>
       </c>
       <c r="D330" s="3" t="n">
-        <v>9616.35172708643</v>
+        <v>9616.35094117179</v>
       </c>
     </row>
     <row r="331">
@@ -6113,7 +6113,7 @@
         <v>9451.508144401849</v>
       </c>
       <c r="D331" s="3" t="n">
-        <v>9542.327763074636</v>
+        <v>9542.326977490835</v>
       </c>
     </row>
     <row r="332">
@@ -6161,7 +6161,7 @@
         <v>9642.229591214917</v>
       </c>
       <c r="D334" s="3" t="n">
-        <v>9757.089085200168</v>
+        <v>9757.089865261816</v>
       </c>
     </row>
     <row r="335">
@@ -6177,7 +6177,7 @@
         <v>9565.805617310687</v>
       </c>
       <c r="D335" s="3" t="n">
-        <v>9748.328685471335</v>
+        <v>9748.327906402183</v>
       </c>
     </row>
     <row r="336">
@@ -6193,7 +6193,7 @@
         <v>9680.103090219525</v>
       </c>
       <c r="D336" s="3" t="n">
-        <v>9824.882806855876</v>
+        <v>9824.882030204268</v>
       </c>
     </row>
     <row r="337">
@@ -6209,7 +6209,7 @@
         <v>9769.37619044818</v>
       </c>
       <c r="D337" s="3" t="n">
-        <v>9872.411193770035</v>
+        <v>9872.410415150393</v>
       </c>
     </row>
     <row r="338">
@@ -6225,7 +6225,7 @@
         <v>9719.329509038711</v>
       </c>
       <c r="D338" s="3" t="n">
-        <v>9769.148437776952</v>
+        <v>9769.146877246505</v>
       </c>
     </row>
     <row r="339">
@@ -6241,7 +6241,7 @@
         <v>9710.537078207124</v>
       </c>
       <c r="D339" s="3" t="n">
-        <v>9931.751254665975</v>
+        <v>9931.752036424141</v>
       </c>
     </row>
     <row r="340">
@@ -6273,7 +6273,7 @@
         <v>9933.721376741936</v>
       </c>
       <c r="D341" s="3" t="n">
-        <v>10033.47290757252</v>
+        <v>10033.4721373253</v>
       </c>
     </row>
     <row r="342">
@@ -6289,7 +6289,7 @@
         <v>9985.120977965982</v>
       </c>
       <c r="D342" s="3" t="n">
-        <v>10024.8896494165</v>
+        <v>10024.88809370418</v>
       </c>
     </row>
     <row r="343">
@@ -6321,7 +6321,7 @@
         <v>9955.362933897948</v>
       </c>
       <c r="D344" s="3" t="n">
-        <v>10257.94714733762</v>
+        <v>10257.94556634709</v>
       </c>
     </row>
     <row r="345">
@@ -6337,7 +6337,7 @@
         <v>9941.836831678509</v>
       </c>
       <c r="D345" s="3" t="n">
-        <v>10146.75700023718</v>
+        <v>10146.75779080876</v>
       </c>
     </row>
     <row r="346">
@@ -6353,7 +6353,7 @@
         <v>9956.715853712527</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>10071.85313094877</v>
+        <v>10071.85233935074</v>
       </c>
     </row>
     <row r="347">
@@ -6369,7 +6369,7 @@
         <v>9905.992196408044</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>10070.476158246</v>
+        <v>10070.47694789298</v>
       </c>
     </row>
     <row r="348">
@@ -6385,7 +6385,7 @@
         <v>9974.976659295266</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>10250.31311659258</v>
+        <v>10250.314705438</v>
       </c>
     </row>
     <row r="349">
@@ -6401,7 +6401,7 @@
         <v>9930.339593193214</v>
       </c>
       <c r="D349" s="3" t="n">
-        <v>10195.27392074444</v>
+        <v>10195.27154918225</v>
       </c>
     </row>
     <row r="350">
@@ -6417,7 +6417,7 @@
         <v>10016.90788576816</v>
       </c>
       <c r="D350" s="3" t="n">
-        <v>10223.33134833522</v>
+        <v>10223.33055820476</v>
       </c>
     </row>
     <row r="351">
@@ -6433,7 +6433,7 @@
         <v>10007.43951101701</v>
       </c>
       <c r="D351" s="3" t="n">
-        <v>10124.02518458984</v>
+        <v>10124.02677134843</v>
       </c>
     </row>
     <row r="352">
@@ -6449,7 +6449,7 @@
         <v>9887.055446905741</v>
       </c>
       <c r="D352" s="3" t="n">
-        <v>10123.35150742241</v>
+        <v>10123.35230273579</v>
       </c>
     </row>
     <row r="353">
@@ -6465,7 +6465,7 @@
         <v>9906.668140327609</v>
       </c>
       <c r="D353" s="3" t="n">
-        <v>10105.64449014561</v>
+        <v>10105.64528406788</v>
       </c>
     </row>
     <row r="354">
@@ -6497,7 +6497,7 @@
         <v>9802.516018064936</v>
       </c>
       <c r="D355" s="3" t="n">
-        <v>9919.382004419056</v>
+        <v>9919.382800758845</v>
       </c>
     </row>
     <row r="356">
@@ -6513,7 +6513,7 @@
         <v>9800.487154330793</v>
       </c>
       <c r="D356" s="3" t="n">
-        <v>10015.59319591484</v>
+        <v>10015.59159629656</v>
       </c>
     </row>
     <row r="357">
@@ -6529,7 +6529,7 @@
         <v>9752.468304680018</v>
       </c>
       <c r="D357" s="3" t="n">
-        <v>9915.853940395351</v>
+        <v>9915.85233960645</v>
       </c>
     </row>
     <row r="358">
@@ -6545,7 +6545,7 @@
         <v>9806.573745533224</v>
       </c>
       <c r="D358" s="3" t="n">
-        <v>9990.43112216024</v>
+        <v>9990.431925837458</v>
       </c>
     </row>
     <row r="359">
@@ -6561,7 +6561,7 @@
         <v>9773.433917916467</v>
       </c>
       <c r="D359" s="3" t="n">
-        <v>9900.560439437972</v>
+        <v>9900.559640035952</v>
       </c>
     </row>
     <row r="360">
@@ -6593,7 +6593,7 @@
         <v>9717.299613329118</v>
       </c>
       <c r="D361" s="3" t="n">
-        <v>9885.497572828099</v>
+        <v>9885.496777752256</v>
       </c>
     </row>
     <row r="362">
@@ -6641,7 +6641,7 @@
         <v>9857.97334675727</v>
       </c>
       <c r="D364" s="3" t="n">
-        <v>9878.97716184584</v>
+        <v>9878.977955479624</v>
       </c>
     </row>
     <row r="365">
@@ -6657,7 +6657,7 @@
         <v>9845.124220432846</v>
       </c>
       <c r="D365" s="3" t="n">
-        <v>10024.13055292542</v>
+        <v>10024.13216089061</v>
       </c>
     </row>
     <row r="366">
@@ -6673,7 +6673,7 @@
         <v>9843.094324723252</v>
       </c>
       <c r="D366" s="3" t="n">
-        <v>9840.328261113431</v>
+        <v>9840.329869265224</v>
       </c>
     </row>
     <row r="367">
@@ -6705,7 +6705,7 @@
         <v>9407.548054194809</v>
       </c>
       <c r="D368" s="3" t="n">
-        <v>9562.937025556472</v>
+        <v>9562.937819538098</v>
       </c>
     </row>
     <row r="369">
@@ -6721,7 +6721,7 @@
         <v>9546.868867808382</v>
       </c>
       <c r="D369" s="3" t="n">
-        <v>9683.522596955459</v>
+        <v>9683.521806036078</v>
       </c>
     </row>
     <row r="370">
@@ -6753,7 +6753,7 @@
         <v>9591.505933910435</v>
       </c>
       <c r="D371" s="3" t="n">
-        <v>9922.855422475895</v>
+        <v>9922.856223981598</v>
       </c>
     </row>
     <row r="372">
@@ -6769,7 +6769,7 @@
         <v>9515.081960006204</v>
       </c>
       <c r="D372" s="3" t="n">
-        <v>9778.393111607635</v>
+        <v>9778.391513244786</v>
       </c>
     </row>
     <row r="373">
@@ -6785,7 +6785,7 @@
         <v>9515.757903925769</v>
       </c>
       <c r="D373" s="3" t="n">
-        <v>9812.584851082966</v>
+        <v>9812.584056745121</v>
       </c>
     </row>
     <row r="374">
@@ -6833,7 +6833,7 @@
         <v>9534.694653428072</v>
       </c>
       <c r="D376" s="3" t="n">
-        <v>9625.732290018757</v>
+        <v>9625.730729335657</v>
       </c>
     </row>
     <row r="377">
@@ -6849,7 +6849,7 @@
         <v>9508.995368803775</v>
       </c>
       <c r="D377" s="3" t="n">
-        <v>9720.490921309012</v>
+        <v>9720.492487081745</v>
       </c>
     </row>
     <row r="378">
@@ -6865,7 +6865,7 @@
         <v>9582.036527183833</v>
       </c>
       <c r="D378" s="3" t="n">
-        <v>9790.055209685464</v>
+        <v>9790.054422668107</v>
       </c>
     </row>
     <row r="379">
@@ -6881,7 +6881,7 @@
         <v>9535.371629323086</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>9741.968922388283</v>
+        <v>9741.969707301982</v>
       </c>
     </row>
     <row r="380">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="B380" s="3" t="n">
-        <v>10167.99</v>
+        <v>10167.98</v>
       </c>
       <c r="C380" s="3" t="n">
         <v>9630.731320754172</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="B381" s="3" t="n">
-        <v>10209.6</v>
+        <v>10209.61</v>
       </c>
       <c r="C381" s="3" t="n">
         <v>9680.77903413909</v>
@@ -6929,7 +6929,7 @@
         <v>9788.312939950483</v>
       </c>
       <c r="D382" s="3" t="n">
-        <v>9991.347903559996</v>
+        <v>9991.348681450087</v>
       </c>
     </row>
     <row r="383">
@@ -6961,7 +6961,7 @@
         <v>9756.526032148306</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>9966.814887265846</v>
+        <v>9966.814109918687</v>
       </c>
     </row>
     <row r="385">
@@ -6977,7 +6977,7 @@
         <v>9734.884474992294</v>
       </c>
       <c r="D385" s="3" t="n">
-        <v>9897.328219229843</v>
+        <v>9897.32899318395</v>
       </c>
     </row>
     <row r="386">
@@ -6993,7 +6993,7 @@
         <v>9742.999929928867</v>
       </c>
       <c r="D386" s="3" t="n">
-        <v>9987.665178883599</v>
+        <v>9987.665956866989</v>
       </c>
     </row>
     <row r="387">
@@ -7009,7 +7009,7 @@
         <v>9742.999929928867</v>
       </c>
       <c r="D387" s="3" t="n">
-        <v>9972.310475023543</v>
+        <v>9972.311251810886</v>
       </c>
     </row>
     <row r="388">
@@ -7025,7 +7025,7 @@
         <v>9742.999929928867</v>
       </c>
       <c r="D388" s="3" t="n">
-        <v>9988.540423276274</v>
+        <v>9988.539646022433</v>
       </c>
     </row>
     <row r="389">
@@ -7057,7 +7057,7 @@
         <v>9768.700246528615</v>
       </c>
       <c r="D390" s="3" t="n">
-        <v>9946.916774045812</v>
+        <v>9946.914443123982</v>
       </c>
     </row>
     <row r="391">
@@ -7089,7 +7089,7 @@
         <v>9826.186438955092</v>
       </c>
       <c r="D392" s="3" t="n">
-        <v>9929.7194219995</v>
+        <v>9929.717119986462</v>
       </c>
     </row>
     <row r="393">
@@ -7105,7 +7105,7 @@
         <v>9869.470585242565</v>
       </c>
       <c r="D393" s="3" t="n">
-        <v>10027.0415159317</v>
+        <v>10027.04228801967</v>
       </c>
     </row>
     <row r="394">
@@ -7121,7 +7121,7 @@
         <v>9885.702527091162</v>
       </c>
       <c r="D394" s="3" t="n">
-        <v>10089.79903495292</v>
+        <v>10089.80058778107</v>
       </c>
     </row>
     <row r="395">
@@ -7137,7 +7137,7 @@
         <v>9872.852368791288</v>
       </c>
       <c r="D395" s="3" t="n">
-        <v>10042.13637556171</v>
+        <v>10042.13482980803</v>
       </c>
     </row>
     <row r="396">
@@ -7153,7 +7153,7 @@
         <v>9840.389517069545</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>10008.4910875543</v>
+        <v>10008.49186206827</v>
       </c>
     </row>
     <row r="397">
@@ -7169,7 +7169,7 @@
         <v>9837.007733520823</v>
       </c>
       <c r="D397" s="3" t="n">
-        <v>9999.152285468386</v>
+        <v>9999.153058659058</v>
       </c>
     </row>
     <row r="398">
@@ -7185,7 +7185,7 @@
         <v>9793.047643313785</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>9990.147900646585</v>
+        <v>9990.147128957267</v>
       </c>
     </row>
     <row r="399">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="B399" s="3" t="n">
-        <v>10290.86</v>
+        <v>10290.85</v>
       </c>
       <c r="C399" s="3" t="n">
         <v>9775.462781650609</v>
@@ -7249,7 +7249,7 @@
         <v>9814.013256550232</v>
       </c>
       <c r="D402" s="3" t="n">
-        <v>10033.73366386042</v>
+        <v>10033.73520167433</v>
       </c>
     </row>
     <row r="403">
@@ -7265,7 +7265,7 @@
         <v>9814.013256550232</v>
       </c>
       <c r="D403" s="3" t="n">
-        <v>10042.84349570846</v>
+        <v>10042.8458068574</v>
       </c>
     </row>
     <row r="404">
@@ -7281,7 +7281,7 @@
         <v>9718.652533143697</v>
       </c>
       <c r="D404" s="3" t="n">
-        <v>9967.69249079958</v>
+        <v>9967.693264109068</v>
       </c>
     </row>
     <row r="405">
@@ -7297,7 +7297,7 @@
         <v>9732.178635363136</v>
       </c>
       <c r="D405" s="3" t="n">
-        <v>9861.812739944342</v>
+        <v>9861.81196956136</v>
       </c>
     </row>
     <row r="406">
@@ -7329,7 +7329,7 @@
         <v>9792.370667418771</v>
       </c>
       <c r="D407" s="3" t="n">
-        <v>9962.364303488048</v>
+        <v>9962.363533944877</v>
       </c>
     </row>
     <row r="408">
@@ -7345,7 +7345,7 @@
         <v>9823.481631301383</v>
       </c>
       <c r="D408" s="3" t="n">
-        <v>9968.865269513355</v>
+        <v>9968.86295999317</v>
       </c>
     </row>
     <row r="409">
@@ -7361,7 +7361,7 @@
         <v>9857.97334675727</v>
       </c>
       <c r="D409" s="3" t="n">
-        <v>9945.486030334359</v>
+        <v>9945.48834458789</v>
       </c>
     </row>
     <row r="410">
@@ -7377,7 +7377,7 @@
         <v>9845.124220432846</v>
       </c>
       <c r="D410" s="3" t="n">
-        <v>10020.63339384832</v>
+        <v>10020.63416748015</v>
       </c>
     </row>
     <row r="411">
@@ -7409,7 +7409,7 @@
         <v>9909.373979956767</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>10038.13841703602</v>
+        <v>10038.13997174749</v>
       </c>
     </row>
     <row r="413">
@@ -7441,7 +7441,7 @@
         <v>9918.842354707918</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>10040.83174524349</v>
+        <v>10040.83252534756</v>
       </c>
     </row>
     <row r="415">
@@ -7457,7 +7457,7 @@
         <v>9945.894559146796</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>10170.23211392907</v>
+        <v>10170.23133324824</v>
       </c>
     </row>
     <row r="416">
@@ -7489,7 +7489,7 @@
         <v>10082.51056510666</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>10339.1608139264</v>
+        <v>10339.16002670539</v>
       </c>
     </row>
     <row r="418">
@@ -7521,7 +7521,7 @@
         <v>10098.06553106024</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>10193.55281443646</v>
+        <v>10193.55516831214</v>
       </c>
     </row>
     <row r="420">
@@ -7537,7 +7537,7 @@
         <v>9940.48391186393</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>10158.54185038061</v>
+        <v>10158.54263801718</v>
       </c>
     </row>
     <row r="421">
@@ -7569,7 +7569,7 @@
         <v>10129.17649494286</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>10423.03065914287</v>
+        <v>10423.03224106638</v>
       </c>
     </row>
     <row r="423">
@@ -7585,7 +7585,7 @@
         <v>10158.93453901089</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>10424.3724786969</v>
+        <v>10424.37406082407</v>
       </c>
     </row>
     <row r="424">
@@ -7601,7 +7601,7 @@
         <v>10112.94455309426</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>10443.32858501393</v>
+        <v>10443.32937721422</v>
       </c>
     </row>
     <row r="425">
@@ -7633,7 +7633,7 @@
         <v>10055.45732869233</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>10496.32728540955</v>
+        <v>10496.32569915979</v>
       </c>
     </row>
     <row r="427">
@@ -7649,7 +7649,7 @@
         <v>10288.1100019783</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>10583.20390006855</v>
+        <v>10583.20074690951</v>
       </c>
     </row>
     <row r="428">
@@ -7665,7 +7665,7 @@
         <v>10320.57388567549</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>10624.30032866943</v>
+        <v>10624.3011215398</v>
       </c>
     </row>
     <row r="429">
@@ -7681,7 +7681,7 @@
         <v>10334.09998789493</v>
       </c>
       <c r="D429" s="3" t="n">
-        <v>10634.33609121712</v>
+        <v>10634.33688311202</v>
       </c>
     </row>
     <row r="430">
@@ -7697,7 +7697,7 @@
         <v>10315.16323839262</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>10611.18608595516</v>
+        <v>10611.18529304239</v>
       </c>
     </row>
     <row r="431">
@@ -7713,7 +7713,7 @@
         <v>10263.08666127356</v>
       </c>
       <c r="D431" s="3" t="n">
-        <v>10666.00483585281</v>
+        <v>10666.00562807004</v>
       </c>
     </row>
     <row r="432">
@@ -7729,7 +7729,7 @@
         <v>10313.13437465848</v>
       </c>
       <c r="D432" s="3" t="n">
-        <v>10610.5465354279</v>
+        <v>10610.54732211445</v>
       </c>
     </row>
     <row r="433">
@@ -7761,7 +7761,7 @@
         <v>10437.57616623804</v>
       </c>
       <c r="D434" s="3" t="n">
-        <v>10797.15043096216</v>
+        <v>10797.14885470499</v>
       </c>
     </row>
     <row r="435">
@@ -7777,7 +7777,7 @@
         <v>10438.92908605261</v>
       </c>
       <c r="D435" s="3" t="n">
-        <v>10783.59516394856</v>
+        <v>10783.59437774555</v>
       </c>
     </row>
     <row r="436">
@@ -7793,7 +7793,7 @@
         <v>10402.40747488714</v>
       </c>
       <c r="D436" s="3" t="n">
-        <v>10863.2203654252</v>
+        <v>10863.22114773472</v>
       </c>
     </row>
     <row r="437">
@@ -7841,7 +7841,7 @@
         <v>10329.36528453163</v>
       </c>
       <c r="D439" s="3" t="n">
-        <v>10689.93999457292</v>
+        <v>10689.93921808243</v>
       </c>
     </row>
     <row r="440">
@@ -7857,7 +7857,7 @@
         <v>10281.3474668563</v>
       </c>
       <c r="D440" s="3" t="n">
-        <v>10638.99984351469</v>
+        <v>10639.00062028507</v>
       </c>
     </row>
     <row r="441">
@@ -7873,7 +7873,7 @@
         <v>10254.29423044198</v>
       </c>
       <c r="D441" s="3" t="n">
-        <v>10607.21023724119</v>
+        <v>10607.2094655774</v>
       </c>
     </row>
     <row r="442">
@@ -7889,7 +7889,7 @@
         <v>10248.88358315911</v>
       </c>
       <c r="D442" s="3" t="n">
-        <v>10559.42105600739</v>
+        <v>10559.42183004636</v>
       </c>
     </row>
     <row r="443">
@@ -7905,7 +7905,7 @@
         <v>10225.21316226896</v>
       </c>
       <c r="D443" s="3" t="n">
-        <v>10566.6423498415</v>
+        <v>10566.64001660383</v>
       </c>
     </row>
     <row r="444">
@@ -7953,7 +7953,7 @@
         <v>10351.68381758265</v>
       </c>
       <c r="D446" s="3" t="n">
-        <v>10720.98897098384</v>
+        <v>10720.98974807657</v>
       </c>
     </row>
     <row r="447">
@@ -7969,7 +7969,7 @@
         <v>10441.63389370632</v>
       </c>
       <c r="D447" s="3" t="n">
-        <v>10895.22214458069</v>
+        <v>10895.22370560308</v>
       </c>
     </row>
     <row r="448">
@@ -7985,7 +7985,7 @@
         <v>10469.36307404021</v>
       </c>
       <c r="D448" s="3" t="n">
-        <v>10868.28283147747</v>
+        <v>10868.28127610452</v>
       </c>
     </row>
     <row r="449">
@@ -8001,7 +8001,7 @@
         <v>10480.86031252551</v>
       </c>
       <c r="D449" s="3" t="n">
-        <v>10862.71131410892</v>
+        <v>10862.70975953331</v>
       </c>
     </row>
     <row r="450">
@@ -8017,7 +8017,7 @@
         <v>10471.39193777436</v>
       </c>
       <c r="D450" s="3" t="n">
-        <v>10874.60777991335</v>
+        <v>10874.60855921151</v>
       </c>
     </row>
     <row r="451">
@@ -8033,7 +8033,7 @@
         <v>10300.28421635861</v>
       </c>
       <c r="D451" s="3" t="n">
-        <v>10817.63998850568</v>
+        <v>10817.63920717165</v>
       </c>
     </row>
     <row r="452">
@@ -8049,7 +8049,7 @@
         <v>10300.28421635861</v>
       </c>
       <c r="D452" s="3" t="n">
-        <v>10756.59073924687</v>
+        <v>10756.58996035587</v>
       </c>
     </row>
     <row r="453">
@@ -8065,7 +8065,7 @@
         <v>10257.00007007113</v>
       </c>
       <c r="D453" s="3" t="n">
-        <v>10706.06938923199</v>
+        <v>10706.06861595645</v>
       </c>
     </row>
     <row r="454">
@@ -8097,7 +8097,7 @@
         <v>10348.30203403393</v>
       </c>
       <c r="D455" s="3" t="n">
-        <v>10817.21638021677</v>
+        <v>10817.21561005434</v>
       </c>
     </row>
     <row r="456">
@@ -8113,7 +8113,7 @@
         <v>10348.30203403393</v>
       </c>
       <c r="D456" s="3" t="n">
-        <v>10775.41766272674</v>
+        <v>10775.4184238721</v>
       </c>
     </row>
     <row r="457">
@@ -8257,7 +8257,7 @@
         <v>10562.01795781759</v>
       </c>
       <c r="D465" s="3" t="n">
-        <v>11010.99274120849</v>
+        <v>11010.99350883457</v>
       </c>
     </row>
     <row r="466">
@@ -8273,7 +8273,7 @@
         <v>10713.51298581147</v>
       </c>
       <c r="D466" s="3" t="n">
-        <v>10910.43198274289</v>
+        <v>10910.43045135876</v>
       </c>
     </row>
     <row r="467">
@@ -8289,7 +8289,7 @@
         <v>10679.69721427515</v>
       </c>
       <c r="D467" s="3" t="n">
-        <v>11117.21081895924</v>
+        <v>11117.2100463199</v>
       </c>
     </row>
     <row r="468">
@@ -8305,7 +8305,7 @@
         <v>10684.430885663</v>
       </c>
       <c r="D468" s="3" t="n">
-        <v>11092.39960735782</v>
+        <v>11092.40037680771</v>
       </c>
     </row>
     <row r="469">
@@ -8321,7 +8321,7 @@
         <v>10679.02023838014</v>
       </c>
       <c r="D469" s="3" t="n">
-        <v>11087.4827569713</v>
+        <v>11087.48429960346</v>
       </c>
     </row>
     <row r="470">
@@ -8337,7 +8337,7 @@
         <v>10564.04682155173</v>
       </c>
       <c r="D470" s="3" t="n">
-        <v>10923.02770073598</v>
+        <v>10923.02693014092</v>
       </c>
     </row>
     <row r="471">
@@ -8369,7 +8369,7 @@
         <v>10495.73933455953</v>
       </c>
       <c r="D472" s="3" t="n">
-        <v>10898.19959124389</v>
+        <v>10898.19804213113</v>
       </c>
     </row>
     <row r="473">
@@ -8385,7 +8385,7 @@
         <v>10466.65723441106</v>
       </c>
       <c r="D473" s="3" t="n">
-        <v>10942.27942015953</v>
+        <v>10942.2771072803</v>
       </c>
     </row>
     <row r="474">
@@ -8401,7 +8401,7 @@
         <v>10445.01567725504</v>
       </c>
       <c r="D474" s="3" t="n">
-        <v>10894.21425324999</v>
+        <v>10894.21348232416</v>
       </c>
     </row>
     <row r="475">
@@ -8417,7 +8417,7 @@
         <v>10436.22324642346</v>
       </c>
       <c r="D475" s="3" t="n">
-        <v>10865.08362710925</v>
+        <v>10865.08285307028</v>
       </c>
     </row>
     <row r="476">
@@ -8433,7 +8433,7 @@
         <v>10487.62387962295</v>
       </c>
       <c r="D476" s="3" t="n">
-        <v>10850.40115407373</v>
+        <v>10850.40038135804</v>
       </c>
     </row>
     <row r="477">
@@ -8449,7 +8449,7 @@
         <v>10418.63941673573</v>
       </c>
       <c r="D477" s="3" t="n">
-        <v>10840.14675184343</v>
+        <v>10840.14597940765</v>
       </c>
     </row>
     <row r="478">
@@ -8465,7 +8465,7 @@
         <v>10484.24209607423</v>
       </c>
       <c r="D478" s="3" t="n">
-        <v>10937.09075949735</v>
+        <v>10937.08998443198</v>
       </c>
     </row>
     <row r="479">
@@ -8545,7 +8545,7 @@
         <v>10249.56055905412</v>
       </c>
       <c r="D483" s="3" t="n">
-        <v>10790.87202618797</v>
+        <v>10790.87280615625</v>
       </c>
     </row>
     <row r="484">
@@ -8561,7 +8561,7 @@
         <v>10349.65495384851</v>
       </c>
       <c r="D484" s="3" t="n">
-        <v>10739.17190452926</v>
+        <v>10739.17268286888</v>
       </c>
     </row>
     <row r="485">
@@ -8593,7 +8593,7 @@
         <v>10374.67829455324</v>
       </c>
       <c r="D486" s="3" t="n">
-        <v>10740.38250822656</v>
+        <v>10740.38328889892</v>
       </c>
     </row>
     <row r="487">
@@ -8609,7 +8609,7 @@
         <v>10376.70715828739</v>
       </c>
       <c r="D487" s="3" t="n">
-        <v>10882.856101188</v>
+        <v>10882.85453020701</v>
       </c>
     </row>
     <row r="488">
@@ -8625,7 +8625,7 @@
         <v>10458.54177947448</v>
       </c>
       <c r="D488" s="3" t="n">
-        <v>10953.64275499114</v>
+        <v>10953.64118375554</v>
       </c>
     </row>
     <row r="489">
@@ -8641,7 +8641,7 @@
         <v>10545.786015969</v>
       </c>
       <c r="D489" s="3" t="n">
-        <v>11083.05892900294</v>
+        <v>11083.0597125764</v>
       </c>
     </row>
     <row r="490">
@@ -8651,13 +8651,13 @@
         </is>
       </c>
       <c r="B490" s="3" t="n">
-        <v>11076.57</v>
+        <v>11076.58</v>
       </c>
       <c r="C490" s="3" t="n">
         <v>10539.69942476656</v>
       </c>
       <c r="D490" s="3" t="n">
-        <v>11084.01089980427</v>
+        <v>11084.012460657</v>
       </c>
     </row>
     <row r="491">
@@ -8689,7 +8689,7 @@
         <v>10670.228839524</v>
       </c>
       <c r="D492" s="3" t="n">
-        <v>11114.1067068507</v>
+        <v>11114.10748908394</v>
       </c>
     </row>
     <row r="493">
@@ -8705,7 +8705,7 @@
         <v>10675.63948680687</v>
       </c>
       <c r="D493" s="3" t="n">
-        <v>11184.49009398344</v>
+        <v>11184.4908811704</v>
       </c>
     </row>
     <row r="494">
@@ -8721,7 +8721,7 @@
         <v>10714.18892973104</v>
       </c>
       <c r="D494" s="3" t="n">
-        <v>11116.95169945967</v>
+        <v>11116.95327111936</v>
       </c>
     </row>
     <row r="495">
@@ -8737,7 +8737,7 @@
         <v>10627.62063715609</v>
       </c>
       <c r="D495" s="3" t="n">
-        <v>11112.54464350242</v>
+        <v>11112.54385266786</v>
       </c>
     </row>
     <row r="496">
@@ -8785,7 +8785,7 @@
         <v>10636.41306798768</v>
       </c>
       <c r="D498" s="3" t="n">
-        <v>11176.46668296786</v>
+        <v>11176.46747439622</v>
       </c>
     </row>
     <row r="499">
@@ -8801,7 +8801,7 @@
         <v>10641.14673937553</v>
       </c>
       <c r="D499" s="3" t="n">
-        <v>11081.80034929721</v>
+        <v>11081.79877119077</v>
       </c>
     </row>
     <row r="500">
@@ -8817,7 +8817,7 @@
         <v>10637.08901190724</v>
       </c>
       <c r="D500" s="3" t="n">
-        <v>11091.73689888814</v>
+        <v>11091.73611004704</v>
       </c>
     </row>
     <row r="501">
@@ -8827,13 +8827,13 @@
         </is>
       </c>
       <c r="B501" s="3" t="n">
-        <v>11179.35</v>
+        <v>11179.36</v>
       </c>
       <c r="C501" s="3" t="n">
         <v>10774.38096178667</v>
       </c>
       <c r="D501" s="3" t="n">
-        <v>11207.2221582229</v>
+        <v>11207.22452894519</v>
       </c>
     </row>
     <row r="502">
@@ -8849,7 +8849,7 @@
         <v>10725.01022429677</v>
       </c>
       <c r="D502" s="3" t="n">
-        <v>11173.21957294626</v>
+        <v>11173.21877549529</v>
       </c>
     </row>
     <row r="503">
@@ -8881,7 +8881,7 @@
         <v>10624.91582950238</v>
       </c>
       <c r="D504" s="3" t="n">
-        <v>11098.67394171197</v>
+        <v>11098.67473502343</v>
       </c>
     </row>
     <row r="505">
@@ -8897,7 +8897,7 @@
         <v>10655.34981748998</v>
       </c>
       <c r="D505" s="3" t="n">
-        <v>11007.57618752944</v>
+        <v>11007.57777573015</v>
       </c>
     </row>
     <row r="506">
@@ -8913,7 +8913,7 @@
         <v>10485.59398391336</v>
       </c>
       <c r="D506" s="3" t="n">
-        <v>10855.12715496683</v>
+        <v>10855.12635870341</v>
       </c>
     </row>
     <row r="507">
@@ -8945,7 +8945,7 @@
         <v>10476.12560916221</v>
       </c>
       <c r="D508" s="3" t="n">
-        <v>10880.89933933327</v>
+        <v>10880.90013593605</v>
       </c>
     </row>
     <row r="509">
@@ -8977,7 +8977,7 @@
         <v>10420.66828046988</v>
       </c>
       <c r="D510" s="3" t="n">
-        <v>10805.50050087342</v>
+        <v>10805.49809320067</v>
       </c>
     </row>
     <row r="511">
@@ -8993,7 +8993,7 @@
         <v>10436.90022231847</v>
       </c>
       <c r="D511" s="3" t="n">
-        <v>10934.53744068349</v>
+        <v>10934.53663322303</v>
       </c>
     </row>
     <row r="512">
@@ -9009,7 +9009,7 @@
         <v>10454.4840520062</v>
       </c>
       <c r="D512" s="3" t="n">
-        <v>10848.98458879063</v>
+        <v>10848.98378569873</v>
       </c>
     </row>
     <row r="513">
@@ -9025,7 +9025,7 @@
         <v>10442.9868135209</v>
       </c>
       <c r="D513" s="3" t="n">
-        <v>10841.80871070483</v>
+        <v>10841.80630206523</v>
       </c>
     </row>
     <row r="514">
@@ -9041,7 +9041,7 @@
         <v>10313.81031857805</v>
       </c>
       <c r="D514" s="3" t="n">
-        <v>10782.90757888309</v>
+        <v>10782.90676953097</v>
       </c>
     </row>
     <row r="515">
@@ -9057,7 +9057,7 @@
         <v>10279.99454704172</v>
       </c>
       <c r="D515" s="3" t="n">
-        <v>10870.19286772776</v>
+        <v>10870.19367773308</v>
       </c>
     </row>
     <row r="516">
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="B516" s="3" t="n">
-        <v>10737.46</v>
+        <v>10737.45</v>
       </c>
       <c r="C516" s="3" t="n">
         <v>10275.25984367842</v>
@@ -9089,7 +9089,7 @@
         <v>10339.51063517779</v>
       </c>
       <c r="D517" s="3" t="n">
-        <v>10917.61606181375</v>
+        <v>10917.6176704067</v>
       </c>
     </row>
     <row r="518">
@@ -9105,7 +9105,7 @@
         <v>10409.17104198458</v>
       </c>
       <c r="D518" s="3" t="n">
-        <v>10965.84367591395</v>
+        <v>10965.84447862417</v>
       </c>
     </row>
     <row r="519">
@@ -9121,7 +9121,7 @@
         <v>10555.2554226956</v>
       </c>
       <c r="D519" s="3" t="n">
-        <v>11011.03780367353</v>
+        <v>11011.03860551856</v>
       </c>
     </row>
     <row r="520">
@@ -9137,7 +9137,7 @@
         <v>10510.61835659354</v>
       </c>
       <c r="D520" s="3" t="n">
-        <v>11029.12327335229</v>
+        <v>11029.12407323776</v>
       </c>
     </row>
     <row r="521">
@@ -9153,7 +9153,7 @@
         <v>10593.80486561977</v>
       </c>
       <c r="D521" s="3" t="n">
-        <v>10941.77483467359</v>
+        <v>10941.77403625554</v>
       </c>
     </row>
     <row r="522">
@@ -9169,7 +9169,7 @@
         <v>10528.20218628127</v>
       </c>
       <c r="D522" s="3" t="n">
-        <v>10977.72765999714</v>
+        <v>10977.72927010007</v>
       </c>
     </row>
     <row r="523">
@@ -9195,13 +9195,13 @@
         </is>
       </c>
       <c r="B524" s="3" t="n">
-        <v>11017.99</v>
+        <v>11017.98</v>
       </c>
       <c r="C524" s="3" t="n">
         <v>10547.81591167859</v>
       </c>
       <c r="D524" s="3" t="n">
-        <v>11074.25499434254</v>
+        <v>11074.25419063138</v>
       </c>
     </row>
     <row r="525">
@@ -9217,7 +9217,7 @@
         <v>10493.03349493037</v>
       </c>
       <c r="D525" s="3" t="n">
-        <v>10907.31252964057</v>
+        <v>10907.31413421282</v>
       </c>
     </row>
     <row r="526">
@@ -9233,7 +9233,7 @@
         <v>10377.3841341824</v>
       </c>
       <c r="D526" s="3" t="n">
-        <v>10846.91338684905</v>
+        <v>10846.91419176474</v>
       </c>
     </row>
     <row r="527">
@@ -9265,7 +9265,7 @@
         <v>10152.84691583301</v>
       </c>
       <c r="D528" s="3" t="n">
-        <v>10643.09749051632</v>
+        <v>10643.09909252678</v>
       </c>
     </row>
     <row r="529">
@@ -9281,7 +9281,7 @@
         <v>10210.33414023494</v>
       </c>
       <c r="D529" s="3" t="n">
-        <v>10643.05321424188</v>
+        <v>10643.05400924986</v>
       </c>
     </row>
     <row r="530">
@@ -9297,7 +9297,7 @@
         <v>10166.3740500279</v>
       </c>
       <c r="D530" s="3" t="n">
-        <v>10564.06354663979</v>
+        <v>10564.06434723785</v>
       </c>
     </row>
     <row r="531">
@@ -9313,7 +9313,7 @@
         <v>10084.5394288408</v>
       </c>
       <c r="D531" s="3" t="n">
-        <v>10465.32256487563</v>
+        <v>10465.32095942131</v>
       </c>
     </row>
     <row r="532">
@@ -9329,7 +9329,7 @@
         <v>9995.942272531713</v>
       </c>
       <c r="D532" s="3" t="n">
-        <v>10420.63737401319</v>
+        <v>10420.63897989161</v>
       </c>
     </row>
     <row r="533">
@@ -9361,7 +9361,7 @@
         <v>10100.7713706894</v>
       </c>
       <c r="D534" s="3" t="n">
-        <v>10560.89240310377</v>
+        <v>10560.89160399019</v>
       </c>
     </row>
     <row r="535">
@@ -9393,7 +9393,7 @@
         <v>10359.79927251923</v>
       </c>
       <c r="D536" s="3" t="n">
-        <v>10906.82656960365</v>
+        <v>10906.82496715215</v>
       </c>
     </row>
     <row r="537">
@@ -9409,7 +9409,7 @@
         <v>10411.87584963829</v>
       </c>
       <c r="D537" s="3" t="n">
-        <v>10973.12370428172</v>
+        <v>10973.1213078571</v>
       </c>
     </row>
     <row r="538">
@@ -9425,7 +9425,7 @@
         <v>10384.1466693044</v>
       </c>
       <c r="D538" s="3" t="n">
-        <v>10882.50634386811</v>
+        <v>10882.50792465492</v>
       </c>
     </row>
     <row r="539">
@@ -9441,7 +9441,7 @@
         <v>10445.01567725504</v>
       </c>
       <c r="D539" s="3" t="n">
-        <v>10924.25676821143</v>
+        <v>10924.25597703755</v>
       </c>
     </row>
     <row r="540">
@@ -9457,7 +9457,7 @@
         <v>10409.17104198458</v>
       </c>
       <c r="D540" s="3" t="n">
-        <v>10958.27753823136</v>
+        <v>10958.27595211737</v>
       </c>
     </row>
     <row r="541">
@@ -9473,7 +9473,7 @@
         <v>10455.15999592576</v>
       </c>
       <c r="D541" s="3" t="n">
-        <v>10858.27838721474</v>
+        <v>10858.27917921136</v>
       </c>
     </row>
     <row r="542">
@@ -9489,7 +9489,7 @@
         <v>10430.13665522103</v>
       </c>
       <c r="D542" s="3" t="n">
-        <v>11072.01323581056</v>
+        <v>11072.01244063289</v>
       </c>
     </row>
     <row r="543">
@@ -9499,13 +9499,13 @@
         </is>
       </c>
       <c r="B543" s="3" t="n">
-        <v>10998.77</v>
+        <v>10998.76</v>
       </c>
       <c r="C543" s="3" t="n">
         <v>10503.17884557653</v>
       </c>
       <c r="D543" s="3" t="n">
-        <v>11038.09436324201</v>
+        <v>11038.09515674012</v>
       </c>
     </row>
     <row r="544">
@@ -9521,7 +9521,7 @@
         <v>10572.16330846376</v>
       </c>
       <c r="D544" s="3" t="n">
-        <v>11239.97246904194</v>
+        <v>11239.97167640907</v>
       </c>
     </row>
     <row r="545">
@@ -9537,7 +9537,7 @@
         <v>10610.03680746836</v>
       </c>
       <c r="D545" s="3" t="n">
-        <v>11081.02361144383</v>
+        <v>11081.02517099029</v>
       </c>
     </row>
     <row r="546">
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="B546" s="3" t="n">
-        <v>11011.89</v>
+        <v>11011.88</v>
       </c>
       <c r="C546" s="3" t="n">
         <v>10549.16779951772</v>
@@ -9569,7 +9569,7 @@
         <v>10587.04129852232</v>
       </c>
       <c r="D547" s="3" t="n">
-        <v>11133.51170084954</v>
+        <v>11133.51248238713</v>
       </c>
     </row>
     <row r="548">
@@ -9617,7 +9617,7 @@
         <v>10689.84153294587</v>
       </c>
       <c r="D550" s="3" t="n">
-        <v>11171.62895087417</v>
+        <v>11171.63050472026</v>
       </c>
     </row>
     <row r="551">
@@ -9633,7 +9633,7 @@
         <v>10684.430885663</v>
       </c>
       <c r="D551" s="3" t="n">
-        <v>11199.68297444408</v>
+        <v>11199.68453219216</v>
       </c>
     </row>
     <row r="552">
@@ -9649,7 +9649,7 @@
         <v>10664.14121634612</v>
       </c>
       <c r="D552" s="3" t="n">
-        <v>11190.70972016914</v>
+        <v>11190.70816462652</v>
       </c>
     </row>
     <row r="553">
@@ -9681,7 +9681,7 @@
         <v>10624.91582950238</v>
       </c>
       <c r="D554" s="3" t="n">
-        <v>11128.44439559466</v>
+        <v>11128.44671781337</v>
       </c>
     </row>
     <row r="555">
@@ -9697,7 +9697,7 @@
         <v>10632.35534051939</v>
       </c>
       <c r="D555" s="3" t="n">
-        <v>11072.60375970249</v>
+        <v>11072.60067677974</v>
       </c>
     </row>
     <row r="556">
@@ -9771,13 +9771,13 @@
         </is>
       </c>
       <c r="B560" s="3" t="n">
-        <v>11409.49</v>
+        <v>11409.48</v>
       </c>
       <c r="C560" s="3" t="n">
         <v>10858.92039062747</v>
       </c>
       <c r="D560" s="3" t="n">
-        <v>11294.10104230342</v>
+        <v>11294.10025641421</v>
       </c>
     </row>
     <row r="561">
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="B562" s="3" t="n">
-        <v>11546.33</v>
+        <v>11546.32</v>
       </c>
       <c r="C562" s="3" t="n">
         <v>10939.40209199999</v>
       </c>
       <c r="D562" s="3" t="n">
-        <v>11430.80736892848</v>
+        <v>11430.80815492794</v>
       </c>
     </row>
     <row r="563">
@@ -9825,7 +9825,7 @@
         <v>10977.95256689961</v>
       </c>
       <c r="D563" s="3" t="n">
-        <v>11503.38098741817</v>
+        <v>11503.38019949318</v>
       </c>
     </row>
     <row r="564">
@@ -9841,7 +9841,7 @@
         <v>10975.24672727046</v>
       </c>
       <c r="D564" s="3" t="n">
-        <v>11555.04898465579</v>
+        <v>11555.04977252145</v>
       </c>
     </row>
     <row r="565">
@@ -9883,7 +9883,7 @@
         </is>
       </c>
       <c r="B567" s="3" t="n">
-        <v>11610.68</v>
+        <v>11610.67</v>
       </c>
       <c r="C567" s="3" t="n">
         <v>11088.19128036472</v>
@@ -9905,7 +9905,7 @@
         <v>11092.92598372802</v>
       </c>
       <c r="D568" s="3" t="n">
-        <v>11659.28433872634</v>
+        <v>11659.28356016616</v>
       </c>
     </row>
     <row r="569">
@@ -9921,7 +9921,7 @@
         <v>11104.42322221331</v>
       </c>
       <c r="D569" s="3" t="n">
-        <v>11699.51093881689</v>
+        <v>11699.51016229251</v>
       </c>
     </row>
     <row r="570">
@@ -9937,7 +9937,7 @@
         <v>11138.9149376692</v>
       </c>
       <c r="D570" s="3" t="n">
-        <v>11477.26966811331</v>
+        <v>11477.27121306974</v>
       </c>
     </row>
     <row r="571">
@@ -9969,7 +9969,7 @@
         <v>11096.9837111963</v>
       </c>
       <c r="D572" s="3" t="n">
-        <v>11582.86258922092</v>
+        <v>11582.86335993466</v>
       </c>
     </row>
     <row r="573">
@@ -9985,7 +9985,7 @@
         <v>11096.9837111963</v>
       </c>
       <c r="D573" s="3" t="n">
-        <v>11561.44563597602</v>
+        <v>11561.4464052647</v>
       </c>
     </row>
     <row r="574">
@@ -10001,7 +10001,7 @@
         <v>11096.9837111963</v>
       </c>
       <c r="D574" s="3" t="n">
-        <v>11616.92153597439</v>
+        <v>11616.92230570419</v>
       </c>
     </row>
     <row r="575">
@@ -10033,7 +10033,7 @@
         <v>11099.01257493045</v>
       </c>
       <c r="D576" s="3" t="n">
-        <v>11549.68934501002</v>
+        <v>11549.68781779937</v>
       </c>
     </row>
     <row r="577">
@@ -10081,7 +10081,7 @@
         <v>11120.65413208646</v>
       </c>
       <c r="D579" s="3" t="n">
-        <v>11524.31773047895</v>
+        <v>11524.31696203849</v>
       </c>
     </row>
     <row r="580">
@@ -10097,7 +10097,7 @@
         <v>11068.57858694285</v>
       </c>
       <c r="D580" s="3" t="n">
-        <v>11531.51974018034</v>
+        <v>11531.52051543233</v>
       </c>
     </row>
     <row r="581">
@@ -10113,7 +10113,7 @@
         <v>11062.49199574042</v>
       </c>
       <c r="D581" s="3" t="n">
-        <v>11509.09042211475</v>
+        <v>11509.0888696259</v>
       </c>
     </row>
     <row r="582">
@@ -10129,7 +10129,7 @@
         <v>11041.52535052852</v>
       </c>
       <c r="D582" s="3" t="n">
-        <v>11504.19924082695</v>
+        <v>11504.19846597368</v>
       </c>
     </row>
     <row r="583">
@@ -10145,7 +10145,7 @@
         <v>11064.52085947456</v>
       </c>
       <c r="D583" s="3" t="n">
-        <v>11673.92537962004</v>
+        <v>11673.92615483807</v>
       </c>
     </row>
     <row r="584">
@@ -10161,7 +10161,7 @@
         <v>11147.70736850079</v>
       </c>
       <c r="D584" s="3" t="n">
-        <v>11646.14092316231</v>
+        <v>11646.13937406641</v>
       </c>
     </row>
     <row r="585">
@@ -10209,7 +10209,7 @@
         <v>11184.22794769082</v>
       </c>
       <c r="D587" s="3" t="n">
-        <v>11683.00627976727</v>
+        <v>11683.00550733148</v>
       </c>
     </row>
     <row r="588">
@@ -10219,13 +10219,13 @@
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>11826.78</v>
+        <v>11826.77</v>
       </c>
       <c r="C588" s="3" t="n">
         <v>11192.34443460284</v>
       </c>
       <c r="D588" s="3" t="n">
-        <v>11721.36761662935</v>
+        <v>11721.36684165726</v>
       </c>
     </row>
     <row r="589">
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="B589" s="3" t="n">
-        <v>11890.15</v>
+        <v>11890.14</v>
       </c>
       <c r="C589" s="3" t="n">
         <v>11219.39663904172</v>
@@ -10257,7 +10257,7 @@
         <v>11145.67850476664</v>
       </c>
       <c r="D590" s="3" t="n">
-        <v>11684.85772810593</v>
+        <v>11684.85928758437</v>
       </c>
     </row>
     <row r="591">
@@ -10305,7 +10305,7 @@
         <v>11354.659725187</v>
       </c>
       <c r="D593" s="3" t="n">
-        <v>11946.13285818381</v>
+        <v>11946.13207941154</v>
       </c>
     </row>
     <row r="594">
@@ -10321,7 +10321,7 @@
         <v>11369.53874722102</v>
       </c>
       <c r="D594" s="3" t="n">
-        <v>11994.28511326782</v>
+        <v>11994.28355399287</v>
       </c>
     </row>
     <row r="595">
@@ -10337,7 +10337,7 @@
         <v>11430.40672319622</v>
       </c>
       <c r="D595" s="3" t="n">
-        <v>12032.08801296159</v>
+        <v>12032.08723172089</v>
       </c>
     </row>
     <row r="596">
@@ -10353,7 +10353,7 @@
         <v>11478.42557284699</v>
       </c>
       <c r="D596" s="3" t="n">
-        <v>12070.99518225775</v>
+        <v>12070.99440273054</v>
       </c>
     </row>
     <row r="597">
@@ -10363,13 +10363,13 @@
         </is>
       </c>
       <c r="B597" s="3" t="n">
-        <v>12156.85</v>
+        <v>12156.84</v>
       </c>
       <c r="C597" s="3" t="n">
         <v>11493.30459488101</v>
       </c>
       <c r="D597" s="3" t="n">
-        <v>12094.22952178802</v>
+        <v>12094.22873976695</v>
       </c>
     </row>
     <row r="598">
@@ -10385,7 +10385,7 @@
         <v>11537.94166098306</v>
       </c>
       <c r="D598" s="3" t="n">
-        <v>12193.97430900758</v>
+        <v>12193.97509128313</v>
       </c>
     </row>
     <row r="599">
@@ -10401,7 +10401,7 @@
         <v>11571.08045662437</v>
       </c>
       <c r="D599" s="3" t="n">
-        <v>12194.71651658656</v>
+        <v>12194.71729951531</v>
       </c>
     </row>
     <row r="600">
@@ -10417,7 +10417,7 @@
         <v>11499.39118608344</v>
       </c>
       <c r="D600" s="3" t="n">
-        <v>11985.85440370046</v>
+        <v>11985.85362141641</v>
       </c>
     </row>
     <row r="601">
@@ -10433,7 +10433,7 @@
         <v>11456.10703979597</v>
       </c>
       <c r="D601" s="3" t="n">
-        <v>12187.09939910401</v>
+        <v>12187.1001842467</v>
       </c>
     </row>
     <row r="602">
@@ -10449,7 +10449,7 @@
         <v>11636.68313596287</v>
       </c>
       <c r="D602" s="3" t="n">
-        <v>12235.2978198878</v>
+        <v>12235.29937996013</v>
       </c>
     </row>
     <row r="603">
@@ -10513,7 +10513,7 @@
         <v>11739.48337038641</v>
       </c>
       <c r="D606" s="3" t="n">
-        <v>12446.75573682838</v>
+        <v>12446.75809841486</v>
       </c>
     </row>
     <row r="607">
@@ -10545,7 +10545,7 @@
         <v>11855.80970702939</v>
       </c>
       <c r="D608" s="3" t="n">
-        <v>12487.17335206019</v>
+        <v>12487.17492317698</v>
       </c>
     </row>
     <row r="609">
@@ -10561,7 +10561,7 @@
         <v>11740.83629020099</v>
       </c>
       <c r="D609" s="3" t="n">
-        <v>12344.84111020914</v>
+        <v>12344.84268510905</v>
       </c>
     </row>
     <row r="610">
@@ -10577,7 +10577,7 @@
         <v>11757.74417596915</v>
       </c>
       <c r="D610" s="3" t="n">
-        <v>12530.69645465464</v>
+        <v>12530.69883097537</v>
       </c>
     </row>
     <row r="611">
@@ -10609,7 +10609,7 @@
         <v>11867.30694551469</v>
       </c>
       <c r="D612" s="3" t="n">
-        <v>12478.63319249279</v>
+        <v>12478.6324051615</v>
       </c>
     </row>
     <row r="613">
@@ -10625,7 +10625,7 @@
         <v>11838.90182126123</v>
       </c>
       <c r="D613" s="3" t="n">
-        <v>12465.85946142305</v>
+        <v>12465.85867489771</v>
       </c>
     </row>
     <row r="614">
@@ -10641,7 +10641,7 @@
         <v>11724.60434835239</v>
       </c>
       <c r="D614" s="3" t="n">
-        <v>12408.1956929734</v>
+        <v>12408.19490575239</v>
       </c>
     </row>
     <row r="615">
@@ -10657,7 +10657,7 @@
         <v>11711.75419005252</v>
       </c>
       <c r="D615" s="3" t="n">
-        <v>12376.0743667502</v>
+        <v>12376.07358227765</v>
       </c>
     </row>
     <row r="616">
@@ -10667,13 +10667,13 @@
         </is>
       </c>
       <c r="B616" s="3" t="n">
-        <v>12993.22</v>
+        <v>12993.21</v>
       </c>
       <c r="C616" s="3" t="n">
         <v>11909.9151478826</v>
       </c>
       <c r="D616" s="3" t="n">
-        <v>12623.73380594486</v>
+        <v>12623.73458989151</v>
       </c>
     </row>
     <row r="617">
@@ -10689,7 +10689,7 @@
         <v>11955.22815790422</v>
       </c>
       <c r="D617" s="3" t="n">
-        <v>12626.28909935422</v>
+        <v>12626.29066648406</v>
       </c>
     </row>
     <row r="618">
@@ -10705,7 +10705,7 @@
         <v>11911.26703572173</v>
       </c>
       <c r="D618" s="3" t="n">
-        <v>12586.58320683137</v>
+        <v>12586.58477477563</v>
       </c>
     </row>
     <row r="619">
@@ -10721,7 +10721,7 @@
         <v>11893.683206034</v>
       </c>
       <c r="D619" s="3" t="n">
-        <v>12574.08222405036</v>
+        <v>12574.07987882687</v>
       </c>
     </row>
     <row r="620">
@@ -10737,7 +10737,7 @@
         <v>11900.44677313145</v>
       </c>
       <c r="D620" s="3" t="n">
-        <v>12564.54932045044</v>
+        <v>12564.54775608595</v>
       </c>
     </row>
     <row r="621">
@@ -10753,7 +10753,7 @@
         <v>11927.49897757032</v>
       </c>
       <c r="D621" s="3" t="n">
-        <v>12616.69096843467</v>
+        <v>12616.69175104955</v>
       </c>
     </row>
     <row r="622">
@@ -10769,7 +10769,7 @@
         <v>12011.36246249156</v>
       </c>
       <c r="D622" s="3" t="n">
-        <v>12775.03255329564</v>
+        <v>12775.03333836201</v>
       </c>
     </row>
     <row r="623">
@@ -10785,7 +10785,7 @@
         <v>12010.00954267698</v>
       </c>
       <c r="D623" s="3" t="n">
-        <v>12716.93405777986</v>
+        <v>12716.93327544489</v>
       </c>
     </row>
     <row r="624">
@@ -10801,7 +10801,7 @@
         <v>11928.17492148989</v>
       </c>
       <c r="D624" s="3" t="n">
-        <v>12575.36807122407</v>
+        <v>12575.36885265986</v>
       </c>
     </row>
     <row r="625">
@@ -10833,7 +10833,7 @@
         <v>12020.1538613477</v>
       </c>
       <c r="D626" s="3" t="n">
-        <v>12712.58940779004</v>
+        <v>12712.59174255451</v>
       </c>
     </row>
     <row r="627">
@@ -10849,7 +10849,7 @@
         <v>12028.94629217929</v>
       </c>
       <c r="D627" s="3" t="n">
-        <v>12577.88901322538</v>
+        <v>12577.8905625417</v>
       </c>
     </row>
     <row r="628">
@@ -10881,7 +10881,7 @@
         <v>12048.55898560116</v>
       </c>
       <c r="D629" s="3" t="n">
-        <v>12724.09985085589</v>
+        <v>12724.10217882578</v>
       </c>
     </row>
     <row r="630">
@@ -10897,7 +10897,7 @@
         <v>12048.55898560116</v>
       </c>
       <c r="D630" s="3" t="n">
-        <v>12708.32362947177</v>
+        <v>12708.32285322735</v>
       </c>
     </row>
     <row r="631">
@@ -10929,7 +10929,7 @@
         <v>11983.63328215767</v>
       </c>
       <c r="D632" s="3" t="n">
-        <v>12647.45293920762</v>
+        <v>12647.45371861606</v>
       </c>
     </row>
     <row r="633">
@@ -10961,7 +10961,7 @@
         <v>12108.07507373723</v>
       </c>
       <c r="D634" s="3" t="n">
-        <v>12804.45953554541</v>
+        <v>12804.45875545837</v>
       </c>
     </row>
     <row r="635">
@@ -10977,7 +10977,7 @@
         <v>12135.80425407112</v>
       </c>
       <c r="D635" s="3" t="n">
-        <v>12935.54041192057</v>
+        <v>12935.53963107002</v>
       </c>
     </row>
     <row r="636">
@@ -10993,7 +10993,7 @@
         <v>12311.64564687472</v>
       </c>
       <c r="D636" s="3" t="n">
-        <v>12890.59018722214</v>
+        <v>12890.59328951917</v>
       </c>
     </row>
     <row r="637">
@@ -11009,7 +11009,7 @@
         <v>12305.55905567229</v>
       </c>
       <c r="D637" s="3" t="n">
-        <v>12954.80782398576</v>
+        <v>12954.80860490417</v>
       </c>
     </row>
     <row r="638">
@@ -11041,7 +11041,7 @@
         <v>12296.09068092114</v>
       </c>
       <c r="D639" s="3" t="n">
-        <v>12923.86997300123</v>
+        <v>12923.86919034391</v>
       </c>
     </row>
     <row r="640">
@@ -11051,13 +11051,13 @@
         </is>
       </c>
       <c r="B640" s="3" t="n">
-        <v>13777.56</v>
+        <v>13777.55</v>
       </c>
       <c r="C640" s="3" t="n">
         <v>12290.68003363827</v>
       </c>
       <c r="D640" s="3" t="n">
-        <v>13039.54061783778</v>
+        <v>13039.53983475635</v>
       </c>
     </row>
     <row r="641">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="B641" s="3" t="n">
-        <v>13863.92</v>
+        <v>13863.91</v>
       </c>
       <c r="C641" s="3" t="n">
         <v>12369.13287127665</v>
       </c>
       <c r="D641" s="3" t="n">
-        <v>13059.92989876617</v>
+        <v>13059.92676094376</v>
       </c>
     </row>
     <row r="642">
@@ -11089,7 +11089,7 @@
         <v>12369.13287127665</v>
       </c>
       <c r="D642" s="3" t="n">
-        <v>13082.80878283587</v>
+        <v>13082.80563951649</v>
       </c>
     </row>
     <row r="643">
@@ -11105,7 +11105,7 @@
         <v>12369.13287127665</v>
       </c>
       <c r="D643" s="3" t="n">
-        <v>13062.15737834552</v>
+        <v>13062.15895025952</v>
       </c>
     </row>
     <row r="644">
@@ -11121,7 +11121,7 @@
         <v>12266.3326368531</v>
       </c>
       <c r="D644" s="3" t="n">
-        <v>13046.20625967981</v>
+        <v>13046.2078397202</v>
       </c>
     </row>
     <row r="645">
@@ -11137,7 +11137,7 @@
         <v>12277.15393141883</v>
       </c>
       <c r="D645" s="3" t="n">
-        <v>13022.53545683621</v>
+        <v>13022.5338813934</v>
       </c>
     </row>
     <row r="646">
@@ -11153,7 +11153,7 @@
         <v>12287.97522598456</v>
       </c>
       <c r="D646" s="3" t="n">
-        <v>12780.7432256396</v>
+        <v>12780.74244299081</v>
       </c>
     </row>
     <row r="647">
@@ -11169,7 +11169,7 @@
         <v>12200.7299575146</v>
       </c>
       <c r="D647" s="3" t="n">
-        <v>12915.8030282903</v>
+        <v>12915.80224554818</v>
       </c>
     </row>
     <row r="648">
@@ -11201,7 +11201,7 @@
         <v>12154.06505965386</v>
       </c>
       <c r="D649" s="3" t="n">
-        <v>12906.28857730108</v>
+        <v>12906.28935812609</v>
       </c>
     </row>
     <row r="650">
@@ -11233,7 +11233,7 @@
         <v>12227.78319392893</v>
       </c>
       <c r="D651" s="3" t="n">
-        <v>13019.63042203244</v>
+        <v>13019.62963234304</v>
       </c>
     </row>
     <row r="652">
@@ -11265,7 +11265,7 @@
         <v>12260.92198957024</v>
       </c>
       <c r="D653" s="3" t="n">
-        <v>12788.69530751203</v>
+        <v>12788.69610402992</v>
       </c>
     </row>
     <row r="654">
@@ -11281,7 +11281,7 @@
         <v>12069.52563081305</v>
       </c>
       <c r="D654" s="3" t="n">
-        <v>12794.05813422245</v>
+        <v>12794.05733591467</v>
       </c>
     </row>
     <row r="655">
@@ -11297,7 +11297,7 @@
         <v>12005.9518152087</v>
       </c>
       <c r="D655" s="3" t="n">
-        <v>12723.47312288464</v>
+        <v>12723.4739215147</v>
       </c>
     </row>
     <row r="656">
@@ -11313,7 +11313,7 @@
         <v>12034.35693946215</v>
       </c>
       <c r="D656" s="3" t="n">
-        <v>12640.24488608022</v>
+        <v>12640.24568112213</v>
       </c>
     </row>
     <row r="657">
@@ -11329,7 +11329,7 @@
         <v>11916.67768300459</v>
       </c>
       <c r="D657" s="3" t="n">
-        <v>12559.59480246285</v>
+        <v>12559.59559938796</v>
       </c>
     </row>
     <row r="658">
@@ -11345,7 +11345,7 @@
         <v>11940.3491358702</v>
       </c>
       <c r="D658" s="3" t="n">
-        <v>12658.52797887628</v>
+        <v>12658.52877474952</v>
       </c>
     </row>
     <row r="659">
@@ -11361,7 +11361,7 @@
         <v>12070.87751865218</v>
       </c>
       <c r="D659" s="3" t="n">
-        <v>12813.79322597672</v>
+        <v>12813.79242978966</v>
       </c>
     </row>
     <row r="660">
@@ -11377,7 +11377,7 @@
         <v>12076.28816593505</v>
       </c>
       <c r="D660" s="3" t="n">
-        <v>12747.53630385242</v>
+        <v>12747.53551140615</v>
       </c>
     </row>
     <row r="661">
@@ -11393,7 +11393,7 @@
         <v>11930.20378522403</v>
       </c>
       <c r="D661" s="3" t="n">
-        <v>12704.41049088068</v>
+        <v>12704.40890532652</v>
       </c>
     </row>
     <row r="662">
@@ -11409,7 +11409,7 @@
         <v>12144.5966849027</v>
       </c>
       <c r="D662" s="3" t="n">
-        <v>12789.22713327038</v>
+        <v>12789.22950501043</v>
       </c>
     </row>
     <row r="663">
@@ -11441,7 +11441,7 @@
         <v>12116.1905286738</v>
       </c>
       <c r="D664" s="3" t="n">
-        <v>12647.60594429359</v>
+        <v>12647.60515268711</v>
       </c>
     </row>
     <row r="665">
@@ -11457,7 +11457,7 @@
         <v>12116.1905286738</v>
       </c>
       <c r="D665" s="3" t="n">
-        <v>12664.62436513589</v>
+        <v>12664.62595564389</v>
       </c>
     </row>
     <row r="666">
@@ -11473,7 +11473,7 @@
         <v>12026.91742844514</v>
       </c>
       <c r="D666" s="3" t="n">
-        <v>12717.49825482174</v>
+        <v>12717.49904599562</v>
       </c>
     </row>
     <row r="667">
@@ -11489,7 +11489,7 @@
         <v>12124.98295950539</v>
       </c>
       <c r="D667" s="3" t="n">
-        <v>12861.32962223568</v>
+        <v>12861.33041256123</v>
       </c>
     </row>
     <row r="668">
@@ -11505,7 +11505,7 @@
         <v>12216.9618993632</v>
       </c>
       <c r="D668" s="3" t="n">
-        <v>12963.88630759762</v>
+        <v>12963.88394214291</v>
       </c>
     </row>
     <row r="669">
@@ -11521,7 +11521,7 @@
         <v>12300.82538428444</v>
       </c>
       <c r="D669" s="3" t="n">
-        <v>12966.88004006369</v>
+        <v>12966.87925226589</v>
       </c>
     </row>
     <row r="670">
@@ -11537,7 +11537,7 @@
         <v>12301.501328204</v>
       </c>
       <c r="D670" s="3" t="n">
-        <v>12988.65945533267</v>
+        <v>12988.6602443774</v>
       </c>
     </row>
     <row r="671">
@@ -11553,7 +11553,7 @@
         <v>12327.87758872332</v>
       </c>
       <c r="D671" s="3" t="n">
-        <v>13067.85174245285</v>
+        <v>13067.85016383754</v>
       </c>
     </row>
     <row r="672">
@@ -11569,7 +11569,7 @@
         <v>12369.13287127665</v>
       </c>
       <c r="D672" s="3" t="n">
-        <v>13038.28357858759</v>
+        <v>13038.28200557065</v>
       </c>
     </row>
     <row r="673">
@@ -11585,7 +11585,7 @@
         <v>12349.52017785478</v>
       </c>
       <c r="D673" s="3" t="n">
-        <v>13057.89125092578</v>
+        <v>13057.89203851153</v>
       </c>
     </row>
     <row r="674">
@@ -11601,7 +11601,7 @@
         <v>12342.75661075733</v>
       </c>
       <c r="D674" s="3" t="n">
-        <v>13089.68768691868</v>
+        <v>13089.6884728163</v>
       </c>
     </row>
     <row r="675">
@@ -11633,7 +11633,7 @@
         <v>12483.43034418548</v>
       </c>
       <c r="D676" s="3" t="n">
-        <v>13107.6093096806</v>
+        <v>13107.61086758147</v>
       </c>
     </row>
     <row r="677">
@@ -11713,7 +11713,7 @@
         <v>12494.25163875122</v>
       </c>
       <c r="D681" s="3" t="n">
-        <v>13117.74519503715</v>
+        <v>13117.74206064149</v>
       </c>
     </row>
     <row r="682">
@@ -11755,13 +11755,13 @@
         </is>
       </c>
       <c r="B684" s="3" t="n">
-        <v>14127.86</v>
+        <v>14127.85</v>
       </c>
       <c r="C684" s="3" t="n">
         <v>12427.9719835177</v>
       </c>
       <c r="D684" s="3" t="n">
-        <v>13169.1340284277</v>
+        <v>13169.13559033223</v>
       </c>
     </row>
     <row r="685">
@@ -11771,13 +11771,13 @@
         </is>
       </c>
       <c r="B685" s="3" t="n">
-        <v>14032.32</v>
+        <v>14032.31</v>
       </c>
       <c r="C685" s="3" t="n">
         <v>12379.95416584238</v>
       </c>
       <c r="D685" s="3" t="n">
-        <v>13088.99233155021</v>
+        <v>13088.98998653025</v>
       </c>
     </row>
     <row r="686">
@@ -11793,7 +11793,7 @@
         <v>12345.46141841104</v>
       </c>
       <c r="D686" s="3" t="n">
-        <v>13062.41063193133</v>
+        <v>13062.40906134061</v>
       </c>
     </row>
     <row r="687">
@@ -11809,7 +11809,7 @@
         <v>12264.30377311896</v>
       </c>
       <c r="D687" s="3" t="n">
-        <v>13140.52169805939</v>
+        <v>13140.52482950287</v>
       </c>
     </row>
     <row r="688">
@@ -11825,7 +11825,7 @@
         <v>12355.60676905721</v>
       </c>
       <c r="D688" s="3" t="n">
-        <v>13129.85974157628</v>
+        <v>13129.86130475326</v>
       </c>
     </row>
     <row r="689">
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="B689" s="3" t="n">
-        <v>13975.07</v>
+        <v>13975.06</v>
       </c>
       <c r="C689" s="3" t="n">
         <v>12331.9353161916</v>
@@ -11857,7 +11857,7 @@
         <v>12479.3726167172</v>
       </c>
       <c r="D690" s="3" t="n">
-        <v>13265.538340385</v>
+        <v>13265.5398994225</v>
       </c>
     </row>
     <row r="691">
@@ -11889,7 +11889,7 @@
         <v>12587.58246644816</v>
       </c>
       <c r="D692" s="3" t="n">
-        <v>13233.8865963145</v>
+        <v>13233.88348183593</v>
       </c>
     </row>
     <row r="693">
@@ -11905,7 +11905,7 @@
         <v>12640.33498748678</v>
       </c>
       <c r="D693" s="3" t="n">
-        <v>13417.08212133489</v>
+        <v>13417.07897346913</v>
       </c>
     </row>
     <row r="694">
@@ -11921,7 +11921,7 @@
         <v>12622.07521387949</v>
       </c>
       <c r="D694" s="3" t="n">
-        <v>13467.65853669041</v>
+        <v>13467.65696061985</v>
       </c>
     </row>
     <row r="695">
@@ -11937,7 +11937,7 @@
         <v>12684.29610966927</v>
       </c>
       <c r="D695" s="3" t="n">
-        <v>13608.52492217967</v>
+        <v>13608.52650176216</v>
       </c>
     </row>
     <row r="696">
@@ -11953,7 +11953,7 @@
         <v>12683.61913377425</v>
       </c>
       <c r="D696" s="3" t="n">
-        <v>13544.09751886677</v>
+        <v>13544.09594992166</v>
       </c>
     </row>
     <row r="697">
@@ -11969,7 +11969,7 @@
         <v>12718.78782512515</v>
       </c>
       <c r="D697" s="3" t="n">
-        <v>13646.1273559541</v>
+        <v>13646.1257761512</v>
       </c>
     </row>
     <row r="698">
@@ -11985,7 +11985,7 @@
         <v>12726.22733614216</v>
       </c>
       <c r="D698" s="3" t="n">
-        <v>13801.85099819014</v>
+        <v>13801.85258340503</v>
       </c>
     </row>
     <row r="699">
@@ -12011,7 +12011,7 @@
         </is>
       </c>
       <c r="B700" s="3" t="n">
-        <v>14539.48</v>
+        <v>14539.47</v>
       </c>
       <c r="C700" s="3" t="n">
         <v>12812.79562871711</v>
@@ -12065,7 +12065,7 @@
         <v>12843.22961670471</v>
       </c>
       <c r="D703" s="3" t="n">
-        <v>13754.55433504426</v>
+        <v>13754.557509749</v>
       </c>
     </row>
     <row r="704">
@@ -12097,7 +12097,7 @@
         <v>12827.67465075113</v>
       </c>
       <c r="D705" s="3" t="n">
-        <v>13796.5357887896</v>
+        <v>13796.53737290167</v>
       </c>
     </row>
     <row r="706">
@@ -12123,13 +12123,13 @@
         </is>
       </c>
       <c r="B707" s="3" t="n">
-        <v>14454.6</v>
+        <v>14454.59</v>
       </c>
       <c r="C707" s="3" t="n">
         <v>12875.6935004019</v>
       </c>
       <c r="D707" s="3" t="n">
-        <v>13765.38183890746</v>
+        <v>13765.3850074709</v>
       </c>
     </row>
     <row r="708">
@@ -12145,7 +12145,7 @@
         <v>12800.62244631225</v>
       </c>
       <c r="D708" s="3" t="n">
-        <v>13759.29579635243</v>
+        <v>13759.29737668126</v>
       </c>
     </row>
     <row r="709">
@@ -12177,7 +12177,7 @@
         <v>12861.49042228745</v>
       </c>
       <c r="D710" s="3" t="n">
-        <v>13896.68104462704</v>
+        <v>13896.67946623233</v>
       </c>
     </row>
     <row r="711">
@@ -12193,7 +12193,7 @@
         <v>12890.57252243592</v>
       </c>
       <c r="D711" s="3" t="n">
-        <v>13838.87696829797</v>
+        <v>13838.87539646869</v>
       </c>
     </row>
     <row r="712">
@@ -12209,7 +12209,7 @@
         <v>12895.30619382377</v>
       </c>
       <c r="D712" s="3" t="n">
-        <v>13896.29350583733</v>
+        <v>13896.29664444034</v>
       </c>
     </row>
     <row r="713">
@@ -12241,7 +12241,7 @@
         <v>12939.26731600626</v>
       </c>
       <c r="D714" s="3" t="n">
-        <v>13899.81190735421</v>
+        <v>13899.81504008707</v>
       </c>
     </row>
     <row r="715">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="B715" s="3" t="n">
-        <v>14603.25</v>
+        <v>14603.24</v>
       </c>
       <c r="C715" s="3" t="n">
         <v>12989.31399741573</v>
       </c>
       <c r="D715" s="3" t="n">
-        <v>14058.33920931743</v>
+        <v>14058.33607190211</v>
       </c>
     </row>
     <row r="716">
@@ -12289,7 +12289,7 @@
         <v>13031.24522388862</v>
       </c>
       <c r="D717" s="3" t="n">
-        <v>13950.25044781253</v>
+        <v>13950.24888746875</v>
       </c>
     </row>
     <row r="718">
@@ -12321,7 +12321,7 @@
         <v>13050.85894928594</v>
       </c>
       <c r="D719" s="3" t="n">
-        <v>14034.38669666398</v>
+        <v>14034.38825288513</v>
       </c>
     </row>
     <row r="720">
@@ -12337,7 +12337,7 @@
         <v>12914.24294332607</v>
       </c>
       <c r="D720" s="3" t="n">
-        <v>13836.4075487461</v>
+        <v>13836.40599266056</v>
       </c>
     </row>
     <row r="721">
@@ -12353,7 +12353,7 @@
         <v>12839.84886513144</v>
       </c>
       <c r="D721" s="3" t="n">
-        <v>13682.77063242404</v>
+        <v>13682.76753097515</v>
       </c>
     </row>
     <row r="722">
@@ -12363,13 +12363,13 @@
         </is>
       </c>
       <c r="B722" s="3" t="n">
-        <v>14328.9</v>
+        <v>14328.89</v>
       </c>
       <c r="C722" s="3" t="n">
         <v>12764.77781104179</v>
       </c>
       <c r="D722" s="3" t="n">
-        <v>13640.08694446893</v>
+        <v>13640.08850069008</v>
       </c>
     </row>
     <row r="723">
@@ -12385,7 +12385,7 @@
         <v>12824.29286720241</v>
       </c>
       <c r="D723" s="3" t="n">
-        <v>13783.72189972357</v>
+        <v>13783.72034316302</v>
       </c>
     </row>
     <row r="724">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="B725" s="3" t="n">
-        <v>14204.51</v>
+        <v>14204.5</v>
       </c>
       <c r="C725" s="3" t="n">
         <v>12721.49366475431</v>
@@ -12449,7 +12449,7 @@
         <v>12680.23838220098</v>
       </c>
       <c r="D727" s="3" t="n">
-        <v>13589.71228602846</v>
+        <v>13589.71072259698</v>
       </c>
     </row>
     <row r="728">
@@ -12475,13 +12475,13 @@
         </is>
       </c>
       <c r="B729" s="3" t="n">
-        <v>14134.87</v>
+        <v>14134.86</v>
       </c>
       <c r="C729" s="3" t="n">
         <v>12714.0541537373</v>
       </c>
       <c r="D729" s="3" t="n">
-        <v>13568.5900389462</v>
+        <v>13568.59317500438</v>
       </c>
     </row>
     <row r="730">
@@ -12497,7 +12497,7 @@
         <v>12902.74570484078</v>
       </c>
       <c r="D730" s="3" t="n">
-        <v>13793.47109121316</v>
+        <v>13793.47422825537</v>
       </c>
     </row>
     <row r="731">
@@ -12513,7 +12513,7 @@
         <v>12776.27504952708</v>
       </c>
       <c r="D731" s="3" t="n">
-        <v>13588.29030259659</v>
+        <v>13588.28716782775</v>
       </c>
     </row>
     <row r="732">
@@ -12529,7 +12529,7 @@
         <v>12263.62782919939</v>
       </c>
       <c r="D732" s="3" t="n">
-        <v>13380.18529917131</v>
+        <v>13380.1868718319</v>
       </c>
     </row>
     <row r="733">
@@ -12577,7 +12577,7 @@
         <v>12262.95188527983</v>
       </c>
       <c r="D735" s="3" t="n">
-        <v>12857.43442807934</v>
+        <v>12857.43598078872</v>
       </c>
     </row>
     <row r="736">
@@ -12609,7 +12609,7 @@
         <v>12312.32262276973</v>
       </c>
       <c r="D737" s="3" t="n">
-        <v>13225.37391264927</v>
+        <v>13225.37702105382</v>
       </c>
     </row>
     <row r="738">
@@ -12641,7 +12641,7 @@
         <v>12453.67230011745</v>
       </c>
       <c r="D739" s="3" t="n">
-        <v>13424.68540012133</v>
+        <v>13424.68850269025</v>
       </c>
     </row>
     <row r="740">
@@ -12657,7 +12657,7 @@
         <v>12484.78326400006</v>
       </c>
       <c r="D740" s="3" t="n">
-        <v>13392.66054123773</v>
+        <v>13392.66362667161</v>
       </c>
     </row>
     <row r="741">
@@ -12689,7 +12689,7 @@
         <v>12719.46480102017</v>
       </c>
       <c r="D742" s="3" t="n">
-        <v>13682.93628781724</v>
+        <v>13682.93474169025</v>
       </c>
     </row>
     <row r="743">
@@ -12705,7 +12705,7 @@
         <v>12756.66132412976</v>
       </c>
       <c r="D743" s="3" t="n">
-        <v>13748.28251913673</v>
+        <v>13748.28559673262</v>
       </c>
     </row>
     <row r="744">
@@ -12721,7 +12721,7 @@
         <v>12728.25619987631</v>
       </c>
       <c r="D744" s="3" t="n">
-        <v>13649.80855432541</v>
+        <v>13649.81008458981</v>
       </c>
     </row>
     <row r="745">
@@ -12731,13 +12731,13 @@
         </is>
       </c>
       <c r="B745" s="3" t="n">
-        <v>14201.89</v>
+        <v>14201.88</v>
       </c>
       <c r="C745" s="3" t="n">
         <v>12740.43041425662</v>
       </c>
       <c r="D745" s="3" t="n">
-        <v>13645.6956327126</v>
+        <v>13645.69410814858</v>
       </c>
     </row>
     <row r="746">
@@ -12753,7 +12753,7 @@
         <v>12761.39602749307</v>
       </c>
       <c r="D746" s="3" t="n">
-        <v>13505.30196902864</v>
+        <v>13505.30348984341</v>
       </c>
     </row>
     <row r="747">
@@ -12769,7 +12769,7 @@
         <v>12765.45375496135</v>
       </c>
       <c r="D747" s="3" t="n">
-        <v>13695.69841134335</v>
+        <v>13695.69535926321</v>
       </c>
     </row>
     <row r="748">
@@ -12785,7 +12785,7 @@
         <v>12756.66132412976</v>
       </c>
       <c r="D748" s="3" t="n">
-        <v>13576.6180639001</v>
+        <v>13576.61958028698</v>
       </c>
     </row>
     <row r="749">
@@ -12801,7 +12801,7 @@
         <v>12764.77781104179</v>
       </c>
       <c r="D749" s="3" t="n">
-        <v>13623.55396076387</v>
+        <v>13623.55244122138</v>
       </c>
     </row>
     <row r="750">
@@ -12817,7 +12817,7 @@
         <v>12760.71905159805</v>
       </c>
       <c r="D750" s="3" t="n">
-        <v>13528.43552872694</v>
+        <v>13528.43401098293</v>
       </c>
     </row>
     <row r="751">
@@ -12833,7 +12833,7 @@
         <v>12904.77456857492</v>
       </c>
       <c r="D751" s="3" t="n">
-        <v>13594.07289397889</v>
+        <v>13594.06984403632</v>
       </c>
     </row>
     <row r="752">
@@ -12849,7 +12849,7 @@
         <v>12860.81447836789</v>
       </c>
       <c r="D752" s="3" t="n">
-        <v>13778.96046360074</v>
+        <v>13778.95893250493</v>
       </c>
     </row>
     <row r="753">
@@ -12865,7 +12865,7 @@
         <v>12940.61920384539</v>
       </c>
       <c r="D753" s="3" t="n">
-        <v>13823.38883796424</v>
+        <v>13823.38730193162</v>
       </c>
     </row>
     <row r="754">
@@ -12881,7 +12881,7 @@
         <v>12814.14854853169</v>
       </c>
       <c r="D754" s="3" t="n">
-        <v>13511.25015779636</v>
+        <v>13511.25322358448</v>
       </c>
     </row>
     <row r="755">
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="B755" s="3" t="n">
-        <v>13915.01</v>
+        <v>13915</v>
       </c>
       <c r="C755" s="3" t="n">
         <v>12663.33049643282</v>
       </c>
       <c r="D755" s="3" t="n">
-        <v>13506.2797159584</v>
+        <v>13506.2781804856</v>
       </c>
     </row>
     <row r="756">
@@ -12913,7 +12913,7 @@
         <v>12576.08522796286</v>
       </c>
       <c r="D756" s="3" t="n">
-        <v>13435.02428769095</v>
+        <v>13435.02275659514</v>
       </c>
     </row>
     <row r="757">
@@ -12929,7 +12929,7 @@
         <v>12420.53247250069</v>
       </c>
       <c r="D757" s="3" t="n">
-        <v>13172.46536498916</v>
+        <v>13172.46383811785</v>
       </c>
     </row>
     <row r="758">
@@ -12961,7 +12961,7 @@
         <v>12583.52473897987</v>
       </c>
       <c r="D759" s="3" t="n">
-        <v>13467.14978273143</v>
+        <v>13467.15131978199</v>
       </c>
     </row>
     <row r="760">
@@ -12977,7 +12977,7 @@
         <v>12521.30384319009</v>
       </c>
       <c r="D760" s="3" t="n">
-        <v>13625.73236861766</v>
+        <v>13625.73390797552</v>
       </c>
     </row>
     <row r="761">
@@ -12993,7 +12993,7 @@
         <v>12754.63246039562</v>
       </c>
       <c r="D761" s="3" t="n">
-        <v>13753.07418155197</v>
+        <v>13753.07572231793</v>
       </c>
     </row>
     <row r="762">
@@ -13019,13 +13019,13 @@
         </is>
       </c>
       <c r="B763" s="3" t="n">
-        <v>14117.43</v>
+        <v>14117.42</v>
       </c>
       <c r="C763" s="3" t="n">
         <v>12793.18293529524</v>
       </c>
       <c r="D763" s="3" t="n">
-        <v>13748.51366057999</v>
+        <v>13748.51672056591</v>
       </c>
     </row>
     <row r="764">
@@ -13041,7 +13041,7 @@
         <v>12868.92993330446</v>
       </c>
       <c r="D764" s="3" t="n">
-        <v>13703.34564630832</v>
+        <v>13703.34717065188</v>
       </c>
     </row>
     <row r="765">
@@ -13057,7 +13057,7 @@
         <v>12803.32725396596</v>
       </c>
       <c r="D765" s="3" t="n">
-        <v>13670.61217706181</v>
+        <v>13670.61370228756</v>
       </c>
     </row>
     <row r="766">
@@ -13073,7 +13073,7 @@
         <v>12983.2274062133</v>
       </c>
       <c r="D766" s="3" t="n">
-        <v>13914.25346157457</v>
+        <v>13914.25498793691</v>
       </c>
     </row>
     <row r="767">
@@ -13089,7 +13089,7 @@
         <v>12900.71684110664</v>
       </c>
       <c r="D767" s="3" t="n">
-        <v>13831.5358584005</v>
+        <v>13831.53433848491</v>
       </c>
     </row>
     <row r="768">
@@ -13105,7 +13105,7 @@
         <v>12985.932213867</v>
       </c>
       <c r="D768" s="3" t="n">
-        <v>13867.49240005067</v>
+        <v>13867.48935991396</v>
       </c>
     </row>
     <row r="769">
@@ -13121,7 +13121,7 @@
         <v>12990.66691723031</v>
       </c>
       <c r="D769" s="3" t="n">
-        <v>13968.63492403738</v>
+        <v>13968.63797761062</v>
       </c>
     </row>
     <row r="770">
@@ -13153,7 +13153,7 @@
         <v>13028.54041623491</v>
       </c>
       <c r="D771" s="3" t="n">
-        <v>13968.82839160696</v>
+        <v>13968.82991574696</v>
       </c>
     </row>
     <row r="772">
@@ -13169,7 +13169,7 @@
         <v>13075.20634607111</v>
       </c>
       <c r="D772" s="3" t="n">
-        <v>13890.96830497787</v>
+        <v>13890.97134066986</v>
       </c>
     </row>
     <row r="773">
@@ -13185,7 +13185,7 @@
         <v>13034.62700743734</v>
       </c>
       <c r="D773" s="3" t="n">
-        <v>13955.83093624296</v>
+        <v>13955.83245508973</v>
       </c>
     </row>
     <row r="774">
@@ -13201,7 +13201,7 @@
         <v>13060.32732403709</v>
       </c>
       <c r="D774" s="3" t="n">
-        <v>13872.05494262548</v>
+        <v>13872.05646600194</v>
       </c>
     </row>
     <row r="775">
@@ -13217,7 +13217,7 @@
         <v>13109.69806152699</v>
       </c>
       <c r="D775" s="3" t="n">
-        <v>13969.09814191456</v>
+        <v>13969.09660852848</v>
       </c>
     </row>
     <row r="776">
@@ -13233,7 +13233,7 @@
         <v>13078.58812961983</v>
       </c>
       <c r="D776" s="3" t="n">
-        <v>13962.99720544431</v>
+        <v>13962.99874096797</v>
       </c>
     </row>
     <row r="777">
@@ -13249,7 +13249,7 @@
         <v>13159.74577491191</v>
       </c>
       <c r="D777" s="3" t="n">
-        <v>14106.38548593119</v>
+        <v>14106.38702325322</v>
       </c>
     </row>
     <row r="778">
@@ -13265,7 +13265,7 @@
         <v>13200.32408157023</v>
       </c>
       <c r="D778" s="3" t="n">
-        <v>14056.60522938117</v>
+        <v>14056.60677525355</v>
       </c>
     </row>
     <row r="779">
@@ -13281,7 +13281,7 @@
         <v>13193.56154644823</v>
       </c>
       <c r="D779" s="3" t="n">
-        <v>14187.98905634746</v>
+        <v>14187.99060205027</v>
       </c>
     </row>
     <row r="780">
@@ -13297,7 +13297,7 @@
         <v>13290.2741576939</v>
       </c>
       <c r="D780" s="3" t="n">
-        <v>14286.26329506956</v>
+        <v>14286.26484077237</v>
       </c>
     </row>
     <row r="781">
@@ -13313,7 +13313,7 @@
         <v>13319.35625784237</v>
       </c>
       <c r="D781" s="3" t="n">
-        <v>14303.52528841159</v>
+        <v>14303.52373812821</v>
       </c>
     </row>
     <row r="782">
@@ -13329,7 +13329,7 @@
         <v>13368.05105141271</v>
       </c>
       <c r="D782" s="3" t="n">
-        <v>14401.61762047437</v>
+        <v>14401.62072372185</v>
       </c>
     </row>
     <row r="783">
@@ -13361,7 +13361,7 @@
         <v>13443.12210550236</v>
       </c>
       <c r="D784" s="3" t="n">
-        <v>14439.19377368036</v>
+        <v>14439.19532881587</v>
       </c>
     </row>
     <row r="785">
@@ -13377,7 +13377,7 @@
         <v>13443.12210550236</v>
       </c>
       <c r="D785" s="3" t="n">
-        <v>14535.3349283654</v>
+        <v>14535.33336965028</v>
       </c>
     </row>
     <row r="786">
@@ -13393,7 +13393,7 @@
         <v>13558.09552233076</v>
       </c>
       <c r="D786" s="3" t="n">
-        <v>14565.53506552673</v>
+        <v>14565.53350370704</v>
       </c>
     </row>
     <row r="787">
@@ -13435,13 +13435,13 @@
         </is>
       </c>
       <c r="B789" s="3" t="n">
-        <v>14950.4</v>
+        <v>14950.39</v>
       </c>
       <c r="C789" s="3" t="n">
         <v>13507.37186502628</v>
       </c>
       <c r="D789" s="3" t="n">
-        <v>14650.02114189975</v>
+        <v>14650.01957363325</v>
       </c>
     </row>
     <row r="790">
@@ -13457,7 +13457,7 @@
         <v>13458.00112753638</v>
       </c>
       <c r="D790" s="3" t="n">
-        <v>14543.79532717013</v>
+        <v>14543.7937559177</v>
       </c>
     </row>
     <row r="791">
@@ -13473,7 +13473,7 @@
         <v>13443.79804942192</v>
       </c>
       <c r="D791" s="3" t="n">
-        <v>14597.91248241685</v>
+        <v>14597.91090872136</v>
       </c>
     </row>
     <row r="792">
@@ -13489,7 +13489,7 @@
         <v>13489.78803533856</v>
       </c>
       <c r="D792" s="3" t="n">
-        <v>14534.02938896634</v>
+        <v>14534.03095631675</v>
       </c>
     </row>
     <row r="793">
@@ -13505,7 +13505,7 @@
         <v>13480.3196605874</v>
       </c>
       <c r="D793" s="3" t="n">
-        <v>14616.20471819309</v>
+        <v>14616.20314683882</v>
       </c>
     </row>
     <row r="794">
@@ -13521,7 +13521,7 @@
         <v>13495.19765064597</v>
       </c>
       <c r="D794" s="3" t="n">
-        <v>14612.51709745534</v>
+        <v>14612.51866587463</v>
       </c>
     </row>
     <row r="795">
@@ -13537,7 +13537,7 @@
         <v>13430.27194720249</v>
       </c>
       <c r="D795" s="3" t="n">
-        <v>14563.10953421137</v>
+        <v>14563.10796635192</v>
       </c>
     </row>
     <row r="796">
@@ -13553,7 +13553,7 @@
         <v>13194.91446626281</v>
       </c>
       <c r="D796" s="3" t="n">
-        <v>14226.95304889631</v>
+        <v>14226.95148660153</v>
       </c>
     </row>
     <row r="797">
@@ -13569,7 +13569,7 @@
         <v>13297.71366871091</v>
       </c>
       <c r="D797" s="3" t="n">
-        <v>14251.62634345198</v>
+        <v>14251.62478502515</v>
       </c>
     </row>
     <row r="798">
@@ -13585,7 +13585,7 @@
         <v>13184.76911561665</v>
       </c>
       <c r="D798" s="3" t="n">
-        <v>14236.09687226064</v>
+        <v>14236.09999243916</v>
       </c>
     </row>
     <row r="799">
@@ -13595,13 +13595,13 @@
         </is>
       </c>
       <c r="B799" s="3" t="n">
-        <v>14730.05</v>
+        <v>14730.04</v>
       </c>
       <c r="C799" s="3" t="n">
         <v>13254.42952242343</v>
       </c>
       <c r="D799" s="3" t="n">
-        <v>14408.86731703933</v>
+        <v>14408.86419672502</v>
       </c>
     </row>
     <row r="800">
@@ -13633,7 +13633,7 @@
         <v>13749.4929130634</v>
       </c>
       <c r="D801" s="3" t="n">
-        <v>15076.80971648069</v>
+        <v>15076.81129713179</v>
       </c>
     </row>
     <row r="802">
@@ -13649,7 +13649,7 @@
         <v>13844.17666057492</v>
       </c>
       <c r="D802" s="3" t="n">
-        <v>15055.00677753586</v>
+        <v>15055.00834909367</v>
       </c>
     </row>
     <row r="803">
@@ -13665,7 +13665,7 @@
         <v>13999.05347211752</v>
       </c>
       <c r="D803" s="3" t="n">
-        <v>15182.25235565373</v>
+        <v>15182.24918899038</v>
       </c>
     </row>
     <row r="804">
@@ -13681,7 +13681,7 @@
         <v>13947.65283891802</v>
       </c>
       <c r="D804" s="3" t="n">
-        <v>15206.76948727691</v>
+        <v>15206.76789644657</v>
       </c>
     </row>
     <row r="805">
@@ -13697,7 +13697,7 @@
         <v>13997.70055230294</v>
       </c>
       <c r="D805" s="3" t="n">
-        <v>15282.46259441805</v>
+        <v>15282.46099644537</v>
       </c>
     </row>
     <row r="806">
@@ -13713,7 +13713,7 @@
         <v>13989.58509736637</v>
       </c>
       <c r="D806" s="3" t="n">
-        <v>15259.79910534825</v>
+        <v>15259.80071127758</v>
       </c>
     </row>
     <row r="807">
@@ -13761,7 +13761,7 @@
         <v>13834.70828582376</v>
       </c>
       <c r="D809" s="3" t="n">
-        <v>15137.25329174869</v>
+        <v>15137.25489301255</v>
       </c>
     </row>
     <row r="810">
@@ -13771,13 +13771,13 @@
         </is>
       </c>
       <c r="B810" s="3" t="n">
-        <v>15554.94</v>
+        <v>15554.93</v>
       </c>
       <c r="C810" s="3" t="n">
         <v>13845.5295803895</v>
       </c>
       <c r="D810" s="3" t="n">
-        <v>15124.25536162995</v>
+        <v>15124.25696097679</v>
       </c>
     </row>
     <row r="811">
@@ -13793,7 +13793,7 @@
         <v>14032.86924365384</v>
       </c>
       <c r="D811" s="3" t="n">
-        <v>15293.99964203434</v>
+        <v>15293.99803337357</v>
       </c>
     </row>
     <row r="812">
@@ -13825,7 +13825,7 @@
         <v>14160.0158428871</v>
       </c>
       <c r="D813" s="3" t="n">
-        <v>15490.84443674244</v>
+        <v>15490.84605558237</v>
       </c>
     </row>
     <row r="814">
@@ -13841,7 +13841,7 @@
         <v>14176.2477847357</v>
       </c>
       <c r="D814" s="3" t="n">
-        <v>15624.76539816466</v>
+        <v>15624.76702251835</v>
       </c>
     </row>
     <row r="815">
@@ -13889,7 +13889,7 @@
         <v>14179.62956828442</v>
       </c>
       <c r="D817" s="3" t="n">
-        <v>15498.04241908672</v>
+        <v>15498.04081298775</v>
       </c>
     </row>
     <row r="818">
@@ -13905,7 +13905,7 @@
         <v>14297.30779276653</v>
       </c>
       <c r="D818" s="3" t="n">
-        <v>15552.22763979649</v>
+        <v>15552.22603096605</v>
       </c>
     </row>
     <row r="819">
@@ -13921,7 +13921,7 @@
         <v>14287.83941801538</v>
       </c>
       <c r="D819" s="3" t="n">
-        <v>15624.41332421901</v>
+        <v>15624.4117086704</v>
       </c>
     </row>
     <row r="820">
@@ -13937,7 +13937,7 @@
         <v>14331.80054019787</v>
       </c>
       <c r="D820" s="3" t="n">
-        <v>15707.07095122926</v>
+        <v>15707.06933715654</v>
       </c>
     </row>
     <row r="821">
@@ -13953,7 +13953,7 @@
         <v>14319.62632581756</v>
       </c>
       <c r="D821" s="3" t="n">
-        <v>15676.27552255463</v>
+        <v>15676.27874968218</v>
       </c>
     </row>
     <row r="822">
@@ -13969,7 +13969,7 @@
         <v>14323.00810936628</v>
       </c>
       <c r="D822" s="3" t="n">
-        <v>15599.97838413585</v>
+        <v>15599.97678146382</v>
       </c>
     </row>
     <row r="823">
@@ -14033,7 +14033,7 @@
         <v>14357.49982482217</v>
       </c>
       <c r="D826" s="3" t="n">
-        <v>15626.9080397604</v>
+        <v>15626.90642507695</v>
       </c>
     </row>
     <row r="827">
@@ -14097,7 +14097,7 @@
         <v>14295.27892903239</v>
       </c>
       <c r="D830" s="3" t="n">
-        <v>15177.20862342331</v>
+        <v>15177.21023992211</v>
       </c>
     </row>
     <row r="831">
@@ -14113,7 +14113,7 @@
         <v>14070.06576676344</v>
       </c>
       <c r="D831" s="3" t="n">
-        <v>15384.80869893113</v>
+        <v>15384.81197715797</v>
       </c>
     </row>
     <row r="832">
@@ -14161,7 +14161,7 @@
         <v>14183.68729575271</v>
       </c>
       <c r="D834" s="3" t="n">
-        <v>15752.34541966763</v>
+        <v>15752.34705002707</v>
       </c>
     </row>
     <row r="835">
@@ -14177,7 +14177,7 @@
         <v>14183.68729575271</v>
       </c>
       <c r="D835" s="3" t="n">
-        <v>15757.26265953416</v>
+        <v>15757.26429040253</v>
       </c>
     </row>
     <row r="836">
@@ -14193,7 +14193,7 @@
         <v>14183.68729575271</v>
       </c>
       <c r="D836" s="3" t="n">
-        <v>15762.89947140838</v>
+        <v>15762.90273409481</v>
       </c>
     </row>
     <row r="837">
@@ -14209,7 +14209,7 @@
         <v>14133.63958236779</v>
       </c>
       <c r="D837" s="3" t="n">
-        <v>15561.61511226959</v>
+        <v>15561.61348462468</v>
       </c>
     </row>
     <row r="838">
@@ -14225,7 +14225,7 @@
         <v>14058.56852827814</v>
       </c>
       <c r="D838" s="3" t="n">
-        <v>15374.8890366878</v>
+        <v>15374.89066336566</v>
       </c>
     </row>
     <row r="839">
@@ -14241,7 +14241,7 @@
         <v>14089.00354824119</v>
       </c>
       <c r="D839" s="3" t="n">
-        <v>15353.14617696729</v>
+        <v>15353.14780727575</v>
       </c>
     </row>
     <row r="840">
@@ -14257,7 +14257,7 @@
         <v>14089.00354824119</v>
       </c>
       <c r="D840" s="3" t="n">
-        <v>15353.14617696729</v>
+        <v>15353.14780727575</v>
       </c>
     </row>
     <row r="841">
@@ -14289,7 +14289,7 @@
         <v>14214.79722765987</v>
       </c>
       <c r="D842" s="3" t="n">
-        <v>15715.24212886139</v>
+        <v>15715.24378107197</v>
       </c>
     </row>
     <row r="843">
@@ -14305,7 +14305,7 @@
         <v>14307.4531434127</v>
       </c>
       <c r="D843" s="3" t="n">
-        <v>15748.80529971365</v>
+        <v>15748.8069459694</v>
       </c>
     </row>
     <row r="844">
@@ -14321,7 +14321,7 @@
         <v>14209.38761235246</v>
       </c>
       <c r="D844" s="3" t="n">
-        <v>15449.3129195985</v>
+        <v>15449.31128618539</v>
       </c>
     </row>
     <row r="845">
@@ -14369,7 +14369,7 @@
         <v>14086.29770861203</v>
       </c>
       <c r="D847" s="3" t="n">
-        <v>15367.00974502878</v>
+        <v>15367.00480254639</v>
       </c>
     </row>
     <row r="848">
@@ -14385,7 +14385,7 @@
         <v>14063.30323164144</v>
       </c>
       <c r="D848" s="3" t="n">
-        <v>15470.71262534888</v>
+        <v>15470.71428139369</v>
       </c>
     </row>
     <row r="849">
@@ -14401,7 +14401,7 @@
         <v>14044.36648213914</v>
       </c>
       <c r="D849" s="3" t="n">
-        <v>15460.57673534455</v>
+        <v>15460.57838803019</v>
       </c>
     </row>
     <row r="850">
@@ -14449,7 +14449,7 @@
         <v>14434.59974264596</v>
       </c>
       <c r="D852" s="3" t="n">
-        <v>15812.74532392893</v>
+        <v>15812.74697072761</v>
       </c>
     </row>
     <row r="853">
@@ -14465,7 +14465,7 @@
         <v>14362.23452818547</v>
       </c>
       <c r="D853" s="3" t="n">
-        <v>15850.53796897985</v>
+        <v>15850.53961971439</v>
       </c>
     </row>
     <row r="854">
@@ -14497,7 +14497,7 @@
         <v>14498.85053414533</v>
       </c>
       <c r="D855" s="3" t="n">
-        <v>15886.83444674217</v>
+        <v>15886.83281639972</v>
       </c>
     </row>
     <row r="856">
@@ -14513,7 +14513,7 @@
         <v>14517.78728364764</v>
       </c>
       <c r="D856" s="3" t="n">
-        <v>15967.06326200706</v>
+        <v>15967.06489168786</v>
       </c>
     </row>
     <row r="857">
@@ -14529,7 +14529,7 @@
         <v>14454.21346804328</v>
       </c>
       <c r="D857" s="3" t="n">
-        <v>15911.50440623841</v>
+        <v>15911.50277747377</v>
       </c>
     </row>
     <row r="858">
@@ -14545,7 +14545,7 @@
         <v>14216.82712336947</v>
       </c>
       <c r="D858" s="3" t="n">
-        <v>15609.14564192084</v>
+        <v>15609.1440211807</v>
       </c>
     </row>
     <row r="859">
@@ -14561,7 +14561,7 @@
         <v>14403.4898107388</v>
       </c>
       <c r="D859" s="3" t="n">
-        <v>15777.20998276855</v>
+        <v>15777.21160700341</v>
       </c>
     </row>
     <row r="860">
@@ -14577,7 +14577,7 @@
         <v>14448.80282076041</v>
       </c>
       <c r="D860" s="3" t="n">
-        <v>15730.59608811111</v>
+        <v>15730.59934156873</v>
       </c>
     </row>
     <row r="861">
@@ -14593,7 +14593,7 @@
         <v>14483.97151211131</v>
       </c>
       <c r="D861" s="3" t="n">
-        <v>15820.79734190363</v>
+        <v>15820.79896922619</v>
       </c>
     </row>
     <row r="862">
@@ -14625,7 +14625,7 @@
         <v>14506.29004516234</v>
       </c>
       <c r="D863" s="3" t="n">
-        <v>15901.36910345939</v>
+        <v>15901.36744795764</v>
       </c>
     </row>
     <row r="864">
@@ -14641,7 +14641,7 @@
         <v>14500.87939787948</v>
       </c>
       <c r="D864" s="3" t="n">
-        <v>15884.6759719493</v>
+        <v>15884.67268646159</v>
       </c>
     </row>
     <row r="865">
@@ -14673,7 +14673,7 @@
         <v>14625.32118945903</v>
       </c>
       <c r="D866" s="3" t="n">
-        <v>15891.46088843351</v>
+        <v>15891.45925729373</v>
       </c>
     </row>
     <row r="867">
@@ -14705,7 +14705,7 @@
         <v>14678.07371049766</v>
       </c>
       <c r="D868" s="3" t="n">
-        <v>15990.11531831068</v>
+        <v>15990.11202780093</v>
       </c>
     </row>
     <row r="869">
@@ -14769,7 +14769,7 @@
         <v>14591.50541792271</v>
       </c>
       <c r="D872" s="3" t="n">
-        <v>15887.13667123399</v>
+        <v>15887.13829289014</v>
       </c>
     </row>
     <row r="873">
@@ -14785,7 +14785,7 @@
         <v>14663.87166435865</v>
       </c>
       <c r="D873" s="3" t="n">
-        <v>15845.41913687649</v>
+        <v>15845.42075427438</v>
       </c>
     </row>
     <row r="874">
@@ -14801,7 +14801,7 @@
         <v>14669.28127966607</v>
       </c>
       <c r="D874" s="3" t="n">
-        <v>15897.7711834599</v>
+        <v>15897.77280145155</v>
       </c>
     </row>
     <row r="875">
@@ -14849,7 +14849,7 @@
         <v>14584.74185082526</v>
       </c>
       <c r="D877" s="3" t="n">
-        <v>15574.92324118106</v>
+        <v>15574.92485683147</v>
       </c>
     </row>
     <row r="878">
@@ -14865,7 +14865,7 @@
         <v>14423.10250416067</v>
       </c>
       <c r="D878" s="3" t="n">
-        <v>15542.14567168258</v>
+        <v>15542.14891092326</v>
       </c>
     </row>
     <row r="879">
@@ -14881,7 +14881,7 @@
         <v>14202.62404525501</v>
       </c>
       <c r="D879" s="3" t="n">
-        <v>15484.77670809852</v>
+        <v>15484.77832980568</v>
       </c>
     </row>
     <row r="880">
@@ -14897,7 +14897,7 @@
         <v>14389.96370851936</v>
       </c>
       <c r="D880" s="3" t="n">
-        <v>15400.21563605362</v>
+        <v>15400.21241197983</v>
       </c>
     </row>
     <row r="881">
@@ -14913,7 +14913,7 @@
         <v>14415.66299314366</v>
       </c>
       <c r="D881" s="3" t="n">
-        <v>15205.4329903398</v>
+        <v>15205.43137287408</v>
       </c>
     </row>
     <row r="882">
@@ -14929,7 +14929,7 @@
         <v>14262.81607731065</v>
       </c>
       <c r="D882" s="3" t="n">
-        <v>15581.85770903042</v>
+        <v>15581.86097310834</v>
       </c>
     </row>
     <row r="883">
@@ -14945,7 +14945,7 @@
         <v>14304.07135986398</v>
       </c>
       <c r="D883" s="3" t="n">
-        <v>15281.33241488437</v>
+        <v>15281.33404398816</v>
       </c>
     </row>
     <row r="884">
@@ -14961,7 +14961,7 @@
         <v>13825.23991107261</v>
       </c>
       <c r="D884" s="3" t="n">
-        <v>14997.92013694002</v>
+        <v>14997.92337302525</v>
       </c>
     </row>
     <row r="885">
@@ -14993,7 +14993,7 @@
         <v>13667.6582918763</v>
       </c>
       <c r="D886" s="3" t="n">
-        <v>14462.56277289765</v>
+        <v>14462.56120130583</v>
       </c>
     </row>
     <row r="887">
@@ -15041,7 +15041,7 @@
         <v>13038.00879098607</v>
       </c>
       <c r="D889" s="3" t="n">
-        <v>13980.97758855907</v>
+        <v>13980.97915370396</v>
       </c>
     </row>
     <row r="890">
@@ -15057,7 +15057,7 @@
         <v>13173.94782105092</v>
       </c>
       <c r="D890" s="3" t="n">
-        <v>13958.88293992657</v>
+        <v>13958.88449434953</v>
       </c>
     </row>
     <row r="891">
@@ -15073,7 +15073,7 @@
         <v>13083.32180100768</v>
       </c>
       <c r="D891" s="3" t="n">
-        <v>13808.12763850878</v>
+        <v>13808.13075532831</v>
       </c>
     </row>
     <row r="892">
@@ -15089,7 +15089,7 @@
         <v>13230.75910153328</v>
       </c>
       <c r="D892" s="3" t="n">
-        <v>14133.08489164865</v>
+        <v>14133.08332884485</v>
       </c>
     </row>
     <row r="893">
@@ -15121,7 +15121,7 @@
         <v>13237.52163665527</v>
       </c>
       <c r="D894" s="3" t="n">
-        <v>14006.16301120276</v>
+        <v>14006.16145749239</v>
       </c>
     </row>
     <row r="895">
@@ -15153,7 +15153,7 @@
         <v>13416.06886908803</v>
       </c>
       <c r="D896" s="3" t="n">
-        <v>14127.1586885704</v>
+        <v>14127.16179806094</v>
       </c>
     </row>
     <row r="897">
@@ -15169,7 +15169,7 @@
         <v>13388.34072072959</v>
       </c>
       <c r="D897" s="3" t="n">
-        <v>14203.67945564894</v>
+        <v>14203.68101830002</v>
       </c>
     </row>
     <row r="898">
@@ -15233,7 +15233,7 @@
         <v>13518.86910351158</v>
       </c>
       <c r="D901" s="3" t="n">
-        <v>14434.17319495029</v>
+        <v>14434.17161562232</v>
       </c>
     </row>
     <row r="902">
@@ -15249,7 +15249,7 @@
         <v>13232.11098937241</v>
       </c>
       <c r="D902" s="3" t="n">
-        <v>14066.31107882371</v>
+        <v>14066.30950811407</v>
       </c>
     </row>
     <row r="903">
@@ -15265,7 +15265,7 @@
         <v>13137.42724186089</v>
       </c>
       <c r="D903" s="3" t="n">
-        <v>14130.75577981994</v>
+        <v>14130.75734720435</v>
       </c>
     </row>
     <row r="904">
@@ -15281,7 +15281,7 @@
         <v>13307.18204346206</v>
       </c>
       <c r="D904" s="3" t="n">
-        <v>14177.26306946959</v>
+        <v>14177.2646375835</v>
       </c>
     </row>
     <row r="905">
@@ -15297,7 +15297,7 @@
         <v>13298.39064460592</v>
       </c>
       <c r="D905" s="3" t="n">
-        <v>14297.23749463829</v>
+        <v>14297.23435176006</v>
       </c>
     </row>
     <row r="906">
@@ -15313,7 +15313,7 @@
         <v>12649.80336223793</v>
       </c>
       <c r="D906" s="3" t="n">
-        <v>13452.21948003909</v>
+        <v>13452.22103524242</v>
       </c>
     </row>
     <row r="907">
@@ -15329,7 +15329,7 @@
         <v>12053.96963288402</v>
       </c>
       <c r="D907" s="3" t="n">
-        <v>12509.8161095975</v>
+        <v>12509.81534150484</v>
       </c>
     </row>
     <row r="908">
@@ -15345,7 +15345,7 @@
         <v>11700.25695156723</v>
       </c>
       <c r="D908" s="3" t="n">
-        <v>12554.83317785286</v>
+        <v>12554.83395008502</v>
       </c>
     </row>
     <row r="909">
@@ -15409,7 +15409,7 @@
         <v>11876.77532026584</v>
       </c>
       <c r="D912" s="3" t="n">
-        <v>12967.98743116694</v>
+        <v>12967.98893813813</v>
       </c>
     </row>
     <row r="913">
@@ -15425,7 +15425,7 @@
         <v>12219.66670701691</v>
       </c>
       <c r="D913" s="3" t="n">
-        <v>12995.32769312684</v>
+        <v>12995.32918876516</v>
       </c>
     </row>
     <row r="914">
@@ -15505,7 +15505,7 @@
         <v>12074.93524612047</v>
       </c>
       <c r="D918" s="3" t="n">
-        <v>12328.61532420411</v>
+        <v>12328.61457990521</v>
       </c>
     </row>
     <row r="919">
@@ -15521,7 +15521,7 @@
         <v>11974.84085132608</v>
       </c>
       <c r="D919" s="3" t="n">
-        <v>12521.93844271107</v>
+        <v>12521.9369691105</v>
       </c>
     </row>
     <row r="920">
@@ -15537,7 +15537,7 @@
         <v>12343.4325546769</v>
       </c>
       <c r="D920" s="3" t="n">
-        <v>12896.91924376619</v>
+        <v>12896.91774919657</v>
       </c>
     </row>
     <row r="921">
@@ -15553,7 +15553,7 @@
         <v>12432.706686881</v>
       </c>
       <c r="D921" s="3" t="n">
-        <v>13196.18673079778</v>
+        <v>13196.18822852293</v>
       </c>
     </row>
     <row r="922">
@@ -15569,7 +15569,7 @@
         <v>12499.66228603408</v>
       </c>
       <c r="D922" s="3" t="n">
-        <v>13239.44133348553</v>
+        <v>13239.43984163042</v>
       </c>
     </row>
     <row r="923">
@@ -15585,7 +15585,7 @@
         <v>12519.27497945595</v>
       </c>
       <c r="D923" s="3" t="n">
-        <v>13278.07363131412</v>
+        <v>13278.07512695244</v>
       </c>
     </row>
     <row r="924">
@@ -15601,7 +15601,7 @@
         <v>12578.114091697</v>
       </c>
       <c r="D924" s="3" t="n">
-        <v>13284.42320456897</v>
+        <v>13284.42171758285</v>
       </c>
     </row>
     <row r="925">
@@ -15617,7 +15617,7 @@
         <v>12624.10407761364</v>
       </c>
       <c r="D925" s="3" t="n">
-        <v>13312.89091384938</v>
+        <v>13312.89240343111</v>
       </c>
     </row>
     <row r="926">
@@ -15633,7 +15633,7 @@
         <v>12624.10407761364</v>
       </c>
       <c r="D926" s="3" t="n">
-        <v>13483.43470430148</v>
+        <v>13483.43620234904</v>
       </c>
     </row>
     <row r="927">
@@ -15665,7 +15665,7 @@
         <v>12952.11644233068</v>
       </c>
       <c r="D928" s="3" t="n">
-        <v>13607.12350008356</v>
+        <v>13607.1249983516</v>
       </c>
     </row>
     <row r="929">
@@ -15681,7 +15681,7 @@
         <v>12889.21960262134</v>
       </c>
       <c r="D929" s="3" t="n">
-        <v>13505.15546495025</v>
+        <v>13505.15396537596</v>
       </c>
     </row>
     <row r="930">
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="B930" s="3" t="n">
-        <v>14472.37</v>
+        <v>14472.36</v>
       </c>
       <c r="C930" s="3" t="n">
         <v>12822.26400346826</v>
       </c>
       <c r="D930" s="3" t="n">
-        <v>13526.81616861129</v>
+        <v>13526.81467292204</v>
       </c>
     </row>
     <row r="931">
@@ -15713,7 +15713,7 @@
         <v>13033.27511959821</v>
       </c>
       <c r="D931" s="3" t="n">
-        <v>13665.09834498712</v>
+        <v>13665.10134603586</v>
       </c>
     </row>
     <row r="932">
@@ -15729,7 +15729,7 @@
         <v>13023.80674484706</v>
       </c>
       <c r="D932" s="3" t="n">
-        <v>13747.36716813599</v>
+        <v>13747.36867961983</v>
       </c>
     </row>
     <row r="933">
@@ -15761,7 +15761,7 @@
         <v>13541.1876365626</v>
       </c>
       <c r="D934" s="3" t="n">
-        <v>14461.22165670706</v>
+        <v>14461.22012769808</v>
       </c>
     </row>
     <row r="935">
@@ -15777,7 +15777,7 @@
         <v>13503.31413755799</v>
       </c>
       <c r="D935" s="3" t="n">
-        <v>14363.2247527646</v>
+        <v>14363.22626947388</v>
       </c>
     </row>
     <row r="936">
@@ -15793,7 +15793,7 @@
         <v>13555.38968270161</v>
       </c>
       <c r="D936" s="3" t="n">
-        <v>14438.05942865124</v>
+        <v>14438.0609458524</v>
       </c>
     </row>
     <row r="937">
@@ -15809,7 +15809,7 @@
         <v>13654.13218965686</v>
       </c>
       <c r="D937" s="3" t="n">
-        <v>14515.53800319208</v>
+        <v>14515.53951893423</v>
       </c>
     </row>
     <row r="938">
@@ -15857,7 +15857,7 @@
         <v>13503.99008147756</v>
       </c>
       <c r="D940" s="3" t="n">
-        <v>14118.35470193542</v>
+        <v>14118.35620488591</v>
       </c>
     </row>
     <row r="941">
@@ -15873,7 +15873,7 @@
         <v>13395.7802317466</v>
       </c>
       <c r="D941" s="3" t="n">
-        <v>14070.03842432718</v>
+        <v>14070.0414187596</v>
       </c>
     </row>
     <row r="942">
@@ -15889,7 +15889,7 @@
         <v>13255.10649831845</v>
       </c>
       <c r="D942" s="3" t="n">
-        <v>14035.12019522652</v>
+        <v>14035.12169899122</v>
       </c>
     </row>
     <row r="943">
@@ -15905,7 +15905,7 @@
         <v>13376.16650634928</v>
       </c>
       <c r="D943" s="3" t="n">
-        <v>13922.85636967624</v>
+        <v>13922.85786141266</v>
       </c>
     </row>
     <row r="944">
@@ -15915,7 +15915,7 @@
         </is>
       </c>
       <c r="B944" s="3" t="n">
-        <v>15105.91</v>
+        <v>15105.9</v>
       </c>
       <c r="C944" s="3" t="n">
         <v>13476.26090114367</v>
@@ -15937,7 +15937,7 @@
         <v>13493.84576280684</v>
       </c>
       <c r="D945" s="3" t="n">
-        <v>14174.60970896426</v>
+        <v>14174.6082125286</v>
       </c>
     </row>
     <row r="946">
@@ -15969,7 +15969,7 @@
         <v>13428.24308346834</v>
       </c>
       <c r="D947" s="3" t="n">
-        <v>14163.07580925661</v>
+        <v>14163.07730026348</v>
       </c>
     </row>
     <row r="948">
@@ -15985,7 +15985,7 @@
         <v>13363.99332394442</v>
       </c>
       <c r="D948" s="3" t="n">
-        <v>14274.29636358823</v>
+        <v>14274.29785788636</v>
       </c>
     </row>
     <row r="949">
@@ -16033,7 +16033,7 @@
         <v>13545.92130795045</v>
       </c>
       <c r="D951" s="3" t="n">
-        <v>14196.54132669947</v>
+        <v>14196.54281200608</v>
       </c>
     </row>
     <row r="952">
@@ -16081,7 +16081,7 @@
         <v>13595.96902133537</v>
       </c>
       <c r="D954" s="3" t="n">
-        <v>14429.05726682762</v>
+        <v>14429.06023588002</v>
       </c>
     </row>
     <row r="955">
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="B958" s="3" t="n">
-        <v>15060.97</v>
+        <v>15060.96</v>
       </c>
       <c r="C958" s="3" t="n">
         <v>13472.20317367538</v>
@@ -16209,7 +16209,7 @@
         <v>13367.37407551769</v>
       </c>
       <c r="D962" s="3" t="n">
-        <v>14155.59560125401</v>
+        <v>14155.59412765345</v>
       </c>
     </row>
     <row r="963">
@@ -16225,7 +16225,7 @@
         <v>13341.67479089339</v>
       </c>
       <c r="D963" s="3" t="n">
-        <v>14310.22539273472</v>
+        <v>14310.22686786209</v>
       </c>
     </row>
     <row r="964">
@@ -16241,7 +16241,7 @@
         <v>13466.11658247295</v>
       </c>
       <c r="D964" s="3" t="n">
-        <v>14345.84689986316</v>
+        <v>14345.84836250408</v>
       </c>
     </row>
     <row r="965">
@@ -16257,7 +16257,7 @@
         <v>13452.59048025351</v>
       </c>
       <c r="D965" s="3" t="n">
-        <v>14337.57048275355</v>
+        <v>14337.56902177511</v>
       </c>
     </row>
     <row r="966">
@@ -16273,7 +16273,7 @@
         <v>13462.05885500466</v>
       </c>
       <c r="D966" s="3" t="n">
-        <v>14361.31543495969</v>
+        <v>14361.31688699744</v>
       </c>
     </row>
     <row r="967">
@@ -16289,7 +16289,7 @@
         <v>13575.67935201849</v>
       </c>
       <c r="D967" s="3" t="n">
-        <v>14422.21211813982</v>
+        <v>14422.21356912572</v>
       </c>
     </row>
     <row r="968">
@@ -16305,7 +16305,7 @@
         <v>13545.92130795045</v>
       </c>
       <c r="D968" s="3" t="n">
-        <v>14447.62615856048</v>
+        <v>14447.62471193461</v>
       </c>
     </row>
     <row r="969">
@@ -16337,7 +16337,7 @@
         <v>13553.36081896746</v>
       </c>
       <c r="D970" s="3" t="n">
-        <v>14412.46152711559</v>
+        <v>14412.46009005818</v>
       </c>
     </row>
     <row r="971">
@@ -16401,7 +16401,7 @@
         <v>13639.92911154241</v>
       </c>
       <c r="D974" s="3" t="n">
-        <v>14494.62136674156</v>
+        <v>14494.62281224764</v>
       </c>
     </row>
     <row r="975">
@@ -16433,7 +16433,7 @@
         <v>13788.04235598757</v>
       </c>
       <c r="D976" s="3" t="n">
-        <v>14629.35832294489</v>
+        <v>14629.35976911256</v>
       </c>
     </row>
     <row r="977">
@@ -16465,7 +16465,7 @@
         <v>13722.43967664907</v>
       </c>
       <c r="D978" s="3" t="n">
-        <v>14667.09143509692</v>
+        <v>14667.08998285558</v>
       </c>
     </row>
     <row r="979">
@@ -16481,7 +16481,7 @@
         <v>13802.24543410202</v>
       </c>
       <c r="D979" s="3" t="n">
-        <v>14624.20231702154</v>
+        <v>14624.20377123072</v>
       </c>
     </row>
     <row r="980">
@@ -16529,7 +16529,7 @@
         <v>13821.85812752389</v>
       </c>
       <c r="D982" s="3" t="n">
-        <v>14816.61410490529</v>
+        <v>14816.61702604769</v>
       </c>
     </row>
     <row r="983">
@@ -16561,7 +16561,7 @@
         <v>13746.78707343424</v>
       </c>
       <c r="D984" s="3" t="n">
-        <v>14746.46746902603</v>
+        <v>14746.46891972351</v>
       </c>
     </row>
     <row r="985">
@@ -16577,7 +16577,7 @@
         <v>13862.43746615765</v>
       </c>
       <c r="D985" s="3" t="n">
-        <v>14815.40069788556</v>
+        <v>14815.3978075181</v>
       </c>
     </row>
     <row r="986">
@@ -16593,7 +16593,7 @@
         <v>13893.54739806482</v>
       </c>
       <c r="D986" s="3" t="n">
-        <v>14776.11324250804</v>
+        <v>14776.11468338254</v>
       </c>
     </row>
     <row r="987">
@@ -16609,7 +16609,7 @@
         <v>13922.62949821329</v>
       </c>
       <c r="D987" s="3" t="n">
-        <v>14861.42065831576</v>
+        <v>14861.41777212189</v>
       </c>
     </row>
     <row r="988">
@@ -16625,7 +16625,7 @@
         <v>14040.98469859042</v>
       </c>
       <c r="D988" s="3" t="n">
-        <v>14856.81509853706</v>
+        <v>14856.81365552484</v>
       </c>
     </row>
     <row r="989">
@@ -16683,13 +16683,13 @@
         </is>
       </c>
       <c r="B992" s="3" t="n">
-        <v>15466.46</v>
+        <v>15466.45</v>
       </c>
       <c r="C992" s="3" t="n">
         <v>13773.84030984857</v>
       </c>
       <c r="D992" s="3" t="n">
-        <v>14924.63223001151</v>
+        <v>14924.63074492545</v>
       </c>
     </row>
     <row r="993">
@@ -16705,7 +16705,7 @@
         <v>13938.18446416687</v>
       </c>
       <c r="D993" s="3" t="n">
-        <v>14938.41132906237</v>
+        <v>14938.40986486064</v>
       </c>
     </row>
     <row r="994">
@@ -16753,7 +16753,7 @@
         <v>13965.2377005812</v>
       </c>
       <c r="D996" s="3" t="n">
-        <v>14865.83961020247</v>
+        <v>14865.84106480196</v>
       </c>
     </row>
     <row r="997">
@@ -16801,7 +16801,7 @@
         <v>14092.38429981446</v>
       </c>
       <c r="D999" s="3" t="n">
-        <v>15169.47333088871</v>
+        <v>15169.47187069066</v>
       </c>
     </row>
     <row r="1000">
@@ -16833,7 +16833,7 @@
         <v>14183.68729575271</v>
       </c>
       <c r="D1001" s="3" t="n">
-        <v>15100.07245930949</v>
+        <v>15100.07101088533</v>
       </c>
     </row>
     <row r="1002">
@@ -16849,7 +16849,7 @@
         <v>14145.13682085309</v>
       </c>
       <c r="D1002" s="3" t="n">
-        <v>15144.29808628155</v>
+        <v>15144.29663020615</v>
       </c>
     </row>
     <row r="1003">
@@ -16865,7 +16865,7 @@
         <v>14168.80827371869</v>
       </c>
       <c r="D1003" s="3" t="n">
-        <v>15069.55202373952</v>
+        <v>15069.55492214833</v>
       </c>
     </row>
     <row r="1004">
@@ -16881,7 +16881,7 @@
         <v>14166.77940998455</v>
       </c>
       <c r="D1004" s="3" t="n">
-        <v>15036.92885135556</v>
+        <v>15036.93030531039</v>
       </c>
     </row>
     <row r="1005">
@@ -16897,7 +16897,7 @@
         <v>14087.65062842661</v>
       </c>
       <c r="D1005" s="3" t="n">
-        <v>15030.22209290196</v>
+        <v>15030.22355008018</v>
       </c>
     </row>
     <row r="1006">
@@ -16929,7 +16929,7 @@
         <v>14216.82712336947</v>
       </c>
       <c r="D1007" s="3" t="n">
-        <v>15238.38927307026</v>
+        <v>15238.39073394687</v>
       </c>
     </row>
     <row r="1008">
@@ -16961,7 +16961,7 @@
         <v>14174.21892100156</v>
       </c>
       <c r="D1009" s="3" t="n">
-        <v>15227.77173803703</v>
+        <v>15227.77027783898</v>
       </c>
     </row>
     <row r="1010">
@@ -16977,7 +16977,7 @@
         <v>14287.16347409582</v>
       </c>
       <c r="D1010" s="3" t="n">
-        <v>15234.98233083666</v>
+        <v>15234.98378840499</v>
       </c>
     </row>
     <row r="1011">
@@ -16993,7 +16993,7 @@
         <v>14246.58413546205</v>
       </c>
       <c r="D1011" s="3" t="n">
-        <v>15277.7244327101</v>
+        <v>15277.72297621059</v>
       </c>
     </row>
     <row r="1012">
@@ -17057,7 +17057,7 @@
         <v>14118.08461641421</v>
       </c>
       <c r="D1015" s="3" t="n">
-        <v>15171.3034301172</v>
+        <v>15171.30488810962</v>
       </c>
     </row>
     <row r="1016">
@@ -17073,7 +17073,7 @@
         <v>14239.14462444504</v>
       </c>
       <c r="D1016" s="3" t="n">
-        <v>15266.05640247732</v>
+        <v>15266.05785741603</v>
       </c>
     </row>
     <row r="1017">
@@ -17089,7 +17089,7 @@
         <v>14138.37428573109</v>
       </c>
       <c r="D1017" s="3" t="n">
-        <v>15226.45776670064</v>
+        <v>15226.4592220805</v>
       </c>
     </row>
     <row r="1018">
@@ -17105,7 +17105,7 @@
         <v>14229.67624969389</v>
       </c>
       <c r="D1018" s="3" t="n">
-        <v>15190.55614313121</v>
+        <v>15190.55759152132</v>
       </c>
     </row>
     <row r="1019">
@@ -17121,7 +17121,7 @@
         <v>14228.32436185476</v>
       </c>
       <c r="D1019" s="3" t="n">
-        <v>15153.26883954462</v>
+        <v>15153.27028104698</v>
       </c>
     </row>
     <row r="1020">
@@ -17137,7 +17137,7 @@
         <v>14307.4531434127</v>
       </c>
       <c r="D1020" s="3" t="n">
-        <v>15283.28200478448</v>
+        <v>15283.28490414369</v>
       </c>
     </row>
     <row r="1021">
@@ -17153,7 +17153,7 @@
         <v>14398.07916345593</v>
       </c>
       <c r="D1021" s="3" t="n">
-        <v>15409.38877548085</v>
+        <v>15409.38732588616</v>
       </c>
     </row>
     <row r="1022">
@@ -17169,7 +17169,7 @@
         <v>14404.16575465836</v>
       </c>
       <c r="D1022" s="3" t="n">
-        <v>15363.12685733597</v>
+        <v>15363.12974878924</v>
       </c>
     </row>
     <row r="1023">
@@ -17185,7 +17185,7 @@
         <v>14423.77948005568</v>
       </c>
       <c r="D1023" s="3" t="n">
-        <v>15455.79336247938</v>
+        <v>15455.79480922393</v>
       </c>
     </row>
     <row r="1024">
@@ -17217,7 +17217,7 @@
         <v>14291.2212015641</v>
       </c>
       <c r="D1025" s="3" t="n">
-        <v>15227.15977638812</v>
+        <v>15227.16120547195</v>
       </c>
     </row>
     <row r="1026">
@@ -17233,7 +17233,7 @@
         <v>14447.44990094584</v>
       </c>
       <c r="D1026" s="3" t="n">
-        <v>15356.60740252562</v>
+        <v>15356.60596799593</v>
       </c>
     </row>
     <row r="1027">
@@ -17265,7 +17265,7 @@
         <v>14496.82167041119</v>
       </c>
       <c r="D1028" s="3" t="n">
-        <v>15623.77287248523</v>
+        <v>15623.77431794051</v>
       </c>
     </row>
     <row r="1029">
@@ -17281,7 +17281,7 @@
         <v>14506.29004516234</v>
       </c>
       <c r="D1029" s="3" t="n">
-        <v>15454.28411227015</v>
+        <v>15454.27979946914</v>
       </c>
     </row>
     <row r="1030">
@@ -17297,7 +17297,7 @@
         <v>14488.0292395796</v>
       </c>
       <c r="D1030" s="3" t="n">
-        <v>15387.66113931468</v>
+        <v>15387.65970334303</v>
       </c>
     </row>
     <row r="1031">
@@ -17345,7 +17345,7 @@
         <v>14523.1979309305</v>
       </c>
       <c r="D1033" s="3" t="n">
-        <v>15587.87819218238</v>
+        <v>15587.87674318145</v>
       </c>
     </row>
     <row r="1034">
@@ -17361,7 +17361,7 @@
         <v>14502.90826161362</v>
       </c>
       <c r="D1034" s="3" t="n">
-        <v>15615.63545699141</v>
+        <v>15615.63401085754</v>
       </c>
     </row>
     <row r="1035">
@@ -17377,7 +17377,7 @@
         <v>14611.11811134458</v>
       </c>
       <c r="D1035" s="3" t="n">
-        <v>15662.96486274447</v>
+        <v>15662.96341715353</v>
       </c>
     </row>
     <row r="1036">
@@ -17393,7 +17393,7 @@
         <v>14662.51874454408</v>
       </c>
       <c r="D1036" s="3" t="n">
-        <v>15683.39718797755</v>
+        <v>15683.39574216602</v>
       </c>
     </row>
     <row r="1037">
@@ -17409,7 +17409,7 @@
         <v>14725.41558425342</v>
       </c>
       <c r="D1037" s="3" t="n">
-        <v>15695.12481431413</v>
+        <v>15695.12626122828</v>
       </c>
     </row>
     <row r="1038">
@@ -17419,7 +17419,7 @@
         </is>
       </c>
       <c r="B1038" s="3" t="n">
-        <v>17037.9</v>
+        <v>17037.89</v>
       </c>
       <c r="C1038" s="3" t="n">
         <v>14776.1392415579</v>
@@ -17537,7 +17537,7 @@
         <v>14734.20801508501</v>
       </c>
       <c r="D1045" s="3" t="n">
-        <v>15765.54612485996</v>
+        <v>15765.54758709377</v>
       </c>
     </row>
     <row r="1046">
@@ -17585,7 +17585,7 @@
         <v>14811.98387682836</v>
       </c>
       <c r="D1048" s="3" t="n">
-        <v>15835.52056524666</v>
+        <v>15835.51910993467</v>
       </c>
     </row>
     <row r="1049">
@@ -17617,7 +17617,7 @@
         <v>14787.63648004319</v>
       </c>
       <c r="D1050" s="3" t="n">
-        <v>15830.45414811393</v>
+        <v>15830.45268564255</v>
       </c>
     </row>
     <row r="1051">
@@ -17697,7 +17697,7 @@
         <v>15115.64987673569</v>
       </c>
       <c r="D1055" s="3" t="n">
-        <v>16214.5046870228</v>
+        <v>16214.5061422839</v>
       </c>
     </row>
     <row r="1056">
@@ -17745,7 +17745,7 @@
         <v>15142.70208117457</v>
       </c>
       <c r="D1058" s="3" t="n">
-        <v>16300.49417384772</v>
+        <v>16300.49564549718</v>
       </c>
     </row>
     <row r="1059">
@@ -17777,7 +17777,7 @@
         <v>15114.29695692111</v>
       </c>
       <c r="D1060" s="3" t="n">
-        <v>16222.90605152933</v>
+        <v>16222.90752862472</v>
       </c>
     </row>
     <row r="1061">
@@ -17841,7 +17841,7 @@
         <v>15060.19151606791</v>
       </c>
       <c r="D1064" s="3" t="n">
-        <v>16251.25319564371</v>
+        <v>16251.25025977553</v>
       </c>
     </row>
     <row r="1065">
@@ -17857,7 +17857,7 @@
         <v>15144.05500098915</v>
       </c>
       <c r="D1065" s="3" t="n">
-        <v>16217.82443353963</v>
+        <v>16217.82296943972</v>
       </c>
     </row>
     <row r="1066">
@@ -17889,7 +17889,7 @@
         <v>14905.99168042032</v>
       </c>
       <c r="D1067" s="3" t="n">
-        <v>15885.11885020578</v>
+        <v>15885.11739170428</v>
       </c>
     </row>
     <row r="1068">
@@ -17905,7 +17905,7 @@
         <v>14845.12370444512</v>
       </c>
       <c r="D1068" s="3" t="n">
-        <v>15759.64247692025</v>
+        <v>15759.64393750854</v>
       </c>
     </row>
     <row r="1069">
@@ -17921,7 +17921,7 @@
         <v>14646.96377859049</v>
       </c>
       <c r="D1069" s="3" t="n">
-        <v>15660.70058812304</v>
+        <v>15660.69912441314</v>
       </c>
     </row>
     <row r="1070">
@@ -17937,7 +17937,7 @@
         <v>14686.86614132924</v>
       </c>
       <c r="D1070" s="3" t="n">
-        <v>15733.9536161706</v>
+        <v>15733.95508106804</v>
       </c>
     </row>
     <row r="1071">
@@ -17969,7 +17969,7 @@
         <v>14622.61638180532</v>
       </c>
       <c r="D1072" s="3" t="n">
-        <v>15711.72191599804</v>
+        <v>15711.7233868163</v>
       </c>
     </row>
     <row r="1073">
@@ -18001,7 +18001,7 @@
         <v>14855.26802311584</v>
       </c>
       <c r="D1074" s="3" t="n">
-        <v>16113.1692328204</v>
+        <v>16113.16776015291</v>
       </c>
     </row>
     <row r="1075">
@@ -18017,7 +18017,7 @@
         <v>15023.67093687788</v>
       </c>
       <c r="D1075" s="3" t="n">
-        <v>16161.60552269625</v>
+        <v>16161.60405572905</v>
       </c>
     </row>
     <row r="1076">
@@ -18033,7 +18033,7 @@
         <v>15013.52661820716</v>
       </c>
       <c r="D1076" s="3" t="n">
-        <v>16109.64470671419</v>
+        <v>16109.6432444634</v>
       </c>
     </row>
     <row r="1077">
@@ -18049,7 +18049,7 @@
         <v>15068.30800297993</v>
       </c>
       <c r="D1077" s="3" t="n">
-        <v>16200.77150920761</v>
+        <v>16200.77297174677</v>
       </c>
     </row>
     <row r="1078">
@@ -18091,7 +18091,7 @@
         </is>
       </c>
       <c r="B1080" s="3" t="n">
-        <v>17023.24</v>
+        <v>17023.23</v>
       </c>
       <c r="C1080" s="3" t="n">
         <v>15018.93726549003</v>
@@ -18113,7 +18113,7 @@
         <v>15052.07606113134</v>
       </c>
       <c r="D1081" s="3" t="n">
-        <v>16131.31872346433</v>
+        <v>16131.32017760576</v>
       </c>
     </row>
     <row r="1082">
@@ -18129,7 +18129,7 @@
         <v>15108.21036571868</v>
       </c>
       <c r="D1082" s="3" t="n">
-        <v>16195.33449116119</v>
+        <v>16195.33303401699</v>
       </c>
     </row>
     <row r="1083">
@@ -18145,7 +18145,7 @@
         <v>15083.86296893351</v>
       </c>
       <c r="D1083" s="3" t="n">
-        <v>16150.25077746963</v>
+        <v>16150.25223493616</v>
       </c>
     </row>
     <row r="1084">
@@ -18177,7 +18177,7 @@
         <v>15066.27913924579</v>
       </c>
       <c r="D1085" s="3" t="n">
-        <v>16259.97063642318</v>
+        <v>16259.9691774637</v>
       </c>
     </row>
     <row r="1086">
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="B1086" s="3" t="n">
-        <v>17049.08</v>
+        <v>17049.07</v>
       </c>
       <c r="C1086" s="3" t="n">
         <v>15010.82077857801</v>
@@ -18257,7 +18257,7 @@
         <v>14782.22686473578</v>
       </c>
       <c r="D1090" s="3" t="n">
-        <v>15713.80958438571</v>
+        <v>15713.81102829716</v>
       </c>
     </row>
     <row r="1091">
@@ -18273,7 +18273,7 @@
         <v>14936.42670038337</v>
       </c>
       <c r="D1091" s="3" t="n">
-        <v>15842.14312987712</v>
+        <v>15842.14168508352</v>
       </c>
     </row>
     <row r="1092">
@@ -18305,7 +18305,7 @@
         <v>15036.52109517775</v>
       </c>
       <c r="D1093" s="3" t="n">
-        <v>16132.34661015854</v>
+        <v>16132.34516114064</v>
       </c>
     </row>
     <row r="1094">
@@ -18321,7 +18321,7 @@
         <v>15068.30800297993</v>
       </c>
       <c r="D1094" s="3" t="n">
-        <v>16126.38639624366</v>
+        <v>16126.38783813626</v>
       </c>
     </row>
     <row r="1095">
@@ -18401,7 +18401,7 @@
         <v>15122.41344383314</v>
       </c>
       <c r="D1099" s="3" t="n">
-        <v>16094.64346151002</v>
+        <v>16094.64202046584</v>
       </c>
     </row>
     <row r="1100">
@@ -18465,7 +18465,7 @@
         <v>15249.5600430664</v>
       </c>
       <c r="D1103" s="3" t="n">
-        <v>16205.16494809827</v>
+        <v>16205.16639754031</v>
       </c>
     </row>
     <row r="1104">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="B1106" s="3" t="n">
-        <v>17380.28</v>
+        <v>17380.27</v>
       </c>
       <c r="C1106" s="3" t="n">
         <v>15322.60223342191</v>
@@ -18545,7 +18545,7 @@
         <v>15440.95743379903</v>
       </c>
       <c r="D1108" s="3" t="n">
-        <v>16494.55845314628</v>
+        <v>16494.55699360984</v>
       </c>
     </row>
     <row r="1109">
@@ -18577,7 +18577,7 @@
         <v>15374.67881054097</v>
       </c>
       <c r="D1110" s="3" t="n">
-        <v>16354.19964894576</v>
+        <v>16354.19673458933</v>
       </c>
     </row>
     <row r="1111">
@@ -18593,7 +18593,7 @@
         <v>15545.78653195672</v>
       </c>
       <c r="D1111" s="3" t="n">
-        <v>16393.38923836453</v>
+        <v>16393.38778166137</v>
       </c>
     </row>
     <row r="1112">
@@ -18609,7 +18609,7 @@
         <v>15524.82091872027</v>
       </c>
       <c r="D1112" s="3" t="n">
-        <v>16432.30340621047</v>
+        <v>16432.30486759607</v>
       </c>
     </row>
     <row r="1113">
@@ -18625,7 +18625,7 @@
         <v>15300.9606762659</v>
       </c>
       <c r="D1113" s="3" t="n">
-        <v>16409.79254977593</v>
+        <v>16409.79400915956</v>
       </c>
     </row>
     <row r="1114">
@@ -18641,7 +18641,7 @@
         <v>15175.16596487176</v>
       </c>
       <c r="D1114" s="3" t="n">
-        <v>16056.11982488356</v>
+        <v>16056.12128248594</v>
       </c>
     </row>
     <row r="1115">
@@ -18721,7 +18721,7 @@
         <v>15176.51785271089</v>
       </c>
       <c r="D1119" s="3" t="n">
-        <v>16151.16627701562</v>
+        <v>16151.16770548867</v>
       </c>
     </row>
     <row r="1120">
@@ -18737,7 +18737,7 @@
         <v>15192.74979455949</v>
       </c>
       <c r="D1120" s="3" t="n">
-        <v>15959.84967773357</v>
+        <v>15959.85108942792</v>
       </c>
     </row>
     <row r="1121">
@@ -18785,7 +18785,7 @@
         <v>15343.56784665836</v>
       </c>
       <c r="D1123" s="3" t="n">
-        <v>16186.5197847973</v>
+        <v>16186.51835303295</v>
       </c>
     </row>
     <row r="1124">
@@ -18817,7 +18817,7 @@
         <v>15234.68102103238</v>
       </c>
       <c r="D1125" s="3" t="n">
-        <v>16016.57617975039</v>
+        <v>16016.57474398228</v>
       </c>
     </row>
     <row r="1126">
@@ -18865,7 +18865,7 @@
         <v>15315.83969829991</v>
       </c>
       <c r="D1128" s="3" t="n">
-        <v>16184.49939679389</v>
+        <v>16184.49796219637</v>
       </c>
     </row>
     <row r="1129">
@@ -18913,7 +18913,7 @@
         <v>15196.13157810821</v>
       </c>
       <c r="D1131" s="3" t="n">
-        <v>15821.50405317734</v>
+        <v>15821.50262465353</v>
       </c>
     </row>
     <row r="1132">
@@ -18929,7 +18929,7 @@
         <v>15186.66320335706</v>
       </c>
       <c r="D1132" s="3" t="n">
-        <v>15842.8048331427</v>
+        <v>15842.8062625828</v>
       </c>
     </row>
     <row r="1133">
@@ -18939,13 +18939,13 @@
         </is>
       </c>
       <c r="B1133" s="3" t="n">
-        <v>17475.81</v>
+        <v>17475.8</v>
       </c>
       <c r="C1133" s="3" t="n">
         <v>15147.43678453787</v>
       </c>
       <c r="D1133" s="3" t="n">
-        <v>15844.11934427288</v>
+        <v>15844.12077383159</v>
       </c>
     </row>
     <row r="1134">
@@ -19057,7 +19057,7 @@
         <v>15453.80759209891</v>
       </c>
       <c r="D1140" s="3" t="n">
-        <v>16235.23718318213</v>
+        <v>16235.23574242622</v>
       </c>
     </row>
     <row r="1141">
@@ -19089,7 +19089,7 @@
         <v>15362.50459616066</v>
       </c>
       <c r="D1142" s="3" t="n">
-        <v>16029.69124159283</v>
+        <v>16029.68980423003</v>
       </c>
     </row>
     <row r="1143">
@@ -19137,7 +19137,7 @@
         <v>15400.37912714072</v>
       </c>
       <c r="D1145" s="3" t="n">
-        <v>16272.63057838592</v>
+        <v>16272.63203936435</v>
       </c>
     </row>
     <row r="1146">
@@ -19153,7 +19153,7 @@
         <v>15317.86856203406</v>
       </c>
       <c r="D1146" s="3" t="n">
-        <v>16149.39486094624</v>
+        <v>16149.39340290274</v>
       </c>
     </row>
     <row r="1147">
@@ -19185,7 +19185,7 @@
         <v>15073.7186502628</v>
       </c>
       <c r="D1148" s="3" t="n">
-        <v>16234.10006313313</v>
+        <v>16234.09859087287</v>
       </c>
     </row>
     <row r="1149">
@@ -19201,7 +19201,7 @@
         <v>15286.08165423188</v>
       </c>
       <c r="D1149" s="3" t="n">
-        <v>16076.89900564352</v>
+        <v>16076.89754529278</v>
       </c>
     </row>
     <row r="1150">
@@ -19217,7 +19217,7 @@
         <v>15230.62329356409</v>
       </c>
       <c r="D1150" s="3" t="n">
-        <v>16064.927706862</v>
+        <v>16064.92624576476</v>
       </c>
     </row>
     <row r="1151">
@@ -19233,7 +19233,7 @@
         <v>15157.58110320859</v>
       </c>
       <c r="D1151" s="3" t="n">
-        <v>15914.30290154154</v>
+        <v>15914.30143182604</v>
       </c>
     </row>
     <row r="1152">
@@ -19265,7 +19265,7 @@
         <v>15169.7553175889</v>
       </c>
       <c r="D1153" s="3" t="n">
-        <v>16136.38946326517</v>
+        <v>16136.38797965515</v>
       </c>
     </row>
     <row r="1154">
@@ -19291,13 +19291,13 @@
         </is>
       </c>
       <c r="B1155" s="3" t="n">
-        <v>17460.59</v>
+        <v>17460.58</v>
       </c>
       <c r="C1155" s="3" t="n">
         <v>15112.94506908198</v>
       </c>
       <c r="D1155" s="3" t="n">
-        <v>15808.78437591487</v>
+        <v>15808.78584610545</v>
       </c>
     </row>
     <row r="1156">
@@ -19313,7 +19313,7 @@
         <v>14858.64980666456</v>
       </c>
       <c r="D1156" s="3" t="n">
-        <v>15873.00652508415</v>
+        <v>15873.00504527437</v>
       </c>
     </row>
     <row r="1157">
@@ -19675,7 +19675,7 @@
         </is>
       </c>
       <c r="B1179" s="3" t="n">
-        <v>17915.3</v>
+        <v>17915.29</v>
       </c>
       <c r="C1179" s="3" t="n">
         <v>15704.0440950726</v>
@@ -19787,7 +19787,7 @@
         </is>
       </c>
       <c r="B1186" s="3" t="n">
-        <v>18334.41</v>
+        <v>18334.4</v>
       </c>
       <c r="C1186" s="3" t="n">
         <v>15833.22059001545</v>
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="B1215" s="3" t="n">
-        <v>18748.64</v>
+        <v>18748.63</v>
       </c>
       <c r="C1215" s="3" t="n">
         <v>16331.66473222869</v>
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="B1228" s="3" t="n">
-        <v>19138.09</v>
+        <v>19138.08</v>
       </c>
       <c r="C1228" s="3" t="n">
         <v>16755.03885232772</v>
@@ -20859,7 +20859,7 @@
         </is>
       </c>
       <c r="B1253" s="3" t="n">
-        <v>19109.38</v>
+        <v>19109.37</v>
       </c>
       <c r="C1253" s="3" t="n">
         <v>17059.38079615461</v>
@@ -20971,7 +20971,7 @@
         </is>
       </c>
       <c r="B1260" s="3" t="n">
-        <v>19619.53</v>
+        <v>19619.52</v>
       </c>
       <c r="C1260" s="3" t="n">
         <v>17421.885908303</v>
@@ -21195,7 +21195,7 @@
         </is>
       </c>
       <c r="B1274" s="3" t="n">
-        <v>19332.53</v>
+        <v>19332.52</v>
       </c>
       <c r="C1274" s="3" t="n">
         <v>17121.60169194439</v>
@@ -21547,7 +21547,7 @@
         </is>
       </c>
       <c r="B1296" s="3" t="n">
-        <v>20249.96</v>
+        <v>20249.95</v>
       </c>
       <c r="C1296" s="3" t="n">
         <v>17423.23779614213</v>
@@ -21707,13 +21707,13 @@
         </is>
       </c>
       <c r="B1306" s="3" t="n">
-        <v>20228.9</v>
+        <v>20264.25</v>
       </c>
       <c r="C1306" s="3" t="n">
         <v>17680.23889818871</v>
       </c>
       <c r="D1306" s="3" t="n">
-        <v>19099.50164015973</v>
+        <v>19161.62925158775</v>
       </c>
     </row>
   </sheetData>
@@ -21835,14 +21835,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9.085865</v>
+        <v>3.232312</v>
       </c>
       <c r="E3" t="n">
-        <v>109.951</v>
+        <v>309.0667</v>
       </c>
       <c r="F3" t="n">
         <v>999</v>
@@ -21869,14 +21869,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48.137654</v>
+        <v>9.085865</v>
       </c>
       <c r="E4" t="n">
-        <v>20.753</v>
+        <v>109.951</v>
       </c>
       <c r="F4" t="n">
         <v>999</v>
@@ -21903,14 +21903,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.232311</v>
+        <v>48.13765</v>
       </c>
       <c r="E5" t="n">
-        <v>309.0668</v>
+        <v>20.753</v>
       </c>
       <c r="F5" t="n">
         <v>999</v>
@@ -21937,14 +21937,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BTC-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.009386</v>
+        <v>0.149672</v>
       </c>
       <c r="E6" t="n">
-        <v>53163.6661</v>
+        <v>3333.961</v>
       </c>
       <c r="F6" t="n">
         <v>499</v>
@@ -21971,14 +21971,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>BTC-USD</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.149672</v>
+        <v>0.009386</v>
       </c>
       <c r="E7" t="n">
-        <v>3333.961</v>
+        <v>53163.6661</v>
       </c>
       <c r="F7" t="n">
         <v>499</v>
@@ -22009,7 +22009,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.232311</v>
+        <v>3.232312</v>
       </c>
       <c r="E8" t="n">
         <v>325.2089</v>
@@ -22083,7 +22083,7 @@
         <v>2.772013</v>
       </c>
       <c r="E10" t="n">
-        <v>371.6967</v>
+        <v>371.6966</v>
       </c>
       <c r="F10" t="n">
         <v>1030.35</v>
@@ -22117,7 +22117,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.004317</v>
+        <v>1.004316</v>
       </c>
       <c r="E11" t="n">
         <v>130.0226</v>
@@ -22228,7 +22228,7 @@
         <v>3.165745</v>
       </c>
       <c r="E14" t="n">
-        <v>316.1562</v>
+        <v>316.1563</v>
       </c>
       <c r="F14" t="n">
         <v>1000.87</v>
@@ -22299,7 +22299,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8.544048999999999</v>
+        <v>8.544038</v>
       </c>
       <c r="E16" t="n">
         <v>25.814</v>
@@ -22339,7 +22339,7 @@
         <v>2.697097</v>
       </c>
       <c r="E17" t="n">
-        <v>378.7708</v>
+        <v>378.7707</v>
       </c>
       <c r="F17" t="n">
         <v>1021.58</v>
@@ -22373,7 +22373,7 @@
         <v>2.697097</v>
       </c>
       <c r="E18" t="n">
-        <v>359.6429</v>
+        <v>359.6428</v>
       </c>
       <c r="F18" t="n">
         <v>969.99</v>
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8.081548</v>
+        <v>8.081549000000001</v>
       </c>
       <c r="E19" t="n">
         <v>112.8713</v>
@@ -22444,7 +22444,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.215838</v>
+        <v>14.215842</v>
       </c>
       <c r="E20" t="n">
         <v>73.1315</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.952799</v>
+        <v>13.952802</v>
       </c>
       <c r="E22" t="n">
         <v>76.81659999999999</v>
@@ -22549,7 +22549,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4.688301</v>
+        <v>4.688309</v>
       </c>
       <c r="E23" t="n">
         <v>29.8343</v>
@@ -22657,7 +22657,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.445042</v>
+        <v>15.445044</v>
       </c>
       <c r="E26" t="n">
         <v>73.4817</v>
@@ -22765,7 +22765,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.642199</v>
+        <v>15.642196</v>
       </c>
       <c r="E29" t="n">
         <v>72.4512</v>
@@ -22799,7 +22799,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.645495</v>
+        <v>1.645494</v>
       </c>
       <c r="E30" t="n">
         <v>74.9425</v>
@@ -22836,7 +22836,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.309338</v>
+        <v>2.309335</v>
       </c>
       <c r="E31" t="n">
         <v>69.20959999999999</v>
@@ -22870,7 +22870,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.11155</v>
+        <v>3.111548</v>
       </c>
       <c r="E32" t="n">
         <v>40.2778</v>
@@ -22907,7 +22907,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9.717483</v>
+        <v>9.717484000000001</v>
       </c>
       <c r="E33" t="n">
         <v>69.89490000000001</v>
@@ -22941,7 +22941,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9.312381</v>
+        <v>9.312383000000001</v>
       </c>
       <c r="E34" t="n">
         <v>69.13039999999999</v>
@@ -22978,7 +22978,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.67834</v>
+        <v>14.678337</v>
       </c>
       <c r="E35" t="n">
         <v>71.70910000000001</v>
@@ -23154,7 +23154,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15.428839</v>
+        <v>15.428837</v>
       </c>
       <c r="E40" t="n">
         <v>72.5813</v>
@@ -23188,7 +23188,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>28.857768</v>
+        <v>28.857767</v>
       </c>
       <c r="E41" t="n">
         <v>71.8141</v>
@@ -23225,7 +23225,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25.634842</v>
+        <v>25.634844</v>
       </c>
       <c r="E42" t="n">
         <v>32.8331</v>
@@ -23438,10 +23438,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.842017</v>
+        <v>2.842018</v>
       </c>
       <c r="E48" t="n">
-        <v>391.1994</v>
+        <v>391.1993</v>
       </c>
       <c r="F48" t="n">
         <v>1111.8</v>
@@ -23546,10 +23546,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.842017</v>
+        <v>2.842018</v>
       </c>
       <c r="E51" t="n">
-        <v>389.8564</v>
+        <v>389.8563</v>
       </c>
       <c r="F51" t="n">
         <v>1107.98</v>
@@ -23583,13 +23583,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>28.500992</v>
+        <v>28.500989</v>
       </c>
       <c r="E52" t="n">
         <v>38.1574</v>
       </c>
       <c r="F52" t="n">
-        <v>1087.53</v>
+        <v>1087.52</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -23617,7 +23617,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>28.500992</v>
+        <v>28.500989</v>
       </c>
       <c r="E53" t="n">
         <v>36.5224</v>
@@ -23654,7 +23654,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6.128741</v>
+        <v>6.12874</v>
       </c>
       <c r="E54" t="n">
         <v>173.5514</v>
@@ -23684,14 +23684,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BTC-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.015854</v>
+        <v>0.304162</v>
       </c>
       <c r="E55" t="n">
-        <v>33514.1682</v>
+        <v>1746.8531</v>
       </c>
       <c r="F55" t="n">
         <v>531.33</v>
@@ -23718,14 +23718,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>BTC-USD</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.304162</v>
+        <v>0.015854</v>
       </c>
       <c r="E56" t="n">
-        <v>1746.8531</v>
+        <v>33514.1682</v>
       </c>
       <c r="F56" t="n">
         <v>531.33</v>
@@ -23756,7 +23756,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6.128741</v>
+        <v>6.12874</v>
       </c>
       <c r="E57" t="n">
         <v>172.6869</v>
@@ -23793,10 +23793,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.563811</v>
+        <v>2.56381</v>
       </c>
       <c r="E58" t="n">
-        <v>414.8131</v>
+        <v>414.813</v>
       </c>
       <c r="F58" t="n">
         <v>1063.5</v>
@@ -23827,7 +23827,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.893828</v>
+        <v>0.893829</v>
       </c>
       <c r="E59" t="n">
         <v>172.2245</v>
@@ -23938,7 +23938,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5.549225</v>
+        <v>5.549223</v>
       </c>
       <c r="E62" t="n">
         <v>88.84439999999999</v>
@@ -23975,7 +23975,7 @@
         <v>0.362645</v>
       </c>
       <c r="E63" t="n">
-        <v>459.832</v>
+        <v>459.8321</v>
       </c>
       <c r="F63" t="n">
         <v>166.76</v>
@@ -24040,10 +24040,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2.926456</v>
+        <v>2.926455</v>
       </c>
       <c r="E65" t="n">
-        <v>472.1315</v>
+        <v>472.1316</v>
       </c>
       <c r="F65" t="n">
         <v>1381.67</v>
@@ -24114,10 +24114,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>36.146935</v>
+        <v>36.146927</v>
       </c>
       <c r="E67" t="n">
-        <v>38.7314</v>
+        <v>38.7315</v>
       </c>
       <c r="F67" t="n">
         <v>1400.02</v>
@@ -24148,13 +24148,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>36.146935</v>
+        <v>36.146927</v>
       </c>
       <c r="E68" t="n">
         <v>39.6226</v>
       </c>
       <c r="F68" t="n">
-        <v>1432.24</v>
+        <v>1432.23</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -24185,7 +24185,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7.183086</v>
+        <v>7.183085</v>
       </c>
       <c r="E69" t="n">
         <v>200.906</v>
@@ -24219,7 +24219,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7.183086</v>
+        <v>7.183085</v>
       </c>
       <c r="E70" t="n">
         <v>208.4801</v>
@@ -24293,10 +24293,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2.898513</v>
+        <v>2.898514</v>
       </c>
       <c r="E72" t="n">
-        <v>489.1049</v>
+        <v>489.1048</v>
       </c>
       <c r="F72" t="n">
         <v>1417.68</v>
@@ -24364,7 +24364,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>15.271016</v>
+        <v>15.271011</v>
       </c>
       <c r="E74" t="n">
         <v>95.7178</v>
@@ -24398,7 +24398,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>17.430454</v>
+        <v>17.430448</v>
       </c>
       <c r="E75" t="n">
         <v>94.6876</v>
@@ -24438,7 +24438,7 @@
         <v>3.093435</v>
       </c>
       <c r="E76" t="n">
-        <v>412.3018</v>
+        <v>412.3017</v>
       </c>
       <c r="F76" t="n">
         <v>1275.43</v>
@@ -24472,7 +24472,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6.728413</v>
+        <v>6.728412</v>
       </c>
       <c r="E77" t="n">
         <v>208.1826</v>
@@ -24506,10 +24506,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2.898513</v>
+        <v>2.898514</v>
       </c>
       <c r="E78" t="n">
-        <v>498.8198</v>
+        <v>498.8199</v>
       </c>
       <c r="F78" t="n">
         <v>1445.84</v>
@@ -24577,7 +24577,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6.728413</v>
+        <v>6.728412</v>
       </c>
       <c r="E80" t="n">
         <v>231.803</v>
@@ -24685,7 +24685,7 @@
         <v>3.353498</v>
       </c>
       <c r="E83" t="n">
-        <v>483.5167</v>
+        <v>483.5168</v>
       </c>
       <c r="F83" t="n">
         <v>1621.47</v>
@@ -25003,7 +25003,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6.368397</v>
+        <v>6.368396</v>
       </c>
       <c r="E92" t="n">
         <v>253.7815</v>
@@ -25037,7 +25037,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.496565</v>
+        <v>1.496563</v>
       </c>
       <c r="E93" t="n">
         <v>105.6971</v>
@@ -25077,10 +25077,10 @@
         <v>2.865477</v>
       </c>
       <c r="E94" t="n">
-        <v>509.7947</v>
+        <v>509.7948</v>
       </c>
       <c r="F94" t="n">
-        <v>1460.8</v>
+        <v>1460.81</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>2.922332</v>
       </c>
       <c r="E101" t="n">
-        <v>513.7974</v>
+        <v>513.7975</v>
       </c>
       <c r="F101" t="n">
         <v>1501.49</v>
@@ -25398,7 +25398,7 @@
         <v>2.922332</v>
       </c>
       <c r="E103" t="n">
-        <v>536.6691</v>
+        <v>536.669</v>
       </c>
       <c r="F103" t="n">
         <v>1568.33</v>
@@ -25472,7 +25472,7 @@
         <v>3055.1378</v>
       </c>
       <c r="F105" t="n">
-        <v>697.5700000000001</v>
+        <v>697.5599999999999</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -25685,7 +25685,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2.692592</v>
+        <v>2.692591</v>
       </c>
       <c r="E111" t="n">
         <v>113.8869</v>
@@ -25756,7 +25756,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>34.272922</v>
+        <v>34.272921</v>
       </c>
       <c r="E113" t="n">
         <v>50.3109</v>
@@ -26040,7 +26040,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4.686942</v>
+        <v>4.686941</v>
       </c>
       <c r="E121" t="n">
         <v>55.3943</v>
@@ -26073,14 +26073,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BTC-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.01449</v>
+        <v>0.463873</v>
       </c>
       <c r="E122" t="n">
-        <v>66659.257</v>
+        <v>2082.2223</v>
       </c>
       <c r="F122" t="n">
         <v>965.89</v>
@@ -26107,14 +26107,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>BTC-USD</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.463873</v>
+        <v>0.01449</v>
       </c>
       <c r="E123" t="n">
-        <v>2082.2223</v>
+        <v>66659.257</v>
       </c>
       <c r="F123" t="n">
         <v>965.89</v>

--- a/backtest/controle-alleen-etf/backtest.xlsx
+++ b/backtest/controle-alleen-etf/backtest.xlsx
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.015277845921852</v>
+        <v>1.014382683105354</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.1506468920904958</v>
+        <v>0.1505445270373906</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>-0.1944115644126416</v>
@@ -490,7 +490,7 @@
         <v>1.09</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>20126.6</v>
+        <v>20117.66</v>
       </c>
     </row>
     <row r="3">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.8813750654515224</v>
+        <v>0.881745130184957</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1349135801877226</v>
+        <v>0.134958279036923</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>-0.2303251037363384</v>
@@ -534,7 +534,7 @@
         <v>0.76</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>18813.75065451522</v>
+        <v>18817.45130184957</v>
       </c>
     </row>
   </sheetData>
@@ -632,7 +632,7 @@
         <v>0.2722609034779582</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3283175535339031</v>
+        <v>0.3283174124835229</v>
       </c>
     </row>
     <row r="6">
@@ -646,7 +646,7 @@
         <v>0.0707564790521269</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.04279549093743906</v>
+        <v>0.04279560166903029</v>
       </c>
     </row>
     <row r="7">
@@ -654,13 +654,13 @@
         <v>2026</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.1839232184622046</v>
+        <v>0.1833973336345114</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0.1705371154006647</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1780296709292142</v>
+        <v>0.1782613882747643</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +741,7 @@
         <v>-0.1071749879932085</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.1119945856225182</v>
+        <v>0.1119938547400288</v>
       </c>
     </row>
     <row r="3">
@@ -788,10 +788,10 @@
         <v>-0.06632527571986369</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.1489283036113314</v>
+        <v>-0.1489282116260049</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1792150117088243</v>
+        <v>0.1792148887073499</v>
       </c>
     </row>
   </sheetData>
@@ -865,7 +865,7 @@
         <v>10050.03756144554</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>10062.54120857029</v>
+        <v>10062.53829425966</v>
       </c>
     </row>
     <row r="4">
@@ -881,7 +881,7 @@
         <v>10084.52228042186</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>10086.33965859571</v>
+        <v>10086.34111348336</v>
       </c>
     </row>
     <row r="5">
@@ -897,7 +897,7 @@
         <v>10066.26517895622</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10092.64978492818</v>
+        <v>10092.65196294408</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         <v>10145.37790961914</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10149.25812375915</v>
+        <v>10149.25666988692</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
         <v>10222.46218809323</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10183.22259138704</v>
+        <v>10183.22332010008</v>
       </c>
     </row>
     <row r="9">
@@ -977,7 +977,7 @@
         <v>10144.026296004</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10246.15132239875</v>
+        <v>10246.15278128033</v>
       </c>
     </row>
     <row r="11">
@@ -993,7 +993,7 @@
         <v>10243.42458032139</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10193.57894475145</v>
+        <v>10193.58039320821</v>
       </c>
     </row>
     <row r="12">
@@ -1009,7 +1009,7 @@
         <v>10261.00484321334</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10323.25931507768</v>
+        <v>10323.26004726003</v>
       </c>
     </row>
     <row r="13">
@@ -1041,7 +1041,7 @@
         <v>10295.48956218965</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>10407.78944998232</v>
+        <v>10407.79018072616</v>
       </c>
     </row>
     <row r="15">
@@ -1057,7 +1057,7 @@
         <v>10401.65004164724</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>10424.14505874293</v>
+        <v>10424.14433028371</v>
       </c>
     </row>
     <row r="16">
@@ -1105,7 +1105,7 @@
         <v>10396.24049188831</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10456.45426303264</v>
+        <v>10456.45353305038</v>
       </c>
     </row>
     <row r="19">
@@ -1137,7 +1137,7 @@
         <v>10444.92540795259</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>10471.06212577554</v>
+        <v>10471.06286246789</v>
       </c>
     </row>
     <row r="21">
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10679.65</v>
+        <v>10679.66</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>10508.4863279124</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>10582.44073844809</v>
+        <v>10582.44147739968</v>
       </c>
     </row>
     <row r="22">
@@ -1185,7 +1185,7 @@
         <v>10645.7504287762</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>10706.82381782822</v>
+        <v>10706.82158452413</v>
       </c>
     </row>
     <row r="24">
@@ -1201,7 +1201,7 @@
         <v>10641.69352439854</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>10723.54860730801</v>
+        <v>10723.54935472118</v>
       </c>
     </row>
     <row r="25">
@@ -1217,7 +1217,7 @@
         <v>10602.47506247086</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>10759.97005119304</v>
+        <v>10759.96930377987</v>
       </c>
     </row>
     <row r="26">
@@ -1233,7 +1233,7 @@
         <v>10641.01668582484</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>10696.10268882129</v>
+        <v>10696.10417743699</v>
       </c>
     </row>
     <row r="27">
@@ -1249,7 +1249,7 @@
         <v>10701.19650821456</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>10753.65663468502</v>
+        <v>10753.65813553601</v>
       </c>
     </row>
     <row r="28">
@@ -1265,7 +1265,7 @@
         <v>10557.84705078425</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>10800.09269528206</v>
+        <v>10800.09420061765</v>
       </c>
     </row>
     <row r="29">
@@ -1281,7 +1281,7 @@
         <v>10651.83578534271</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>10826.24838040459</v>
+        <v>10826.24913288624</v>
       </c>
     </row>
     <row r="30">
@@ -1297,7 +1297,7 @@
         <v>10678.88250237126</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>10866.78861969356</v>
+        <v>10866.78937499297</v>
       </c>
     </row>
     <row r="31">
@@ -1329,7 +1329,7 @@
         <v>10438.84005138608</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>10668.84451240237</v>
+        <v>10668.84526166865</v>
       </c>
     </row>
     <row r="33">
@@ -1345,7 +1345,7 @@
         <v>10321.86047241063</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>10461.01723663064</v>
+        <v>10461.01648738129</v>
       </c>
     </row>
     <row r="34">
@@ -1361,7 +1361,7 @@
         <v>10410.44068897627</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>10311.17731410176</v>
+        <v>10311.17880772652</v>
       </c>
     </row>
     <row r="35">
@@ -1377,7 +1377,7 @@
         <v>10228.54857642586</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>10479.07341733606</v>
+        <v>10479.07266981284</v>
       </c>
     </row>
     <row r="36">
@@ -1393,7 +1393,7 @@
         <v>10198.12076182721</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>10400.12070476778</v>
+        <v>10400.11995636458</v>
       </c>
     </row>
     <row r="37">
@@ -1409,7 +1409,7 @@
         <v>10316.45195441781</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>10524.60232925226</v>
+        <v>10524.60008376329</v>
       </c>
     </row>
     <row r="38">
@@ -1425,7 +1425,7 @@
         <v>10592.33176976057</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>10759.54307425485</v>
+        <v>10759.54457365048</v>
       </c>
     </row>
     <row r="39">
@@ -1441,7 +1441,7 @@
         <v>10507.80948933871</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>10797.77746598849</v>
+        <v>10797.77596523904</v>
       </c>
     </row>
     <row r="40">
@@ -1457,7 +1457,7 @@
         <v>10547.02795126638</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>10659.56646070945</v>
+        <v>10659.56720651493</v>
       </c>
     </row>
     <row r="41">
@@ -1473,7 +1473,7 @@
         <v>10483.46703130657</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>10809.71859828243</v>
+        <v>10809.71934754025</v>
       </c>
     </row>
     <row r="42">
@@ -1489,7 +1489,7 @@
         <v>10468.59205917715</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>10696.4185730606</v>
+        <v>10696.41707699889</v>
       </c>
     </row>
     <row r="43">
@@ -1505,7 +1505,7 @@
         <v>10365.81267728966</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>10647.70134149973</v>
+        <v>10647.69984193479</v>
       </c>
     </row>
     <row r="44">
@@ -1521,7 +1521,7 @@
         <v>10382.04029480034</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>10837.25907294887</v>
+        <v>10837.25681877852</v>
       </c>
     </row>
     <row r="45">
@@ -1585,7 +1585,7 @@
         <v>10380.6886811852</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>10685.66088170617</v>
+        <v>10685.6601313991</v>
       </c>
     </row>
     <row r="49">
@@ -1601,7 +1601,7 @@
         <v>10479.4101269289</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>10782.88843677416</v>
+        <v>10782.88993605135</v>
       </c>
     </row>
     <row r="50">
@@ -1617,7 +1617,7 @@
         <v>10603.82770785212</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>10810.42419673055</v>
+        <v>10810.42270291955</v>
       </c>
     </row>
     <row r="51">
@@ -1633,7 +1633,7 @@
         <v>10606.53196684853</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>10811.89409584002</v>
+        <v>10811.8926018259</v>
       </c>
     </row>
     <row r="52">
@@ -1649,7 +1649,7 @@
         <v>10668.74024142708</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>10967.88535598477</v>
+        <v>10967.88610319487</v>
       </c>
     </row>
     <row r="53">
@@ -1665,7 +1665,7 @@
         <v>10730.94851600563</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>10953.33836680019</v>
+        <v>10953.33687314148</v>
       </c>
     </row>
     <row r="54">
@@ -1681,7 +1681,7 @@
         <v>10672.79714580475</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>10982.13492831002</v>
+        <v>10982.13642398257</v>
       </c>
     </row>
     <row r="55">
@@ -1697,7 +1697,7 @@
         <v>10728.9200638168</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>10908.03415698989</v>
+        <v>10908.0326672912</v>
       </c>
     </row>
     <row r="56">
@@ -1729,7 +1729,7 @@
         <v>10702.54915359582</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>10930.73566396185</v>
+        <v>10930.73640793962</v>
       </c>
     </row>
     <row r="58">
@@ -1745,7 +1745,7 @@
         <v>10750.55826285253</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>10995.92507335039</v>
+        <v>10995.92357601938</v>
       </c>
     </row>
     <row r="59">
@@ -1761,7 +1761,7 @@
         <v>10718.77780287262</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>10802.57508429176</v>
+        <v>10802.57658409355</v>
       </c>
     </row>
     <row r="60">
@@ -1793,7 +1793,7 @@
         <v>10477.38167474007</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>10737.14624833269</v>
+        <v>10737.14699735363</v>
       </c>
     </row>
     <row r="62">
@@ -1809,7 +1809,7 @@
         <v>10343.49867144636</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>10669.87388096528</v>
+        <v>10669.87239045436</v>
       </c>
     </row>
     <row r="63">
@@ -1841,7 +1841,7 @@
         <v>10522.00968642667</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>10784.27703684186</v>
+        <v>10784.27927014595</v>
       </c>
     </row>
     <row r="65">
@@ -1857,7 +1857,7 @@
         <v>10486.84812887667</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>10565.81088077842</v>
+        <v>10565.81014123455</v>
       </c>
     </row>
     <row r="66">
@@ -1873,7 +1873,7 @@
         <v>10344.85131682762</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>10555.86060399417</v>
+        <v>10555.8628196306</v>
       </c>
     </row>
     <row r="67">
@@ -1889,7 +1889,7 @@
         <v>10430.04940405705</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>10598.79427152137</v>
+        <v>10598.79649616942</v>
       </c>
     </row>
     <row r="68">
@@ -1905,7 +1905,7 @@
         <v>10314.42247046286</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>10411.21408179466</v>
+        <v>10411.21334023687</v>
       </c>
     </row>
     <row r="69">
@@ -1921,7 +1921,7 @@
         <v>10271.8239427312</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>10376.70335152408</v>
+        <v>10376.70260466935</v>
       </c>
     </row>
     <row r="70">
@@ -1937,7 +1937,7 @@
         <v>10355.66938457937</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>10249.4127345821</v>
+        <v>10249.41124268351</v>
       </c>
     </row>
     <row r="71">
@@ -1969,7 +1969,7 @@
         <v>9703.157792429087</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>10092.59928147532</v>
+        <v>10092.59853539908</v>
       </c>
     </row>
     <row r="73">
@@ -2001,7 +2001,7 @@
         <v>10011.49490632544</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>9976.849568451198</v>
+        <v>9976.848819937983</v>
       </c>
     </row>
     <row r="75">
@@ -2017,7 +2017,7 @@
         <v>10064.91356534108</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>9981.453832448089</v>
+        <v>9981.453079873339</v>
       </c>
     </row>
     <row r="76">
@@ -2033,7 +2033,7 @@
         <v>9932.382175662515</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>10317.90769000817</v>
+        <v>10317.90617182778</v>
       </c>
     </row>
     <row r="77">
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>10119.72</v>
+        <v>10119.73</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>10141.99784381517</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>10498.70990118136</v>
+        <v>10498.71141863409</v>
       </c>
     </row>
     <row r="78">
@@ -2065,7 +2065,7 @@
         <v>10227.87173785217</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>10496.92004513237</v>
+        <v>10496.91778461572</v>
       </c>
     </row>
     <row r="79">
@@ -2081,7 +2081,7 @@
         <v>10250.86258226916</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>10557.22831253162</v>
+        <v>10557.23056416375</v>
       </c>
     </row>
     <row r="80">
@@ -2097,7 +2097,7 @@
         <v>10068.97046971875</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>10285.37317681345</v>
+        <v>10285.3709303601</v>
       </c>
     </row>
     <row r="81">
@@ -2129,7 +2129,7 @@
         <v>10023.66665122457</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>10161.01308861285</v>
+        <v>10161.01234994048</v>
       </c>
     </row>
     <row r="83">
@@ -2161,7 +2161,7 @@
         <v>10212.99573395663</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>10425.39829157577</v>
+        <v>10425.39977330358</v>
       </c>
     </row>
     <row r="85">
@@ -2177,7 +2177,7 @@
         <v>10150.11165257051</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>10237.86605742173</v>
+        <v>10237.86457572764</v>
       </c>
     </row>
     <row r="86">
@@ -2209,7 +2209,7 @@
         <v>9984.448189296892</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>10052.87679824847</v>
+        <v>10052.87456466516</v>
       </c>
     </row>
     <row r="88">
@@ -2225,7 +2225,7 @@
         <v>10066.94201752991</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>10268.05056703445</v>
+        <v>10268.05131542913</v>
       </c>
     </row>
     <row r="89">
@@ -2241,7 +2241,7 @@
         <v>10025.01826483971</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>10233.88677481753</v>
+        <v>10233.88453960945</v>
       </c>
     </row>
     <row r="90">
@@ -2257,7 +2257,7 @@
         <v>9983.09554391563</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>9999.009303721912</v>
+        <v>9999.010047581251</v>
       </c>
     </row>
     <row r="91">
@@ -2273,7 +2273,7 @@
         <v>9864.088544517457</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>9941.94694569115</v>
+        <v>9941.949923429933</v>
       </c>
     </row>
     <row r="92">
@@ -2289,7 +2289,7 @@
         <v>9751.842708493365</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>9985.227922710788</v>
+        <v>9985.23091341277</v>
       </c>
     </row>
     <row r="93">
@@ -2305,7 +2305,7 @@
         <v>9776.185166525504</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>9884.666303335322</v>
+        <v>9884.668547859566</v>
       </c>
     </row>
     <row r="94">
@@ -2321,7 +2321,7 @@
         <v>9720.73805532103</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>9692.63635081925</v>
+        <v>9692.637097707855</v>
       </c>
     </row>
     <row r="95">
@@ -2331,13 +2331,13 @@
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>9699.92</v>
+        <v>9699.93</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>9589.560342789848</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>9858.899353762605</v>
+        <v>9858.901599073766</v>
       </c>
     </row>
     <row r="96">
@@ -2353,7 +2353,7 @@
         <v>9895.192165923674</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>10179.97952798146</v>
+        <v>10179.98028411007</v>
       </c>
     </row>
     <row r="97">
@@ -2369,7 +2369,7 @@
         <v>9945.905534176789</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>10162.68293633794</v>
+        <v>10162.6867202391</v>
       </c>
     </row>
     <row r="98">
@@ -2385,7 +2385,7 @@
         <v>9885.0499049795</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>9976.795811232389</v>
+        <v>9976.795056804556</v>
       </c>
     </row>
     <row r="99">
@@ -2433,7 +2433,7 @@
         <v>9876.259257650468</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>10162.68358413644</v>
+        <v>10162.68511331682</v>
       </c>
     </row>
     <row r="102">
@@ -2449,7 +2449,7 @@
         <v>9833.659698152695</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>10037.52384240676</v>
+        <v>10037.52306429491</v>
       </c>
     </row>
     <row r="103">
@@ -2481,7 +2481,7 @@
         <v>9760.633355822396</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>10206.25315588918</v>
+        <v>10206.25082663054</v>
       </c>
     </row>
     <row r="105">
@@ -2497,7 +2497,7 @@
         <v>9696.395597288891</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>9999.057049200228</v>
+        <v>9999.056285092276</v>
       </c>
     </row>
     <row r="106">
@@ -2513,7 +2513,7 @@
         <v>9797.822333795117</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>9925.594044907737</v>
+        <v>9925.591740120108</v>
       </c>
     </row>
     <row r="107">
@@ -2529,7 +2529,7 @@
         <v>9690.310240722385</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>9926.847543952881</v>
+        <v>9926.849091985883</v>
       </c>
     </row>
     <row r="108">
@@ -2545,7 +2545,7 @@
         <v>9777.537811906766</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>10134.82898191183</v>
+        <v>10134.8297551414</v>
       </c>
     </row>
     <row r="109">
@@ -2577,7 +2577,7 @@
         <v>10010.14226094418</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>10414.21481065774</v>
+        <v>10414.21404295357</v>
       </c>
     </row>
     <row r="111">
@@ -2593,7 +2593,7 @@
         <v>10164.98765646604</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>10454.70706356716</v>
+        <v>10454.7078259066</v>
       </c>
     </row>
     <row r="112">
@@ -2609,7 +2609,7 @@
         <v>10238.69083737003</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>10505.01524428018</v>
+        <v>10505.01294558489</v>
       </c>
     </row>
     <row r="113">
@@ -2625,7 +2625,7 @@
         <v>10346.87976901646</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>10652.93490176215</v>
+        <v>10652.93643783036</v>
       </c>
     </row>
     <row r="114">
@@ -2641,7 +2641,7 @@
         <v>10324.56576317315</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>10503.81150044614</v>
+        <v>10503.81380193393</v>
       </c>
     </row>
     <row r="115">
@@ -2657,7 +2657,7 @@
         <v>10318.48040660665</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>10684.846803869</v>
+        <v>10684.84603507333</v>
       </c>
     </row>
     <row r="116">
@@ -2673,7 +2673,7 @@
         <v>10374.60229285257</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>10733.8359859932</v>
+        <v>10733.83444885886</v>
       </c>
     </row>
     <row r="117">
@@ -2689,7 +2689,7 @@
         <v>10407.05959140617</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>10837.44086416992</v>
+        <v>10837.43932316016</v>
       </c>
     </row>
     <row r="118">
@@ -2721,7 +2721,7 @@
         <v>10436.13476062355</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>10795.99290683117</v>
+        <v>10795.99138105224</v>
       </c>
     </row>
     <row r="120">
@@ -2737,7 +2737,7 @@
         <v>10426.66830648695</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>10562.86267783643</v>
+        <v>10562.86040358656</v>
       </c>
     </row>
     <row r="121">
@@ -2753,7 +2753,7 @@
         <v>10393.5362328919</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>10678.39901438497</v>
+        <v>10678.39672175657</v>
       </c>
     </row>
     <row r="122">
@@ -2785,7 +2785,7 @@
         <v>10542.29524008114</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>10727.32732200016</v>
+        <v>10727.32500921619</v>
       </c>
     </row>
     <row r="124">
@@ -2801,7 +2801,7 @@
         <v>10338.764928495</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>10687.66607434434</v>
+        <v>10687.66762601588</v>
       </c>
     </row>
     <row r="125">
@@ -2833,7 +2833,7 @@
         <v>10454.39186208919</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>10753.8093593387</v>
+        <v>10753.80858053292</v>
       </c>
     </row>
     <row r="127">
@@ -2849,7 +2849,7 @@
         <v>10298.87065975975</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>10550.47930800068</v>
+        <v>10550.47853063345</v>
       </c>
     </row>
     <row r="128">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>10442.81</v>
+        <v>10442.8</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>10353.64093239053</v>
@@ -2897,7 +2897,7 @@
         <v>10369.86958166733</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>10488.19614098668</v>
+        <v>10488.19691752472</v>
       </c>
     </row>
     <row r="131">
@@ -2913,7 +2913,7 @@
         <v>10369.86958166733</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>10561.45276927493</v>
+        <v>10561.45355123684</v>
       </c>
     </row>
     <row r="132">
@@ -2945,7 +2945,7 @@
         <v>10378.66022899636</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>10775.38978340212</v>
+        <v>10775.38899859713</v>
       </c>
     </row>
     <row r="134">
@@ -2993,7 +2993,7 @@
         <v>10151.46429795177</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>10264.53247038594</v>
+        <v>10264.53325132398</v>
       </c>
     </row>
     <row r="137">
@@ -3009,7 +3009,7 @@
         <v>9967.54373321252</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>10347.08564176772</v>
+        <v>10347.08720712993</v>
       </c>
     </row>
     <row r="138">
@@ -3025,7 +3025,7 @@
         <v>9981.742898534367</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>10138.23485569863</v>
+        <v>10138.23327618853</v>
       </c>
     </row>
     <row r="139">
@@ -3041,7 +3041,7 @@
         <v>10071.67472871516</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>10234.16813048755</v>
+        <v>10234.16892548036</v>
       </c>
     </row>
     <row r="140">
@@ -3057,7 +3057,7 @@
         <v>10126.44500134594</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>10580.68125212415</v>
+        <v>10580.68365710574</v>
       </c>
     </row>
     <row r="141">
@@ -3073,7 +3073,7 @@
         <v>10150.78745937808</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>10239.03230756488</v>
+        <v>10239.03311310927</v>
       </c>
     </row>
     <row r="142">
@@ -3089,7 +3089,7 @@
         <v>9932.382175662515</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>10269.6097631216</v>
+        <v>10269.61056623748</v>
       </c>
     </row>
     <row r="143">
@@ -3105,7 +3105,7 @@
         <v>10075.05582628525</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>10343.10019750394</v>
+        <v>10343.10180784819</v>
       </c>
     </row>
     <row r="144">
@@ -3121,7 +3121,7 @@
         <v>9943.877081987954</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>10638.36827180138</v>
+        <v>10638.3666644357</v>
       </c>
     </row>
     <row r="145">
@@ -3185,7 +3185,7 @@
         <v>9511.123418934498</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>9860.371623791812</v>
+        <v>9860.372424640032</v>
       </c>
     </row>
     <row r="149">
@@ -3233,7 +3233,7 @@
         <v>9776.185166525504</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>10103.41683787557</v>
+        <v>10103.42091395551</v>
       </c>
     </row>
     <row r="152">
@@ -3265,7 +3265,7 @@
         <v>9787.680072850942</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>10210.99773916104</v>
+        <v>10210.99854974007</v>
       </c>
     </row>
     <row r="154">
@@ -3281,7 +3281,7 @@
         <v>9649.740165179564</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>9698.206522479069</v>
+        <v>9698.207324689551</v>
       </c>
     </row>
     <row r="155">
@@ -3329,7 +3329,7 @@
         <v>9551.693494477317</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>9803.027390316773</v>
+        <v>9803.02658977321</v>
       </c>
     </row>
     <row r="158">
@@ -3361,7 +3361,7 @@
         <v>9503.008578413039</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>9661.754962263762</v>
+        <v>9661.755750377299</v>
       </c>
     </row>
     <row r="160">
@@ -3377,7 +3377,7 @@
         <v>9644.330615420631</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>9900.836962769481</v>
+        <v>9900.837754563807</v>
       </c>
     </row>
     <row r="161">
@@ -3393,7 +3393,7 @@
         <v>9831.631245963859</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>10100.0982694228</v>
+        <v>10100.09748104701</v>
       </c>
     </row>
     <row r="162">
@@ -3409,7 +3409,7 @@
         <v>9891.811068353576</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>10101.50745009472</v>
+        <v>10101.50666160893</v>
       </c>
     </row>
     <row r="163">
@@ -3441,7 +3441,7 @@
         <v>9793.089622609876</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>9961.119730712271</v>
+        <v>9961.12209558591</v>
       </c>
     </row>
     <row r="165">
@@ -3457,7 +3457,7 @@
         <v>9814.050983071917</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>10226.97838008691</v>
+        <v>10226.97917429276</v>
       </c>
     </row>
     <row r="166">
@@ -3489,7 +3489,7 @@
         <v>9870.849707891535</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>10022.14983805535</v>
+        <v>10022.15062693881</v>
       </c>
     </row>
     <row r="168">
@@ -3505,7 +3505,7 @@
         <v>9832.983891345122</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>10151.05931794798</v>
+        <v>10151.06090082576</v>
       </c>
     </row>
     <row r="169">
@@ -3521,7 +3521,7 @@
         <v>9851.240992810757</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>10033.93249146459</v>
+        <v>10033.9340732762</v>
       </c>
     </row>
     <row r="170">
@@ -3537,7 +3537,7 @@
         <v>9758.604903633561</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>9777.901151775062</v>
+        <v>9777.90194127625</v>
       </c>
     </row>
     <row r="171">
@@ -3553,7 +3553,7 @@
         <v>9463.114309677791</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>9582.405918159269</v>
+        <v>9582.404324518211</v>
       </c>
     </row>
     <row r="172">
@@ -3617,7 +3617,7 @@
         <v>8951.247915961412</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>9153.817998320865</v>
+        <v>9153.818807562957</v>
       </c>
     </row>
     <row r="176">
@@ -3633,7 +3633,7 @@
         <v>8965.447081283257</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>9094.707009490148</v>
+        <v>9094.706207203501</v>
       </c>
     </row>
     <row r="177">
@@ -3649,7 +3649,7 @@
         <v>9010.075092969866</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>9142.763820297543</v>
+        <v>9142.763013771579</v>
       </c>
     </row>
     <row r="178">
@@ -3665,7 +3665,7 @@
         <v>9110.826022668522</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>9346.762701507931</v>
+        <v>9346.760288682561</v>
       </c>
     </row>
     <row r="179">
@@ -3681,7 +3681,7 @@
         <v>9095.950018772985</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>9319.31327487829</v>
+        <v>9319.314078248042</v>
       </c>
     </row>
     <row r="180">
@@ -3697,7 +3697,7 @@
         <v>9116.911379235025</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>9382.613504998457</v>
+        <v>9382.615106948657</v>
       </c>
     </row>
     <row r="181">
@@ -3713,7 +3713,7 @@
         <v>9330.583951765346</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>9721.424500624684</v>
+        <v>9721.425304950571</v>
       </c>
     </row>
     <row r="182">
@@ -3761,7 +3761,7 @@
         <v>9274.461033753299</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>9475.59839674232</v>
+        <v>9475.596788614994</v>
       </c>
     </row>
     <row r="185">
@@ -3777,7 +3777,7 @@
         <v>9183.176558191248</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>9467.853470839087</v>
+        <v>9467.850230892032</v>
       </c>
     </row>
     <row r="186">
@@ -3793,7 +3793,7 @@
         <v>9223.747665500186</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>9539.600026923705</v>
+        <v>9539.599219340089</v>
       </c>
     </row>
     <row r="187">
@@ -3809,7 +3809,7 @@
         <v>9282.57484250864</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>9579.581283733101</v>
+        <v>9579.580472764837</v>
       </c>
     </row>
     <row r="188">
@@ -3825,7 +3825,7 @@
         <v>9251.471221102423</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>9598.373108643176</v>
+        <v>9598.373919670652</v>
       </c>
     </row>
     <row r="189">
@@ -3835,13 +3835,13 @@
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>9695.799999999999</v>
+        <v>9695.809999999999</v>
       </c>
       <c r="C189" s="3" t="n">
         <v>9452.972048733616</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>9795.578321904159</v>
+        <v>9795.576672095178</v>
       </c>
     </row>
     <row r="190">
@@ -3857,7 +3857,7 @@
         <v>9642.977970039368</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>10011.83937456039</v>
+        <v>10011.84103591111</v>
       </c>
     </row>
     <row r="191">
@@ -3889,7 +3889,7 @@
         <v>9645.682229035776</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>9909.073685843539</v>
+        <v>9909.072021175945</v>
       </c>
     </row>
     <row r="193">
@@ -3905,7 +3905,7 @@
         <v>9668.673073452772</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>9937.308493340755</v>
+        <v>9937.309335498461</v>
       </c>
     </row>
     <row r="194">
@@ -3953,7 +3953,7 @@
         <v>9611.197510059461</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>10071.42477866841</v>
+        <v>10071.42393467451</v>
       </c>
     </row>
     <row r="197">
@@ -3969,7 +3969,7 @@
         <v>9651.091778794709</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>9918.365886672622</v>
+        <v>9918.367562848063</v>
       </c>
     </row>
     <row r="198">
@@ -3985,7 +3985,7 @@
         <v>9664.615137308983</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>10137.29456417519</v>
+        <v>10137.29623227818</v>
       </c>
     </row>
     <row r="199">
@@ -4001,7 +4001,7 @@
         <v>9794.442267991139</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>10115.9971094026</v>
+        <v>10115.99793643099</v>
       </c>
     </row>
     <row r="200">
@@ -4033,7 +4033,7 @@
         <v>9815.403628453179</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>10134.35003022628</v>
+        <v>10134.35085808392</v>
       </c>
     </row>
     <row r="202">
@@ -4065,7 +4065,7 @@
         <v>9799.850785983952</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>10022.82546591498</v>
+        <v>10022.82463837044</v>
       </c>
     </row>
     <row r="204">
@@ -4081,7 +4081,7 @@
         <v>9898.573263493772</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>10379.91862629731</v>
+        <v>10379.91779095969</v>
       </c>
     </row>
     <row r="205">
@@ -4113,7 +4113,7 @@
         <v>10121.7122901607</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>10597.65956234734</v>
+        <v>10597.66039254042</v>
       </c>
     </row>
     <row r="207">
@@ -4129,7 +4129,7 @@
         <v>10139.96939162633</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>10549.79989761056</v>
+        <v>10549.79823981368</v>
       </c>
     </row>
     <row r="208">
@@ -4145,7 +4145,7 @@
         <v>10141.99784381517</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>10425.9590275189</v>
+        <v>10425.95655369379</v>
       </c>
     </row>
     <row r="209">
@@ -4161,7 +4161,7 @@
         <v>10241.39612813256</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>10699.40366016096</v>
+        <v>10699.40449334934</v>
       </c>
     </row>
     <row r="210">
@@ -4177,7 +4177,7 @@
         <v>10206.23457058255</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>10690.11490667557</v>
+        <v>10690.11240759238</v>
       </c>
     </row>
     <row r="211">
@@ -4193,7 +4193,7 @@
         <v>10187.30166230935</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>10578.16845908139</v>
+        <v>10578.16680768161</v>
       </c>
     </row>
     <row r="212">
@@ -4209,7 +4209,7 @@
         <v>10255.5952934544</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>10645.79460805965</v>
+        <v>10645.79544000421</v>
       </c>
     </row>
     <row r="213">
@@ -4225,7 +4225,7 @@
         <v>10149.43584576293</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>10575.6961992564</v>
+        <v>10575.69536949489</v>
       </c>
     </row>
     <row r="214">
@@ -4273,7 +4273,7 @@
         <v>10398.26894407714</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>10853.86640655896</v>
+        <v>10853.86804692485</v>
       </c>
     </row>
     <row r="217">
@@ -4289,7 +4289,7 @@
         <v>10513.21903909764</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>10962.68464033863</v>
+        <v>10962.6838153325</v>
       </c>
     </row>
     <row r="218">
@@ -4305,7 +4305,7 @@
         <v>10564.60924592445</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>11086.22502879241</v>
+        <v>11086.22669413704</v>
       </c>
     </row>
     <row r="219">
@@ -4337,7 +4337,7 @@
         <v>10557.17124397668</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>11019.78208401043</v>
+        <v>11019.78042164439</v>
       </c>
     </row>
     <row r="221">
@@ -4353,7 +4353,7 @@
         <v>10492.2576786356</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>10968.98184772008</v>
+        <v>10968.98268634091</v>
       </c>
     </row>
     <row r="222">
@@ -4385,7 +4385,7 @@
         <v>10354.31777096422</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>10876.76204096597</v>
+        <v>10876.76118965272</v>
       </c>
     </row>
     <row r="224">
@@ -4401,7 +4401,7 @@
         <v>10394.21203969947</v>
       </c>
       <c r="D224" s="3" t="n">
-        <v>10881.53525718162</v>
+        <v>10881.53610615094</v>
       </c>
     </row>
     <row r="225">
@@ -4417,7 +4417,7 @@
         <v>10446.27805333385</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>11032.73682243503</v>
+        <v>11032.73852000141</v>
       </c>
     </row>
     <row r="226">
@@ -4433,7 +4433,7 @@
         <v>10297.51801437849</v>
       </c>
       <c r="D226" s="3" t="n">
-        <v>10656.95161914305</v>
+        <v>10656.95246774003</v>
       </c>
     </row>
     <row r="227">
@@ -4449,7 +4449,7 @@
         <v>10112.24583602409</v>
       </c>
       <c r="D227" s="3" t="n">
-        <v>10621.21510897267</v>
+        <v>10621.21596035357</v>
       </c>
     </row>
     <row r="228">
@@ -4465,7 +4465,7 @@
         <v>10012.8475517067</v>
       </c>
       <c r="D228" s="3" t="n">
-        <v>10425.58489322406</v>
+        <v>10425.58658317506</v>
       </c>
     </row>
     <row r="229">
@@ -4491,13 +4491,13 @@
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>10177.35</v>
+        <v>10177.36</v>
       </c>
       <c r="C230" s="3" t="n">
         <v>9858.678994758526</v>
       </c>
       <c r="D230" s="3" t="n">
-        <v>10352.84365399511</v>
+        <v>10352.84196825807</v>
       </c>
     </row>
     <row r="231">
@@ -4513,7 +4513,7 @@
         <v>9993.237804859804</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>10332.94043981243</v>
+        <v>10332.93958959929</v>
       </c>
     </row>
     <row r="232">
@@ -4529,7 +4529,7 @@
         <v>9931.706368854942</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>10377.67499893279</v>
+        <v>10377.6741450388</v>
       </c>
     </row>
     <row r="233">
@@ -4545,7 +4545,7 @@
         <v>9919.534623955815</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>10294.05370660607</v>
+        <v>10294.05285638447</v>
       </c>
     </row>
     <row r="234">
@@ -4561,7 +4561,7 @@
         <v>9878.964548412994</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>10536.45090734931</v>
+        <v>10536.45176223335</v>
       </c>
     </row>
     <row r="235">
@@ -4577,7 +4577,7 @@
         <v>10022.3140058433</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>10501.60748495645</v>
+        <v>10501.60663843253</v>
       </c>
     </row>
     <row r="236">
@@ -4625,7 +4625,7 @@
         <v>9990.533545863396</v>
       </c>
       <c r="D238" s="3" t="n">
-        <v>10174.40970046597</v>
+        <v>10174.41137114121</v>
       </c>
     </row>
     <row r="239">
@@ -4657,7 +4657,7 @@
         <v>9858.678994758526</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>10244.46467542002</v>
+        <v>10244.46552293397</v>
       </c>
     </row>
     <row r="241">
@@ -4689,7 +4689,7 @@
         <v>9701.129340240252</v>
       </c>
       <c r="D242" s="3" t="n">
-        <v>10205.97435747246</v>
+        <v>10205.97351319928</v>
       </c>
     </row>
     <row r="243">
@@ -4705,7 +4705,7 @@
         <v>9688.957595341122</v>
       </c>
       <c r="D243" s="3" t="n">
-        <v>10081.54271664224</v>
+        <v>10081.54187297837</v>
       </c>
     </row>
     <row r="244">
@@ -4721,7 +4721,7 @@
         <v>9809.318271886674</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>9964.101097024344</v>
+        <v>9964.098551106321</v>
       </c>
     </row>
     <row r="245">
@@ -4785,7 +4785,7 @@
         <v>9500.304319416631</v>
       </c>
       <c r="D248" s="3" t="n">
-        <v>9940.209175008582</v>
+        <v>9940.208295763601</v>
       </c>
     </row>
     <row r="249">
@@ -4801,7 +4801,7 @@
         <v>9535.465876966637</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>10164.86363423166</v>
+        <v>10164.8645159982</v>
       </c>
     </row>
     <row r="250">
@@ -4817,7 +4817,7 @@
         <v>9306.241493733207</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>9837.729948812797</v>
+        <v>9837.730820408467</v>
       </c>
     </row>
     <row r="251">
@@ -4833,7 +4833,7 @@
         <v>9371.830865881857</v>
       </c>
       <c r="D251" s="3" t="n">
-        <v>9565.998223350693</v>
+        <v>9565.999945015628</v>
       </c>
     </row>
     <row r="252">
@@ -4849,7 +4849,7 @@
         <v>9354.926409797486</v>
       </c>
       <c r="D252" s="3" t="n">
-        <v>9855.518194186188</v>
+        <v>9855.516466039571</v>
       </c>
     </row>
     <row r="253">
@@ -4881,7 +4881,7 @@
         <v>9529.379488634013</v>
       </c>
       <c r="D254" s="3" t="n">
-        <v>9942.677172824788</v>
+        <v>9942.678867801886</v>
       </c>
     </row>
     <row r="255">
@@ -4913,7 +4913,7 @@
         <v>9416.457845802348</v>
       </c>
       <c r="D256" s="3" t="n">
-        <v>9756.454365856032</v>
+        <v>9756.455230250909</v>
       </c>
     </row>
     <row r="257">
@@ -4929,7 +4929,7 @@
         <v>9376.5635770671</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>9735.699161277533</v>
+        <v>9735.701768855266</v>
       </c>
     </row>
     <row r="258">
@@ -4993,7 +4993,7 @@
         <v>9322.469111243889</v>
       </c>
       <c r="D261" s="3" t="n">
-        <v>9654.877249392663</v>
+        <v>9654.874646181019</v>
       </c>
     </row>
     <row r="262">
@@ -5025,7 +5025,7 @@
         <v>9429.305397509048</v>
       </c>
       <c r="D263" s="3" t="n">
-        <v>9922.608862255773</v>
+        <v>9922.60714353547</v>
       </c>
     </row>
     <row r="264">
@@ -5041,7 +5041,7 @@
         <v>9467.171214055461</v>
       </c>
       <c r="D264" s="3" t="n">
-        <v>9834.830211135126</v>
+        <v>9834.827637623879</v>
       </c>
     </row>
     <row r="265">
@@ -5057,7 +5057,7 @@
         <v>9482.724056524688</v>
       </c>
       <c r="D265" s="3" t="n">
-        <v>9849.614404104597</v>
+        <v>9849.616136888239</v>
       </c>
     </row>
     <row r="266">
@@ -5073,7 +5073,7 @@
         <v>9442.15294921575</v>
       </c>
       <c r="D266" s="3" t="n">
-        <v>10076.16710693965</v>
+        <v>10076.16537635622</v>
       </c>
     </row>
     <row r="267">
@@ -5089,7 +5089,7 @@
         <v>9540.198588151879</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>10115.48099965996</v>
+        <v>10115.48271599406</v>
       </c>
     </row>
     <row r="268">
@@ -5121,7 +5121,7 @@
         <v>9662.586685120148</v>
       </c>
       <c r="D269" s="3" t="n">
-        <v>10093.48351950802</v>
+        <v>10093.48606722852</v>
       </c>
     </row>
     <row r="270">
@@ -5153,7 +5153,7 @@
         <v>9711.948439758116</v>
       </c>
       <c r="D271" s="3" t="n">
-        <v>10274.23558217106</v>
+        <v>10274.23473327788</v>
       </c>
     </row>
     <row r="272">
@@ -5169,7 +5169,7 @@
         <v>9782.946329899582</v>
       </c>
       <c r="D272" s="3" t="n">
-        <v>10213.13830888429</v>
+        <v>10213.13915886907</v>
       </c>
     </row>
     <row r="273">
@@ -5185,7 +5185,7 @@
         <v>9799.850785983952</v>
       </c>
       <c r="D273" s="3" t="n">
-        <v>10239.1023511578</v>
+        <v>10239.10320704869</v>
       </c>
     </row>
     <row r="274">
@@ -5201,7 +5201,7 @@
         <v>9735.614059216565</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>9990.62685237243</v>
+        <v>9990.625995753851</v>
       </c>
     </row>
     <row r="275">
@@ -5217,7 +5217,7 @@
         <v>9631.483063713931</v>
       </c>
       <c r="D275" s="3" t="n">
-        <v>9951.730492206121</v>
+        <v>9951.728767884111</v>
       </c>
     </row>
     <row r="276">
@@ -5233,7 +5233,7 @@
         <v>9548.989235480909</v>
       </c>
       <c r="D276" s="3" t="n">
-        <v>10162.03816037272</v>
+        <v>10162.03902826213</v>
       </c>
     </row>
     <row r="277">
@@ -5249,7 +5249,7 @@
         <v>9586.855052027322</v>
       </c>
       <c r="D277" s="3" t="n">
-        <v>10074.10154699903</v>
+        <v>10074.09984254498</v>
       </c>
     </row>
     <row r="278">
@@ -5265,7 +5265,7 @@
         <v>9678.139527589374</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>10037.64691193683</v>
+        <v>10037.64860110924</v>
       </c>
     </row>
     <row r="279">
@@ -5281,7 +5281,7 @@
         <v>9572.655886705477</v>
       </c>
       <c r="D279" s="3" t="n">
-        <v>9770.179032464011</v>
+        <v>9770.179871837936</v>
       </c>
     </row>
     <row r="280">
@@ -5297,7 +5297,7 @@
         <v>9795.118074798711</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>10370.16099083059</v>
+        <v>10370.16183534063</v>
       </c>
     </row>
     <row r="281">
@@ -5313,7 +5313,7 @@
         <v>9765.366067007637</v>
       </c>
       <c r="D281" s="3" t="n">
-        <v>10293.12494968677</v>
+        <v>10293.12661008982</v>
       </c>
     </row>
     <row r="282">
@@ -5345,7 +5345,7 @@
         <v>9853.945251807165</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>10165.88448652562</v>
+        <v>10165.88612648541</v>
       </c>
     </row>
     <row r="284">
@@ -5361,7 +5361,7 @@
         <v>9720.73805532103</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>10050.75002068898</v>
+        <v>10050.75083761425</v>
       </c>
     </row>
     <row r="285">
@@ -5377,7 +5377,7 @@
         <v>9678.139527589374</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>9984.190182747618</v>
+        <v>9984.189368741652</v>
       </c>
     </row>
     <row r="286">
@@ -5409,7 +5409,7 @@
         <v>9780.917877710746</v>
       </c>
       <c r="D287" s="3" t="n">
-        <v>10055.07004817834</v>
+        <v>10055.06922912078</v>
       </c>
     </row>
     <row r="288">
@@ -5425,7 +5425,7 @@
         <v>9849.212540621922</v>
       </c>
       <c r="D288" s="3" t="n">
-        <v>10275.12887829121</v>
+        <v>10275.12640068371</v>
       </c>
     </row>
     <row r="289">
@@ -5441,7 +5441,7 @@
         <v>9886.402550360763</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>10274.30060531822</v>
+        <v>10274.29896405548</v>
       </c>
     </row>
     <row r="290">
@@ -5457,7 +5457,7 @@
         <v>9902.630167871443</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>10170.585995001</v>
+        <v>10170.5843703061</v>
       </c>
     </row>
     <row r="291">
@@ -5489,7 +5489,7 @@
         <v>9814.050983071917</v>
       </c>
       <c r="D292" s="3" t="n">
-        <v>10053.06195030355</v>
+        <v>10053.06276646731</v>
       </c>
     </row>
     <row r="293">
@@ -5505,7 +5505,7 @@
         <v>9755.899612871035</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>10057.1222247029</v>
+        <v>10057.12304260121</v>
       </c>
     </row>
     <row r="294">
@@ -5521,7 +5521,7 @@
         <v>9814.726789879489</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>10395.07014342672</v>
+        <v>10395.07096299194</v>
       </c>
     </row>
     <row r="295">
@@ -5537,7 +5537,7 @@
         <v>9916.153526385717</v>
       </c>
       <c r="D295" s="3" t="n">
-        <v>10286.93428161347</v>
+        <v>10286.93346997671</v>
       </c>
     </row>
     <row r="296">
@@ -5553,7 +5553,7 @@
         <v>9873.554998654061</v>
       </c>
       <c r="D296" s="3" t="n">
-        <v>10174.47876332082</v>
+        <v>10174.47956701212</v>
       </c>
     </row>
     <row r="297">
@@ -5569,7 +5569,7 @@
         <v>9787.00426604337</v>
       </c>
       <c r="D297" s="3" t="n">
-        <v>9976.509052665344</v>
+        <v>9976.509855155078</v>
       </c>
     </row>
     <row r="298">
@@ -5585,7 +5585,7 @@
         <v>9650.415971987137</v>
       </c>
       <c r="D298" s="3" t="n">
-        <v>9876.971576910453</v>
+        <v>9876.97077080756</v>
       </c>
     </row>
     <row r="299">
@@ -5601,7 +5601,7 @@
         <v>9598.349958352761</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>9886.458707113567</v>
+        <v>9886.457090609259</v>
       </c>
     </row>
     <row r="300">
@@ -5665,7 +5665,7 @@
         <v>9764.013421626374</v>
       </c>
       <c r="D303" s="3" t="n">
-        <v>10038.2598135806</v>
+        <v>10038.26061625655</v>
       </c>
     </row>
     <row r="304">
@@ -5697,7 +5697,7 @@
         <v>9407.668230239435</v>
       </c>
       <c r="D305" s="3" t="n">
-        <v>9607.420043964476</v>
+        <v>9607.419251408677</v>
       </c>
     </row>
     <row r="306">
@@ -5713,7 +5713,7 @@
         <v>9331.935565380491</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>9525.922816380602</v>
+        <v>9525.922021159347</v>
       </c>
     </row>
     <row r="307">
@@ -5729,7 +5729,7 @@
         <v>9295.422394215342</v>
       </c>
       <c r="D307" s="3" t="n">
-        <v>9494.691948134747</v>
+        <v>9494.692747527537</v>
       </c>
     </row>
     <row r="308">
@@ -5745,7 +5745,7 @@
         <v>9260.260836665337</v>
       </c>
       <c r="D308" s="3" t="n">
-        <v>9481.217141289997</v>
+        <v>9481.217938457385</v>
       </c>
     </row>
     <row r="309">
@@ -5777,7 +5777,7 @@
         <v>9284.603294697476</v>
       </c>
       <c r="D310" s="3" t="n">
-        <v>9489.730323575113</v>
+        <v>9489.727931057545</v>
       </c>
     </row>
     <row r="311">
@@ -5793,7 +5793,7 @@
         <v>9306.917300540779</v>
       </c>
       <c r="D311" s="3" t="n">
-        <v>9550.3927141533</v>
+        <v>9550.391118126272</v>
       </c>
     </row>
     <row r="312">
@@ -5809,7 +5809,7 @@
         <v>9306.917300540779</v>
       </c>
       <c r="D312" s="3" t="n">
-        <v>9492.671811151526</v>
+        <v>9492.670224770607</v>
       </c>
     </row>
     <row r="313">
@@ -5825,7 +5825,7 @@
         <v>9308.269945922042</v>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9479.746406807999</v>
+        <v>9479.748792547942</v>
       </c>
     </row>
     <row r="314">
@@ -5857,7 +5857,7 @@
         <v>9325.850208813987</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>9540.289645570778</v>
+        <v>9540.290441638228</v>
       </c>
     </row>
     <row r="316">
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="B317" s="3" t="n">
-        <v>9916.610000000001</v>
+        <v>9916.620000000001</v>
       </c>
       <c r="C317" s="3" t="n">
         <v>9447.562498974683</v>
@@ -5905,7 +5905,7 @@
         <v>9353.573764416224</v>
       </c>
       <c r="D318" s="3" t="n">
-        <v>9432.098652311301</v>
+        <v>9432.097067402683</v>
       </c>
     </row>
     <row r="319">
@@ -5921,7 +5921,7 @@
         <v>9438.096044838079</v>
       </c>
       <c r="D319" s="3" t="n">
-        <v>9622.845892093464</v>
+        <v>9622.845089806815</v>
       </c>
     </row>
     <row r="320">
@@ -5937,7 +5937,7 @@
         <v>9384.001579014868</v>
       </c>
       <c r="D320" s="3" t="n">
-        <v>9459.640181371267</v>
+        <v>9459.641776941582</v>
       </c>
     </row>
     <row r="321">
@@ -5953,7 +5953,7 @@
         <v>9473.933409195657</v>
       </c>
       <c r="D321" s="3" t="n">
-        <v>9753.954637614301</v>
+        <v>9753.955441779444</v>
       </c>
     </row>
     <row r="322">
@@ -5969,7 +5969,7 @@
         <v>9530.056327207703</v>
       </c>
       <c r="D322" s="3" t="n">
-        <v>9625.743473510314</v>
+        <v>9625.745855645426</v>
       </c>
     </row>
     <row r="323">
@@ -5979,13 +5979,13 @@
         </is>
       </c>
       <c r="B323" s="3" t="n">
-        <v>9895.719999999999</v>
+        <v>9895.73</v>
       </c>
       <c r="C323" s="3" t="n">
         <v>9429.305397509048</v>
       </c>
       <c r="D323" s="3" t="n">
-        <v>9623.83519147078</v>
+        <v>9623.835979829671</v>
       </c>
     </row>
     <row r="324">
@@ -6001,7 +6001,7 @@
         <v>9513.151871123333</v>
       </c>
       <c r="D324" s="3" t="n">
-        <v>9740.329860721535</v>
+        <v>9740.328284849827</v>
       </c>
     </row>
     <row r="325">
@@ -6017,7 +6017,7 @@
         <v>9540.198588151879</v>
       </c>
       <c r="D325" s="3" t="n">
-        <v>9751.223939046202</v>
+        <v>9751.223153090401</v>
       </c>
     </row>
     <row r="326">
@@ -6065,7 +6065,7 @@
         <v>9647.034874417039</v>
       </c>
       <c r="D328" s="3" t="n">
-        <v>9713.263282769478</v>
+        <v>9713.264064071385</v>
       </c>
     </row>
     <row r="329">
@@ -6081,7 +6081,7 @@
         <v>9592.264601786255</v>
       </c>
       <c r="D329" s="3" t="n">
-        <v>9592.524538766211</v>
+        <v>9592.525322733529</v>
       </c>
     </row>
     <row r="330">
@@ -6097,7 +6097,7 @@
         <v>9449.590951163518</v>
       </c>
       <c r="D330" s="3" t="n">
-        <v>9518.683206094103</v>
+        <v>9518.682422456803</v>
       </c>
     </row>
     <row r="331">
@@ -6113,7 +6113,7 @@
         <v>9517.884582308574</v>
       </c>
       <c r="D331" s="3" t="n">
-        <v>9663.76059855628</v>
+        <v>9663.762160618659</v>
       </c>
     </row>
     <row r="332">
@@ -6129,7 +6129,7 @@
         <v>9660.558232931313</v>
       </c>
       <c r="D332" s="3" t="n">
-        <v>9751.633990929009</v>
+        <v>9751.634769717781</v>
       </c>
     </row>
     <row r="333">
@@ -6145,7 +6145,7 @@
         <v>9640.273711042963</v>
       </c>
       <c r="D333" s="3" t="n">
-        <v>9732.911624640325</v>
+        <v>9732.91318089798</v>
       </c>
     </row>
     <row r="334">
@@ -6161,7 +6161,7 @@
         <v>9563.865239376446</v>
       </c>
       <c r="D334" s="3" t="n">
-        <v>9724.173710359328</v>
+        <v>9724.172933220538</v>
       </c>
     </row>
     <row r="335">
@@ -6225,7 +6225,7 @@
         <v>9708.567342188018</v>
       </c>
       <c r="D338" s="3" t="n">
-        <v>9907.142576217997</v>
+        <v>9907.143356039142</v>
       </c>
     </row>
     <row r="339">
@@ -6257,7 +6257,7 @@
         <v>9931.706368854942</v>
       </c>
       <c r="D340" s="3" t="n">
-        <v>10008.61372209052</v>
+        <v>10008.61218541308</v>
       </c>
     </row>
     <row r="341">
@@ -6305,7 +6305,7 @@
         <v>9953.343536124556</v>
       </c>
       <c r="D343" s="3" t="n">
-        <v>10232.52943922538</v>
+        <v>10232.53022776197</v>
       </c>
     </row>
     <row r="344">
@@ -6321,7 +6321,7 @@
         <v>9939.820177610283</v>
       </c>
       <c r="D344" s="3" t="n">
-        <v>10121.6147965904</v>
+        <v>10121.61637381584</v>
       </c>
     </row>
     <row r="345">
@@ -6337,7 +6337,7 @@
         <v>9954.696181505818</v>
       </c>
       <c r="D345" s="3" t="n">
-        <v>10046.89810073858</v>
+        <v>10046.89731110196</v>
       </c>
     </row>
     <row r="346">
@@ -6353,7 +6353,7 @@
         <v>9903.982813252705</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>10045.52217485154</v>
+        <v>10045.52296254195</v>
       </c>
     </row>
     <row r="347">
@@ -6369,7 +6369,7 @@
         <v>9972.953282971454</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>10224.91590490751</v>
+        <v>10224.9151124532</v>
       </c>
     </row>
     <row r="348">
@@ -6385,7 +6385,7 @@
         <v>9928.325271284844</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>10170.01071441012</v>
+        <v>10170.00992584812</v>
       </c>
     </row>
     <row r="349">
@@ -6417,7 +6417,7 @@
         <v>10005.40954975893</v>
       </c>
       <c r="D350" s="3" t="n">
-        <v>10098.93930254346</v>
+        <v>10098.94009395694</v>
       </c>
     </row>
     <row r="351">
@@ -6433,7 +6433,7 @@
         <v>9885.0499049795</v>
       </c>
       <c r="D351" s="3" t="n">
-        <v>10098.26967269775</v>
+        <v>10098.26887935498</v>
       </c>
     </row>
     <row r="352">
@@ -6449,7 +6449,7 @@
         <v>9904.658620060278</v>
       </c>
       <c r="D352" s="3" t="n">
-        <v>10080.60652671007</v>
+        <v>10080.60573475496</v>
       </c>
     </row>
     <row r="353">
@@ -6465,7 +6465,7 @@
         <v>9808.641433312983</v>
       </c>
       <c r="D353" s="3" t="n">
-        <v>9880.067689614305</v>
+        <v>9880.066897523891</v>
       </c>
     </row>
     <row r="354">
@@ -6497,7 +6497,7 @@
         <v>9798.499172368807</v>
       </c>
       <c r="D355" s="3" t="n">
-        <v>9990.774382236053</v>
+        <v>9990.775180063447</v>
       </c>
     </row>
     <row r="356">
@@ -6513,7 +6513,7 @@
         <v>9750.490063112102</v>
       </c>
       <c r="D356" s="3" t="n">
-        <v>9891.282256735085</v>
+        <v>9891.283055146336</v>
       </c>
     </row>
     <row r="357">
@@ -6545,7 +6545,7 @@
         <v>9771.451423574143</v>
       </c>
       <c r="D358" s="3" t="n">
-        <v>9876.02904491735</v>
+        <v>9876.029842338628</v>
       </c>
     </row>
     <row r="359">
@@ -6561,7 +6561,7 @@
         <v>9667.320428071509</v>
       </c>
       <c r="D359" s="3" t="n">
-        <v>9869.670004662679</v>
+        <v>9869.670804639369</v>
       </c>
     </row>
     <row r="360">
@@ -6577,7 +6577,7 @@
         <v>9715.328505562096</v>
       </c>
       <c r="D360" s="3" t="n">
-        <v>9861.002707646752</v>
+        <v>9861.003500752573</v>
       </c>
     </row>
     <row r="361">
@@ -6593,7 +6593,7 @@
         <v>9875.583450842896</v>
       </c>
       <c r="D361" s="3" t="n">
-        <v>10084.57082822543</v>
+        <v>10084.5716265098</v>
       </c>
     </row>
     <row r="362">
@@ -6625,7 +6625,7 @@
         <v>9855.973703996</v>
       </c>
       <c r="D363" s="3" t="n">
-        <v>9854.50082923829</v>
+        <v>9854.499245903618</v>
       </c>
     </row>
     <row r="364">
@@ -6641,7 +6641,7 @@
         <v>9843.127184055416</v>
       </c>
       <c r="D364" s="3" t="n">
-        <v>9999.293781040766</v>
+        <v>9999.292979050264</v>
       </c>
     </row>
     <row r="365">
@@ -6657,7 +6657,7 @@
         <v>9841.097700100463</v>
       </c>
       <c r="D365" s="3" t="n">
-        <v>9815.946910665094</v>
+        <v>9815.94610858152</v>
       </c>
     </row>
     <row r="366">
@@ -6673,7 +6673,7 @@
         <v>9632.158870521504</v>
       </c>
       <c r="D366" s="3" t="n">
-        <v>9642.160790656708</v>
+        <v>9642.159191820347</v>
       </c>
     </row>
     <row r="367">
@@ -6689,7 +6689,7 @@
         <v>9405.639778050599</v>
       </c>
       <c r="D367" s="3" t="n">
-        <v>9539.242979042729</v>
+        <v>9539.244563071361</v>
       </c>
     </row>
     <row r="368">
@@ -6705,7 +6705,7 @@
         <v>9544.93233110324</v>
       </c>
       <c r="D368" s="3" t="n">
-        <v>9659.526607227719</v>
+        <v>9659.527396187377</v>
       </c>
     </row>
     <row r="369">
@@ -6769,7 +6769,7 @@
         <v>9513.827677930905</v>
       </c>
       <c r="D372" s="3" t="n">
-        <v>9788.271440572373</v>
+        <v>9788.270648202722</v>
       </c>
     </row>
     <row r="373">
@@ -6801,7 +6801,7 @@
         <v>9609.169057870628</v>
       </c>
       <c r="D374" s="3" t="n">
-        <v>9661.455165587191</v>
+        <v>9661.4543802322</v>
       </c>
     </row>
     <row r="375">
@@ -6817,7 +6817,7 @@
         <v>9532.760586204111</v>
       </c>
       <c r="D375" s="3" t="n">
-        <v>9601.88030192652</v>
+        <v>9601.879523518484</v>
       </c>
     </row>
     <row r="376">
@@ -6849,7 +6849,7 @@
         <v>9580.092856887126</v>
       </c>
       <c r="D377" s="3" t="n">
-        <v>9765.797622633041</v>
+        <v>9765.798407700344</v>
       </c>
     </row>
     <row r="378">
@@ -6865,7 +6865,7 @@
         <v>9533.437424777801</v>
       </c>
       <c r="D378" s="3" t="n">
-        <v>9717.832831405047</v>
+        <v>9717.832048436192</v>
       </c>
     </row>
     <row r="379">
@@ -6881,7 +6881,7 @@
         <v>9628.777772951405</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>9829.566652378069</v>
+        <v>9829.564310503096</v>
       </c>
     </row>
     <row r="380">
@@ -6897,7 +6897,7 @@
         <v>9678.815334396946</v>
       </c>
       <c r="D380" s="3" t="n">
-        <v>9883.368765882089</v>
+        <v>9883.370326539754</v>
       </c>
     </row>
     <row r="381">
@@ -6913,7 +6913,7 @@
         <v>9786.32742746968</v>
       </c>
       <c r="D381" s="3" t="n">
-        <v>9966.592333787039</v>
+        <v>9966.591557824388</v>
       </c>
     </row>
     <row r="382">
@@ -6929,7 +6929,7 @@
         <v>9810.669885501818</v>
       </c>
       <c r="D382" s="3" t="n">
-        <v>10098.39304765339</v>
+        <v>10098.39226441377</v>
       </c>
     </row>
     <row r="383">
@@ -6961,7 +6961,7 @@
         <v>9732.909800220159</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>9872.804833434546</v>
+        <v>9872.804061398125</v>
       </c>
     </row>
     <row r="385">
@@ -6977,7 +6977,7 @@
         <v>9741.023608975498</v>
       </c>
       <c r="D385" s="3" t="n">
-        <v>9962.917182067822</v>
+        <v>9962.916406012104</v>
       </c>
     </row>
     <row r="386">
@@ -6993,7 +6993,7 @@
         <v>9741.023608975498</v>
       </c>
       <c r="D386" s="3" t="n">
-        <v>9947.600524953972</v>
+        <v>9947.599750091334</v>
       </c>
     </row>
     <row r="387">
@@ -7009,7 +7009,7 @@
         <v>9741.023608975498</v>
       </c>
       <c r="D387" s="3" t="n">
-        <v>9963.790258526613</v>
+        <v>9963.791033854592</v>
       </c>
     </row>
     <row r="388">
@@ -7025,7 +7025,7 @@
         <v>9807.965626505411</v>
       </c>
       <c r="D388" s="3" t="n">
-        <v>10007.03900545373</v>
+        <v>10007.03667000117</v>
       </c>
     </row>
     <row r="389">
@@ -7041,7 +7041,7 @@
         <v>9766.718712388902</v>
       </c>
       <c r="D389" s="3" t="n">
-        <v>9922.269743753153</v>
+        <v>9922.267418606831</v>
       </c>
     </row>
     <row r="390">
@@ -7057,7 +7057,7 @@
         <v>9750.490063112102</v>
       </c>
       <c r="D390" s="3" t="n">
-        <v>9978.765026403382</v>
+        <v>9978.764257159297</v>
       </c>
     </row>
     <row r="391">
@@ -7073,7 +7073,7 @@
         <v>9824.193244016093</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>9905.114247109786</v>
+        <v>9905.115012546172</v>
       </c>
     </row>
     <row r="392">
@@ -7089,7 +7089,7 @@
         <v>9867.468610321437</v>
       </c>
       <c r="D392" s="3" t="n">
-        <v>10002.19672933537</v>
+        <v>10002.19595916047</v>
       </c>
     </row>
     <row r="393">
@@ -7105,7 +7105,7 @@
         <v>9883.697259598237</v>
       </c>
       <c r="D393" s="3" t="n">
-        <v>10064.8002981139</v>
+        <v>10064.79874913332</v>
       </c>
     </row>
     <row r="394">
@@ -7121,7 +7121,7 @@
         <v>9870.849707891535</v>
       </c>
       <c r="D394" s="3" t="n">
-        <v>10017.2518743632</v>
+        <v>10017.25341628684</v>
       </c>
     </row>
     <row r="395">
@@ -7137,7 +7137,7 @@
         <v>9838.393441104055</v>
       </c>
       <c r="D395" s="3" t="n">
-        <v>9983.689947023475</v>
+        <v>9983.690719618377</v>
       </c>
     </row>
     <row r="396">
@@ -7153,7 +7153,7 @@
         <v>9835.012343533957</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>9974.376602204085</v>
+        <v>9974.377373478961</v>
       </c>
     </row>
     <row r="397">
@@ -7169,7 +7169,7 @@
         <v>9791.061170421041</v>
       </c>
       <c r="D397" s="3" t="n">
-        <v>9965.393758474998</v>
+        <v>9965.392988697758</v>
       </c>
     </row>
     <row r="398">
@@ -7185,7 +7185,7 @@
         <v>9773.479875762978</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>9747.589628780886</v>
+        <v>9747.588863682939</v>
       </c>
     </row>
     <row r="399">
@@ -7227,13 +7227,13 @@
         </is>
       </c>
       <c r="B401" s="3" t="n">
-        <v>10351.28</v>
+        <v>10351.29</v>
       </c>
       <c r="C401" s="3" t="n">
         <v>9812.022530883081</v>
       </c>
       <c r="D401" s="3" t="n">
-        <v>10008.87306260646</v>
+        <v>10008.87536361178</v>
       </c>
     </row>
     <row r="402">
@@ -7249,7 +7249,7 @@
         <v>9812.022530883081</v>
       </c>
       <c r="D402" s="3" t="n">
-        <v>10017.96032378255</v>
+        <v>10017.96186073084</v>
       </c>
     </row>
     <row r="403">
@@ -7281,7 +7281,7 @@
         <v>9730.204509457633</v>
       </c>
       <c r="D404" s="3" t="n">
-        <v>9837.376585161323</v>
+        <v>9837.375048213038</v>
       </c>
     </row>
     <row r="405">
@@ -7297,7 +7297,7 @@
         <v>9667.996234879081</v>
       </c>
       <c r="D405" s="3" t="n">
-        <v>9716.504624667761</v>
+        <v>9716.503860221343</v>
       </c>
     </row>
     <row r="406">
@@ -7313,7 +7313,7 @@
         <v>9790.38433184735</v>
       </c>
       <c r="D406" s="3" t="n">
-        <v>9937.679005053407</v>
+        <v>9937.678237416992</v>
       </c>
     </row>
     <row r="407">
@@ -7329,7 +7329,7 @@
         <v>9821.488985019685</v>
       </c>
       <c r="D407" s="3" t="n">
-        <v>9944.163862829548</v>
+        <v>9944.162326964413</v>
       </c>
     </row>
     <row r="408">
@@ -7345,7 +7345,7 @@
         <v>9855.973703996</v>
       </c>
       <c r="D408" s="3" t="n">
-        <v>9920.847167688502</v>
+        <v>9920.845628675621</v>
       </c>
     </row>
     <row r="409">
@@ -7361,7 +7361,7 @@
         <v>9843.127184055416</v>
       </c>
       <c r="D409" s="3" t="n">
-        <v>9995.805256873227</v>
+        <v>9995.806028588169</v>
       </c>
     </row>
     <row r="410">
@@ -7377,7 +7377,7 @@
         <v>9870.173901083963</v>
       </c>
       <c r="D410" s="3" t="n">
-        <v>9960.756245340297</v>
+        <v>9960.759326750716</v>
       </c>
     </row>
     <row r="411">
@@ -7393,7 +7393,7 @@
         <v>9907.363910822804</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>10013.268461067</v>
+        <v>10013.26691020776</v>
       </c>
     </row>
     <row r="412">
@@ -7425,7 +7425,7 @@
         <v>9916.830364959407</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>10015.95590219979</v>
+        <v>10015.95434585751</v>
       </c>
     </row>
     <row r="414">
@@ -7441,7 +7441,7 @@
         <v>9943.877081987954</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>10145.034090259</v>
+        <v>10145.03253276604</v>
       </c>
     </row>
     <row r="415">
@@ -7457,7 +7457,7 @@
         <v>10085.87492580312</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>10268.58231381735</v>
+        <v>10268.58075239823</v>
       </c>
     </row>
     <row r="416">
@@ -7473,7 +7473,7 @@
         <v>10080.46537604419</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>10313.54109434332</v>
+        <v>10313.54266488423</v>
       </c>
     </row>
     <row r="417">
@@ -7489,7 +7489,7 @@
         <v>10116.30274040176</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>10272.59039737499</v>
+        <v>10272.59196104489</v>
       </c>
     </row>
     <row r="418">
@@ -7521,7 +7521,7 @@
         <v>9938.46753222902</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>10133.37123509976</v>
+        <v>10133.37044941478</v>
       </c>
     </row>
     <row r="420">
@@ -7601,7 +7601,7 @@
         <v>10054.77027263078</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>10335.17124597447</v>
+        <v>10335.17203434177</v>
       </c>
     </row>
     <row r="425">
@@ -7649,7 +7649,7 @@
         <v>10318.48040660665</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>10597.97645801063</v>
+        <v>10597.97724891644</v>
       </c>
     </row>
     <row r="428">
@@ -7665,7 +7665,7 @@
         <v>10332.00376512092</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>10607.98656325713</v>
+        <v>10607.98577332437</v>
       </c>
     </row>
     <row r="429">
@@ -7681,7 +7681,7 @@
         <v>10313.07085684771</v>
       </c>
       <c r="D429" s="3" t="n">
-        <v>10584.89550047372</v>
+        <v>10584.8939185775</v>
       </c>
     </row>
     <row r="430">
@@ -7697,7 +7697,7 @@
         <v>10261.00484321334</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>10639.57604950802</v>
+        <v>10639.57763001661</v>
       </c>
     </row>
     <row r="431">
@@ -7713,7 +7713,7 @@
         <v>10311.04240465888</v>
       </c>
       <c r="D431" s="3" t="n">
-        <v>10584.25673745203</v>
+        <v>10584.25595271471</v>
       </c>
     </row>
     <row r="432">
@@ -7729,7 +7729,7 @@
         <v>10340.11757387626</v>
       </c>
       <c r="D432" s="3" t="n">
-        <v>10711.82854957153</v>
+        <v>10711.82933662732</v>
       </c>
     </row>
     <row r="433">
@@ -7745,7 +7745,7 @@
         <v>10435.45895381598</v>
       </c>
       <c r="D433" s="3" t="n">
-        <v>10770.39748515262</v>
+        <v>10770.39512662528</v>
       </c>
     </row>
     <row r="434">
@@ -7825,7 +7825,7 @@
         <v>10327.27002216956</v>
       </c>
       <c r="D438" s="3" t="n">
-        <v>10663.45346703037</v>
+        <v>10663.45191789732</v>
       </c>
     </row>
     <row r="439">
@@ -7841,7 +7841,7 @@
         <v>10279.26194467897</v>
       </c>
       <c r="D439" s="3" t="n">
-        <v>10612.64030950157</v>
+        <v>10612.63953465585</v>
       </c>
     </row>
     <row r="440">
@@ -7857,7 +7857,7 @@
         <v>10252.21419588431</v>
       </c>
       <c r="D440" s="3" t="n">
-        <v>10580.92869088727</v>
+        <v>10580.9271513837</v>
       </c>
     </row>
     <row r="441">
@@ -7873,7 +7873,7 @@
         <v>10246.80464612537</v>
       </c>
       <c r="D441" s="3" t="n">
-        <v>10533.25869514347</v>
+        <v>10533.25715090133</v>
       </c>
     </row>
     <row r="442">
@@ -7889,7 +7889,7 @@
         <v>10223.13902666692</v>
       </c>
       <c r="D442" s="3" t="n">
-        <v>10540.46055196977</v>
+        <v>10540.46132778858</v>
       </c>
     </row>
     <row r="443">
@@ -7905,7 +7905,7 @@
         <v>10212.99573395663</v>
       </c>
       <c r="D443" s="3" t="n">
-        <v>10652.29730567133</v>
+        <v>10652.29808121931</v>
       </c>
     </row>
     <row r="444">
@@ -7921,7 +7921,7 @@
         <v>10310.36556608519</v>
       </c>
       <c r="D444" s="3" t="n">
-        <v>10612.20657476351</v>
+        <v>10612.20503028448</v>
       </c>
     </row>
     <row r="445">
@@ -7937,7 +7937,7 @@
         <v>10349.58402801286</v>
       </c>
       <c r="D445" s="3" t="n">
-        <v>10694.42473639255</v>
+        <v>10694.42396122528</v>
       </c>
     </row>
     <row r="446">
@@ -7953,7 +7953,7 @@
         <v>10439.51585819365</v>
       </c>
       <c r="D446" s="3" t="n">
-        <v>10868.22775595483</v>
+        <v>10868.22853453209</v>
       </c>
     </row>
     <row r="447">
@@ -7969,7 +7969,7 @@
         <v>10467.23941379589</v>
       </c>
       <c r="D447" s="3" t="n">
-        <v>10841.35285958488</v>
+        <v>10841.35441110397</v>
       </c>
     </row>
     <row r="448">
@@ -7985,7 +7985,7 @@
         <v>10478.73432012133</v>
       </c>
       <c r="D448" s="3" t="n">
-        <v>10835.79514759925</v>
+        <v>10835.79669832296</v>
       </c>
     </row>
     <row r="449">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="B450" s="3" t="n">
-        <v>10915.56</v>
+        <v>10915.55</v>
       </c>
       <c r="C450" s="3" t="n">
         <v>10298.19485295218</v>
       </c>
       <c r="D450" s="3" t="n">
-        <v>10790.83783290973</v>
+        <v>10790.83705351168</v>
       </c>
     </row>
     <row r="451">
@@ -8027,13 +8027,13 @@
         </is>
       </c>
       <c r="B451" s="3" t="n">
-        <v>10912.64</v>
+        <v>10912.63</v>
       </c>
       <c r="C451" s="3" t="n">
         <v>10298.19485295218</v>
       </c>
       <c r="D451" s="3" t="n">
-        <v>10729.93829136421</v>
+        <v>10729.93751440312</v>
       </c>
     </row>
     <row r="452">
@@ -8049,7 +8049,7 @@
         <v>10254.91948664683</v>
       </c>
       <c r="D452" s="3" t="n">
-        <v>10679.54366477674</v>
+        <v>10679.54289341721</v>
       </c>
     </row>
     <row r="453">
@@ -8065,7 +8065,7 @@
         <v>10297.51801437849</v>
       </c>
       <c r="D453" s="3" t="n">
-        <v>10712.18501270566</v>
+        <v>10712.18578152664</v>
       </c>
     </row>
     <row r="454">
@@ -8081,7 +8081,7 @@
         <v>10346.20293044277</v>
       </c>
       <c r="D454" s="3" t="n">
-        <v>10790.41371543217</v>
+        <v>10790.41448368631</v>
       </c>
     </row>
     <row r="455">
@@ -8097,7 +8097,7 @@
         <v>10346.20293044277</v>
       </c>
       <c r="D455" s="3" t="n">
-        <v>10748.71628812204</v>
+        <v>10748.71780664086</v>
       </c>
     </row>
     <row r="456">
@@ -8113,7 +8113,7 @@
         <v>10344.17447825393</v>
       </c>
       <c r="D456" s="3" t="n">
-        <v>10666.48411660729</v>
+        <v>10666.48562444769</v>
       </c>
     </row>
     <row r="457">
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B457" s="3" t="n">
-        <v>10960.08</v>
+        <v>10960.07</v>
       </c>
       <c r="C457" s="3" t="n">
         <v>10334.03221730975</v>
@@ -8145,7 +8145,7 @@
         <v>10389.47829674811</v>
       </c>
       <c r="D458" s="3" t="n">
-        <v>10769.49808242649</v>
+        <v>10769.49883539897</v>
       </c>
     </row>
     <row r="459">
@@ -8161,7 +8161,7 @@
         <v>10481.43857911774</v>
       </c>
       <c r="D459" s="3" t="n">
-        <v>10801.81613021549</v>
+        <v>10801.81537665923</v>
       </c>
     </row>
     <row r="460">
@@ -8177,7 +8177,7 @@
         <v>10490.22922644677</v>
       </c>
       <c r="D460" s="3" t="n">
-        <v>10752.80358841307</v>
+        <v>10752.80434356021</v>
       </c>
     </row>
     <row r="461">
@@ -8193,7 +8193,7 @@
         <v>10504.42942353473</v>
       </c>
       <c r="D461" s="3" t="n">
-        <v>10818.58893915824</v>
+        <v>10818.58969892534</v>
       </c>
     </row>
     <row r="462">
@@ -8203,13 +8203,13 @@
         </is>
       </c>
       <c r="B462" s="3" t="n">
-        <v>11043.47</v>
+        <v>11043.46</v>
       </c>
       <c r="C462" s="3" t="n">
         <v>10542.97104688872</v>
       </c>
       <c r="D462" s="3" t="n">
-        <v>10878.41697566441</v>
+        <v>10878.41773623543</v>
       </c>
     </row>
     <row r="463">
@@ -8241,7 +8241,7 @@
         <v>10559.87550297309</v>
       </c>
       <c r="D464" s="3" t="n">
-        <v>10983.71070727181</v>
+        <v>10983.70994154774</v>
       </c>
     </row>
     <row r="465">
@@ -8257,7 +8257,7 @@
         <v>10711.33980092485</v>
       </c>
       <c r="D465" s="3" t="n">
-        <v>10883.39758655963</v>
+        <v>10883.39835035448</v>
       </c>
     </row>
     <row r="466">
@@ -8273,7 +8273,7 @@
         <v>10677.53088875611</v>
       </c>
       <c r="D466" s="3" t="n">
-        <v>11089.6648344428</v>
+        <v>11089.66560516772</v>
       </c>
     </row>
     <row r="467">
@@ -8289,7 +8289,7 @@
         <v>10682.26359994135</v>
       </c>
       <c r="D467" s="3" t="n">
-        <v>11064.91586706821</v>
+        <v>11064.91509952485</v>
       </c>
     </row>
     <row r="468">
@@ -8321,7 +8321,7 @@
         <v>10561.90395516192</v>
       </c>
       <c r="D469" s="3" t="n">
-        <v>10895.96132157857</v>
+        <v>10895.96209026426</v>
       </c>
     </row>
     <row r="470">
@@ -8353,7 +8353,7 @@
         <v>10493.61032401686</v>
       </c>
       <c r="D471" s="3" t="n">
-        <v>10871.19626801056</v>
+        <v>10871.19704064776</v>
       </c>
     </row>
     <row r="472">
@@ -8385,7 +8385,7 @@
         <v>10442.89695576375</v>
       </c>
       <c r="D473" s="3" t="n">
-        <v>10867.22003578529</v>
+        <v>10867.22080480094</v>
       </c>
     </row>
     <row r="474">
@@ -8401,7 +8401,7 @@
         <v>10434.10630843472</v>
       </c>
       <c r="D474" s="3" t="n">
-        <v>10838.16158577452</v>
+        <v>10838.16081365345</v>
       </c>
     </row>
     <row r="475">
@@ -8417,7 +8417,7 @@
         <v>10485.49651526152</v>
       </c>
       <c r="D475" s="3" t="n">
-        <v>10823.51626477421</v>
+        <v>10823.51549397313</v>
       </c>
     </row>
     <row r="476">
@@ -8433,7 +8433,7 @@
         <v>10416.52604554278</v>
       </c>
       <c r="D476" s="3" t="n">
-        <v>10813.2865001581</v>
+        <v>10813.28727067996</v>
       </c>
     </row>
     <row r="477">
@@ -8449,7 +8449,7 @@
         <v>10482.11541769143</v>
       </c>
       <c r="D477" s="3" t="n">
-        <v>10909.99184571341</v>
+        <v>10909.98952627863</v>
       </c>
     </row>
     <row r="478">
@@ -8513,7 +8513,7 @@
         <v>10240.04348275129</v>
       </c>
       <c r="D481" s="3" t="n">
-        <v>10695.48419565746</v>
+        <v>10695.48263945065</v>
       </c>
     </row>
     <row r="482">
@@ -8545,7 +8545,7 @@
         <v>10347.55557582403</v>
       </c>
       <c r="D483" s="3" t="n">
-        <v>10712.56028742534</v>
+        <v>10712.56339306957</v>
       </c>
     </row>
     <row r="484">
@@ -8577,7 +8577,7 @@
         <v>10372.57384066374</v>
       </c>
       <c r="D485" s="3" t="n">
-        <v>10713.76944201013</v>
+        <v>10713.77022074815</v>
       </c>
     </row>
     <row r="486">
@@ -8625,7 +8625,7 @@
         <v>10543.64685369629</v>
       </c>
       <c r="D488" s="3" t="n">
-        <v>11055.59678366883</v>
+        <v>11055.59756530078</v>
       </c>
     </row>
     <row r="489">
@@ -8641,7 +8641,7 @@
         <v>10537.56149712978</v>
       </c>
       <c r="D489" s="3" t="n">
-        <v>11056.54717732944</v>
+        <v>11056.54795582209</v>
       </c>
     </row>
     <row r="490">
@@ -8657,7 +8657,7 @@
         <v>10620.73216393649</v>
       </c>
       <c r="D490" s="3" t="n">
-        <v>10976.40722669225</v>
+        <v>10976.40800067482</v>
       </c>
     </row>
     <row r="491">
@@ -8737,7 +8737,7 @@
         <v>10613.9699687963</v>
       </c>
       <c r="D495" s="3" t="n">
-        <v>11052.99161610244</v>
+        <v>11052.99398315927</v>
       </c>
     </row>
     <row r="496">
@@ -8753,7 +8753,7 @@
         <v>10634.25552245077</v>
       </c>
       <c r="D496" s="3" t="n">
-        <v>11096.94040996782</v>
+        <v>11096.94357382795</v>
       </c>
     </row>
     <row r="497">
@@ -8769,7 +8769,7 @@
         <v>10634.25552245077</v>
       </c>
       <c r="D497" s="3" t="n">
-        <v>11148.77150715107</v>
+        <v>11148.77466502059</v>
       </c>
     </row>
     <row r="498">
@@ -8779,13 +8779,13 @@
         </is>
       </c>
       <c r="B498" s="3" t="n">
-        <v>11039.65</v>
+        <v>11039.64</v>
       </c>
       <c r="C498" s="3" t="n">
         <v>10638.98823363601</v>
       </c>
       <c r="D498" s="3" t="n">
-        <v>11054.3413169785</v>
+        <v>11054.33895568413</v>
       </c>
     </row>
     <row r="499">
@@ -8801,7 +8801,7 @@
         <v>10634.93132925834</v>
       </c>
       <c r="D499" s="3" t="n">
-        <v>11064.25481998641</v>
+        <v>11064.25324621336</v>
       </c>
     </row>
     <row r="500">
@@ -8817,7 +8817,7 @@
         <v>10772.19543012214</v>
       </c>
       <c r="D500" s="3" t="n">
-        <v>11179.45393383958</v>
+        <v>11179.45551040503</v>
       </c>
     </row>
     <row r="501">
@@ -8833,7 +8833,7 @@
         <v>10722.83470725029</v>
       </c>
       <c r="D501" s="3" t="n">
-        <v>11145.53640210073</v>
+        <v>11145.53401567553</v>
       </c>
     </row>
     <row r="502">
@@ -8865,7 +8865,7 @@
         <v>10622.76061612533</v>
       </c>
       <c r="D503" s="3" t="n">
-        <v>11071.17467881485</v>
+        <v>11071.17230477745</v>
       </c>
     </row>
     <row r="504">
@@ -8875,13 +8875,13 @@
         </is>
       </c>
       <c r="B504" s="3" t="n">
-        <v>10991.02</v>
+        <v>10991.01</v>
       </c>
       <c r="C504" s="3" t="n">
         <v>10653.18843072397</v>
       </c>
       <c r="D504" s="3" t="n">
-        <v>10980.3018533315</v>
+        <v>10980.30106119875</v>
       </c>
     </row>
     <row r="505">
@@ -8897,7 +8897,7 @@
         <v>10483.46703130657</v>
       </c>
       <c r="D505" s="3" t="n">
-        <v>10828.23055568451</v>
+        <v>10828.22976139405</v>
       </c>
     </row>
     <row r="506">
@@ -8913,7 +8913,7 @@
         <v>10479.4101269289</v>
       </c>
       <c r="D506" s="3" t="n">
-        <v>10795.25036814294</v>
+        <v>10795.25195545473</v>
       </c>
     </row>
     <row r="507">
@@ -8929,7 +8929,7 @@
         <v>10474.00057716997</v>
       </c>
       <c r="D507" s="3" t="n">
-        <v>10853.93808766096</v>
+        <v>10853.93967691892</v>
       </c>
     </row>
     <row r="508">
@@ -8945,7 +8945,7 @@
         <v>10390.1551353218</v>
       </c>
       <c r="D508" s="3" t="n">
-        <v>10751.87632639876</v>
+        <v>10751.87712529239</v>
       </c>
     </row>
     <row r="509">
@@ -8961,7 +8961,7 @@
         <v>10418.55449773161</v>
       </c>
       <c r="D509" s="3" t="n">
-        <v>10778.72686544125</v>
+        <v>10778.72366316515</v>
       </c>
     </row>
     <row r="510">
@@ -8977,7 +8977,7 @@
         <v>10434.78314700841</v>
       </c>
       <c r="D510" s="3" t="n">
-        <v>10907.44327485301</v>
+        <v>10907.4448857725</v>
       </c>
     </row>
     <row r="511">
@@ -8993,7 +8993,7 @@
         <v>10452.36340990035</v>
       </c>
       <c r="D511" s="3" t="n">
-        <v>10822.10401052794</v>
+        <v>10822.10481162996</v>
       </c>
     </row>
     <row r="512">
@@ -9009,7 +9009,7 @@
         <v>10440.86850357491</v>
       </c>
       <c r="D512" s="3" t="n">
-        <v>10814.94350979462</v>
+        <v>10814.94270890411</v>
       </c>
     </row>
     <row r="513">
@@ -9025,7 +9025,7 @@
         <v>10311.71821146645</v>
       </c>
       <c r="D513" s="3" t="n">
-        <v>10756.18911635765</v>
+        <v>10756.18830901093</v>
       </c>
     </row>
     <row r="514">
@@ -9051,13 +9051,13 @@
         </is>
       </c>
       <c r="B515" s="3" t="n">
-        <v>10725.5</v>
+        <v>10725.49</v>
       </c>
       <c r="C515" s="3" t="n">
         <v>10273.17555634635</v>
       </c>
       <c r="D515" s="3" t="n">
-        <v>10803.30451451221</v>
+        <v>10803.3029038634</v>
       </c>
     </row>
     <row r="516">
@@ -9073,7 +9073,7 @@
         <v>10337.41331487985</v>
       </c>
       <c r="D516" s="3" t="n">
-        <v>10890.56623347681</v>
+        <v>10890.56703578042</v>
       </c>
     </row>
     <row r="517">
@@ -9089,7 +9089,7 @@
         <v>10407.05959140617</v>
       </c>
       <c r="D517" s="3" t="n">
-        <v>10938.67274563068</v>
+        <v>10938.67354635196</v>
       </c>
     </row>
     <row r="518">
@@ -9121,7 +9121,7 @@
         <v>10508.4863279124</v>
       </c>
       <c r="D519" s="3" t="n">
-        <v>11001.79634815467</v>
+        <v>11001.79555025114</v>
       </c>
     </row>
     <row r="520">
@@ -9153,7 +9153,7 @@
         <v>10526.06659080434</v>
       </c>
       <c r="D521" s="3" t="n">
-        <v>10950.52728383514</v>
+        <v>10950.52888994859</v>
       </c>
     </row>
     <row r="522">
@@ -9185,7 +9185,7 @@
         <v>10545.67633765124</v>
       </c>
       <c r="D523" s="3" t="n">
-        <v>11046.81384139977</v>
+        <v>11046.81303968002</v>
       </c>
     </row>
     <row r="524">
@@ -9217,7 +9217,7 @@
         <v>10375.27913142626</v>
       </c>
       <c r="D525" s="3" t="n">
-        <v>10820.03633654243</v>
+        <v>10820.03713946372</v>
       </c>
     </row>
     <row r="526">
@@ -9233,7 +9233,7 @@
         <v>10190.68275987944</v>
       </c>
       <c r="D526" s="3" t="n">
-        <v>10638.65058281431</v>
+        <v>10638.6513820971</v>
       </c>
     </row>
     <row r="527">
@@ -9265,7 +9265,7 @@
         <v>10208.26302277139</v>
       </c>
       <c r="D528" s="3" t="n">
-        <v>10616.682087183</v>
+        <v>10616.68288022113</v>
       </c>
     </row>
     <row r="529">
@@ -9281,7 +9281,7 @@
         <v>10164.31184965847</v>
       </c>
       <c r="D529" s="3" t="n">
-        <v>10537.88893708521</v>
+        <v>10537.89053431392</v>
       </c>
     </row>
     <row r="530">
@@ -9313,7 +9313,7 @@
         <v>9993.914643433494</v>
       </c>
       <c r="D531" s="3" t="n">
-        <v>10394.81814506237</v>
+        <v>10394.81654316297</v>
       </c>
     </row>
     <row r="532">
@@ -9329,7 +9329,7 @@
         <v>10006.08535656651</v>
       </c>
       <c r="D532" s="3" t="n">
-        <v>10521.09473314716</v>
+        <v>10521.09553424918</v>
       </c>
     </row>
     <row r="533">
@@ -9345,7 +9345,7 @@
         <v>10098.72247750982</v>
       </c>
       <c r="D533" s="3" t="n">
-        <v>10534.72405519215</v>
+        <v>10534.72485232569</v>
       </c>
     </row>
     <row r="534">
@@ -9361,7 +9361,7 @@
         <v>10208.26302277139</v>
       </c>
       <c r="D534" s="3" t="n">
-        <v>10683.24178927242</v>
+        <v>10683.24098943113</v>
       </c>
     </row>
     <row r="535">
@@ -9393,7 +9393,7 @@
         <v>10409.76385040258</v>
       </c>
       <c r="D536" s="3" t="n">
-        <v>10945.93393887268</v>
+        <v>10945.93473570162</v>
       </c>
     </row>
     <row r="537">
@@ -9409,7 +9409,7 @@
         <v>10382.04029480034</v>
       </c>
       <c r="D537" s="3" t="n">
-        <v>10855.54269345869</v>
+        <v>10855.54111658871</v>
       </c>
     </row>
     <row r="538">
@@ -9457,7 +9457,7 @@
         <v>10453.03921670792</v>
       </c>
       <c r="D540" s="3" t="n">
-        <v>10831.37318984308</v>
+        <v>10831.37239980886</v>
       </c>
     </row>
     <row r="541">
@@ -9473,7 +9473,7 @@
         <v>10428.02095186821</v>
       </c>
       <c r="D541" s="3" t="n">
-        <v>11044.57844768069</v>
+        <v>11044.57924088808</v>
       </c>
     </row>
     <row r="542">
@@ -9505,7 +9505,7 @@
         <v>10570.01879568338</v>
       </c>
       <c r="D543" s="3" t="n">
-        <v>11212.1215176952</v>
+        <v>11212.1223083641</v>
       </c>
     </row>
     <row r="544">
@@ -9537,7 +9537,7 @@
         <v>10547.02795126638</v>
       </c>
       <c r="D545" s="3" t="n">
-        <v>11091.28730317815</v>
+        <v>11091.28652363629</v>
       </c>
     </row>
     <row r="546">
@@ -9553,7 +9553,7 @@
         <v>10584.8937678128</v>
       </c>
       <c r="D546" s="3" t="n">
-        <v>11105.92610596163</v>
+        <v>11105.92532636052</v>
       </c>
     </row>
     <row r="547">
@@ -9569,7 +9569,7 @@
         <v>10594.3602219494</v>
       </c>
       <c r="D547" s="3" t="n">
-        <v>11136.75479348963</v>
+        <v>11136.75401769617</v>
       </c>
     </row>
     <row r="548">
@@ -9585,7 +9585,7 @@
         <v>10599.09396490076</v>
       </c>
       <c r="D548" s="3" t="n">
-        <v>11072.9713011272</v>
+        <v>11072.97207416216</v>
       </c>
     </row>
     <row r="549">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="B550" s="3" t="n">
-        <v>11133.58</v>
+        <v>11133.57</v>
       </c>
       <c r="C550" s="3" t="n">
         <v>10682.26359994135</v>
@@ -9633,7 +9633,7 @@
         <v>10661.97804628689</v>
       </c>
       <c r="D551" s="3" t="n">
-        <v>11162.98239750914</v>
+        <v>11162.98162166497</v>
       </c>
     </row>
     <row r="552">
@@ -9665,7 +9665,7 @@
         <v>10622.76061612533</v>
       </c>
       <c r="D553" s="3" t="n">
-        <v>11100.86903245516</v>
+        <v>11100.87057676501</v>
       </c>
     </row>
     <row r="554">
@@ -9681,7 +9681,7 @@
         <v>10630.1986180731</v>
       </c>
       <c r="D554" s="3" t="n">
-        <v>11045.16599512972</v>
+        <v>11045.16522630874</v>
       </c>
     </row>
     <row r="555">
@@ -9713,7 +9713,7 @@
         <v>10798.56634034312</v>
       </c>
       <c r="D556" s="3" t="n">
-        <v>11270.88197249625</v>
+        <v>11270.8811956367</v>
       </c>
     </row>
     <row r="557">
@@ -9729,7 +9729,7 @@
         <v>10786.39562721011</v>
       </c>
       <c r="D557" s="3" t="n">
-        <v>11215.7447396641</v>
+        <v>11215.74629394168</v>
       </c>
     </row>
     <row r="558">
@@ -9745,7 +9745,7 @@
         <v>10840.49009303332</v>
       </c>
       <c r="D558" s="3" t="n">
-        <v>11265.67135489948</v>
+        <v>11265.67057414759</v>
       </c>
     </row>
     <row r="559">
@@ -9761,7 +9761,7 @@
         <v>10856.717710544</v>
       </c>
       <c r="D559" s="3" t="n">
-        <v>11266.11519513359</v>
+        <v>11266.11676301749</v>
       </c>
     </row>
     <row r="560">
@@ -9841,7 +9841,7 @@
         <v>11012.91471968101</v>
       </c>
       <c r="D564" s="3" t="n">
-        <v>11650.64344299973</v>
+        <v>11650.64422657777</v>
       </c>
     </row>
     <row r="565">
@@ -9873,7 +9873,7 @@
         <v>11085.94209377743</v>
       </c>
       <c r="D566" s="3" t="n">
-        <v>11461.88528927238</v>
+        <v>11461.88759832465</v>
       </c>
     </row>
     <row r="567">
@@ -9889,7 +9889,7 @@
         <v>11090.67583672879</v>
       </c>
       <c r="D567" s="3" t="n">
-        <v>11630.39599279804</v>
+        <v>11630.39521616697</v>
       </c>
     </row>
     <row r="568">
@@ -9905,7 +9905,7 @@
         <v>11102.17074305423</v>
       </c>
       <c r="D568" s="3" t="n">
-        <v>11670.52136905753</v>
+        <v>11670.5229182582</v>
       </c>
     </row>
     <row r="569">
@@ -9921,7 +9921,7 @@
         <v>11136.65546203054</v>
       </c>
       <c r="D569" s="3" t="n">
-        <v>11448.83076700386</v>
+        <v>11448.83153756805</v>
       </c>
     </row>
     <row r="570">
@@ -9937,7 +9937,7 @@
         <v>11052.81002018238</v>
       </c>
       <c r="D570" s="3" t="n">
-        <v>11594.69980866593</v>
+        <v>11594.70135476969</v>
       </c>
     </row>
     <row r="571">
@@ -9985,7 +9985,7 @@
         <v>11094.73274110646</v>
       </c>
       <c r="D573" s="3" t="n">
-        <v>11588.13891469659</v>
+        <v>11588.13814687401</v>
       </c>
     </row>
     <row r="574">
@@ -10001,7 +10001,7 @@
         <v>11056.86692456005</v>
       </c>
       <c r="D574" s="3" t="n">
-        <v>11585.16688170566</v>
+        <v>11585.16764794594</v>
       </c>
     </row>
     <row r="575">
@@ -10065,7 +10065,7 @@
         <v>11118.39836056491</v>
       </c>
       <c r="D578" s="3" t="n">
-        <v>11495.7622587259</v>
+        <v>11495.76302526234</v>
       </c>
     </row>
     <row r="579">
@@ -10075,7 +10075,7 @@
         </is>
       </c>
       <c r="B579" s="3" t="n">
-        <v>11559.81</v>
+        <v>11559.8</v>
       </c>
       <c r="C579" s="3" t="n">
         <v>11066.33337869665</v>
@@ -10113,7 +10113,7 @@
         <v>11039.28562990199</v>
       </c>
       <c r="D581" s="3" t="n">
-        <v>11475.69515770222</v>
+        <v>11475.69438476887</v>
       </c>
     </row>
     <row r="582">
@@ -10145,7 +10145,7 @@
         <v>11145.44610935957</v>
       </c>
       <c r="D583" s="3" t="n">
-        <v>11617.28282181616</v>
+        <v>11617.28359444496</v>
       </c>
     </row>
     <row r="584">
@@ -10161,7 +10161,7 @@
         <v>11144.09346397831</v>
       </c>
       <c r="D584" s="3" t="n">
-        <v>11703.5843890804</v>
+        <v>11703.5836150893</v>
       </c>
     </row>
     <row r="585">
@@ -10177,7 +10177,7 @@
         <v>11104.87500205064</v>
       </c>
       <c r="D585" s="3" t="n">
-        <v>11652.89488439518</v>
+        <v>11652.89565537392</v>
       </c>
     </row>
     <row r="586">
@@ -10187,13 +10187,13 @@
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>11801.46</v>
+        <v>11801.45</v>
       </c>
       <c r="C586" s="3" t="n">
         <v>11181.95928052472</v>
       </c>
       <c r="D586" s="3" t="n">
-        <v>11654.05915001732</v>
+        <v>11654.0576089736</v>
       </c>
     </row>
     <row r="587">
@@ -10203,13 +10203,13 @@
         </is>
       </c>
       <c r="B587" s="3" t="n">
-        <v>11813.6</v>
+        <v>11813.59</v>
       </c>
       <c r="C587" s="3" t="n">
         <v>11190.07412104618</v>
       </c>
       <c r="D587" s="3" t="n">
-        <v>11692.32543851865</v>
+        <v>11692.32389241489</v>
       </c>
     </row>
     <row r="588">
@@ -10225,7 +10225,7 @@
         <v>11217.12083807473</v>
       </c>
       <c r="D588" s="3" t="n">
-        <v>11649.39864061475</v>
+        <v>11649.39786756287</v>
       </c>
     </row>
     <row r="589">
@@ -10241,7 +10241,7 @@
         <v>11143.41765717074</v>
       </c>
       <c r="D589" s="3" t="n">
-        <v>11655.90524035547</v>
+        <v>11655.90601816267</v>
       </c>
     </row>
     <row r="590">
@@ -10257,7 +10257,7 @@
         <v>11188.04566885735</v>
       </c>
       <c r="D590" s="3" t="n">
-        <v>11752.01176919164</v>
+        <v>11752.01332380776</v>
       </c>
     </row>
     <row r="591">
@@ -10289,7 +10289,7 @@
         <v>11352.3564867497</v>
       </c>
       <c r="D592" s="3" t="n">
-        <v>11916.53454225235</v>
+        <v>11916.53298856708</v>
       </c>
     </row>
     <row r="593">
@@ -10321,7 +10321,7 @@
         <v>11428.08811984252</v>
       </c>
       <c r="D594" s="3" t="n">
-        <v>12002.27516552145</v>
+        <v>12002.27594482641</v>
       </c>
     </row>
     <row r="595">
@@ -10353,7 +10353,7 @@
         <v>11490.97323299477</v>
       </c>
       <c r="D596" s="3" t="n">
-        <v>12064.26192137796</v>
+        <v>12064.26270146135</v>
       </c>
     </row>
     <row r="597">
@@ -10369,7 +10369,7 @@
         <v>11535.60124468137</v>
       </c>
       <c r="D597" s="3" t="n">
-        <v>12163.76112354173</v>
+        <v>12163.75956286725</v>
       </c>
     </row>
     <row r="598">
@@ -10385,7 +10385,7 @@
         <v>11568.73331827643</v>
       </c>
       <c r="D598" s="3" t="n">
-        <v>12164.50227373523</v>
+        <v>12164.50149274641</v>
       </c>
     </row>
     <row r="599">
@@ -10417,7 +10417,7 @@
         <v>11453.78322325592</v>
       </c>
       <c r="D600" s="3" t="n">
-        <v>12156.90325100126</v>
+        <v>12156.90168460671</v>
       </c>
     </row>
     <row r="601">
@@ -10433,7 +10433,7 @@
         <v>11634.32269042508</v>
       </c>
       <c r="D601" s="3" t="n">
-        <v>12204.98146358323</v>
+        <v>12204.98379789345</v>
       </c>
     </row>
     <row r="602">
@@ -10449,7 +10449,7 @@
         <v>11653.93243727197</v>
       </c>
       <c r="D602" s="3" t="n">
-        <v>12267.26045183564</v>
+        <v>12267.2612367676</v>
       </c>
     </row>
     <row r="603">
@@ -10465,7 +10465,7 @@
         <v>11680.30334749295</v>
       </c>
       <c r="D603" s="3" t="n">
-        <v>12346.64326314411</v>
+        <v>12346.64247541987</v>
       </c>
     </row>
     <row r="604">
@@ -10497,7 +10497,7 @@
         <v>11737.10207231257</v>
       </c>
       <c r="D605" s="3" t="n">
-        <v>12415.91621991576</v>
+        <v>12415.91779040576</v>
       </c>
     </row>
     <row r="606">
@@ -10529,7 +10529,7 @@
         <v>11853.40481271433</v>
       </c>
       <c r="D607" s="3" t="n">
-        <v>12456.23447123365</v>
+        <v>12456.2336876217</v>
       </c>
     </row>
     <row r="608">
@@ -10545,7 +10545,7 @@
         <v>11738.45471769383</v>
       </c>
       <c r="D608" s="3" t="n">
-        <v>12314.25490090674</v>
+        <v>12314.25411540792</v>
       </c>
     </row>
     <row r="609">
@@ -10593,7 +10593,7 @@
         <v>11864.89971903977</v>
       </c>
       <c r="D611" s="3" t="n">
-        <v>12447.713905065</v>
+        <v>12447.71469044545</v>
       </c>
     </row>
     <row r="612">
@@ -10609,7 +10609,7 @@
         <v>11836.50035662996</v>
       </c>
       <c r="D612" s="3" t="n">
-        <v>12434.97182446983</v>
+        <v>12434.97260904633</v>
       </c>
     </row>
     <row r="613">
@@ -10625,7 +10625,7 @@
         <v>11722.22606841703</v>
       </c>
       <c r="D613" s="3" t="n">
-        <v>12377.450148788</v>
+        <v>12377.44936351755</v>
       </c>
     </row>
     <row r="614">
@@ -10641,7 +10641,7 @@
         <v>11709.37851671033</v>
       </c>
       <c r="D614" s="3" t="n">
-        <v>12345.40763230502</v>
+        <v>12345.40997989143</v>
       </c>
     </row>
     <row r="615">
@@ -10673,7 +10673,7 @@
         <v>11952.80309703172</v>
       </c>
       <c r="D616" s="3" t="n">
-        <v>12595.00395331402</v>
+        <v>12595.00473493744</v>
       </c>
     </row>
     <row r="617">
@@ -10689,7 +10689,7 @@
         <v>11908.85089215269</v>
       </c>
       <c r="D617" s="3" t="n">
-        <v>12555.39800725212</v>
+        <v>12555.39566116325</v>
       </c>
     </row>
     <row r="618">
@@ -10705,7 +10705,7 @@
         <v>11891.27062926074</v>
       </c>
       <c r="D618" s="3" t="n">
-        <v>12542.92565527243</v>
+        <v>12542.92487546825</v>
       </c>
     </row>
     <row r="619">
@@ -10721,7 +10721,7 @@
         <v>11898.03282440094</v>
       </c>
       <c r="D619" s="3" t="n">
-        <v>12533.41559141071</v>
+        <v>12533.41715189906</v>
       </c>
     </row>
     <row r="620">
@@ -10737,7 +10737,7 @@
         <v>11925.07954142948</v>
       </c>
       <c r="D620" s="3" t="n">
-        <v>12585.43116578713</v>
+        <v>12585.42960443567</v>
       </c>
     </row>
     <row r="621">
@@ -10753,7 +10753,7 @@
         <v>12008.92601504377</v>
       </c>
       <c r="D621" s="3" t="n">
-        <v>12743.38042018469</v>
+        <v>12743.37885394239</v>
       </c>
     </row>
     <row r="622">
@@ -10769,7 +10769,7 @@
         <v>12007.57336966251</v>
       </c>
       <c r="D622" s="3" t="n">
-        <v>12685.42353322568</v>
+        <v>12685.42587441525</v>
       </c>
     </row>
     <row r="623">
@@ -10785,7 +10785,7 @@
         <v>11925.75534823706</v>
       </c>
       <c r="D623" s="3" t="n">
-        <v>12544.20987570558</v>
+        <v>12544.21065520515</v>
       </c>
     </row>
     <row r="624">
@@ -10801,7 +10801,7 @@
         <v>11964.29800335716</v>
       </c>
       <c r="D624" s="3" t="n">
-        <v>12606.81534587626</v>
+        <v>12606.81690475693</v>
       </c>
     </row>
     <row r="625">
@@ -10833,7 +10833,7 @@
         <v>12026.50627793571</v>
       </c>
       <c r="D626" s="3" t="n">
-        <v>12546.72533734921</v>
+        <v>12546.72379187176</v>
       </c>
     </row>
     <row r="627">
@@ -10849,7 +10849,7 @@
         <v>11944.68825651026</v>
       </c>
       <c r="D627" s="3" t="n">
-        <v>12544.1732321506</v>
+        <v>12544.17168565776</v>
       </c>
     </row>
     <row r="628">
@@ -10881,7 +10881,7 @@
         <v>12046.11499301649</v>
       </c>
       <c r="D629" s="3" t="n">
-        <v>12676.83444572608</v>
+        <v>12676.83522004714</v>
       </c>
     </row>
     <row r="630">
@@ -10929,7 +10929,7 @@
         <v>12089.39035932184</v>
       </c>
       <c r="D632" s="3" t="n">
-        <v>12692.06050561908</v>
+        <v>12692.0620606921</v>
       </c>
     </row>
     <row r="633">
@@ -10945,7 +10945,7 @@
         <v>12105.61900859864</v>
       </c>
       <c r="D633" s="3" t="n">
-        <v>12772.73370080617</v>
+        <v>12772.73136634369</v>
       </c>
     </row>
     <row r="634">
@@ -10961,7 +10961,7 @@
         <v>12133.34256420087</v>
       </c>
       <c r="D634" s="3" t="n">
-        <v>12903.48745183525</v>
+        <v>12903.48667291948</v>
       </c>
     </row>
     <row r="635">
@@ -10977,7 +10977,7 @@
         <v>12309.14828841866</v>
       </c>
       <c r="D635" s="3" t="n">
-        <v>12858.65248262058</v>
+        <v>12858.64938801035</v>
       </c>
     </row>
     <row r="636">
@@ -10993,7 +10993,7 @@
         <v>12303.06293185216</v>
       </c>
       <c r="D636" s="3" t="n">
-        <v>12922.70946033856</v>
+        <v>12922.71023932204</v>
       </c>
     </row>
     <row r="637">
@@ -11009,7 +11009,7 @@
         <v>12265.87292211332</v>
       </c>
       <c r="D637" s="3" t="n">
-        <v>12952.37715393719</v>
+        <v>12952.38028567719</v>
       </c>
     </row>
     <row r="638">
@@ -11025,7 +11025,7 @@
         <v>12293.59647771556</v>
       </c>
       <c r="D638" s="3" t="n">
-        <v>12891.84670679053</v>
+        <v>12891.84748750859</v>
       </c>
     </row>
     <row r="639">
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="B639" s="3" t="n">
-        <v>13762.2</v>
+        <v>13762.19</v>
       </c>
       <c r="C639" s="3" t="n">
         <v>12288.18692795662</v>
       </c>
       <c r="D639" s="3" t="n">
-        <v>13007.23465068765</v>
+        <v>13007.23308840541</v>
       </c>
     </row>
     <row r="640">
@@ -11057,7 +11057,7 @@
         <v>12366.62385181197</v>
       </c>
       <c r="D640" s="3" t="n">
-        <v>13027.56950442037</v>
+        <v>13027.56559186089</v>
       </c>
     </row>
     <row r="641">
@@ -11073,7 +11073,7 @@
         <v>12366.62385181197</v>
       </c>
       <c r="D641" s="3" t="n">
-        <v>13050.39169831513</v>
+        <v>13050.38777890147</v>
       </c>
     </row>
     <row r="642">
@@ -11089,7 +11089,7 @@
         <v>12366.62385181197</v>
       </c>
       <c r="D642" s="3" t="n">
-        <v>13029.79381533004</v>
+        <v>13029.79224731089</v>
       </c>
     </row>
     <row r="643">
@@ -11105,7 +11105,7 @@
         <v>12263.84446992448</v>
       </c>
       <c r="D643" s="3" t="n">
-        <v>13013.88144004471</v>
+        <v>13013.88222810741</v>
       </c>
     </row>
     <row r="644">
@@ -11137,7 +11137,7 @@
         <v>12285.48266896021</v>
       </c>
       <c r="D645" s="3" t="n">
-        <v>12749.07615721549</v>
+        <v>12749.07537650593</v>
       </c>
     </row>
     <row r="646">
@@ -11147,13 +11147,13 @@
         </is>
       </c>
       <c r="B646" s="3" t="n">
-        <v>13606.42</v>
+        <v>13606.41</v>
       </c>
       <c r="C646" s="3" t="n">
         <v>12198.25509777583</v>
       </c>
       <c r="D646" s="3" t="n">
-        <v>12883.79975009613</v>
+        <v>12883.79896929348</v>
       </c>
     </row>
     <row r="647">
@@ -11185,7 +11185,7 @@
         <v>12151.59966566651</v>
       </c>
       <c r="D648" s="3" t="n">
-        <v>12874.30887572015</v>
+        <v>12874.30809682985</v>
       </c>
     </row>
     <row r="649">
@@ -11201,7 +11201,7 @@
         <v>12208.39839048613</v>
       </c>
       <c r="D649" s="3" t="n">
-        <v>12750.52073723901</v>
+        <v>12750.5199580356</v>
       </c>
     </row>
     <row r="650">
@@ -11217,7 +11217,7 @@
         <v>12225.3028465705</v>
       </c>
       <c r="D650" s="3" t="n">
-        <v>12987.36987563764</v>
+        <v>12987.37145110308</v>
       </c>
     </row>
     <row r="651">
@@ -11233,7 +11233,7 @@
         <v>12286.15847576779</v>
       </c>
       <c r="D651" s="3" t="n">
-        <v>12825.8529532532</v>
+        <v>12825.85216442891</v>
       </c>
     </row>
     <row r="652">
@@ -11249,7 +11249,7 @@
         <v>12258.43492016555</v>
       </c>
       <c r="D652" s="3" t="n">
-        <v>12757.00854942618</v>
+        <v>12757.00775488189</v>
       </c>
     </row>
     <row r="653">
@@ -11265,7 +11265,7 @@
         <v>12067.07738524465</v>
       </c>
       <c r="D653" s="3" t="n">
-        <v>12762.35570103677</v>
+        <v>12762.35649736653</v>
       </c>
     </row>
     <row r="654">
@@ -11281,7 +11281,7 @@
         <v>12003.51646528484</v>
       </c>
       <c r="D654" s="3" t="n">
-        <v>12691.94717637289</v>
+        <v>12691.94797302413</v>
       </c>
     </row>
     <row r="655">
@@ -11329,7 +11329,7 @@
         <v>11937.92709313619</v>
       </c>
       <c r="D657" s="3" t="n">
-        <v>12627.16374593893</v>
+        <v>12627.16453984018</v>
       </c>
     </row>
     <row r="658">
@@ -11345,7 +11345,7 @@
         <v>12068.4289988598</v>
       </c>
       <c r="D658" s="3" t="n">
-        <v>12782.04269205275</v>
+        <v>12782.04348626704</v>
       </c>
     </row>
     <row r="659">
@@ -11377,7 +11377,7 @@
         <v>11927.78380042589</v>
       </c>
       <c r="D660" s="3" t="n">
-        <v>12672.93019572071</v>
+        <v>12672.93177734622</v>
       </c>
     </row>
     <row r="661">
@@ -11393,7 +11393,7 @@
         <v>12142.1332115299</v>
       </c>
       <c r="D661" s="3" t="n">
-        <v>12757.53984013615</v>
+        <v>12757.53905151501</v>
       </c>
     </row>
     <row r="662">
@@ -11409,7 +11409,7 @@
         <v>12146.19011590757</v>
       </c>
       <c r="D662" s="3" t="n">
-        <v>12829.92262422961</v>
+        <v>12829.92025333976</v>
       </c>
     </row>
     <row r="663">
@@ -11425,7 +11425,7 @@
         <v>12113.73281735398</v>
       </c>
       <c r="D663" s="3" t="n">
-        <v>12616.2687694811</v>
+        <v>12616.26797983605</v>
       </c>
     </row>
     <row r="664">
@@ -11441,7 +11441,7 @@
         <v>12113.73281735398</v>
       </c>
       <c r="D664" s="3" t="n">
-        <v>12633.24502608681</v>
+        <v>12633.24581937035</v>
       </c>
     </row>
     <row r="665">
@@ -11473,7 +11473,7 @@
         <v>12122.52346468301</v>
       </c>
       <c r="D666" s="3" t="n">
-        <v>12829.4636746061</v>
+        <v>12829.4620978715</v>
       </c>
     </row>
     <row r="667">
@@ -11489,7 +11489,7 @@
         <v>12214.48374705263</v>
       </c>
       <c r="D667" s="3" t="n">
-        <v>12931.76152437178</v>
+        <v>12931.76073784057</v>
       </c>
     </row>
     <row r="668">
@@ -11505,7 +11505,7 @@
         <v>12298.33022066692</v>
       </c>
       <c r="D668" s="3" t="n">
-        <v>12934.74941346551</v>
+        <v>12934.75019931132</v>
       </c>
     </row>
     <row r="669">
@@ -11521,7 +11521,7 @@
         <v>12299.00602747449</v>
       </c>
       <c r="D669" s="3" t="n">
-        <v>12956.47643586202</v>
+        <v>12956.47407459306</v>
       </c>
     </row>
     <row r="670">
@@ -11553,7 +11553,7 @@
         <v>12366.62385181197</v>
       </c>
       <c r="D671" s="3" t="n">
-        <v>13005.97524785862</v>
+        <v>13005.97367873927</v>
       </c>
     </row>
     <row r="672">
@@ -11569,7 +11569,7 @@
         <v>12347.01513673119</v>
       </c>
       <c r="D672" s="3" t="n">
-        <v>13025.53669040941</v>
+        <v>13025.53904731225</v>
       </c>
     </row>
     <row r="673">
@@ -11617,7 +11617,7 @@
         <v>12480.8981400249</v>
       </c>
       <c r="D675" s="3" t="n">
-        <v>13075.13311287432</v>
+        <v>13075.13000479284</v>
       </c>
     </row>
     <row r="676">
@@ -11633,7 +11633,7 @@
         <v>12441.67967809723</v>
       </c>
       <c r="D676" s="3" t="n">
-        <v>13120.45012115333</v>
+        <v>13120.44856396498</v>
       </c>
     </row>
     <row r="677">
@@ -11681,7 +11681,7 @@
         <v>12488.33614197267</v>
       </c>
       <c r="D679" s="3" t="n">
-        <v>13145.13622857733</v>
+        <v>13145.13466957819</v>
       </c>
     </row>
     <row r="680">
@@ -11697,7 +11697,7 @@
         <v>12491.71723954277</v>
       </c>
       <c r="D680" s="3" t="n">
-        <v>13085.23998474063</v>
+        <v>13085.23920308329</v>
       </c>
     </row>
     <row r="681">
@@ -11713,7 +11713,7 @@
         <v>12445.7365824749</v>
       </c>
       <c r="D681" s="3" t="n">
-        <v>13187.07235061757</v>
+        <v>13187.07391574282</v>
       </c>
     </row>
     <row r="682">
@@ -11729,7 +11729,7 @@
         <v>12475.48859026597</v>
       </c>
       <c r="D682" s="3" t="n">
-        <v>13144.58228244245</v>
+        <v>13144.58384252471</v>
       </c>
     </row>
     <row r="683">
@@ -11745,7 +11745,7 @@
         <v>12425.45102882043</v>
       </c>
       <c r="D683" s="3" t="n">
-        <v>13136.50383296327</v>
+        <v>13136.50539099775</v>
       </c>
     </row>
     <row r="684">
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="B685" s="3" t="n">
-        <v>13980.31</v>
+        <v>13980.3</v>
       </c>
       <c r="C685" s="3" t="n">
         <v>12342.95720058741</v>
@@ -11793,7 +11793,7 @@
         <v>12261.81601773565</v>
       </c>
       <c r="D686" s="3" t="n">
-        <v>13107.96395945053</v>
+        <v>13107.96239760829</v>
       </c>
     </row>
     <row r="687">
@@ -11825,7 +11825,7 @@
         <v>12329.43384207313</v>
       </c>
       <c r="D688" s="3" t="n">
-        <v>13046.65245507674</v>
+        <v>13046.6509035407</v>
       </c>
     </row>
     <row r="689">
@@ -11841,7 +11841,7 @@
         <v>12476.84123564723</v>
       </c>
       <c r="D689" s="3" t="n">
-        <v>13232.67238675061</v>
+        <v>13232.67083157605</v>
       </c>
     </row>
     <row r="690">
@@ -11857,7 +11857,7 @@
         <v>12522.82086094898</v>
       </c>
       <c r="D690" s="3" t="n">
-        <v>13241.3503728383</v>
+        <v>13241.3488166146</v>
       </c>
     </row>
     <row r="691">
@@ -11873,7 +11873,7 @@
         <v>12585.02913552753</v>
       </c>
       <c r="D691" s="3" t="n">
-        <v>13201.09285157629</v>
+        <v>13201.09440495708</v>
       </c>
     </row>
     <row r="692">
@@ -11889,7 +11889,7 @@
         <v>12637.77095596948</v>
       </c>
       <c r="D692" s="3" t="n">
-        <v>13383.83285534958</v>
+        <v>13383.8344253826</v>
       </c>
     </row>
     <row r="693">
@@ -11921,7 +11921,7 @@
         <v>12681.72316084852</v>
       </c>
       <c r="D694" s="3" t="n">
-        <v>13574.80443779351</v>
+        <v>13574.80758913079</v>
       </c>
     </row>
     <row r="695">
@@ -11937,7 +11937,7 @@
         <v>12681.04632227483</v>
       </c>
       <c r="D695" s="3" t="n">
-        <v>13510.53981203331</v>
+        <v>13510.53511686048</v>
       </c>
     </row>
     <row r="696">
@@ -11953,7 +11953,7 @@
         <v>12716.20787982483</v>
       </c>
       <c r="D696" s="3" t="n">
-        <v>13612.31370085096</v>
+        <v>13612.31212496246</v>
       </c>
     </row>
     <row r="697">
@@ -11985,7 +11985,7 @@
         <v>12792.61635149135</v>
       </c>
       <c r="D698" s="3" t="n">
-        <v>13753.14819749645</v>
+        <v>13753.15134873195</v>
       </c>
     </row>
     <row r="699">
@@ -12001,7 +12001,7 @@
         <v>12810.19661438329</v>
       </c>
       <c r="D699" s="3" t="n">
-        <v>13751.08017838447</v>
+        <v>13751.08332914612</v>
       </c>
     </row>
     <row r="700">
@@ -12017,7 +12017,7 @@
         <v>12863.61527339893</v>
       </c>
       <c r="D700" s="3" t="n">
-        <v>13701.94068961506</v>
+        <v>13701.93754156119</v>
       </c>
     </row>
     <row r="701">
@@ -12033,7 +12033,7 @@
         <v>12813.57771195339</v>
       </c>
       <c r="D701" s="3" t="n">
-        <v>13741.24082758071</v>
+        <v>13741.24240824152</v>
       </c>
     </row>
     <row r="702">
@@ -12065,7 +12065,7 @@
         <v>12831.15797484534</v>
       </c>
       <c r="D703" s="3" t="n">
-        <v>13715.60772472719</v>
+        <v>13715.60614794181</v>
       </c>
     </row>
     <row r="704">
@@ -12075,13 +12075,13 @@
         </is>
       </c>
       <c r="B704" s="3" t="n">
-        <v>14406.15</v>
+        <v>14406.14</v>
       </c>
       <c r="C704" s="3" t="n">
         <v>12825.07261827883</v>
       </c>
       <c r="D704" s="3" t="n">
-        <v>13762.34787043923</v>
+        <v>13762.35261100022</v>
       </c>
     </row>
     <row r="705">
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="B706" s="3" t="n">
-        <v>14438.48</v>
+        <v>14438.47</v>
       </c>
       <c r="C706" s="3" t="n">
         <v>12873.08172753554</v>
@@ -12145,7 +12145,7 @@
         <v>12818.31145490475</v>
       </c>
       <c r="D708" s="3" t="n">
-        <v>13815.1968272055</v>
+        <v>13815.19840334787</v>
       </c>
     </row>
     <row r="709">
@@ -12161,7 +12161,7 @@
         <v>12858.88153044757</v>
       </c>
       <c r="D709" s="3" t="n">
-        <v>13862.24814890176</v>
+        <v>13862.24499993417</v>
       </c>
     </row>
     <row r="710">
@@ -12177,7 +12177,7 @@
         <v>12887.95773143107</v>
       </c>
       <c r="D710" s="3" t="n">
-        <v>13804.5872982628</v>
+        <v>13804.58416239352</v>
       </c>
     </row>
     <row r="711">
@@ -12209,7 +12209,7 @@
         <v>12915.68025526719</v>
       </c>
       <c r="D712" s="3" t="n">
-        <v>13858.20357507664</v>
+        <v>13858.20513827269</v>
       </c>
     </row>
     <row r="713">
@@ -12225,7 +12225,7 @@
         <v>12936.64264749535</v>
       </c>
       <c r="D713" s="3" t="n">
-        <v>13865.37437901562</v>
+        <v>13865.3728165303</v>
       </c>
     </row>
     <row r="714">
@@ -12241,7 +12241,7 @@
         <v>12986.67917717477</v>
       </c>
       <c r="D714" s="3" t="n">
-        <v>14023.50419566739</v>
+        <v>14023.50106602589</v>
       </c>
     </row>
     <row r="715">
@@ -12257,7 +12257,7 @@
         <v>12963.6893645239</v>
       </c>
       <c r="D715" s="3" t="n">
-        <v>13878.82737498578</v>
+        <v>13878.82893713273</v>
       </c>
     </row>
     <row r="716">
@@ -12273,7 +12273,7 @@
         <v>13028.60189809886</v>
       </c>
       <c r="D716" s="3" t="n">
-        <v>13915.68326250108</v>
+        <v>13915.68170602348</v>
       </c>
     </row>
     <row r="717">
@@ -12289,7 +12289,7 @@
         <v>13028.60189809886</v>
       </c>
       <c r="D717" s="3" t="n">
-        <v>13937.56479411353</v>
+        <v>13937.56634876336</v>
       </c>
     </row>
     <row r="718">
@@ -12299,13 +12299,13 @@
         </is>
       </c>
       <c r="B718" s="3" t="n">
-        <v>14724.37</v>
+        <v>14724.36</v>
       </c>
       <c r="C718" s="3" t="n">
         <v>13048.21164494575</v>
       </c>
       <c r="D718" s="3" t="n">
-        <v>13999.61880631318</v>
+        <v>13999.61259685248</v>
       </c>
     </row>
     <row r="719">
@@ -12337,7 +12337,7 @@
         <v>12837.24436317796</v>
       </c>
       <c r="D720" s="3" t="n">
-        <v>13648.86930617361</v>
+        <v>13648.86775929152</v>
       </c>
     </row>
     <row r="721">
@@ -12353,7 +12353,7 @@
         <v>12762.18853689271</v>
       </c>
       <c r="D721" s="3" t="n">
-        <v>13606.28827969005</v>
+        <v>13606.28983205523</v>
       </c>
     </row>
     <row r="722">
@@ -12385,7 +12385,7 @@
         <v>12943.40381086943</v>
       </c>
       <c r="D723" s="3" t="n">
-        <v>13739.82120188912</v>
+        <v>13739.82275592986</v>
       </c>
     </row>
     <row r="724">
@@ -12401,7 +12401,7 @@
         <v>12718.91317058736</v>
       </c>
       <c r="D724" s="3" t="n">
-        <v>13476.84716262436</v>
+        <v>13476.84404333979</v>
       </c>
     </row>
     <row r="725">
@@ -12417,7 +12417,7 @@
         <v>12652.64695986502</v>
       </c>
       <c r="D725" s="3" t="n">
-        <v>13420.44551276244</v>
+        <v>13420.44707401243</v>
       </c>
     </row>
     <row r="726">
@@ -12433,7 +12433,7 @@
         <v>12677.66625647085</v>
       </c>
       <c r="D726" s="3" t="n">
-        <v>13556.03843129626</v>
+        <v>13556.04310996919</v>
       </c>
     </row>
     <row r="727">
@@ -12449,7 +12449,7 @@
         <v>12701.3318759293</v>
       </c>
       <c r="D727" s="3" t="n">
-        <v>13560.91650648249</v>
+        <v>13560.91806568471</v>
       </c>
     </row>
     <row r="728">
@@ -12465,7 +12465,7 @@
         <v>12711.47516863959</v>
       </c>
       <c r="D728" s="3" t="n">
-        <v>13534.97320830634</v>
+        <v>13534.97477245019</v>
       </c>
     </row>
     <row r="729">
@@ -12497,7 +12497,7 @@
         <v>12773.68344321814</v>
       </c>
       <c r="D730" s="3" t="n">
-        <v>13554.61840378025</v>
+        <v>13554.61996728104</v>
       </c>
     </row>
     <row r="731">
@@ -12513,7 +12513,7 @@
         <v>12261.14021092808</v>
       </c>
       <c r="D731" s="3" t="n">
-        <v>13347.03373419688</v>
+        <v>13347.03530296076</v>
       </c>
     </row>
     <row r="732">
@@ -12529,7 +12529,7 @@
         <v>11985.2593638192</v>
       </c>
       <c r="D732" s="3" t="n">
-        <v>12811.95902559701</v>
+        <v>12811.95980111965</v>
       </c>
     </row>
     <row r="733">
@@ -12539,13 +12539,13 @@
         </is>
       </c>
       <c r="B733" s="3" t="n">
-        <v>13367.17</v>
+        <v>13367.16</v>
       </c>
       <c r="C733" s="3" t="n">
         <v>12092.09565008436</v>
       </c>
       <c r="D733" s="3" t="n">
-        <v>12882.67743429575</v>
+        <v>12882.68052501411</v>
       </c>
     </row>
     <row r="734">
@@ -12561,7 +12561,7 @@
         <v>12260.4644041205</v>
       </c>
       <c r="D734" s="3" t="n">
-        <v>12825.57655514299</v>
+        <v>12825.5781040051</v>
       </c>
     </row>
     <row r="735">
@@ -12577,7 +12577,7 @@
         <v>12260.4644041205</v>
       </c>
       <c r="D735" s="3" t="n">
-        <v>13119.77667560873</v>
+        <v>13119.77822420018</v>
       </c>
     </row>
     <row r="736">
@@ -12593,7 +12593,7 @@
         <v>12309.82512699235</v>
       </c>
       <c r="D736" s="3" t="n">
-        <v>13192.60591756741</v>
+        <v>13192.60746791872</v>
       </c>
     </row>
     <row r="737">
@@ -12609,7 +12609,7 @@
         <v>12330.11068064682</v>
       </c>
       <c r="D737" s="3" t="n">
-        <v>13201.84280007788</v>
+        <v>13201.84435070013</v>
       </c>
     </row>
     <row r="738">
@@ -12625,7 +12625,7 @@
         <v>12451.14613223383</v>
       </c>
       <c r="D738" s="3" t="n">
-        <v>13391.4250998768</v>
+        <v>13391.42664731752</v>
       </c>
     </row>
     <row r="739">
@@ -12635,13 +12635,13 @@
         </is>
       </c>
       <c r="B739" s="3" t="n">
-        <v>13866.64</v>
+        <v>13866.63</v>
       </c>
       <c r="C739" s="3" t="n">
         <v>12482.25078540616</v>
       </c>
       <c r="D739" s="3" t="n">
-        <v>13359.48111329773</v>
+        <v>13359.47649661444</v>
       </c>
     </row>
     <row r="740">
@@ -12673,7 +12673,7 @@
         <v>12716.88471839853</v>
       </c>
       <c r="D741" s="3" t="n">
-        <v>13649.03146193133</v>
+        <v>13649.03300422736</v>
       </c>
     </row>
     <row r="742">
@@ -12689,7 +12689,7 @@
         <v>12754.07369637125</v>
       </c>
       <c r="D742" s="3" t="n">
-        <v>13714.21885705339</v>
+        <v>13714.21732206825</v>
       </c>
     </row>
     <row r="743">
@@ -12721,7 +12721,7 @@
         <v>12737.84607886057</v>
       </c>
       <c r="D744" s="3" t="n">
-        <v>13611.88462321247</v>
+        <v>13611.88310242599</v>
       </c>
     </row>
     <row r="745">
@@ -12769,7 +12769,7 @@
         <v>12754.07369637125</v>
       </c>
       <c r="D747" s="3" t="n">
-        <v>13542.98123856513</v>
+        <v>13542.97972593553</v>
       </c>
     </row>
     <row r="748">
@@ -12817,7 +12817,7 @@
         <v>12902.15689675292</v>
       </c>
       <c r="D750" s="3" t="n">
-        <v>13560.38979418427</v>
+        <v>13560.39131537702</v>
       </c>
     </row>
     <row r="751">
@@ -12833,7 +12833,7 @@
         <v>12858.20572364</v>
       </c>
       <c r="D751" s="3" t="n">
-        <v>13744.81467147871</v>
+        <v>13744.81772608289</v>
       </c>
     </row>
     <row r="752">
@@ -12849,7 +12849,7 @@
         <v>12937.9942611105</v>
       </c>
       <c r="D752" s="3" t="n">
-        <v>13789.1329474034</v>
+        <v>13789.13601185674</v>
       </c>
     </row>
     <row r="753">
@@ -12897,7 +12897,7 @@
         <v>12573.5342292021</v>
       </c>
       <c r="D755" s="3" t="n">
-        <v>13401.73222048879</v>
+        <v>13401.7306931867</v>
       </c>
     </row>
     <row r="756">
@@ -12913,7 +12913,7 @@
         <v>12418.01302687266</v>
       </c>
       <c r="D756" s="3" t="n">
-        <v>13139.82386903493</v>
+        <v>13139.82539212299</v>
       </c>
     </row>
     <row r="757">
@@ -12929,7 +12929,7 @@
         <v>12557.30661169142</v>
       </c>
       <c r="D757" s="3" t="n">
-        <v>13315.58270352889</v>
+        <v>13315.58422990005</v>
       </c>
     </row>
     <row r="758">
@@ -12961,7 +12961,7 @@
         <v>12518.76395657131</v>
       </c>
       <c r="D759" s="3" t="n">
-        <v>13591.97389474888</v>
+        <v>13591.97235920521</v>
       </c>
     </row>
     <row r="760">
@@ -13009,7 +13009,7 @@
         <v>12790.58789930252</v>
       </c>
       <c r="D762" s="3" t="n">
-        <v>13714.44789079423</v>
+        <v>13714.45246940016</v>
       </c>
     </row>
     <row r="763">
@@ -13041,7 +13041,7 @@
         <v>12800.73016024669</v>
       </c>
       <c r="D764" s="3" t="n">
-        <v>13636.73942988701</v>
+        <v>13636.74095133359</v>
       </c>
     </row>
     <row r="765">
@@ -13067,13 +13067,13 @@
         </is>
       </c>
       <c r="B766" s="3" t="n">
-        <v>14206.92</v>
+        <v>14206.91</v>
       </c>
       <c r="C766" s="3" t="n">
         <v>12898.09999237525</v>
       </c>
       <c r="D766" s="3" t="n">
-        <v>13797.26437800865</v>
+        <v>13797.26286185907</v>
       </c>
     </row>
     <row r="767">
@@ -13099,13 +13099,13 @@
         </is>
       </c>
       <c r="B768" s="3" t="n">
-        <v>14347</v>
+        <v>14346.99</v>
       </c>
       <c r="C768" s="3" t="n">
         <v>12988.03182255604</v>
       </c>
       <c r="D768" s="3" t="n">
-        <v>13934.02678855313</v>
+        <v>13934.02526554955</v>
       </c>
     </row>
     <row r="769">
@@ -13137,7 +13137,7 @@
         <v>13025.89763910245</v>
       </c>
       <c r="D770" s="3" t="n">
-        <v>13934.22129183633</v>
+        <v>13934.21977147282</v>
       </c>
     </row>
     <row r="771">
@@ -13179,13 +13179,13 @@
         </is>
       </c>
       <c r="B773" s="3" t="n">
-        <v>14344.7</v>
+        <v>14344.69</v>
       </c>
       <c r="C773" s="3" t="n">
         <v>13057.67809908236</v>
       </c>
       <c r="D773" s="3" t="n">
-        <v>13837.68610412685</v>
+        <v>13837.68306492311</v>
       </c>
     </row>
     <row r="774">
@@ -13217,7 +13217,7 @@
         <v>13075.93520054799</v>
       </c>
       <c r="D775" s="3" t="n">
-        <v>13928.39846125112</v>
+        <v>13928.39999297009</v>
       </c>
     </row>
     <row r="776">
@@ -13233,7 +13233,7 @@
         <v>13157.07638339975</v>
       </c>
       <c r="D776" s="3" t="n">
-        <v>14071.43452258977</v>
+        <v>14071.43145556399</v>
       </c>
     </row>
     <row r="777">
@@ -13249,7 +13249,7 @@
         <v>13197.64645894257</v>
       </c>
       <c r="D777" s="3" t="n">
-        <v>14021.77607696986</v>
+        <v>14021.77761901191</v>
       </c>
     </row>
     <row r="778">
@@ -13265,7 +13265,7 @@
         <v>13190.88529556849</v>
       </c>
       <c r="D778" s="3" t="n">
-        <v>14152.83590580425</v>
+        <v>14152.83744767715</v>
       </c>
     </row>
     <row r="779">
@@ -13281,7 +13281,7 @@
         <v>13287.57828912336</v>
       </c>
       <c r="D779" s="3" t="n">
-        <v>14250.86664274319</v>
+        <v>14250.86510087029</v>
       </c>
     </row>
     <row r="780">
@@ -13297,7 +13297,7 @@
         <v>13316.65449010686</v>
       </c>
       <c r="D780" s="3" t="n">
-        <v>14268.08277637645</v>
+        <v>14268.0858692607</v>
       </c>
     </row>
     <row r="781">
@@ -13329,7 +13329,7 @@
         <v>13472.85149924387</v>
       </c>
       <c r="D782" s="3" t="n">
-        <v>14494.66481325234</v>
+        <v>14494.66636223292</v>
       </c>
     </row>
     <row r="783">
@@ -13345,7 +13345,7 @@
         <v>13440.39523245639</v>
       </c>
       <c r="D783" s="3" t="n">
-        <v>14403.41665164888</v>
+        <v>14403.41510036664</v>
       </c>
     </row>
     <row r="784">
@@ -13361,7 +13361,7 @@
         <v>13440.39523245639</v>
       </c>
       <c r="D784" s="3" t="n">
-        <v>14499.31803500728</v>
+        <v>14499.31648015431</v>
       </c>
     </row>
     <row r="785">
@@ -13377,7 +13377,7 @@
         <v>13555.34532747689</v>
       </c>
       <c r="D785" s="3" t="n">
-        <v>14529.44178187522</v>
+        <v>14529.44489777491</v>
       </c>
     </row>
     <row r="786">
@@ -13393,7 +13393,7 @@
         <v>13540.46932358136</v>
       </c>
       <c r="D786" s="3" t="n">
-        <v>14629.69541794455</v>
+        <v>14629.696980633</v>
       </c>
     </row>
     <row r="787">
@@ -13403,13 +13403,13 @@
         </is>
       </c>
       <c r="B787" s="3" t="n">
-        <v>14887.79</v>
+        <v>14887.78</v>
       </c>
       <c r="C787" s="3" t="n">
         <v>13485.02221237688</v>
       </c>
       <c r="D787" s="3" t="n">
-        <v>14553.15616972763</v>
+        <v>14553.15461265764</v>
       </c>
     </row>
     <row r="788">
@@ -13425,7 +13425,7 @@
         <v>13504.63195922378</v>
       </c>
       <c r="D788" s="3" t="n">
-        <v>14613.71850761384</v>
+        <v>14613.72007199453</v>
       </c>
     </row>
     <row r="789">
@@ -13441,7 +13441,7 @@
         <v>13455.27123635193</v>
       </c>
       <c r="D789" s="3" t="n">
-        <v>14507.75745831259</v>
+        <v>14507.7590256718</v>
       </c>
     </row>
     <row r="790">
@@ -13473,7 +13473,7 @@
         <v>13487.05169633184</v>
       </c>
       <c r="D791" s="3" t="n">
-        <v>14498.01884876533</v>
+        <v>14498.0204122322</v>
       </c>
     </row>
     <row r="792">
@@ -13505,7 +13505,7 @@
         <v>13492.46021432465</v>
       </c>
       <c r="D793" s="3" t="n">
-        <v>14576.31051864097</v>
+        <v>14576.30895410787</v>
       </c>
     </row>
     <row r="794">
@@ -13521,7 +13521,7 @@
         <v>13427.54768074969</v>
       </c>
       <c r="D794" s="3" t="n">
-        <v>14527.02537638858</v>
+        <v>14527.02381241394</v>
       </c>
     </row>
     <row r="795">
@@ -13537,7 +13537,7 @@
         <v>13192.23794094976</v>
       </c>
       <c r="D795" s="3" t="n">
-        <v>14191.70181234221</v>
+        <v>14191.70025391845</v>
       </c>
     </row>
     <row r="796">
@@ -13547,7 +13547,7 @@
         </is>
       </c>
       <c r="B796" s="3" t="n">
-        <v>14688.07</v>
+        <v>14688.06</v>
       </c>
       <c r="C796" s="3" t="n">
         <v>13295.01629107113</v>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="B797" s="3" t="n">
-        <v>14591.55</v>
+        <v>14591.54</v>
       </c>
       <c r="C797" s="3" t="n">
         <v>13182.09464823946</v>
@@ -13601,7 +13601,7 @@
         <v>13657.44787079069</v>
       </c>
       <c r="D799" s="3" t="n">
-        <v>14649.19109205538</v>
+        <v>14649.18954436093</v>
       </c>
     </row>
     <row r="800">
@@ -13649,7 +13649,7 @@
         <v>13996.21383105181</v>
       </c>
       <c r="D802" s="3" t="n">
-        <v>15144.6325197307</v>
+        <v>15144.63094032217</v>
       </c>
     </row>
     <row r="803">
@@ -13681,7 +13681,7 @@
         <v>13994.86118567054</v>
       </c>
       <c r="D804" s="3" t="n">
-        <v>15244.59603914135</v>
+        <v>15244.5976331546</v>
       </c>
     </row>
     <row r="805">
@@ -13697,7 +13697,7 @@
         <v>13986.7473769152</v>
       </c>
       <c r="D805" s="3" t="n">
-        <v>15221.99030712478</v>
+        <v>15221.98870517458</v>
       </c>
     </row>
     <row r="806">
@@ -13707,7 +13707,7 @@
         </is>
       </c>
       <c r="B806" s="3" t="n">
-        <v>15474.67</v>
+        <v>15474.66</v>
       </c>
       <c r="C806" s="3" t="n">
         <v>13812.96907312013</v>
@@ -13745,7 +13745,7 @@
         <v>13831.90198139334</v>
       </c>
       <c r="D808" s="3" t="n">
-        <v>15099.74493564517</v>
+        <v>15099.75132483031</v>
       </c>
     </row>
     <row r="809">
@@ -13793,7 +13793,7 @@
         <v>14183.51446159503</v>
       </c>
       <c r="D811" s="3" t="n">
-        <v>15415.71444433602</v>
+        <v>15415.71767724266</v>
       </c>
     </row>
     <row r="812">
@@ -13809,7 +13809,7 @@
         <v>14157.14355137406</v>
       </c>
       <c r="D812" s="3" t="n">
-        <v>15452.45994261505</v>
+        <v>15452.46317227266</v>
       </c>
     </row>
     <row r="813">
@@ -13825,7 +13825,7 @@
         <v>14173.37220065086</v>
       </c>
       <c r="D813" s="3" t="n">
-        <v>15586.0523127333</v>
+        <v>15586.05393306221</v>
       </c>
     </row>
     <row r="814">
@@ -13873,7 +13873,7 @@
         <v>14176.75329822096</v>
       </c>
       <c r="D816" s="3" t="n">
-        <v>15459.64010266375</v>
+        <v>15459.64170478316</v>
       </c>
     </row>
     <row r="817">
@@ -13889,7 +13889,7 @@
         <v>14294.40765223787</v>
       </c>
       <c r="D817" s="3" t="n">
-        <v>15513.6910616809</v>
+        <v>15513.69266652502</v>
       </c>
     </row>
     <row r="818">
@@ -13905,7 +13905,7 @@
         <v>14284.94119810126</v>
       </c>
       <c r="D818" s="3" t="n">
-        <v>15585.69949081996</v>
+        <v>15585.69787927432</v>
       </c>
     </row>
     <row r="819">
@@ -13915,13 +13915,13 @@
         </is>
       </c>
       <c r="B819" s="3" t="n">
-        <v>16138.92</v>
+        <v>16138.91</v>
       </c>
       <c r="C819" s="3" t="n">
         <v>14328.8934029803</v>
       </c>
       <c r="D819" s="3" t="n">
-        <v>15668.15231054977</v>
+        <v>15668.15070047638</v>
       </c>
     </row>
     <row r="820">
@@ -13937,7 +13937,7 @@
         <v>14316.72165808117</v>
       </c>
       <c r="D820" s="3" t="n">
-        <v>15637.43318612225</v>
+        <v>15637.4364052537</v>
       </c>
     </row>
     <row r="821">
@@ -13979,13 +13979,13 @@
         </is>
       </c>
       <c r="B823" s="3" t="n">
-        <v>15963.98</v>
+        <v>15963.97</v>
       </c>
       <c r="C823" s="3" t="n">
         <v>14295.76029761913</v>
       </c>
       <c r="D823" s="3" t="n">
-        <v>15477.49075725438</v>
+        <v>15477.48915395034</v>
       </c>
     </row>
     <row r="824">
@@ -14001,7 +14001,7 @@
         <v>14381.63522342225</v>
       </c>
       <c r="D824" s="3" t="n">
-        <v>15630.06919871833</v>
+        <v>15630.07080540709</v>
       </c>
     </row>
     <row r="825">
@@ -14017,7 +14017,7 @@
         <v>14354.58747462758</v>
       </c>
       <c r="D825" s="3" t="n">
-        <v>15588.1848036439</v>
+        <v>15588.18641432652</v>
       </c>
     </row>
     <row r="826">
@@ -14033,7 +14033,7 @@
         <v>14285.61803667495</v>
       </c>
       <c r="D826" s="3" t="n">
-        <v>15633.88790807665</v>
+        <v>15633.89113952806</v>
       </c>
     </row>
     <row r="827">
@@ -14049,7 +14049,7 @@
         <v>14304.55094494816</v>
       </c>
       <c r="D827" s="3" t="n">
-        <v>15646.87087405323</v>
+        <v>15646.87248424515</v>
       </c>
     </row>
     <row r="828">
@@ -14081,7 +14081,7 @@
         <v>14292.37920004903</v>
       </c>
       <c r="D829" s="3" t="n">
-        <v>15139.60608914638</v>
+        <v>15139.6044766529</v>
       </c>
     </row>
     <row r="830">
@@ -14097,7 +14097,7 @@
         <v>14067.21172119327</v>
       </c>
       <c r="D830" s="3" t="n">
-        <v>15346.69345784646</v>
+        <v>15346.6918227944</v>
       </c>
     </row>
     <row r="831">
@@ -14107,13 +14107,13 @@
         </is>
       </c>
       <c r="B831" s="3" t="n">
-        <v>15860.18</v>
+        <v>15860.17</v>
       </c>
       <c r="C831" s="3" t="n">
         <v>14087.49727484774</v>
       </c>
       <c r="D831" s="3" t="n">
-        <v>15508.99670888384</v>
+        <v>15508.99834161743</v>
       </c>
     </row>
     <row r="832">
@@ -14145,7 +14145,7 @@
         <v>14180.81020259863</v>
       </c>
       <c r="D833" s="3" t="n">
-        <v>15713.31785152902</v>
+        <v>15713.3129725697</v>
       </c>
     </row>
     <row r="834">
@@ -14161,7 +14161,7 @@
         <v>14180.81020259863</v>
       </c>
       <c r="D834" s="3" t="n">
-        <v>15718.2229085803</v>
+        <v>15718.21802809798</v>
       </c>
     </row>
     <row r="835">
@@ -14177,7 +14177,7 @@
         <v>14180.81020259863</v>
       </c>
       <c r="D835" s="3" t="n">
-        <v>15723.8441273302</v>
+        <v>15723.84575463131</v>
       </c>
     </row>
     <row r="836">
@@ -14193,7 +14193,7 @@
         <v>14130.77264115309</v>
       </c>
       <c r="D836" s="3" t="n">
-        <v>15523.05525530989</v>
+        <v>15523.05687892186</v>
       </c>
     </row>
     <row r="837">
@@ -14209,7 +14209,7 @@
         <v>14055.71681486783</v>
       </c>
       <c r="D837" s="3" t="n">
-        <v>15336.7934691715</v>
+        <v>15336.79671446613</v>
       </c>
     </row>
     <row r="838">
@@ -14225,7 +14225,7 @@
         <v>14086.14566123259</v>
       </c>
       <c r="D838" s="3" t="n">
-        <v>15315.10610970746</v>
+        <v>15315.10448343854</v>
       </c>
     </row>
     <row r="839">
@@ -14241,7 +14241,7 @@
         <v>14086.14566123259</v>
       </c>
       <c r="D839" s="3" t="n">
-        <v>15315.10610970746</v>
+        <v>15315.10448343854</v>
       </c>
     </row>
     <row r="840">
@@ -14257,7 +14257,7 @@
         <v>14240.31421818077</v>
       </c>
       <c r="D840" s="3" t="n">
-        <v>15357.60193385827</v>
+        <v>15357.60029906021</v>
       </c>
     </row>
     <row r="841">
@@ -14273,7 +14273,7 @@
         <v>14211.91382400484</v>
       </c>
       <c r="D841" s="3" t="n">
-        <v>15676.30488993147</v>
+        <v>15676.308186165</v>
       </c>
     </row>
     <row r="842">
@@ -14283,13 +14283,13 @@
         </is>
       </c>
       <c r="B842" s="3" t="n">
-        <v>16315.39</v>
+        <v>16315.38</v>
       </c>
       <c r="C842" s="3" t="n">
         <v>14304.55094494816</v>
       </c>
       <c r="D842" s="3" t="n">
-        <v>15709.78325056815</v>
+        <v>15709.78489274485</v>
       </c>
     </row>
     <row r="843">
@@ -14305,7 +14305,7 @@
         <v>14206.50530601203</v>
       </c>
       <c r="D843" s="3" t="n">
-        <v>15411.03294619483</v>
+        <v>15411.03131682894</v>
       </c>
     </row>
     <row r="844">
@@ -14321,7 +14321,7 @@
         <v>14210.5622103897</v>
       </c>
       <c r="D844" s="3" t="n">
-        <v>15494.45869083183</v>
+        <v>15494.46032662846</v>
       </c>
     </row>
     <row r="845">
@@ -14331,13 +14331,13 @@
         </is>
       </c>
       <c r="B845" s="3" t="n">
-        <v>15972.23</v>
+        <v>15972.22</v>
       </c>
       <c r="C845" s="3" t="n">
         <v>14220.0286645263</v>
       </c>
       <c r="D845" s="3" t="n">
-        <v>15540.78484628314</v>
+        <v>15540.78648697056</v>
       </c>
     </row>
     <row r="846">
@@ -14353,7 +14353,7 @@
         <v>14083.44037047007</v>
       </c>
       <c r="D846" s="3" t="n">
-        <v>15328.92877041492</v>
+        <v>15328.93205723893</v>
       </c>
     </row>
     <row r="847">
@@ -14385,7 +14385,7 @@
         <v>14041.51764954599</v>
       </c>
       <c r="D848" s="3" t="n">
-        <v>15422.27050129249</v>
+        <v>15422.27214988315</v>
       </c>
     </row>
     <row r="849">
@@ -14401,7 +14401,7 @@
         <v>14261.95138545039</v>
       </c>
       <c r="D849" s="3" t="n">
-        <v>15639.45066756896</v>
+        <v>15639.44738368963</v>
       </c>
     </row>
     <row r="850">
@@ -14465,7 +14465,7 @@
         <v>14370.14031709681</v>
       </c>
       <c r="D853" s="3" t="n">
-        <v>15736.58040698656</v>
+        <v>15736.57878298529</v>
       </c>
     </row>
     <row r="854">
@@ -14481,7 +14481,7 @@
         <v>14495.90951163517</v>
       </c>
       <c r="D854" s="3" t="n">
-        <v>15847.47039196155</v>
+        <v>15847.47201826437</v>
       </c>
     </row>
     <row r="855">
@@ -14497,7 +14497,7 @@
         <v>14514.84241990838</v>
       </c>
       <c r="D855" s="3" t="n">
-        <v>15927.50204364604</v>
+        <v>15927.50041800323</v>
       </c>
     </row>
     <row r="856">
@@ -14529,7 +14529,7 @@
         <v>14213.9433079598</v>
       </c>
       <c r="D857" s="3" t="n">
-        <v>15570.46802173046</v>
+        <v>15570.46640500616</v>
       </c>
     </row>
     <row r="858">
@@ -14561,7 +14561,7 @@
         <v>14445.87195018963</v>
       </c>
       <c r="D859" s="3" t="n">
-        <v>15691.62078005441</v>
+        <v>15691.62240275255</v>
       </c>
     </row>
     <row r="860">
@@ -14593,7 +14593,7 @@
         <v>14629.79251492888</v>
       </c>
       <c r="D861" s="3" t="n">
-        <v>15739.83439285807</v>
+        <v>15739.83276520135</v>
       </c>
     </row>
     <row r="862">
@@ -14609,7 +14609,7 @@
         <v>14503.34751358294</v>
       </c>
       <c r="D862" s="3" t="n">
-        <v>15861.96738362094</v>
+        <v>15861.96573222116</v>
       </c>
     </row>
     <row r="863">
@@ -14641,7 +14641,7 @@
         <v>14458.71950189633</v>
       </c>
       <c r="D864" s="3" t="n">
-        <v>15839.89414297394</v>
+        <v>15839.89740597025</v>
       </c>
     </row>
     <row r="865">
@@ -14657,7 +14657,7 @@
         <v>14622.35451298111</v>
       </c>
       <c r="D865" s="3" t="n">
-        <v>15852.08211615938</v>
+        <v>15852.08374325756</v>
       </c>
     </row>
     <row r="866">
@@ -14667,7 +14667,7 @@
         </is>
       </c>
       <c r="B866" s="3" t="n">
-        <v>16139.74</v>
+        <v>16139.73</v>
       </c>
       <c r="C866" s="3" t="n">
         <v>14594.63095737888</v>
@@ -14689,7 +14689,7 @@
         <v>14675.09633342306</v>
       </c>
       <c r="D867" s="3" t="n">
-        <v>15950.49207406372</v>
+        <v>15950.49371524202</v>
       </c>
     </row>
     <row r="868">
@@ -14737,7 +14737,7 @@
         <v>14622.35451298111</v>
       </c>
       <c r="D870" s="3" t="n">
-        <v>15954.83323932397</v>
+        <v>15954.82998235252</v>
       </c>
     </row>
     <row r="871">
@@ -14833,7 +14833,7 @@
         <v>14581.78340567217</v>
       </c>
       <c r="D876" s="3" t="n">
-        <v>15536.33364488654</v>
+        <v>15536.33203323936</v>
       </c>
     </row>
     <row r="877">
@@ -14849,7 +14849,7 @@
         <v>14420.17684677623</v>
       </c>
       <c r="D877" s="3" t="n">
-        <v>15503.63567929363</v>
+        <v>15503.6389105082</v>
       </c>
     </row>
     <row r="878">
@@ -14865,7 +14865,7 @@
         <v>14199.74311087183</v>
       </c>
       <c r="D878" s="3" t="n">
-        <v>15446.41371635351</v>
+        <v>15446.41048097566</v>
       </c>
     </row>
     <row r="879">
@@ -14881,7 +14881,7 @@
         <v>14387.04477318118</v>
       </c>
       <c r="D879" s="3" t="n">
-        <v>15362.05409875195</v>
+        <v>15362.05570679457</v>
       </c>
     </row>
     <row r="880">
@@ -14891,13 +14891,13 @@
         </is>
       </c>
       <c r="B880" s="3" t="n">
-        <v>15756.9</v>
+        <v>15756.89</v>
       </c>
       <c r="C880" s="3" t="n">
         <v>14412.73884482846</v>
       </c>
       <c r="D880" s="3" t="n">
-        <v>15167.75568389203</v>
+        <v>15167.75407043403</v>
       </c>
     </row>
     <row r="881">
@@ -14913,7 +14913,7 @@
         <v>14259.92293326155</v>
       </c>
       <c r="D881" s="3" t="n">
-        <v>15543.25094700938</v>
+        <v>15543.24931901425</v>
       </c>
     </row>
     <row r="882">
@@ -14945,7 +14945,7 @@
         <v>13822.43552725673</v>
       </c>
       <c r="D883" s="3" t="n">
-        <v>14960.76022884364</v>
+        <v>14960.75861481018</v>
       </c>
     </row>
     <row r="884">
@@ -14961,7 +14961,7 @@
         <v>13624.31579719564</v>
       </c>
       <c r="D884" s="3" t="n">
-        <v>14919.56260371273</v>
+        <v>14919.5641961859</v>
       </c>
     </row>
     <row r="885">
@@ -14977,7 +14977,7 @@
         <v>13664.88587273846</v>
       </c>
       <c r="D885" s="3" t="n">
-        <v>14426.72774766535</v>
+        <v>14426.72617996758</v>
       </c>
     </row>
     <row r="886">
@@ -14993,7 +14993,7 @@
         <v>13411.31903147289</v>
       </c>
       <c r="D886" s="3" t="n">
-        <v>14516.98392325537</v>
+        <v>14516.98235454227</v>
       </c>
     </row>
     <row r="887">
@@ -15009,7 +15009,7 @@
         <v>13311.24494034793</v>
       </c>
       <c r="D887" s="3" t="n">
-        <v>14035.8024172764</v>
+        <v>14035.80397549711</v>
       </c>
     </row>
     <row r="888">
@@ -15041,7 +15041,7 @@
         <v>13171.27554872159</v>
       </c>
       <c r="D889" s="3" t="n">
-        <v>13924.29592169047</v>
+        <v>13924.29747226191</v>
       </c>
     </row>
     <row r="890">
@@ -15057,7 +15057,7 @@
         <v>13080.66791173323</v>
       </c>
       <c r="D890" s="3" t="n">
-        <v>13773.918822143</v>
+        <v>13773.91571304626</v>
       </c>
     </row>
     <row r="891">
@@ -15105,7 +15105,7 @@
         <v>13234.83646868141</v>
       </c>
       <c r="D893" s="3" t="n">
-        <v>13971.45729356803</v>
+        <v>13971.45884342866</v>
       </c>
     </row>
     <row r="894">
@@ -15121,7 +15121,7 @@
         <v>13370.07211735638</v>
       </c>
       <c r="D894" s="3" t="n">
-        <v>14097.39983982273</v>
+        <v>14097.40138680647</v>
       </c>
     </row>
     <row r="895">
@@ -15137,7 +15137,7 @@
         <v>13413.34748366173</v>
       </c>
       <c r="D895" s="3" t="n">
-        <v>14092.15472032389</v>
+        <v>14092.15937300275</v>
       </c>
     </row>
     <row r="896">
@@ -15153,7 +15153,7 @@
         <v>13385.62495982561</v>
       </c>
       <c r="D896" s="3" t="n">
-        <v>14168.48588590081</v>
+        <v>14168.48744467998</v>
       </c>
     </row>
     <row r="897">
@@ -15169,7 +15169,7 @@
         <v>13616.20095667418</v>
       </c>
       <c r="D897" s="3" t="n">
-        <v>14450.09516534867</v>
+        <v>14450.09360355712</v>
       </c>
     </row>
     <row r="898">
@@ -15179,7 +15179,7 @@
         </is>
       </c>
       <c r="B898" s="3" t="n">
-        <v>15148.22</v>
+        <v>15148.21</v>
       </c>
       <c r="C898" s="3" t="n">
         <v>13637.16231713622</v>
@@ -15217,7 +15217,7 @@
         <v>13516.12686554921</v>
       </c>
       <c r="D900" s="3" t="n">
-        <v>14398.40693738545</v>
+        <v>14398.40378655597</v>
       </c>
     </row>
     <row r="901">
@@ -15249,7 +15249,7 @@
         <v>13134.76237755645</v>
       </c>
       <c r="D902" s="3" t="n">
-        <v>14095.7460257801</v>
+        <v>14095.74446227931</v>
       </c>
     </row>
     <row r="903">
@@ -15345,7 +15345,7 @@
         <v>12096.82836126961</v>
       </c>
       <c r="D908" s="3" t="n">
-        <v>12405.70113753217</v>
+        <v>12405.70191273331</v>
       </c>
     </row>
     <row r="909">
@@ -15361,7 +15361,7 @@
         <v>11538.98131048535</v>
       </c>
       <c r="D909" s="3" t="n">
-        <v>13627.28547427465</v>
+        <v>13627.28855670038</v>
       </c>
     </row>
     <row r="910">
@@ -15377,7 +15377,7 @@
         <v>11996.07846333707</v>
       </c>
       <c r="D910" s="3" t="n">
-        <v>13063.91988315608</v>
+        <v>13063.92142836287</v>
       </c>
     </row>
     <row r="911">
@@ -15393,7 +15393,7 @@
         <v>11874.36617317637</v>
       </c>
       <c r="D911" s="3" t="n">
-        <v>12935.8541291534</v>
+        <v>12935.85563239066</v>
       </c>
     </row>
     <row r="912">
@@ -15403,13 +15403,13 @@
         </is>
       </c>
       <c r="B912" s="3" t="n">
-        <v>13849.96</v>
+        <v>13849.95</v>
       </c>
       <c r="C912" s="3" t="n">
         <v>12217.18800604904</v>
       </c>
       <c r="D912" s="3" t="n">
-        <v>12963.12665930834</v>
+        <v>12963.12815124081</v>
       </c>
     </row>
     <row r="913">
@@ -15441,7 +15441,7 @@
         <v>12188.11283683166</v>
       </c>
       <c r="D914" s="3" t="n">
-        <v>12695.96760202893</v>
+        <v>12695.97059922946</v>
       </c>
     </row>
     <row r="915">
@@ -15505,7 +15505,7 @@
         <v>11972.4118121125</v>
       </c>
       <c r="D918" s="3" t="n">
-        <v>12490.91038452162</v>
+        <v>12490.91185447093</v>
       </c>
     </row>
     <row r="919">
@@ -15537,7 +15537,7 @@
         <v>12430.18477177179</v>
       </c>
       <c r="D920" s="3" t="n">
-        <v>13163.49099874665</v>
+        <v>13163.48950473253</v>
       </c>
     </row>
     <row r="921">
@@ -15563,13 +15563,13 @@
         </is>
       </c>
       <c r="B922" s="3" t="n">
-        <v>14180.74</v>
+        <v>14180.73</v>
       </c>
       <c r="C922" s="3" t="n">
         <v>12516.73550438248</v>
       </c>
       <c r="D922" s="3" t="n">
-        <v>13245.17499959033</v>
+        <v>13245.17350765787</v>
       </c>
     </row>
     <row r="923">
@@ -15579,13 +15579,13 @@
         </is>
       </c>
       <c r="B923" s="3" t="n">
-        <v>14209.72</v>
+        <v>14209.71</v>
       </c>
       <c r="C923" s="3" t="n">
         <v>12575.56268139093</v>
       </c>
       <c r="D923" s="3" t="n">
-        <v>13251.50734807745</v>
+        <v>13251.50586477575</v>
       </c>
     </row>
     <row r="924">
@@ -15601,7 +15601,7 @@
         <v>12621.5433384588</v>
       </c>
       <c r="D924" s="3" t="n">
-        <v>13279.90452068353</v>
+        <v>13279.9060065744</v>
       </c>
     </row>
     <row r="925">
@@ -15617,7 +15617,7 @@
         <v>12621.5433384588</v>
       </c>
       <c r="D925" s="3" t="n">
-        <v>13450.02723575601</v>
+        <v>13450.03022442747</v>
       </c>
     </row>
     <row r="926">
@@ -15633,7 +15633,7 @@
         <v>12930.55625916273</v>
       </c>
       <c r="D926" s="3" t="n">
-        <v>13683.99898167286</v>
+        <v>13684.00047976548</v>
       </c>
     </row>
     <row r="927">
@@ -15649,7 +15649,7 @@
         <v>12949.48916743594</v>
       </c>
       <c r="D927" s="3" t="n">
-        <v>13573.40955833507</v>
+        <v>13573.4080637794</v>
       </c>
     </row>
     <row r="928">
@@ -15665,7 +15665,7 @@
         <v>12886.60508604981</v>
       </c>
       <c r="D928" s="3" t="n">
-        <v>13471.69118697943</v>
+        <v>13471.6926828381</v>
       </c>
     </row>
     <row r="929">
@@ -15681,7 +15681,7 @@
         <v>12819.6630685199</v>
       </c>
       <c r="D929" s="3" t="n">
-        <v>13493.29822409285</v>
+        <v>13493.29673210958</v>
       </c>
     </row>
     <row r="930">
@@ -15697,7 +15697,7 @@
         <v>13030.63138205381</v>
       </c>
       <c r="D930" s="3" t="n">
-        <v>13631.24075667258</v>
+        <v>13631.23925986618</v>
       </c>
     </row>
     <row r="931">
@@ -15761,7 +15761,7 @@
         <v>13500.57505484611</v>
       </c>
       <c r="D934" s="3" t="n">
-        <v>14327.63586513003</v>
+        <v>14327.6328392276</v>
       </c>
     </row>
     <row r="935">
@@ -15793,7 +15793,7 @@
         <v>13651.36251422419</v>
       </c>
       <c r="D936" s="3" t="n">
-        <v>14479.57474105288</v>
+        <v>14479.57322906641</v>
       </c>
     </row>
     <row r="937">
@@ -15809,7 +15809,7 @@
         <v>13571.57397675369</v>
       </c>
       <c r="D937" s="3" t="n">
-        <v>14502.06522771087</v>
+        <v>14502.0637150305</v>
       </c>
     </row>
     <row r="938">
@@ -15819,13 +15819,13 @@
         </is>
       </c>
       <c r="B938" s="3" t="n">
-        <v>15214.41</v>
+        <v>15214.4</v>
       </c>
       <c r="C938" s="3" t="n">
         <v>13602.00179135234</v>
       </c>
       <c r="D938" s="3" t="n">
-        <v>14394.28691902913</v>
+        <v>14394.28541252562</v>
       </c>
     </row>
     <row r="939">
@@ -15835,13 +15835,13 @@
         </is>
       </c>
       <c r="B939" s="3" t="n">
-        <v>15145.93</v>
+        <v>15145.92</v>
       </c>
       <c r="C939" s="3" t="n">
         <v>13501.25086165368</v>
       </c>
       <c r="D939" s="3" t="n">
-        <v>14083.37254801658</v>
+        <v>14083.37404724309</v>
       </c>
     </row>
     <row r="940">
@@ -15857,7 +15857,7 @@
         <v>13393.06296177338</v>
       </c>
       <c r="D940" s="3" t="n">
-        <v>14035.17748094242</v>
+        <v>14035.17598743598</v>
       </c>
     </row>
     <row r="941">
@@ -15873,7 +15873,7 @@
         <v>13252.41776333947</v>
       </c>
       <c r="D941" s="3" t="n">
-        <v>14000.34427796815</v>
+        <v>14000.34277792944</v>
       </c>
     </row>
     <row r="942">
@@ -15889,7 +15889,7 @@
         <v>13373.45321492648</v>
       </c>
       <c r="D942" s="3" t="n">
-        <v>13888.3586172967</v>
+        <v>13888.35712925646</v>
       </c>
     </row>
     <row r="943">
@@ -15905,7 +15905,7 @@
         <v>13473.52730605144</v>
       </c>
       <c r="D943" s="3" t="n">
-        <v>14157.59384674704</v>
+        <v>14157.59533273948</v>
       </c>
     </row>
     <row r="944">
@@ -15937,7 +15937,7 @@
         <v>13424.84238998716</v>
       </c>
       <c r="D945" s="3" t="n">
-        <v>14325.98063731674</v>
+        <v>14325.98214378634</v>
       </c>
     </row>
     <row r="946">
@@ -15953,7 +15953,7 @@
         <v>13425.51922856085</v>
       </c>
       <c r="D946" s="3" t="n">
-        <v>14127.98433365779</v>
+        <v>14127.9828463453</v>
       </c>
     </row>
     <row r="947">
@@ -15995,7 +15995,7 @@
         </is>
       </c>
       <c r="B949" s="3" t="n">
-        <v>15113.65</v>
+        <v>15113.64</v>
       </c>
       <c r="C949" s="3" t="n">
         <v>13531.67867625232</v>
@@ -16017,7 +16017,7 @@
         <v>13543.17358257776</v>
       </c>
       <c r="D950" s="3" t="n">
-        <v>14161.36840690557</v>
+        <v>14161.36692527921</v>
       </c>
     </row>
     <row r="951">
@@ -16049,7 +16049,7 @@
         <v>13585.77314207554</v>
       </c>
       <c r="D952" s="3" t="n">
-        <v>14337.51094106659</v>
+        <v>14337.51242453755</v>
       </c>
     </row>
     <row r="953">
@@ -16059,13 +16059,13 @@
         </is>
       </c>
       <c r="B953" s="3" t="n">
-        <v>15188.59</v>
+        <v>15188.58</v>
       </c>
       <c r="C953" s="3" t="n">
         <v>13593.2111440233</v>
       </c>
       <c r="D953" s="3" t="n">
-        <v>14393.30526081357</v>
+        <v>14393.30822250932</v>
       </c>
     </row>
     <row r="954">
@@ -16107,13 +16107,13 @@
         </is>
       </c>
       <c r="B956" s="3" t="n">
-        <v>14973.9</v>
+        <v>14973.89</v>
       </c>
       <c r="C956" s="3" t="n">
         <v>13421.46232418319</v>
       </c>
       <c r="D956" s="3" t="n">
-        <v>14036.68494299207</v>
+        <v>14036.68348412744</v>
       </c>
     </row>
     <row r="957">
@@ -16193,7 +16193,7 @@
         <v>13364.66256759745</v>
       </c>
       <c r="D961" s="3" t="n">
-        <v>14120.5211726403</v>
+        <v>14120.519702691</v>
       </c>
     </row>
     <row r="962">
@@ -16209,7 +16209,7 @@
         <v>13338.96849595016</v>
       </c>
       <c r="D962" s="3" t="n">
-        <v>14274.7707687128</v>
+        <v>14274.76929724046</v>
       </c>
     </row>
     <row r="963">
@@ -16219,13 +16219,13 @@
         </is>
       </c>
       <c r="B963" s="3" t="n">
-        <v>15020.01</v>
+        <v>15020</v>
       </c>
       <c r="C963" s="3" t="n">
         <v>13463.38504510727</v>
       </c>
       <c r="D963" s="3" t="n">
-        <v>14310.30107069665</v>
+        <v>14310.30252971347</v>
       </c>
     </row>
     <row r="964">
@@ -16241,7 +16241,7 @@
         <v>13449.86168659299</v>
       </c>
       <c r="D964" s="3" t="n">
-        <v>14302.04370335589</v>
+        <v>14302.04516071435</v>
       </c>
     </row>
     <row r="965">
@@ -16257,7 +16257,7 @@
         <v>13459.3281407296</v>
       </c>
       <c r="D965" s="3" t="n">
-        <v>14325.73127819149</v>
+        <v>14325.7327266314</v>
       </c>
     </row>
     <row r="966">
@@ -16289,7 +16289,7 @@
         <v>13543.17358257776</v>
       </c>
       <c r="D967" s="3" t="n">
-        <v>14411.82525686522</v>
+        <v>14411.82814294812</v>
       </c>
     </row>
     <row r="968">
@@ -16305,7 +16305,7 @@
         <v>13522.88906068941</v>
       </c>
       <c r="D968" s="3" t="n">
-        <v>14334.17256180014</v>
+        <v>14334.17399753079</v>
       </c>
     </row>
     <row r="969">
@@ -16321,7 +16321,7 @@
         <v>13550.61158452553</v>
       </c>
       <c r="D969" s="3" t="n">
-        <v>14376.75064166647</v>
+        <v>14376.74777467305</v>
       </c>
     </row>
     <row r="970">
@@ -16337,7 +16337,7 @@
         <v>13692.6094283407</v>
       </c>
       <c r="D970" s="3" t="n">
-        <v>14496.56080371442</v>
+        <v>14496.55793543475</v>
       </c>
     </row>
     <row r="971">
@@ -16353,7 +16353,7 @@
         <v>13597.94488697466</v>
       </c>
       <c r="D971" s="3" t="n">
-        <v>14531.97039235328</v>
+        <v>14531.96751706749</v>
       </c>
     </row>
     <row r="972">
@@ -16385,7 +16385,7 @@
         <v>13637.16231713622</v>
       </c>
       <c r="D973" s="3" t="n">
-        <v>14458.70834934325</v>
+        <v>14458.70979126768</v>
       </c>
     </row>
     <row r="974">
@@ -16433,7 +16433,7 @@
         <v>13698.6947849072</v>
       </c>
       <c r="D976" s="3" t="n">
-        <v>14577.12571783192</v>
+        <v>14577.12282565669</v>
       </c>
     </row>
     <row r="977">
@@ -16459,7 +16459,7 @@
         </is>
       </c>
       <c r="B978" s="3" t="n">
-        <v>15388.75</v>
+        <v>15388.74</v>
       </c>
       <c r="C978" s="3" t="n">
         <v>13799.44571460586</v>
@@ -16475,13 +16475,13 @@
         </is>
       </c>
       <c r="B979" s="3" t="n">
-        <v>15306.99</v>
+        <v>15306.98</v>
       </c>
       <c r="C979" s="3" t="n">
         <v>13606.05869573001</v>
       </c>
       <c r="D979" s="3" t="n">
-        <v>14711.01724194448</v>
+        <v>14711.0186999121</v>
       </c>
     </row>
     <row r="980">
@@ -16497,7 +16497,7 @@
         <v>13866.38773213577</v>
       </c>
       <c r="D980" s="3" t="n">
-        <v>14764.96757967242</v>
+        <v>14764.96612525862</v>
       </c>
     </row>
     <row r="981">
@@ -16513,7 +16513,7 @@
         <v>13819.05442968664</v>
       </c>
       <c r="D981" s="3" t="n">
-        <v>14779.90181894021</v>
+        <v>14779.90473284467</v>
       </c>
     </row>
     <row r="982">
@@ -16529,7 +16529,7 @@
         <v>13835.95888577101</v>
       </c>
       <c r="D982" s="3" t="n">
-        <v>14788.49311680628</v>
+        <v>14788.49602688639</v>
       </c>
     </row>
     <row r="983">
@@ -16539,7 +16539,7 @@
         </is>
       </c>
       <c r="B983" s="3" t="n">
-        <v>15428.26</v>
+        <v>15428.25</v>
       </c>
       <c r="C983" s="3" t="n">
         <v>13743.99860340138</v>
@@ -16561,7 +16561,7 @@
         <v>13859.62553699557</v>
       </c>
       <c r="D984" s="3" t="n">
-        <v>14778.68853526838</v>
+        <v>14778.68997687127</v>
       </c>
     </row>
     <row r="985">
@@ -16593,7 +16593,7 @@
         <v>13919.80535938529</v>
       </c>
       <c r="D986" s="3" t="n">
-        <v>14824.59735164175</v>
+        <v>14824.59591212048</v>
       </c>
     </row>
     <row r="987">
@@ -16603,13 +16603,13 @@
         </is>
       </c>
       <c r="B987" s="3" t="n">
-        <v>15570.62</v>
+        <v>15570.61</v>
       </c>
       <c r="C987" s="3" t="n">
         <v>14038.13655197589</v>
       </c>
       <c r="D987" s="3" t="n">
-        <v>14820.0046428562</v>
+        <v>14820.00320341945</v>
       </c>
     </row>
     <row r="988">
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="B990" s="3" t="n">
-        <v>15780.11</v>
+        <v>15780.1</v>
       </c>
       <c r="C990" s="3" t="n">
         <v>14190.9524635428</v>
       </c>
       <c r="D990" s="3" t="n">
-        <v>15128.296025122</v>
+        <v>15128.2975058006</v>
       </c>
     </row>
     <row r="991">
@@ -16667,7 +16667,7 @@
         </is>
       </c>
       <c r="B991" s="3" t="n">
-        <v>15449.17</v>
+        <v>15449.16</v>
       </c>
       <c r="C991" s="3" t="n">
         <v>13771.04635219605</v>
@@ -16689,7 +16689,7 @@
         <v>13935.3571700884</v>
       </c>
       <c r="D992" s="3" t="n">
-        <v>14901.39871714336</v>
+        <v>14901.39725656959</v>
       </c>
     </row>
     <row r="993">
@@ -16705,7 +16705,7 @@
         <v>13902.22509649335</v>
       </c>
       <c r="D993" s="3" t="n">
-        <v>14829.11551569112</v>
+        <v>14829.11259390028</v>
       </c>
     </row>
     <row r="994">
@@ -16769,7 +16769,7 @@
         <v>14086.14566123259</v>
       </c>
       <c r="D997" s="3" t="n">
-        <v>14934.56644491076</v>
+        <v>14934.56499202012</v>
       </c>
     </row>
     <row r="998">
@@ -16785,7 +16785,7 @@
         <v>14089.52572703657</v>
       </c>
       <c r="D998" s="3" t="n">
-        <v>15131.88673796537</v>
+        <v>15131.88528138536</v>
       </c>
     </row>
     <row r="999">
@@ -16795,13 +16795,13 @@
         </is>
       </c>
       <c r="B999" s="3" t="n">
-        <v>16027.89</v>
+        <v>16027.88</v>
       </c>
       <c r="C999" s="3" t="n">
         <v>14106.43018312095</v>
       </c>
       <c r="D999" s="3" t="n">
-        <v>15107.47600225823</v>
+        <v>15107.47455298906</v>
       </c>
     </row>
     <row r="1000">
@@ -16817,7 +16817,7 @@
         <v>14180.81020259863</v>
       </c>
       <c r="D1000" s="3" t="n">
-        <v>15062.65638152942</v>
+        <v>15062.6578263647</v>
       </c>
     </row>
     <row r="1001">
@@ -16827,13 +16827,13 @@
         </is>
       </c>
       <c r="B1001" s="3" t="n">
-        <v>15914.54</v>
+        <v>15914.53</v>
       </c>
       <c r="C1001" s="3" t="n">
         <v>14142.26754747852</v>
       </c>
       <c r="D1001" s="3" t="n">
-        <v>15106.77387203479</v>
+        <v>15106.77241956722</v>
       </c>
     </row>
     <row r="1002">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="B1002" s="3" t="n">
-        <v>15870.76</v>
+        <v>15870.75</v>
       </c>
       <c r="C1002" s="3" t="n">
         <v>14165.93419870309</v>
       </c>
       <c r="D1002" s="3" t="n">
-        <v>15032.21445928346</v>
+        <v>15032.21590489706</v>
       </c>
     </row>
     <row r="1003">
@@ -16865,7 +16865,7 @@
         <v>14163.90574651426</v>
       </c>
       <c r="D1003" s="3" t="n">
-        <v>14999.66777357233</v>
+        <v>14999.6721246291</v>
       </c>
     </row>
     <row r="1004">
@@ -16881,7 +16881,7 @@
         <v>14084.79301585133</v>
       </c>
       <c r="D1004" s="3" t="n">
-        <v>14992.98053368429</v>
+        <v>14992.98198725194</v>
       </c>
     </row>
     <row r="1005">
@@ -16945,7 +16945,7 @@
         <v>14171.34374846202</v>
       </c>
       <c r="D1008" s="3" t="n">
-        <v>15190.04215116138</v>
+        <v>15190.04069458138</v>
       </c>
     </row>
     <row r="1009">
@@ -16971,13 +16971,13 @@
         </is>
       </c>
       <c r="B1010" s="3" t="n">
-        <v>16015.72</v>
+        <v>16015.71</v>
       </c>
       <c r="C1010" s="3" t="n">
         <v>14243.69428398475</v>
       </c>
       <c r="D1010" s="3" t="n">
-        <v>15239.869617548</v>
+        <v>15239.86816465737</v>
       </c>
     </row>
     <row r="1011">
@@ -16993,7 +16993,7 @@
         <v>14144.29599966736</v>
       </c>
       <c r="D1011" s="3" t="n">
-        <v>15105.39944300381</v>
+        <v>15105.40089171452</v>
       </c>
     </row>
     <row r="1012">
@@ -17003,13 +17003,13 @@
         </is>
       </c>
       <c r="B1012" s="3" t="n">
-        <v>15835.48</v>
+        <v>15835.47</v>
       </c>
       <c r="C1012" s="3" t="n">
         <v>14176.75329822096</v>
       </c>
       <c r="D1012" s="3" t="n">
-        <v>15092.16500201281</v>
+        <v>15092.16644945425</v>
       </c>
     </row>
     <row r="1013">
@@ -17025,7 +17025,7 @@
         <v>14022.58474127278</v>
       </c>
       <c r="D1013" s="3" t="n">
-        <v>14949.50351576087</v>
+        <v>14949.50207129796</v>
       </c>
     </row>
     <row r="1014">
@@ -17035,13 +17035,13 @@
         </is>
       </c>
       <c r="B1014" s="3" t="n">
-        <v>15895.53</v>
+        <v>15895.52</v>
       </c>
       <c r="C1014" s="3" t="n">
         <v>14115.22083044998</v>
       </c>
       <c r="D1014" s="3" t="n">
-        <v>15133.71230261358</v>
+        <v>15133.71375699342</v>
       </c>
     </row>
     <row r="1015">
@@ -17051,7 +17051,7 @@
         </is>
       </c>
       <c r="B1015" s="3" t="n">
-        <v>15952.57</v>
+        <v>15952.56</v>
       </c>
       <c r="C1015" s="3" t="n">
         <v>14236.25628203698</v>
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="B1017" s="3" t="n">
-        <v>16013.32</v>
+        <v>16013.31</v>
       </c>
       <c r="C1017" s="3" t="n">
         <v>14226.78982790038</v>
@@ -17121,7 +17121,7 @@
         <v>14304.55094494816</v>
       </c>
       <c r="D1019" s="3" t="n">
-        <v>15245.41631136573</v>
+        <v>15245.41486527812</v>
       </c>
     </row>
     <row r="1020">
@@ -17137,7 +17137,7 @@
         <v>14395.15858193652</v>
       </c>
       <c r="D1020" s="3" t="n">
-        <v>15371.20627925504</v>
+        <v>15371.20772525796</v>
       </c>
     </row>
     <row r="1021">
@@ -17153,7 +17153,7 @@
         <v>14401.24393850302</v>
       </c>
       <c r="D1021" s="3" t="n">
-        <v>15325.06187603772</v>
+        <v>15325.06331818216</v>
       </c>
     </row>
     <row r="1022">
@@ -17185,7 +17185,7 @@
         <v>14299.8172019968</v>
       </c>
       <c r="D1023" s="3" t="n">
-        <v>15347.52300202312</v>
+        <v>15347.5244406137</v>
       </c>
     </row>
     <row r="1024">
@@ -17201,7 +17201,7 @@
         <v>14288.32229567136</v>
       </c>
       <c r="D1024" s="3" t="n">
-        <v>15189.43167478068</v>
+        <v>15189.43310032357</v>
       </c>
     </row>
     <row r="1025">
@@ -17217,7 +17217,7 @@
         <v>14444.51930480837</v>
       </c>
       <c r="D1025" s="3" t="n">
-        <v>15318.5557018718</v>
+        <v>15318.55713284705</v>
       </c>
     </row>
     <row r="1026">
@@ -17233,7 +17233,7 @@
         <v>14460.0721472776</v>
       </c>
       <c r="D1026" s="3" t="n">
-        <v>15440.48748728903</v>
+        <v>15440.48605203231</v>
       </c>
     </row>
     <row r="1027">
@@ -17265,7 +17265,7 @@
         <v>14503.34751358294</v>
       </c>
       <c r="D1028" s="3" t="n">
-        <v>15415.99038731451</v>
+        <v>15415.98895327623</v>
       </c>
     </row>
     <row r="1029">
@@ -17281,7 +17281,7 @@
         <v>14485.09041211731</v>
       </c>
       <c r="D1029" s="3" t="n">
-        <v>15349.53106053148</v>
+        <v>15349.53249294511</v>
       </c>
     </row>
     <row r="1030">
@@ -17329,7 +17329,7 @@
         <v>14520.25196966731</v>
       </c>
       <c r="D1032" s="3" t="n">
-        <v>15549.25488474328</v>
+        <v>15549.25343933265</v>
       </c>
     </row>
     <row r="1033">
@@ -17345,7 +17345,7 @@
         <v>14499.96641601285</v>
       </c>
       <c r="D1033" s="3" t="n">
-        <v>15576.94193065125</v>
+        <v>15576.94337320192</v>
       </c>
     </row>
     <row r="1034">
@@ -17371,7 +17371,7 @@
         </is>
       </c>
       <c r="B1035" s="3" t="n">
-        <v>16782.81</v>
+        <v>16782.8</v>
       </c>
       <c r="C1035" s="3" t="n">
         <v>14659.54452271995</v>
@@ -17393,7 +17393,7 @@
         <v>14722.42860410608</v>
       </c>
       <c r="D1036" s="3" t="n">
-        <v>15656.23721684333</v>
+        <v>15656.23577351432</v>
       </c>
     </row>
     <row r="1037">
@@ -17409,7 +17409,7 @@
         <v>14773.14197235919</v>
       </c>
       <c r="D1037" s="3" t="n">
-        <v>15729.3340979263</v>
+        <v>15729.33265304028</v>
       </c>
     </row>
     <row r="1038">
@@ -17425,7 +17425,7 @@
         <v>14749.47635290074</v>
       </c>
       <c r="D1038" s="3" t="n">
-        <v>15673.95398271383</v>
+        <v>15673.95253755702</v>
       </c>
     </row>
     <row r="1039">
@@ -17457,7 +17457,7 @@
         <v>14880.65509719804</v>
       </c>
       <c r="D1040" s="3" t="n">
-        <v>15827.60059346504</v>
+        <v>15827.60204835269</v>
       </c>
     </row>
     <row r="1041">
@@ -17489,7 +17489,7 @@
         <v>14707.55260021054</v>
       </c>
       <c r="D1042" s="3" t="n">
-        <v>15675.94059878206</v>
+        <v>15675.94205737585</v>
       </c>
     </row>
     <row r="1043">
@@ -17505,7 +17505,7 @@
         <v>14633.84941930655</v>
       </c>
       <c r="D1043" s="3" t="n">
-        <v>15704.9294757408</v>
+        <v>15704.93093881921</v>
       </c>
     </row>
     <row r="1044">
@@ -17521,7 +17521,7 @@
         <v>14731.21925143511</v>
       </c>
       <c r="D1044" s="3" t="n">
-        <v>15726.48259566</v>
+        <v>15726.48405427072</v>
       </c>
     </row>
     <row r="1045">
@@ -17531,13 +17531,13 @@
         </is>
       </c>
       <c r="B1045" s="3" t="n">
-        <v>16870.88</v>
+        <v>16870.87</v>
       </c>
       <c r="C1045" s="3" t="n">
         <v>14706.87679340297</v>
       </c>
       <c r="D1045" s="3" t="n">
-        <v>15560.30647272796</v>
+        <v>15560.30501963418</v>
       </c>
     </row>
     <row r="1046">
@@ -17553,7 +17553,7 @@
         <v>14560.82204521013</v>
       </c>
       <c r="D1046" s="3" t="n">
-        <v>15577.36998254505</v>
+        <v>15577.36853606829</v>
       </c>
     </row>
     <row r="1047">
@@ -17563,13 +17563,13 @@
         </is>
       </c>
       <c r="B1047" s="3" t="n">
-        <v>17052.57</v>
+        <v>17052.56</v>
       </c>
       <c r="C1047" s="3" t="n">
         <v>14808.97933671677</v>
       </c>
       <c r="D1047" s="3" t="n">
-        <v>15796.28365489177</v>
+        <v>15796.28220318571</v>
       </c>
     </row>
     <row r="1048">
@@ -17601,7 +17601,7 @@
         <v>14784.63687868463</v>
       </c>
       <c r="D1049" s="3" t="n">
-        <v>15791.22979121783</v>
+        <v>15791.22833237013</v>
       </c>
     </row>
     <row r="1050">
@@ -17659,7 +17659,7 @@
         </is>
       </c>
       <c r="B1053" s="3" t="n">
-        <v>17220.22</v>
+        <v>17220.21</v>
       </c>
       <c r="C1053" s="3" t="n">
         <v>15088.24128139574</v>
@@ -17697,7 +17697,7 @@
         <v>15134.89774527118</v>
       </c>
       <c r="D1055" s="3" t="n">
-        <v>16071.59365133157</v>
+        <v>16071.59656828207</v>
       </c>
     </row>
     <row r="1056">
@@ -17713,7 +17713,7 @@
         <v>15117.31748237924</v>
       </c>
       <c r="D1056" s="3" t="n">
-        <v>16167.34592184616</v>
+        <v>16167.34445947852</v>
       </c>
     </row>
     <row r="1057">
@@ -17777,7 +17777,7 @@
         <v>14905.67336203775</v>
       </c>
       <c r="D1060" s="3" t="n">
-        <v>15993.45082383281</v>
+        <v>15993.44935183592</v>
       </c>
     </row>
     <row r="1061">
@@ -17809,7 +17809,7 @@
         <v>15002.36635559262</v>
       </c>
       <c r="D1062" s="3" t="n">
-        <v>16192.65312829806</v>
+        <v>16192.65019631956</v>
       </c>
     </row>
     <row r="1063">
@@ -17825,7 +17825,7 @@
         <v>15057.1366282234</v>
       </c>
       <c r="D1063" s="3" t="n">
-        <v>16210.98619196897</v>
+        <v>16210.9847276721</v>
       </c>
     </row>
     <row r="1064">
@@ -17841,7 +17841,7 @@
         <v>15140.98310183769</v>
       </c>
       <c r="D1064" s="3" t="n">
-        <v>16177.63879845642</v>
+        <v>16177.64025892861</v>
       </c>
     </row>
     <row r="1065">
@@ -17851,13 +17851,13 @@
         </is>
       </c>
       <c r="B1065" s="3" t="n">
-        <v>16905.9</v>
+        <v>16905.89</v>
       </c>
       <c r="C1065" s="3" t="n">
         <v>14945.567630773</v>
       </c>
       <c r="D1065" s="3" t="n">
-        <v>15902.73559599453</v>
+        <v>15902.73705587453</v>
       </c>
     </row>
     <row r="1066">
@@ -17873,7 +17873,7 @@
         <v>14902.96807127523</v>
       </c>
       <c r="D1066" s="3" t="n">
-        <v>15845.76050118081</v>
+        <v>15845.75904629315</v>
       </c>
     </row>
     <row r="1067">
@@ -17889,7 +17889,7 @@
         <v>14842.11244207794</v>
       </c>
       <c r="D1067" s="3" t="n">
-        <v>15720.59503262074</v>
+        <v>15720.59357565147</v>
       </c>
     </row>
     <row r="1068">
@@ -17921,7 +17921,7 @@
         <v>14683.88698075209</v>
       </c>
       <c r="D1069" s="3" t="n">
-        <v>15694.97128874086</v>
+        <v>15694.96982747311</v>
       </c>
     </row>
     <row r="1070">
@@ -17953,7 +17953,7 @@
         <v>14619.65025398471</v>
       </c>
       <c r="D1071" s="3" t="n">
-        <v>15672.79175125864</v>
+        <v>15672.79321843255</v>
       </c>
     </row>
     <row r="1072">
@@ -18001,7 +18001,7 @@
         <v>15020.62345705825</v>
       </c>
       <c r="D1074" s="3" t="n">
-        <v>16121.56064608657</v>
+        <v>16121.55918275419</v>
       </c>
     </row>
     <row r="1075">
@@ -18017,7 +18017,7 @@
         <v>15010.48119611408</v>
       </c>
       <c r="D1075" s="3" t="n">
-        <v>16069.72857749051</v>
+        <v>16069.72711886285</v>
       </c>
     </row>
     <row r="1076">
@@ -18049,7 +18049,7 @@
         <v>15007.10009854398</v>
       </c>
       <c r="D1077" s="3" t="n">
-        <v>16084.61118464369</v>
+        <v>16084.60972593135</v>
       </c>
     </row>
     <row r="1078">
@@ -18065,7 +18065,7 @@
         <v>15009.80435754039</v>
       </c>
       <c r="D1078" s="3" t="n">
-        <v>16105.80179642143</v>
+        <v>16105.80325435521</v>
       </c>
     </row>
     <row r="1079">
@@ -18113,7 +18113,7 @@
         <v>15105.14573748011</v>
       </c>
       <c r="D1081" s="3" t="n">
-        <v>16155.20604164296</v>
+        <v>16155.20458810925</v>
       </c>
     </row>
     <row r="1082">
@@ -18129,7 +18129,7 @@
         <v>15080.80327944797</v>
       </c>
       <c r="D1082" s="3" t="n">
-        <v>16110.23548925735</v>
+        <v>16110.2369431126</v>
       </c>
     </row>
     <row r="1083">
@@ -18145,7 +18145,7 @@
         <v>15097.03192872477</v>
       </c>
       <c r="D1083" s="3" t="n">
-        <v>16094.64482488122</v>
+        <v>16094.64627858432</v>
       </c>
     </row>
     <row r="1084">
@@ -18177,7 +18177,7 @@
         <v>15007.77590535155</v>
       </c>
       <c r="D1085" s="3" t="n">
-        <v>16156.0965020634</v>
+        <v>16156.09794833723</v>
       </c>
     </row>
     <row r="1086">
@@ -18193,7 +18193,7 @@
         <v>14915.13981617436</v>
       </c>
       <c r="D1086" s="3" t="n">
-        <v>15930.3962956474</v>
+        <v>15930.39485407833</v>
       </c>
     </row>
     <row r="1087">
@@ -18209,7 +18209,7 @@
         <v>14942.8633717766</v>
       </c>
       <c r="D1087" s="3" t="n">
-        <v>15908.75591188333</v>
+        <v>15908.75447009422</v>
       </c>
     </row>
     <row r="1088">
@@ -18241,7 +18241,7 @@
         <v>14779.22836069182</v>
       </c>
       <c r="D1089" s="3" t="n">
-        <v>15674.87280653299</v>
+        <v>15674.87424686674</v>
       </c>
     </row>
     <row r="1090">
@@ -18251,13 +18251,13 @@
         </is>
       </c>
       <c r="B1090" s="3" t="n">
-        <v>16829.7</v>
+        <v>16829.69</v>
       </c>
       <c r="C1090" s="3" t="n">
         <v>14933.39691763999</v>
       </c>
       <c r="D1090" s="3" t="n">
-        <v>15802.88836906109</v>
+        <v>15802.88692784736</v>
       </c>
     </row>
     <row r="1091">
@@ -18289,7 +18289,7 @@
         <v>15033.47100876496</v>
       </c>
       <c r="D1092" s="3" t="n">
-        <v>16092.37278522197</v>
+        <v>16092.37423064952</v>
       </c>
     </row>
     <row r="1093">
@@ -18299,7 +18299,7 @@
         </is>
       </c>
       <c r="B1093" s="3" t="n">
-        <v>17090.02</v>
+        <v>17090.01</v>
       </c>
       <c r="C1093" s="3" t="n">
         <v>15065.25146874486</v>
@@ -18353,7 +18353,7 @@
         <v>15078.77482725914</v>
       </c>
       <c r="D1096" s="3" t="n">
-        <v>16114.78975849369</v>
+        <v>16114.79119444435</v>
       </c>
     </row>
     <row r="1097">
@@ -18363,7 +18363,7 @@
         </is>
       </c>
       <c r="B1097" s="3" t="n">
-        <v>17039.02</v>
+        <v>17039.01</v>
       </c>
       <c r="C1097" s="3" t="n">
         <v>15087.56547458817</v>
@@ -18513,7 +18513,7 @@
         <v>15445.26331135637</v>
       </c>
       <c r="D1106" s="3" t="n">
-        <v>16379.76844647394</v>
+        <v>16379.76989812923</v>
       </c>
     </row>
     <row r="1107">
@@ -18545,7 +18545,7 @@
         <v>15460.81512205948</v>
       </c>
       <c r="D1108" s="3" t="n">
-        <v>16359.90080291461</v>
+        <v>16359.89935239327</v>
       </c>
     </row>
     <row r="1109">
@@ -18577,7 +18577,7 @@
         <v>15542.63314348493</v>
       </c>
       <c r="D1110" s="3" t="n">
-        <v>16352.77005307735</v>
+        <v>16352.76859998358</v>
       </c>
     </row>
     <row r="1111">
@@ -18587,13 +18587,13 @@
         </is>
       </c>
       <c r="B1111" s="3" t="n">
-        <v>17673.21</v>
+        <v>17673.2</v>
       </c>
       <c r="C1111" s="3" t="n">
         <v>15521.67178302289</v>
       </c>
       <c r="D1111" s="3" t="n">
-        <v>16391.58780023987</v>
+        <v>16391.58925800448</v>
       </c>
     </row>
     <row r="1112">
@@ -18609,7 +18609,7 @@
         <v>15297.85694954839</v>
       </c>
       <c r="D1112" s="3" t="n">
-        <v>16369.13272071852</v>
+        <v>16369.13417648612</v>
       </c>
     </row>
     <row r="1113">
@@ -18641,7 +18641,7 @@
         <v>15185.6111135243</v>
       </c>
       <c r="D1114" s="3" t="n">
-        <v>16078.61478895844</v>
+        <v>16078.61623194914</v>
       </c>
     </row>
     <row r="1115">
@@ -18673,7 +18673,7 @@
         <v>15251.87629248052</v>
       </c>
       <c r="D1116" s="3" t="n">
-        <v>16131.67397179947</v>
+        <v>16131.67253209192</v>
       </c>
     </row>
     <row r="1117">
@@ -18721,7 +18721,7 @@
         <v>15189.66801790197</v>
       </c>
       <c r="D1119" s="3" t="n">
-        <v>15920.30470739283</v>
+        <v>15920.30611558931</v>
       </c>
     </row>
     <row r="1120">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="B1121" s="3" t="n">
-        <v>17390.35</v>
+        <v>17390.34</v>
       </c>
       <c r="C1121" s="3" t="n">
         <v>15172.08775501002</v>
@@ -18763,13 +18763,13 @@
         </is>
       </c>
       <c r="B1122" s="3" t="n">
-        <v>17513.63</v>
+        <v>17513.62</v>
       </c>
       <c r="C1122" s="3" t="n">
         <v>15340.45547728005</v>
       </c>
       <c r="D1122" s="3" t="n">
-        <v>16146.4117479511</v>
+        <v>16146.41031973435</v>
       </c>
     </row>
     <row r="1123">
@@ -18843,7 +18843,7 @@
         </is>
       </c>
       <c r="B1127" s="3" t="n">
-        <v>17637.23</v>
+        <v>17637.22</v>
       </c>
       <c r="C1127" s="3" t="n">
         <v>15312.73295344393</v>
@@ -18875,7 +18875,7 @@
         </is>
       </c>
       <c r="B1129" s="3" t="n">
-        <v>17662.52</v>
+        <v>17662.51</v>
       </c>
       <c r="C1129" s="3" t="n">
         <v>15340.45547728005</v>
@@ -18923,7 +18923,7 @@
         </is>
       </c>
       <c r="B1132" s="3" t="n">
-        <v>17456.27</v>
+        <v>17456.26</v>
       </c>
       <c r="C1132" s="3" t="n">
         <v>15144.36419940779</v>
@@ -18961,7 +18961,7 @@
         <v>15353.97986756044</v>
       </c>
       <c r="D1134" s="3" t="n">
-        <v>15931.07148240856</v>
+        <v>15931.07005451344</v>
       </c>
     </row>
     <row r="1135">
@@ -18977,7 +18977,7 @@
         <v>15333.69431390597</v>
       </c>
       <c r="D1135" s="3" t="n">
-        <v>15973.98324845736</v>
+        <v>15973.98181292996</v>
       </c>
     </row>
     <row r="1136">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="B1137" s="3" t="n">
-        <v>17658.59</v>
+        <v>17658.58</v>
       </c>
       <c r="C1137" s="3" t="n">
         <v>15270.80920075373</v>
@@ -19025,7 +19025,7 @@
         <v>15332.3416685247</v>
       </c>
       <c r="D1138" s="3" t="n">
-        <v>16034.15409215033</v>
+        <v>16034.15552706859</v>
       </c>
     </row>
     <row r="1139">
@@ -19041,7 +19041,7 @@
         <v>15450.6728611153</v>
       </c>
       <c r="D1139" s="3" t="n">
-        <v>16195.00986363666</v>
+        <v>16195.00842645063</v>
       </c>
     </row>
     <row r="1140">
@@ -19057,7 +19057,7 @@
         <v>15420.92085332423</v>
       </c>
       <c r="D1140" s="3" t="n">
-        <v>16050.62799329767</v>
+        <v>16050.62656096873</v>
       </c>
     </row>
     <row r="1141">
@@ -19099,13 +19099,13 @@
         </is>
       </c>
       <c r="B1143" s="3" t="n">
-        <v>17548.9</v>
+        <v>17548.89</v>
       </c>
       <c r="C1143" s="3" t="n">
         <v>15233.61919101488</v>
       </c>
       <c r="D1143" s="3" t="n">
-        <v>16001.41653107174</v>
+        <v>16001.41797783625</v>
       </c>
     </row>
     <row r="1144">
@@ -19121,7 +19121,7 @@
         <v>15397.25523386578</v>
       </c>
       <c r="D1144" s="3" t="n">
-        <v>16232.31060629458</v>
+        <v>16232.31206365304</v>
       </c>
     </row>
     <row r="1145">
@@ -19147,13 +19147,13 @@
         </is>
       </c>
       <c r="B1146" s="3" t="n">
-        <v>17610.59</v>
+        <v>17610.58</v>
       </c>
       <c r="C1146" s="3" t="n">
         <v>15314.76140563276</v>
       </c>
       <c r="D1146" s="3" t="n">
-        <v>15935.96775372634</v>
+        <v>15935.96921160937</v>
       </c>
     </row>
     <row r="1147">
@@ -19249,7 +19249,7 @@
         <v>15166.67820525109</v>
       </c>
       <c r="D1152" s="3" t="n">
-        <v>16096.40706646216</v>
+        <v>16096.4055865282</v>
       </c>
     </row>
     <row r="1153">
@@ -19531,7 +19531,7 @@
         </is>
       </c>
       <c r="B1170" s="3" t="n">
-        <v>17543.21</v>
+        <v>17543.2</v>
       </c>
       <c r="C1170" s="3" t="n">
         <v>15237.67712715867</v>
@@ -19547,7 +19547,7 @@
         </is>
       </c>
       <c r="B1171" s="3" t="n">
-        <v>17573.92</v>
+        <v>17573.91</v>
       </c>
       <c r="C1171" s="3" t="n">
         <v>15278.92404127518</v>
@@ -19579,7 +19579,7 @@
         </is>
       </c>
       <c r="B1173" s="3" t="n">
-        <v>17724.04</v>
+        <v>17724.03</v>
       </c>
       <c r="C1173" s="3" t="n">
         <v>15443.91066597511</v>
@@ -19755,7 +19755,7 @@
         </is>
       </c>
       <c r="B1184" s="3" t="n">
-        <v>18153.74</v>
+        <v>18153.73</v>
       </c>
       <c r="C1184" s="3" t="n">
         <v>15728.58216041301</v>
@@ -19787,7 +19787,7 @@
         </is>
       </c>
       <c r="B1186" s="3" t="n">
-        <v>18282.17</v>
+        <v>18282.16</v>
       </c>
       <c r="C1186" s="3" t="n">
         <v>15830.00889691924</v>
@@ -19819,7 +19819,7 @@
         </is>
       </c>
       <c r="B1188" s="3" t="n">
-        <v>18450.85</v>
+        <v>18450.84</v>
       </c>
       <c r="C1188" s="3" t="n">
         <v>15986.20590605625</v>
@@ -19883,7 +19883,7 @@
         </is>
       </c>
       <c r="B1192" s="3" t="n">
-        <v>18775.76</v>
+        <v>18775.75</v>
       </c>
       <c r="C1192" s="3" t="n">
         <v>16218.81138685978</v>
@@ -19915,7 +19915,7 @@
         </is>
       </c>
       <c r="B1194" s="3" t="n">
-        <v>18819.78</v>
+        <v>18819.77</v>
       </c>
       <c r="C1194" s="3" t="n">
         <v>16286.42921119726</v>
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="B1197" s="3" t="n">
-        <v>18810.91</v>
+        <v>18810.9</v>
       </c>
       <c r="C1197" s="3" t="n">
         <v>16281.01966143833</v>
@@ -19995,7 +19995,7 @@
         </is>
       </c>
       <c r="B1199" s="3" t="n">
-        <v>18947.46</v>
+        <v>18947.45</v>
       </c>
       <c r="C1199" s="3" t="n">
         <v>16414.90266473204</v>
@@ -20139,7 +20139,7 @@
         </is>
       </c>
       <c r="B1208" s="3" t="n">
-        <v>19363.82</v>
+        <v>19363.81</v>
       </c>
       <c r="C1208" s="3" t="n">
         <v>16808.43889762394</v>
@@ -20267,7 +20267,7 @@
         </is>
       </c>
       <c r="B1216" s="3" t="n">
-        <v>19088.46</v>
+        <v>19088.45</v>
       </c>
       <c r="C1216" s="3" t="n">
         <v>16608.28968360789</v>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="B1224" s="3" t="n">
-        <v>19146.63</v>
+        <v>19146.62</v>
       </c>
       <c r="C1224" s="3" t="n">
         <v>16869.29452682122</v>
@@ -20555,7 +20555,7 @@
         </is>
       </c>
       <c r="B1234" s="3" t="n">
-        <v>19078.89</v>
+        <v>19078.88</v>
       </c>
       <c r="C1234" s="3" t="n">
         <v>16832.78135565608</v>
@@ -20715,7 +20715,7 @@
         </is>
       </c>
       <c r="B1244" s="3" t="n">
-        <v>19310.2</v>
+        <v>19310.19</v>
       </c>
       <c r="C1244" s="3" t="n">
         <v>17043.74863742387</v>
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="B1250" s="3" t="n">
-        <v>18843.7</v>
+        <v>18843.69</v>
       </c>
       <c r="C1250" s="3" t="n">
         <v>16727.29771477218</v>
@@ -20827,7 +20827,7 @@
         </is>
       </c>
       <c r="B1251" s="3" t="n">
-        <v>18903.07</v>
+        <v>18903.06</v>
       </c>
       <c r="C1251" s="3" t="n">
         <v>16800.32508886859</v>
@@ -20859,7 +20859,7 @@
         </is>
       </c>
       <c r="B1253" s="3" t="n">
-        <v>19409.85</v>
+        <v>19409.84</v>
       </c>
       <c r="C1253" s="3" t="n">
         <v>17283.11631336759</v>
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="B1277" s="3" t="n">
-        <v>19518.05</v>
+        <v>19518.04</v>
       </c>
       <c r="C1277" s="3" t="n">
         <v>17219.55539340778</v>
@@ -21291,7 +21291,7 @@
         </is>
       </c>
       <c r="B1280" s="3" t="n">
-        <v>19253.74</v>
+        <v>19253.73</v>
       </c>
       <c r="C1280" s="3" t="n">
         <v>16963.96009995338</v>
@@ -21307,7 +21307,7 @@
         </is>
       </c>
       <c r="B1281" s="3" t="n">
-        <v>19469.75</v>
+        <v>19469.74</v>
       </c>
       <c r="C1281" s="3" t="n">
         <v>17126.24246565689</v>
@@ -21339,7 +21339,7 @@
         </is>
       </c>
       <c r="B1283" s="3" t="n">
-        <v>19271.59</v>
+        <v>19271.58</v>
       </c>
       <c r="C1283" s="3" t="n">
         <v>17013.9966296328</v>
@@ -21451,7 +21451,7 @@
         </is>
       </c>
       <c r="B1290" s="3" t="n">
-        <v>20067.64</v>
+        <v>20067.63</v>
       </c>
       <c r="C1290" s="3" t="n">
         <v>17360.19956007556</v>
@@ -21547,7 +21547,7 @@
         </is>
       </c>
       <c r="B1296" s="3" t="n">
-        <v>20445.89</v>
+        <v>20445.88</v>
       </c>
       <c r="C1296" s="3" t="n">
         <v>17587.39652288628</v>
@@ -21579,7 +21579,7 @@
         </is>
       </c>
       <c r="B1298" s="3" t="n">
-        <v>20729.13</v>
+        <v>20729.12</v>
       </c>
       <c r="C1298" s="3" t="n">
         <v>17833.52433043796</v>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="B1299" s="3" t="n">
-        <v>20540.35</v>
+        <v>20540.34</v>
       </c>
       <c r="C1299" s="3" t="n">
         <v>17776.72560561834</v>
@@ -21707,13 +21707,13 @@
         </is>
       </c>
       <c r="B1306" s="3" t="n">
-        <v>20126.6</v>
+        <v>20117.66</v>
       </c>
       <c r="C1306" s="3" t="n">
         <v>17655.01434722376</v>
       </c>
       <c r="D1306" s="3" t="n">
-        <v>18813.75065451522</v>
+        <v>18817.45130184957</v>
       </c>
     </row>
   </sheetData>
@@ -21835,14 +21835,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.201653</v>
+        <v>9.019085</v>
       </c>
       <c r="E3" t="n">
-        <v>312.0263</v>
+        <v>110.7651</v>
       </c>
       <c r="F3" t="n">
         <v>999</v>
@@ -21869,14 +21869,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9.019085</v>
+        <v>3.201654</v>
       </c>
       <c r="E4" t="n">
-        <v>110.7651</v>
+        <v>312.0263</v>
       </c>
       <c r="F4" t="n">
         <v>999</v>
@@ -21907,7 +21907,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.126966</v>
+        <v>48.126959</v>
       </c>
       <c r="E5" t="n">
         <v>20.7576</v>
@@ -22009,10 +22009,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.201653</v>
+        <v>3.201654</v>
       </c>
       <c r="E8" t="n">
-        <v>325.2089</v>
+        <v>325.209</v>
       </c>
       <c r="F8" t="n">
         <v>1041.21</v>
@@ -22083,7 +22083,7 @@
         <v>2.770634</v>
       </c>
       <c r="E10" t="n">
-        <v>371.6966</v>
+        <v>371.6967</v>
       </c>
       <c r="F10" t="n">
         <v>1029.84</v>
@@ -22117,7 +22117,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.941005</v>
+        <v>0.941006</v>
       </c>
       <c r="E11" t="n">
         <v>130.0226</v>
@@ -22154,10 +22154,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3.164386</v>
+        <v>3.164385</v>
       </c>
       <c r="E12" t="n">
-        <v>331.7732</v>
+        <v>331.7733</v>
       </c>
       <c r="F12" t="n">
         <v>1049.86</v>
@@ -22225,10 +22225,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.164386</v>
+        <v>3.164385</v>
       </c>
       <c r="E14" t="n">
-        <v>316.1564</v>
+        <v>316.1563</v>
       </c>
       <c r="F14" t="n">
         <v>1000.44</v>
@@ -22299,7 +22299,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8.576404</v>
+        <v>8.5764</v>
       </c>
       <c r="E16" t="n">
         <v>25.814</v>
@@ -22336,10 +22336,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.694161</v>
+        <v>2.694162</v>
       </c>
       <c r="E17" t="n">
-        <v>378.7708</v>
+        <v>378.7707</v>
       </c>
       <c r="F17" t="n">
         <v>1020.47</v>
@@ -22370,7 +22370,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.694161</v>
+        <v>2.694162</v>
       </c>
       <c r="E18" t="n">
         <v>359.6428</v>
@@ -22444,7 +22444,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.126481</v>
+        <v>14.126479</v>
       </c>
       <c r="E20" t="n">
         <v>73.1315</v>
@@ -22478,7 +22478,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6.130246</v>
+        <v>6.130245</v>
       </c>
       <c r="E21" t="n">
         <v>162.0115</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.937322</v>
+        <v>13.937321</v>
       </c>
       <c r="E22" t="n">
         <v>76.81659999999999</v>
@@ -22549,7 +22549,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4.68402</v>
+        <v>4.684018</v>
       </c>
       <c r="E23" t="n">
         <v>29.8343</v>
@@ -22589,7 +22589,7 @@
         <v>2.69838</v>
       </c>
       <c r="E24" t="n">
-        <v>385.3193</v>
+        <v>385.3192</v>
       </c>
       <c r="F24" t="n">
         <v>1039.74</v>
@@ -22657,7 +22657,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.427841</v>
+        <v>15.427842</v>
       </c>
       <c r="E26" t="n">
         <v>73.4817</v>
@@ -22691,7 +22691,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6.130246</v>
+        <v>6.130245</v>
       </c>
       <c r="E27" t="n">
         <v>160.371</v>
@@ -22728,7 +22728,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6.152085</v>
+        <v>6.152084</v>
       </c>
       <c r="E28" t="n">
         <v>35.3909</v>
@@ -22765,7 +22765,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.624799</v>
+        <v>15.624801</v>
       </c>
       <c r="E29" t="n">
         <v>72.4512</v>
@@ -22836,7 +22836,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.306741</v>
+        <v>2.30674</v>
       </c>
       <c r="E31" t="n">
         <v>69.20959999999999</v>
@@ -22870,7 +22870,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.10811</v>
+        <v>3.108112</v>
       </c>
       <c r="E32" t="n">
         <v>40.2778</v>
@@ -22907,7 +22907,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9.708176</v>
+        <v>9.70818</v>
       </c>
       <c r="E33" t="n">
         <v>69.89490000000001</v>
@@ -23188,7 +23188,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>28.825669</v>
+        <v>28.825671</v>
       </c>
       <c r="E41" t="n">
         <v>71.8141</v>
@@ -23225,7 +23225,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25.606347</v>
+        <v>25.606345</v>
       </c>
       <c r="E42" t="n">
         <v>32.8331</v>
@@ -23258,14 +23258,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9.182786</v>
+        <v>5.96594</v>
       </c>
       <c r="E43" t="n">
-        <v>111.1201</v>
+        <v>171.0362</v>
       </c>
       <c r="F43" t="n">
         <v>1020.39</v>
@@ -23292,14 +23292,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.96594</v>
+        <v>9.182786</v>
       </c>
       <c r="E44" t="n">
-        <v>171.0362</v>
+        <v>111.1201</v>
       </c>
       <c r="F44" t="n">
         <v>1020.39</v>
@@ -23333,7 +23333,7 @@
         <v>3.028556</v>
       </c>
       <c r="E45" t="n">
-        <v>285.6162</v>
+        <v>285.6163</v>
       </c>
       <c r="F45" t="n">
         <v>865</v>
@@ -23438,10 +23438,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.838851</v>
+        <v>2.83885</v>
       </c>
       <c r="E48" t="n">
-        <v>391.1993</v>
+        <v>391.1994</v>
       </c>
       <c r="F48" t="n">
         <v>1110.56</v>
@@ -23546,7 +23546,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.838851</v>
+        <v>2.83885</v>
       </c>
       <c r="E51" t="n">
         <v>389.8563</v>
@@ -23583,7 +23583,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>28.469224</v>
+        <v>28.469223</v>
       </c>
       <c r="E52" t="n">
         <v>38.1574</v>
@@ -23617,7 +23617,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>28.469224</v>
+        <v>28.469223</v>
       </c>
       <c r="E53" t="n">
         <v>36.5224</v>
@@ -23796,7 +23796,7 @@
         <v>2.560923</v>
       </c>
       <c r="E58" t="n">
-        <v>414.813</v>
+        <v>414.8131</v>
       </c>
       <c r="F58" t="n">
         <v>1062.3</v>
@@ -23938,7 +23938,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5.54287</v>
+        <v>5.542865</v>
       </c>
       <c r="E62" t="n">
         <v>88.84439999999999</v>
@@ -23972,10 +23972,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.362268</v>
+        <v>0.362269</v>
       </c>
       <c r="E63" t="n">
-        <v>459.8321</v>
+        <v>459.832</v>
       </c>
       <c r="F63" t="n">
         <v>166.58</v>
@@ -24077,7 +24077,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.772865</v>
+        <v>0.772864</v>
       </c>
       <c r="E66" t="n">
         <v>222.5484</v>
@@ -24114,10 +24114,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>36.106607</v>
+        <v>36.106599</v>
       </c>
       <c r="E67" t="n">
-        <v>38.7314</v>
+        <v>38.7315</v>
       </c>
       <c r="F67" t="n">
         <v>1398.46</v>
@@ -24148,7 +24148,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>36.106607</v>
+        <v>36.106599</v>
       </c>
       <c r="E68" t="n">
         <v>39.6226</v>
@@ -24293,10 +24293,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2.895279</v>
+        <v>2.895278</v>
       </c>
       <c r="E72" t="n">
-        <v>489.1048</v>
+        <v>489.1049</v>
       </c>
       <c r="F72" t="n">
         <v>1416.09</v>
@@ -24364,7 +24364,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>15.253895</v>
+        <v>15.253896</v>
       </c>
       <c r="E74" t="n">
         <v>95.7178</v>
@@ -24398,7 +24398,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>17.411021</v>
+        <v>17.411023</v>
       </c>
       <c r="E75" t="n">
         <v>94.6876</v>
@@ -24506,10 +24506,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2.895279</v>
+        <v>2.895278</v>
       </c>
       <c r="E78" t="n">
-        <v>498.8199</v>
+        <v>498.8198</v>
       </c>
       <c r="F78" t="n">
         <v>1444.22</v>
@@ -24685,7 +24685,7 @@
         <v>3.349753</v>
       </c>
       <c r="E83" t="n">
-        <v>483.5168</v>
+        <v>483.5167</v>
       </c>
       <c r="F83" t="n">
         <v>1619.66</v>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6.917696</v>
+        <v>6.917695</v>
       </c>
       <c r="E85" t="n">
         <v>230.972</v>
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2.064725</v>
+        <v>2.064723</v>
       </c>
       <c r="E87" t="n">
         <v>105.7528</v>
@@ -24858,7 +24858,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6.917696</v>
+        <v>6.917695</v>
       </c>
       <c r="E88" t="n">
         <v>236.9596</v>
@@ -25003,7 +25003,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6.36128</v>
+        <v>6.361279</v>
       </c>
       <c r="E92" t="n">
         <v>253.7815</v>
@@ -25037,7 +25037,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.494943</v>
+        <v>1.494944</v>
       </c>
       <c r="E93" t="n">
         <v>105.6971</v>
@@ -25123,7 +25123,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>-182.66</v>
+        <v>-182.67</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>31.523928</v>
+        <v>31.523925</v>
       </c>
       <c r="E98" t="n">
         <v>98.42919999999999</v>
@@ -25290,7 +25290,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>29.630957</v>
+        <v>29.630955</v>
       </c>
       <c r="E100" t="n">
         <v>98.75060000000001</v>
@@ -25323,14 +25323,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3.275605</v>
+        <v>2.919064</v>
       </c>
       <c r="E101" t="n">
-        <v>457.8719</v>
+        <v>513.7974</v>
       </c>
       <c r="F101" t="n">
         <v>1499.81</v>
@@ -25357,14 +25357,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2.919065</v>
+        <v>3.275605</v>
       </c>
       <c r="E102" t="n">
-        <v>513.7974</v>
+        <v>457.8719</v>
       </c>
       <c r="F102" t="n">
         <v>1499.81</v>
@@ -25395,7 +25395,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2.919065</v>
+        <v>2.919064</v>
       </c>
       <c r="E103" t="n">
         <v>536.669</v>
@@ -25432,7 +25432,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6.229603</v>
+        <v>6.229602</v>
       </c>
       <c r="E104" t="n">
         <v>247.9142</v>
@@ -25685,7 +25685,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2.689519</v>
+        <v>2.689518</v>
       </c>
       <c r="E111" t="n">
         <v>113.8869</v>
@@ -25756,7 +25756,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>34.234577</v>
+        <v>34.234574</v>
       </c>
       <c r="E113" t="n">
         <v>50.3109</v>
@@ -25898,7 +25898,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5.299863</v>
+        <v>5.299862</v>
       </c>
       <c r="E117" t="n">
         <v>48.5727</v>
@@ -25932,7 +25932,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5.166439</v>
+        <v>5.166438</v>
       </c>
       <c r="E118" t="n">
         <v>324.5462</v>
@@ -25969,7 +25969,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2.132724</v>
+        <v>2.132723</v>
       </c>
       <c r="E119" t="n">
         <v>125.7971</v>
@@ -26040,7 +26040,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4.681687</v>
+        <v>4.681686</v>
       </c>
       <c r="E121" t="n">
         <v>55.3943</v>
@@ -26216,7 +26216,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2.24472</v>
+        <v>2.244719</v>
       </c>
       <c r="E126" t="n">
         <v>128.8744</v>
